--- a/data/processed/BR_processed.xlsx
+++ b/data/processed/BR_processed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X150"/>
+  <dimension ref="A1:Y150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>dVdt_calc</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Xlag1_calc</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -629,6 +634,9 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="n">
+        <v>0.2375268817204247</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -695,19 +703,22 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4903461668748211</v>
+        <v>0.4903420873872533</v>
       </c>
       <c r="U3" t="n">
         <v>1.500919151193634</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8697864594476341</v>
+        <v>0.8697864594635797</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4264964563897695</v>
+        <v>0.4264929081145402</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.2375268817204247</v>
       </c>
     </row>
     <row r="4">
@@ -775,19 +786,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9691757340237577</v>
+        <v>0.9691654194616852</v>
       </c>
       <c r="U4" t="n">
         <v>1.500919151193634</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8697842876382202</v>
+        <v>0.8697842876925073</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8429738254141033</v>
+        <v>0.8429648540226919</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.4903420873872533</v>
       </c>
     </row>
     <row r="5">
@@ -855,19 +869,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.954474381720427</v>
+        <v>3.954474381720702</v>
       </c>
       <c r="U5" t="n">
         <v>1.500919151193634</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.845891655819139e-16</v>
+        <v>-4.47965964071775e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.125400564608871e-15</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.9691654194616852</v>
       </c>
     </row>
     <row r="6">
@@ -935,20 +952,23 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>6.7877309713434</v>
+        <v>6.787730965875914</v>
       </c>
       <c r="U6" t="n">
-        <v>1.537009290157266</v>
+        <v>1.537009290079959</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6572400721599998</v>
+        <v>0.657240012143226</v>
       </c>
       <c r="W6" t="n">
-        <v>4.218204528543614</v>
+        <v>4.218204117755936</v>
       </c>
       <c r="X6" t="n">
         <v>0.05501666666666669</v>
       </c>
+      <c r="Y6" t="n">
+        <v>3.954474381720702</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1015,20 +1035,23 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>14.38561328163448</v>
+        <v>14.38561312952787</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6429413734906</v>
+        <v>1.642941373413292</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4009197978747317</v>
+        <v>0.4009206109703933</v>
       </c>
       <c r="W7" t="n">
-        <v>5.101728441014436</v>
+        <v>5.101740083919494</v>
       </c>
       <c r="X7" t="n">
         <v>0.07603333333333334</v>
       </c>
+      <c r="Y7" t="n">
+        <v>6.787730965875914</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,20 +1118,23 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>18.58021353707609</v>
+        <v>18.58021291932988</v>
       </c>
       <c r="U8" t="n">
-        <v>1.707928040157266</v>
+        <v>1.707928040079959</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3394407843388956</v>
+        <v>0.3394416002502794</v>
       </c>
       <c r="W8" t="n">
-        <v>5.366591007225076</v>
+        <v>5.36660598856385</v>
       </c>
       <c r="X8" t="n">
         <v>0.08643333333333333</v>
       </c>
+      <c r="Y8" t="n">
+        <v>14.38561312952787</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1175,20 +1201,23 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>23.31328567069746</v>
+        <v>23.31328380098466</v>
       </c>
       <c r="U9" t="n">
-        <v>1.787719151268377</v>
+        <v>1.78771915119107</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2921426567609487</v>
+        <v>0.2921430095194034</v>
       </c>
       <c r="W9" t="n">
-        <v>5.536719175926916</v>
+        <v>5.536726955787929</v>
       </c>
       <c r="X9" t="n">
         <v>0.09770000000000005</v>
       </c>
+      <c r="Y9" t="n">
+        <v>18.58021291932988</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1255,20 +1284,23 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>26.65402038712101</v>
+        <v>26.65401311124306</v>
       </c>
       <c r="U10" t="n">
-        <v>1.848680836312359</v>
+        <v>1.848679151181504</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2251989634134583</v>
+        <v>0.2252313546719042</v>
       </c>
       <c r="W10" t="n">
-        <v>5.969296685343798</v>
+        <v>5.970158382675687</v>
       </c>
       <c r="X10" t="n">
         <v>0.0023</v>
       </c>
+      <c r="Y10" t="n">
+        <v>23.31328380098466</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1335,20 +1367,23 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>26.8145671512291</v>
+        <v>26.81456003824498</v>
       </c>
       <c r="U11" t="n">
-        <v>1.851714850230572</v>
+        <v>1.851713165069686</v>
       </c>
       <c r="V11" t="n">
-        <v>0.006094880997606118</v>
+        <v>0.006079853433416887</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1282670523799451</v>
+        <v>0.1278640288312575</v>
       </c>
       <c r="X11" t="n">
         <v>0.002428333333333334</v>
       </c>
+      <c r="Y11" t="n">
+        <v>26.65401311124306</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1415,20 +1450,23 @@
         <v>0.1310102834270957</v>
       </c>
       <c r="T12" t="n">
-        <v>27.04657194999543</v>
+        <v>27.04656525594052</v>
       </c>
       <c r="U12" t="n">
-        <v>1.856117558563905</v>
+        <v>1.856115873403019</v>
       </c>
       <c r="V12" t="n">
-        <v>0.006462730079758033</v>
+        <v>0.006462808694442893</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1368600051072877</v>
+        <v>0.1368620630507388</v>
       </c>
       <c r="X12" t="n">
         <v>0.002603333333333333</v>
       </c>
+      <c r="Y12" t="n">
+        <v>26.81456003824498</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1495,20 +1533,23 @@
         <v>0.3150449672599142</v>
       </c>
       <c r="T13" t="n">
-        <v>27.34710404954932</v>
+        <v>27.34710021604569</v>
       </c>
       <c r="U13" t="n">
-        <v>1.861851961341683</v>
+        <v>1.861850276180797</v>
       </c>
       <c r="V13" t="n">
-        <v>0.006890025903620562</v>
+        <v>0.006889873878741359</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1470751989734178</v>
+        <v>0.1470709834936617</v>
       </c>
       <c r="X13" t="n">
         <v>0.002815</v>
       </c>
+      <c r="Y13" t="n">
+        <v>27.04656525594052</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1575,20 +1616,23 @@
         <v>0.462353720667521</v>
       </c>
       <c r="T14" t="n">
-        <v>27.65075512742524</v>
+        <v>27.65075345661634</v>
       </c>
       <c r="U14" t="n">
-        <v>1.867681961341683</v>
+        <v>1.867680276180797</v>
       </c>
       <c r="V14" t="n">
-        <v>0.007275897093367976</v>
+        <v>0.007276059687110452</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1565474199088301</v>
+        <v>0.1565518660143671</v>
       </c>
       <c r="X14" t="n">
         <v>0.003015</v>
       </c>
+      <c r="Y14" t="n">
+        <v>27.34710021604569</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1655,20 +1699,23 @@
         <v>0.6209461221159972</v>
       </c>
       <c r="T15" t="n">
-        <v>27.964866247524</v>
+        <v>27.96486690381572</v>
       </c>
       <c r="U15" t="n">
-        <v>1.873751336341683</v>
+        <v>1.873749651180797</v>
       </c>
       <c r="V15" t="n">
-        <v>0.007634538708099028</v>
+        <v>0.007634494500556047</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1655910984587926</v>
+        <v>0.1655898230009548</v>
       </c>
       <c r="X15" t="n">
         <v>0.003210000000000001</v>
       </c>
+      <c r="Y15" t="n">
+        <v>27.65075345661634</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1735,20 +1782,23 @@
         <v>0.9523209449429346</v>
       </c>
       <c r="T16" t="n">
-        <v>28.14125833024534</v>
+        <v>28.14125939280519</v>
       </c>
       <c r="U16" t="n">
-        <v>1.877176961341683</v>
+        <v>1.877175276180797</v>
       </c>
       <c r="V16" t="n">
-        <v>0.00782056716799282</v>
+        <v>0.007820573031697493</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1703845556327245</v>
+        <v>0.1703846824654642</v>
       </c>
       <c r="X16" t="n">
         <v>0.003315</v>
       </c>
+      <c r="Y16" t="n">
+        <v>27.96486690381572</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1815,20 +1865,23 @@
         <v>1.25504016023201</v>
       </c>
       <c r="T17" t="n">
-        <v>28.31681859237364</v>
+        <v>28.31682006754251</v>
       </c>
       <c r="U17" t="n">
-        <v>1.880598891897238</v>
+        <v>1.880597206736353</v>
       </c>
       <c r="V17" t="n">
-        <v>0.007995857028660904</v>
+        <v>0.007995870233119741</v>
       </c>
       <c r="W17" t="n">
-        <v>0.174971318264154</v>
+        <v>0.1749716551880656</v>
       </c>
       <c r="X17" t="n">
         <v>0.003416666666666667</v>
       </c>
+      <c r="Y17" t="n">
+        <v>28.14125939280519</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1895,20 +1948,23 @@
         <v>1.69587337268752</v>
       </c>
       <c r="T18" t="n">
-        <v>28.48804543680405</v>
+        <v>28.48804706694351</v>
       </c>
       <c r="U18" t="n">
-        <v>1.883948391897238</v>
+        <v>1.883946706736353</v>
       </c>
       <c r="V18" t="n">
-        <v>0.008158139631829394</v>
+        <v>0.008158145764426144</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1792827320209608</v>
+        <v>0.1792828694645364</v>
       </c>
       <c r="X18" t="n">
         <v>0.003513333333333334</v>
       </c>
+      <c r="Y18" t="n">
+        <v>28.31682006754251</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1989,6 +2045,9 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="n">
+        <v>0.1675555555555282</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2055,19 +2114,22 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4827828269359632</v>
+        <v>0.4827780837741287</v>
       </c>
       <c r="U20" t="n">
         <v>1.543349336870027</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8697874489821747</v>
+        <v>0.8697874489981038</v>
       </c>
       <c r="W20" t="n">
-        <v>0.4199184434530343</v>
+        <v>0.4199143179180922</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.1675555555555282</v>
       </c>
     </row>
     <row r="21">
@@ -2135,19 +2197,22 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9966419340210195</v>
+        <v>0.9966296871455165</v>
       </c>
       <c r="U21" t="n">
         <v>1.543349336870027</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8697854481849796</v>
+        <v>0.8697854482402663</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8668646512624173</v>
+        <v>0.8668539991634194</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.4827780837741287</v>
       </c>
     </row>
     <row r="22">
@@ -2215,19 +2280,22 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.969873663474281</v>
+        <v>1.969843362886117</v>
       </c>
       <c r="U22" t="n">
         <v>1.543349336870027</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8697791544244261</v>
+        <v>0.8697791547051218</v>
       </c>
       <c r="W22" t="n">
-        <v>1.713355049339606</v>
+        <v>1.713328695072581</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.9966296871455165</v>
       </c>
     </row>
     <row r="23">
@@ -2295,20 +2363,23 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>6.396536303932576</v>
+        <v>6.39653778402671</v>
       </c>
       <c r="U23" t="n">
-        <v>1.571874336813973</v>
+        <v>1.571874336868414</v>
       </c>
       <c r="V23" t="n">
-        <v>0.864309395015518</v>
+        <v>0.8643084461602091</v>
       </c>
       <c r="W23" t="n">
-        <v>5.285238171843372</v>
+        <v>5.285233325413895</v>
       </c>
       <c r="X23" t="n">
         <v>0.05979999999999999</v>
       </c>
+      <c r="Y23" t="n">
+        <v>1.969843362886117</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2375,20 +2446,23 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>14.63100691365394</v>
+        <v>14.63100688485572</v>
       </c>
       <c r="U24" t="n">
-        <v>1.689429336813975</v>
+        <v>1.689429336868414</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3957845830066714</v>
+        <v>0.3957858234025597</v>
       </c>
       <c r="W24" t="n">
-        <v>5.110891467438628</v>
+        <v>5.110909605641546</v>
       </c>
       <c r="X24" t="n">
         <v>0.07849999999999997</v>
       </c>
+      <c r="Y24" t="n">
+        <v>6.39653778402671</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2455,20 +2529,23 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>18.43528592165496</v>
+        <v>18.43528574219912</v>
       </c>
       <c r="U25" t="n">
-        <v>1.74995378125842</v>
+        <v>1.749953781312859</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3344090156365166</v>
+        <v>0.3344093586730498</v>
       </c>
       <c r="W25" t="n">
-        <v>5.252969589036153</v>
+        <v>5.252975861906697</v>
       </c>
       <c r="X25" t="n">
         <v>0.08656666666666669</v>
       </c>
+      <c r="Y25" t="n">
+        <v>14.63100688485572</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2535,20 +2612,23 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>23.11964778924071</v>
+        <v>23.1196475823968</v>
       </c>
       <c r="U26" t="n">
-        <v>1.83071253125842</v>
+        <v>1.830712531312859</v>
       </c>
       <c r="V26" t="n">
-        <v>0.2835002427290387</v>
+        <v>0.2835003395666355</v>
       </c>
       <c r="W26" t="n">
-        <v>5.338485672999335</v>
+        <v>5.338487864124922</v>
       </c>
       <c r="X26" t="n">
         <v>0.09628333333333336</v>
       </c>
+      <c r="Y26" t="n">
+        <v>18.43528574219912</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2615,20 +2695,23 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>26.32780256221319</v>
+        <v>26.32781437148795</v>
       </c>
       <c r="U27" t="n">
-        <v>1.890462531258419</v>
+        <v>1.890462531312858</v>
       </c>
       <c r="V27" t="n">
-        <v>0.2576109596141595</v>
+        <v>0.2576119613728513</v>
       </c>
       <c r="W27" t="n">
-        <v>5.34951071379465</v>
+        <v>5.349539487463413</v>
       </c>
       <c r="X27" t="n">
         <v>0.1028833333333333</v>
       </c>
+      <c r="Y27" t="n">
+        <v>23.1196475823968</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2695,20 +2778,23 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>27.23142901640801</v>
+        <v>27.23145296079409</v>
       </c>
       <c r="U28" t="n">
-        <v>1.908002341677709</v>
+        <v>1.90800233686873</v>
       </c>
       <c r="V28" t="n">
-        <v>0.01870882700703183</v>
+        <v>0.01870831010401795</v>
       </c>
       <c r="W28" t="n">
-        <v>0.3981447792948562</v>
+        <v>0.3981310530798082</v>
       </c>
       <c r="X28" t="n">
         <v>0.007799999999999998</v>
       </c>
+      <c r="Y28" t="n">
+        <v>26.32781437148795</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2775,20 +2861,23 @@
         <v>0.1961577414134905</v>
       </c>
       <c r="T29" t="n">
-        <v>27.96944792584428</v>
+        <v>27.96947227861317</v>
       </c>
       <c r="U29" t="n">
-        <v>1.922571091677708</v>
+        <v>1.92257108686873</v>
       </c>
       <c r="V29" t="n">
-        <v>0.02051080217046494</v>
+        <v>0.02051071490900611</v>
       </c>
       <c r="W29" t="n">
-        <v>0.4449265486506412</v>
+        <v>0.4449244950655394</v>
       </c>
       <c r="X29" t="n">
         <v>0.008849999999999998</v>
       </c>
+      <c r="Y29" t="n">
+        <v>27.23145296079409</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2855,20 +2944,23 @@
         <v>0.4648676866334254</v>
       </c>
       <c r="T30" t="n">
-        <v>28.96833593102093</v>
+        <v>28.96836793855088</v>
       </c>
       <c r="U30" t="n">
-        <v>1.942647675011042</v>
+        <v>1.942647670202063</v>
       </c>
       <c r="V30" t="n">
-        <v>0.02241098137984284</v>
+        <v>0.02241121869123013</v>
       </c>
       <c r="W30" t="n">
-        <v>0.49830161738856</v>
+        <v>0.498309042119181</v>
       </c>
       <c r="X30" t="n">
         <v>0.01012</v>
       </c>
+      <c r="Y30" t="n">
+        <v>27.96947227861317</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2935,20 +3027,23 @@
         <v>0.5273275582417261</v>
       </c>
       <c r="T31" t="n">
-        <v>30.01251949831358</v>
+        <v>30.012551032435</v>
       </c>
       <c r="U31" t="n">
-        <v>1.964087675011042</v>
+        <v>1.964087670202063</v>
       </c>
       <c r="V31" t="n">
-        <v>0.02393225965834785</v>
+        <v>0.02393237134192201</v>
       </c>
       <c r="W31" t="n">
-        <v>0.5452905486507985</v>
+        <v>0.5452944730724245</v>
       </c>
       <c r="X31" t="n">
         <v>0.01132</v>
       </c>
+      <c r="Y31" t="n">
+        <v>28.96836793855088</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3015,20 +3110,23 @@
         <v>0.5669120469218694</v>
       </c>
       <c r="T32" t="n">
-        <v>31.10794101823598</v>
+        <v>31.10797224513737</v>
       </c>
       <c r="U32" t="n">
-        <v>1.987094341677708</v>
+        <v>1.98709433686873</v>
       </c>
       <c r="V32" t="n">
-        <v>0.02516136086860845</v>
+        <v>0.02516111466725047</v>
       </c>
       <c r="W32" t="n">
-        <v>0.5873438611068159</v>
+        <v>0.5873367913989104</v>
       </c>
       <c r="X32" t="n">
         <v>0.01248</v>
       </c>
+      <c r="Y32" t="n">
+        <v>30.012551032435</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3095,20 +3193,23 @@
         <v>1.314363106233276</v>
       </c>
       <c r="T33" t="n">
-        <v>31.74610874627464</v>
+        <v>31.7461397651932</v>
       </c>
       <c r="U33" t="n">
-        <v>2.000747675011041</v>
+        <v>2.000747670202063</v>
       </c>
       <c r="V33" t="n">
-        <v>0.02574271870805249</v>
+        <v>0.02574269341415964</v>
       </c>
       <c r="W33" t="n">
-        <v>0.6090544983942522</v>
+        <v>0.6090542900136535</v>
       </c>
       <c r="X33" t="n">
         <v>0.01312</v>
       </c>
+      <c r="Y33" t="n">
+        <v>31.10797224513737</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3189,6 +3290,9 @@
       <c r="X34" t="n">
         <v>0</v>
       </c>
+      <c r="Y34" t="n">
+        <v>0.103563218390794</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3255,19 +3359,22 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.1876439516009391</v>
+        <v>0.1876424209014686</v>
       </c>
       <c r="U35" t="n">
         <v>1.6359</v>
       </c>
       <c r="V35" t="n">
-        <v>0.8697890236962834</v>
+        <v>0.8697890237002148</v>
       </c>
       <c r="W35" t="n">
-        <v>0.1632106494654935</v>
+        <v>0.1632093180806331</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.103563218390794</v>
       </c>
     </row>
     <row r="36">
@@ -3335,19 +3442,22 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0.4609692556672049</v>
+        <v>0.4609639455099775</v>
       </c>
       <c r="U36" t="n">
         <v>1.6359</v>
       </c>
       <c r="V36" t="n">
-        <v>0.8697882736986251</v>
+        <v>0.8697882737141917</v>
       </c>
       <c r="W36" t="n">
-        <v>0.4009456531149183</v>
+        <v>0.4009410344096061</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.1876424209014686</v>
       </c>
     </row>
     <row r="37">
@@ -3415,19 +3525,22 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0.6719884257688047</v>
+        <v>0.6719795776715501</v>
       </c>
       <c r="U37" t="n">
         <v>1.6359</v>
       </c>
       <c r="V37" t="n">
-        <v>0.8697876206528812</v>
+        <v>0.8697876206817885</v>
       </c>
       <c r="W37" t="n">
-        <v>0.5844872139557239</v>
+        <v>0.5844795180096907</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.4609639455099775</v>
       </c>
     </row>
     <row r="38">
@@ -3495,19 +3608,22 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>1.053247010961298</v>
+        <v>1.053231018727321</v>
       </c>
       <c r="U38" t="n">
         <v>1.6359</v>
       </c>
       <c r="V38" t="n">
-        <v>0.8697862357021112</v>
+        <v>0.8697862357667031</v>
       </c>
       <c r="W38" t="n">
-        <v>0.916099752928528</v>
+        <v>0.9160858431715664</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.6719795776715501</v>
       </c>
     </row>
     <row r="39">
@@ -3575,19 +3691,22 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>1.627056256939925</v>
+        <v>1.627028120987539</v>
       </c>
       <c r="U39" t="n">
         <v>1.6359</v>
       </c>
       <c r="V39" t="n">
-        <v>0.8697834488595909</v>
+        <v>0.8697834490239056</v>
       </c>
       <c r="W39" t="n">
-        <v>1.415186602649785</v>
+        <v>1.415162130731426</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.053231018727321</v>
       </c>
     </row>
     <row r="40">
@@ -3655,19 +3774,22 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.513470785693847</v>
+        <v>2.513422373865418</v>
       </c>
       <c r="U40" t="n">
         <v>1.6359</v>
       </c>
       <c r="V40" t="n">
-        <v>0.8697759160899778</v>
+        <v>0.8697759166886067</v>
       </c>
       <c r="W40" t="n">
-        <v>2.186156355192262</v>
+        <v>2.186114249254447</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.627028120987539</v>
       </c>
     </row>
     <row r="41">
@@ -3735,19 +3857,22 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>3.88275791062797</v>
+        <v>3.88267907174743</v>
       </c>
       <c r="U41" t="n">
         <v>1.6359</v>
       </c>
       <c r="V41" t="n">
-        <v>0.8697188965321527</v>
+        <v>0.8697189075862428</v>
       </c>
       <c r="W41" t="n">
-        <v>3.376907925532845</v>
+        <v>3.376839400788142</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.513422373865418</v>
       </c>
     </row>
     <row r="42">
@@ -3815,20 +3940,23 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>4.8826297223348</v>
+        <v>4.882614170106039</v>
       </c>
       <c r="U42" t="n">
-        <v>1.641660256712525</v>
+        <v>1.641660000006185</v>
       </c>
       <c r="V42" t="n">
-        <v>0.4571088878274394</v>
+        <v>0.457110420613514</v>
       </c>
       <c r="W42" t="n">
-        <v>2.144451894232631</v>
+        <v>2.144452534020647</v>
       </c>
       <c r="X42" t="n">
         <v>0.02939999999999999</v>
       </c>
+      <c r="Y42" t="n">
+        <v>3.88267907174743</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3895,20 +4023,23 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>6.953429030428417</v>
+        <v>6.953413241326642</v>
       </c>
       <c r="U43" t="n">
-        <v>1.670550281569188</v>
+        <v>1.670550000006185</v>
       </c>
       <c r="V43" t="n">
-        <v>0.373358661151164</v>
+        <v>0.3733596810734912</v>
       </c>
       <c r="W43" t="n">
-        <v>2.451272880196358</v>
+        <v>2.451274381636189</v>
       </c>
       <c r="X43" t="n">
         <v>0.03479999999999999</v>
       </c>
+      <c r="Y43" t="n">
+        <v>4.882614170106039</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3975,20 +4106,23 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>9.420036406826952</v>
+        <v>9.420021220382974</v>
       </c>
       <c r="U44" t="n">
-        <v>1.706317781038939</v>
+        <v>1.706317500006185</v>
       </c>
       <c r="V44" t="n">
-        <v>0.314011667519268</v>
+        <v>0.3140130595450921</v>
       </c>
       <c r="W44" t="n">
-        <v>2.734413753692936</v>
+        <v>2.734422421515149</v>
       </c>
       <c r="X44" t="n">
         <v>0.04049999999999999</v>
       </c>
+      <c r="Y44" t="n">
+        <v>6.953413241326642</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4055,20 +4189,23 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>10.82064712212295</v>
+        <v>10.82063195981635</v>
       </c>
       <c r="U45" t="n">
-        <v>1.727317780926275</v>
+        <v>1.727317500006185</v>
       </c>
       <c r="V45" t="n">
-        <v>0.2900462310619981</v>
+        <v>0.2900471450746221</v>
       </c>
       <c r="W45" t="n">
-        <v>2.865985568136984</v>
+        <v>2.865991398084063</v>
       </c>
       <c r="X45" t="n">
         <v>0.04350000000000001</v>
       </c>
+      <c r="Y45" t="n">
+        <v>9.420021220382974</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4135,20 +4272,23 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>12.93605825499262</v>
+        <v>12.93604319285868</v>
       </c>
       <c r="U46" t="n">
-        <v>1.760033614288186</v>
+        <v>1.760033333339518</v>
       </c>
       <c r="V46" t="n">
-        <v>0.2616420627212657</v>
+        <v>0.2616432243634472</v>
       </c>
       <c r="W46" t="n">
-        <v>3.033292093129437</v>
+        <v>3.033303532280296</v>
       </c>
       <c r="X46" t="n">
         <v>0.0478</v>
       </c>
+      <c r="Y46" t="n">
+        <v>10.82063195981635</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4215,20 +4355,23 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>14.89841730328731</v>
+        <v>14.89840119804066</v>
       </c>
       <c r="U47" t="n">
-        <v>1.791510280956264</v>
+        <v>1.791510000006185</v>
       </c>
       <c r="V47" t="n">
-        <v>0.2409315833998279</v>
+        <v>0.2409319032006425</v>
       </c>
       <c r="W47" t="n">
-        <v>3.160387397647408</v>
+        <v>3.160388678482699</v>
       </c>
       <c r="X47" t="n">
         <v>0.0516</v>
       </c>
+      <c r="Y47" t="n">
+        <v>12.93604319285868</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4295,20 +4438,23 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>16.8807279193231</v>
+        <v>16.88071097278224</v>
       </c>
       <c r="U48" t="n">
-        <v>1.824471114281384</v>
+        <v>1.824470833339518</v>
       </c>
       <c r="V48" t="n">
-        <v>0.2237692549352461</v>
+        <v>0.2237696426626202</v>
       </c>
       <c r="W48" t="n">
-        <v>3.265730450498203</v>
+        <v>3.26573363836168</v>
       </c>
       <c r="X48" t="n">
         <v>0.0553</v>
       </c>
+      <c r="Y48" t="n">
+        <v>14.89840119804066</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4375,20 +4521,23 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>19.99437755940318</v>
+        <v>19.99434722561607</v>
       </c>
       <c r="U49" t="n">
-        <v>1.878764940125168</v>
+        <v>1.878764027797204</v>
       </c>
       <c r="V49" t="n">
-        <v>0.006624104141946579</v>
+        <v>0.006624136125296541</v>
       </c>
       <c r="W49" t="n">
-        <v>0.1111957162639446</v>
+        <v>0.1111961767348054</v>
       </c>
       <c r="X49" t="n">
         <v>0.001996666666666667</v>
       </c>
+      <c r="Y49" t="n">
+        <v>16.88071097278224</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4455,20 +4604,23 @@
         <v>0.09290978010103844</v>
       </c>
       <c r="T50" t="n">
-        <v>20.118231009696</v>
+        <v>20.11820097131467</v>
       </c>
       <c r="U50" t="n">
-        <v>1.880991523458501</v>
+        <v>1.880990611130537</v>
       </c>
       <c r="V50" t="n">
-        <v>0.006756697091481876</v>
+        <v>0.006756799854998181</v>
       </c>
       <c r="W50" t="n">
-        <v>0.1139890981262553</v>
+        <v>0.1139909847038225</v>
       </c>
       <c r="X50" t="n">
         <v>0.002051666666666667</v>
       </c>
+      <c r="Y50" t="n">
+        <v>19.99434722561607</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4535,20 +4687,23 @@
         <v>0.1714635834683609</v>
       </c>
       <c r="T51" t="n">
-        <v>20.22571977901286</v>
+        <v>20.22568990616278</v>
       </c>
       <c r="U51" t="n">
-        <v>1.882928190125168</v>
+        <v>1.882927277797204</v>
       </c>
       <c r="V51" t="n">
-        <v>0.006866574313274501</v>
+        <v>0.006866587876487551</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1163418855636403</v>
+        <v>0.1163419771341342</v>
       </c>
       <c r="X51" t="n">
         <v>0.002098333333333333</v>
       </c>
+      <c r="Y51" t="n">
+        <v>20.11820097131467</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4615,20 +4770,23 @@
         <v>0.1940649581558863</v>
       </c>
       <c r="T52" t="n">
-        <v>20.34331500131972</v>
+        <v>20.34328539823888</v>
       </c>
       <c r="U52" t="n">
-        <v>1.885051523458501</v>
+        <v>1.885050611130537</v>
       </c>
       <c r="V52" t="n">
-        <v>0.006981696184601927</v>
+        <v>0.006981703852210943</v>
       </c>
       <c r="W52" t="n">
-        <v>0.1188462149255302</v>
+        <v>0.1188461867469677</v>
       </c>
       <c r="X52" t="n">
         <v>0.002148333333333333</v>
       </c>
+      <c r="Y52" t="n">
+        <v>20.22568990616278</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4695,20 +4853,23 @@
         <v>0.2229784488956445</v>
       </c>
       <c r="T53" t="n">
-        <v>20.47352500365051</v>
+        <v>20.4734955867161</v>
       </c>
       <c r="U53" t="n">
-        <v>1.88740822484739</v>
+        <v>1.887407312519426</v>
       </c>
       <c r="V53" t="n">
-        <v>0.007103313807944911</v>
+        <v>0.007103353408241623</v>
       </c>
       <c r="W53" t="n">
-        <v>0.1215384124780076</v>
+        <v>0.1215390370561618</v>
       </c>
       <c r="X53" t="n">
         <v>0.0022025</v>
       </c>
+      <c r="Y53" t="n">
+        <v>20.34328539823888</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4775,20 +4936,23 @@
         <v>0.2989185664601128</v>
       </c>
       <c r="T54" t="n">
-        <v>20.58184747469485</v>
+        <v>20.58181820907232</v>
       </c>
       <c r="U54" t="n">
-        <v>1.889373273458501</v>
+        <v>1.889372361130537</v>
       </c>
       <c r="V54" t="n">
-        <v>0.007200123015874504</v>
+        <v>0.007200136730610088</v>
       </c>
       <c r="W54" t="n">
-        <v>0.1237178182753322</v>
+        <v>0.1237179128155578</v>
       </c>
       <c r="X54" t="n">
         <v>0.002246666666666667</v>
       </c>
+      <c r="Y54" t="n">
+        <v>20.4734955867161</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4869,6 +5033,9 @@
       <c r="X55" t="n">
         <v>0</v>
       </c>
+      <c r="Y55" t="n">
+        <v>0.04347826086957973</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4935,19 +5102,22 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0.07877735757490756</v>
+        <v>0.07877665028313477</v>
       </c>
       <c r="U56" t="n">
         <v>1.6309</v>
       </c>
       <c r="V56" t="n">
-        <v>0.8697885714915191</v>
+        <v>0.8697885714934885</v>
       </c>
       <c r="W56" t="n">
-        <v>0.06851964531095545</v>
+        <v>0.0685190301168099</v>
       </c>
       <c r="X56" t="n">
         <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.04347826086957973</v>
       </c>
     </row>
     <row r="57">
@@ -5015,19 +5185,22 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>0.1935257950828547</v>
+        <v>0.1935233159348465</v>
       </c>
       <c r="U57" t="n">
         <v>1.6309</v>
       </c>
       <c r="V57" t="n">
-        <v>0.8697882427885985</v>
+        <v>0.8697882427959044</v>
       </c>
       <c r="W57" t="n">
-        <v>0.1683264612393826</v>
+        <v>0.1683243049070068</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.07877665028313477</v>
       </c>
     </row>
     <row r="58">
@@ -5095,19 +5268,22 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>0.2821166457621606</v>
+        <v>0.2821125744158577</v>
       </c>
       <c r="U58" t="n">
         <v>1.6309</v>
       </c>
       <c r="V58" t="n">
-        <v>0.8697879757876925</v>
+        <v>0.8697879758002416</v>
       </c>
       <c r="W58" t="n">
-        <v>0.2453816662534832</v>
+        <v>0.2453781250489639</v>
       </c>
       <c r="X58" t="n">
         <v>0</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.1935233159348465</v>
       </c>
     </row>
     <row r="59">
@@ -5175,19 +5351,22 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.423360277871885</v>
+        <v>0.4233533352689145</v>
       </c>
       <c r="U59" t="n">
         <v>1.6309</v>
       </c>
       <c r="V59" t="n">
-        <v>0.8697875240762146</v>
+        <v>0.8697875240992518</v>
       </c>
       <c r="W59" t="n">
-        <v>0.3682334878824051</v>
+        <v>0.3682274493027096</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0.2821125744158577</v>
       </c>
     </row>
     <row r="60">
@@ -5255,19 +5434,22 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0.6830777716102368</v>
+        <v>0.6830650288966243</v>
       </c>
       <c r="U60" t="n">
         <v>1.6309</v>
       </c>
       <c r="V60" t="n">
-        <v>0.8697865983213184</v>
+        <v>0.8697865983701096</v>
       </c>
       <c r="W60" t="n">
-        <v>0.5941318913577743</v>
+        <v>0.5941208079495756</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0.4233533352689145</v>
       </c>
     </row>
     <row r="61">
@@ -5335,19 +5517,22 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>1.055219250414442</v>
+        <v>1.055197276700928</v>
       </c>
       <c r="U61" t="n">
         <v>1.6309</v>
       </c>
       <c r="V61" t="n">
-        <v>0.8697850038777518</v>
+        <v>0.8697850039830985</v>
       </c>
       <c r="W61" t="n">
-        <v>0.9178138798136037</v>
+        <v>0.9177947675182717</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0.6830650288966243</v>
       </c>
     </row>
     <row r="62">
@@ -5415,19 +5600,22 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>1.630101710046153</v>
+        <v>1.630064373644841</v>
       </c>
       <c r="U62" t="n">
         <v>1.6309</v>
       </c>
       <c r="V62" t="n">
-        <v>0.8697816271365439</v>
+        <v>0.8697816274052284</v>
       </c>
       <c r="W62" t="n">
-        <v>1.417832517762005</v>
+        <v>1.417800043684095</v>
       </c>
       <c r="X62" t="n">
         <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1.055197276700928</v>
       </c>
     </row>
     <row r="63">
@@ -5495,19 +5683,22 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>2.481930984762753</v>
+        <v>2.48186964610957</v>
       </c>
       <c r="U63" t="n">
         <v>1.6309</v>
       </c>
       <c r="V63" t="n">
-        <v>0.8697724275704246</v>
+        <v>0.8697724285645281</v>
       </c>
       <c r="W63" t="n">
-        <v>2.158715137679354</v>
+        <v>2.158661789477307</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1.630064373644841</v>
       </c>
     </row>
     <row r="64">
@@ -5575,19 +5766,22 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>4.183103260869579</v>
+        <v>4.183103260869902</v>
       </c>
       <c r="U64" t="n">
         <v>1.6309</v>
       </c>
       <c r="V64" t="n">
-        <v>-8.675339222483571e-16</v>
+        <v>-5.168314036484844e-09</v>
       </c>
       <c r="W64" t="n">
-        <v>-3.628983979072079e-15</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
         <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>2.48186964610957</v>
       </c>
     </row>
     <row r="65">
@@ -5655,20 +5849,23 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>6.644075991229286</v>
+        <v>6.644072702977562</v>
       </c>
       <c r="U65" t="n">
-        <v>1.664920062606579</v>
+        <v>1.664919999994332</v>
       </c>
       <c r="V65" t="n">
-        <v>0.4562842780514302</v>
+        <v>0.4562847876418082</v>
       </c>
       <c r="W65" t="n">
-        <v>2.869966998262312</v>
+        <v>2.869968957550593</v>
       </c>
       <c r="X65" t="n">
         <v>0.04049999999999999</v>
       </c>
+      <c r="Y65" t="n">
+        <v>4.183103260869902</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5735,20 +5932,23 @@
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>8.113666366447722</v>
+        <v>8.113663161137396</v>
       </c>
       <c r="U66" t="n">
-        <v>1.685920062608388</v>
+        <v>1.685919999994332</v>
       </c>
       <c r="V66" t="n">
-        <v>0.3963147406335269</v>
+        <v>0.3963156913428896</v>
       </c>
       <c r="W66" t="n">
-        <v>3.006217288784263</v>
+        <v>3.006223807136208</v>
       </c>
       <c r="X66" t="n">
         <v>0.04350000000000001</v>
       </c>
+      <c r="Y66" t="n">
+        <v>6.644072702977562</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5815,20 +6015,23 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>10.33156895921553</v>
+        <v>10.33156584395486</v>
       </c>
       <c r="U67" t="n">
-        <v>1.718635895943307</v>
+        <v>1.718635833327665</v>
       </c>
       <c r="V67" t="n">
-        <v>0.335492011815783</v>
+        <v>0.3354923777667394</v>
       </c>
       <c r="W67" t="n">
-        <v>3.178809453750654</v>
+        <v>3.178812265626877</v>
       </c>
       <c r="X67" t="n">
         <v>0.0478</v>
       </c>
+      <c r="Y67" t="n">
+        <v>8.113663161137396</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5895,20 +6098,23 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>12.38719106701872</v>
+        <v>12.38718794333273</v>
       </c>
       <c r="U68" t="n">
-        <v>1.750112562610262</v>
+        <v>1.750112499994332</v>
       </c>
       <c r="V68" t="n">
-        <v>0.2966288721656819</v>
+        <v>0.2966300583922875</v>
       </c>
       <c r="W68" t="n">
-        <v>3.309176830509442</v>
+        <v>3.309190676977103</v>
       </c>
       <c r="X68" t="n">
         <v>0.0516</v>
       </c>
+      <c r="Y68" t="n">
+        <v>10.33156584395486</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5975,20 +6181,23 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>14.80438979014453</v>
+        <v>14.80438644777559</v>
       </c>
       <c r="U69" t="n">
-        <v>1.788633395943458</v>
+        <v>1.788633333327665</v>
       </c>
       <c r="V69" t="n">
-        <v>0.2630895496454869</v>
+        <v>0.2630897918530912</v>
       </c>
       <c r="W69" t="n">
-        <v>3.432199968917847</v>
+        <v>3.43220276357191</v>
       </c>
       <c r="X69" t="n">
         <v>0.05589999999999999</v>
       </c>
+      <c r="Y69" t="n">
+        <v>12.38718794333273</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6055,20 +6264,23 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>15.01969587212995</v>
+        <v>15.01969250760888</v>
       </c>
       <c r="U70" t="n">
-        <v>1.792146596631902</v>
+        <v>1.792146527764305</v>
       </c>
       <c r="V70" t="n">
-        <v>0.009244307906717498</v>
+        <v>0.009244326228632355</v>
       </c>
       <c r="W70" t="n">
-        <v>0.1221129472243336</v>
+        <v>0.1221131944166381</v>
       </c>
       <c r="X70" t="n">
         <v>0.001996666666666667</v>
       </c>
+      <c r="Y70" t="n">
+        <v>14.80438644777559</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6135,20 +6347,23 @@
         <v>0.05810793948216079</v>
       </c>
       <c r="T71" t="n">
-        <v>15.15570103214544</v>
+        <v>15.15569778641188</v>
       </c>
       <c r="U71" t="n">
-        <v>1.794373179965235</v>
+        <v>1.794373111097638</v>
       </c>
       <c r="V71" t="n">
-        <v>0.009401957732386484</v>
+        <v>0.009401995746227973</v>
       </c>
       <c r="W71" t="n">
-        <v>0.125164397725636</v>
+        <v>0.1251649463817385</v>
       </c>
       <c r="X71" t="n">
         <v>0.002051666666666667</v>
       </c>
+      <c r="Y71" t="n">
+        <v>15.01969250760888</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6215,20 +6430,23 @@
         <v>0.1219400842896329</v>
       </c>
       <c r="T72" t="n">
-        <v>15.27798261225939</v>
+        <v>15.27797946826978</v>
       </c>
       <c r="U72" t="n">
-        <v>1.796379818854124</v>
+        <v>1.796379749986527</v>
       </c>
       <c r="V72" t="n">
-        <v>0.00953582654555562</v>
+        <v>0.009535924639375432</v>
       </c>
       <c r="W72" t="n">
-        <v>0.1278279583969302</v>
+        <v>0.12782943008243</v>
       </c>
       <c r="X72" t="n">
         <v>0.0021</v>
       </c>
+      <c r="Y72" t="n">
+        <v>15.15569778641188</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6295,20 +6513,23 @@
         <v>0.1703755277559266</v>
       </c>
       <c r="T73" t="n">
-        <v>15.40717948332247</v>
+        <v>15.40717642178005</v>
       </c>
       <c r="U73" t="n">
-        <v>1.798504818854124</v>
+        <v>1.798504749986527</v>
       </c>
       <c r="V73" t="n">
-        <v>0.009669652955602136</v>
+        <v>0.009669490718981348</v>
       </c>
       <c r="W73" t="n">
-        <v>0.1305637593990719</v>
+        <v>0.1305612331413965</v>
       </c>
       <c r="X73" t="n">
         <v>0.00215</v>
       </c>
+      <c r="Y73" t="n">
+        <v>15.27797946826978</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6375,20 +6596,23 @@
         <v>0.2036432131066642</v>
       </c>
       <c r="T74" t="n">
-        <v>15.54576751668215</v>
+        <v>15.54576471769251</v>
       </c>
       <c r="U74" t="n">
-        <v>1.800789881354124</v>
+        <v>1.800789812486527</v>
       </c>
       <c r="V74" t="n">
-        <v>0.009804920718641658</v>
+        <v>0.009804969956134207</v>
       </c>
       <c r="W74" t="n">
-        <v>0.1334113877651218</v>
+        <v>0.1334121284519593</v>
       </c>
       <c r="X74" t="n">
         <v>0.0022025</v>
       </c>
+      <c r="Y74" t="n">
+        <v>15.40717642178005</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6455,20 +6679,23 @@
         <v>0.2220723133576301</v>
       </c>
       <c r="T75" t="n">
-        <v>15.66240312562252</v>
+        <v>15.66240050531441</v>
       </c>
       <c r="U75" t="n">
-        <v>1.802717492465235</v>
+        <v>1.802717423597638</v>
       </c>
       <c r="V75" t="n">
-        <v>0.009912773572118169</v>
+        <v>0.009912768036938789</v>
       </c>
       <c r="W75" t="n">
-        <v>0.1357455654918702</v>
+        <v>0.1357454553421338</v>
       </c>
       <c r="X75" t="n">
         <v>0.002245833333333333</v>
       </c>
+      <c r="Y75" t="n">
+        <v>15.54576471769251</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6549,6 +6776,9 @@
       <c r="X76" t="n">
         <v>0</v>
       </c>
+      <c r="Y76" t="n">
+        <v>0.2107142857143181</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6615,19 +6845,22 @@
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>0.3708775341706001</v>
+        <v>0.3708747165822192</v>
       </c>
       <c r="U77" t="n">
         <v>1.74784</v>
       </c>
       <c r="V77" t="n">
-        <v>0.8697860788195604</v>
+        <v>0.8697860788312014</v>
       </c>
       <c r="W77" t="n">
-        <v>0.3225841161685138</v>
+        <v>0.3225816654736816</v>
       </c>
       <c r="X77" t="n">
         <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0.2107142857143181</v>
       </c>
     </row>
     <row r="78">
@@ -6695,19 +6928,22 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>0.7018481459559693</v>
+        <v>0.7018410357461898</v>
       </c>
       <c r="U78" t="n">
         <v>1.74784</v>
       </c>
       <c r="V78" t="n">
-        <v>0.8697845624433599</v>
+        <v>0.8697845624794842</v>
       </c>
       <c r="W78" t="n">
-        <v>0.6104566825319961</v>
+        <v>0.6104504982066478</v>
       </c>
       <c r="X78" t="n">
         <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0.3708747165822192</v>
       </c>
     </row>
     <row r="79">
@@ -6775,19 +7011,22 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>1.367244992801531</v>
+        <v>1.367227741518679</v>
       </c>
       <c r="U79" t="n">
         <v>1.74784</v>
       </c>
       <c r="V79" t="n">
-        <v>0.8697802338818956</v>
+        <v>0.8697802340255848</v>
       </c>
       <c r="W79" t="n">
-        <v>1.189202669612766</v>
+        <v>1.189187664984388</v>
       </c>
       <c r="X79" t="n">
         <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0.7018410357461898</v>
       </c>
     </row>
     <row r="80">
@@ -6855,19 +7094,22 @@
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>2.270883576432389</v>
+        <v>2.270850112990517</v>
       </c>
       <c r="U80" t="n">
         <v>1.74784</v>
       </c>
       <c r="V80" t="n">
-        <v>0.8697680787831714</v>
+        <v>0.8697680795100844</v>
       </c>
       <c r="W80" t="n">
-        <v>1.975142045413856</v>
+        <v>1.97511294163102</v>
       </c>
       <c r="X80" t="n">
         <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>1.367227741518679</v>
       </c>
     </row>
     <row r="81">
@@ -6935,19 +7177,22 @@
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>3.740289285714318</v>
+        <v>3.740289285714594</v>
       </c>
       <c r="U81" t="n">
         <v>1.74784</v>
       </c>
       <c r="V81" t="n">
-        <v>4.508010304642209e-15</v>
+        <v>-4.426896485969155e-09</v>
       </c>
       <c r="W81" t="n">
-        <v>1.6861262642343e-14</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
         <v>0</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>2.270850112990517</v>
       </c>
     </row>
     <row r="82">
@@ -7015,20 +7260,23 @@
         <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>5.78068420787188</v>
+        <v>5.780684203697608</v>
       </c>
       <c r="U82" t="n">
-        <v>1.777849722400284</v>
+        <v>1.777849722226023</v>
       </c>
       <c r="V82" t="n">
-        <v>0.5739981704745749</v>
+        <v>0.5739981969170489</v>
       </c>
       <c r="W82" t="n">
-        <v>3.164197670712829</v>
+        <v>3.164197821268447</v>
       </c>
       <c r="X82" t="n">
         <v>0.04733333333333335</v>
       </c>
+      <c r="Y82" t="n">
+        <v>3.740289285714594</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7095,20 +7343,23 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>9.058698460871806</v>
+        <v>9.058698433022704</v>
       </c>
       <c r="U83" t="n">
-        <v>1.828277500178062</v>
+        <v>1.828277500003801</v>
       </c>
       <c r="V83" t="n">
-        <v>0.4289166290863223</v>
+        <v>0.4289169262259255</v>
       </c>
       <c r="W83" t="n">
-        <v>3.603004394556907</v>
+        <v>3.60300707515135</v>
       </c>
       <c r="X83" t="n">
         <v>0.057</v>
       </c>
+      <c r="Y83" t="n">
+        <v>5.780684203697608</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7175,20 +7426,23 @@
         <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>11.41819297099323</v>
+        <v>11.41819283039667</v>
       </c>
       <c r="U84" t="n">
-        <v>1.866383055733617</v>
+        <v>1.866383055559356</v>
       </c>
       <c r="V84" t="n">
-        <v>0.3703726888099824</v>
+        <v>0.3703725849593388</v>
       </c>
       <c r="W84" t="n">
-        <v>3.841524987422555</v>
+        <v>3.841523754297543</v>
       </c>
       <c r="X84" t="n">
         <v>0.06333333333333334</v>
       </c>
+      <c r="Y84" t="n">
+        <v>9.058698433022704</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7255,20 +7509,23 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>16.5290644969196</v>
+        <v>16.52906369449629</v>
       </c>
       <c r="U85" t="n">
-        <v>1.954627500178062</v>
+        <v>1.9546275000038</v>
       </c>
       <c r="V85" t="n">
-        <v>0.2931594725776646</v>
+        <v>0.2931603594131192</v>
       </c>
       <c r="W85" t="n">
-        <v>4.202967276846747</v>
+        <v>4.202981731311067</v>
       </c>
       <c r="X85" t="n">
         <v>0.07599999999999998</v>
       </c>
+      <c r="Y85" t="n">
+        <v>11.41819283039667</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7335,20 +7592,23 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>20.39252078962898</v>
+        <v>20.39251849328181</v>
       </c>
       <c r="U86" t="n">
-        <v>2.027077500178062</v>
+        <v>2.027077500003801</v>
       </c>
       <c r="V86" t="n">
-        <v>0.2562598679346962</v>
+        <v>0.2562602744628768</v>
       </c>
       <c r="W86" t="n">
-        <v>4.370679604819023</v>
+        <v>4.370687402708426</v>
       </c>
       <c r="X86" t="n">
         <v>0.08500000000000002</v>
       </c>
+      <c r="Y86" t="n">
+        <v>16.52906369449629</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7415,20 +7675,23 @@
         <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>23.31772155071208</v>
+        <v>23.31766948771998</v>
       </c>
       <c r="U87" t="n">
-        <v>2.085608331283068</v>
+        <v>2.085607250005868</v>
       </c>
       <c r="V87" t="n">
-        <v>0.01021572733951788</v>
+        <v>0.01021601143463817</v>
       </c>
       <c r="W87" t="n">
-        <v>0.2005298830652665</v>
+        <v>0.200536040231481</v>
       </c>
       <c r="X87" t="n">
         <v>0.003370000000000001</v>
       </c>
+      <c r="Y87" t="n">
+        <v>20.39251849328181</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7495,20 +7758,23 @@
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>23.51202335629257</v>
+        <v>23.51196957197683</v>
       </c>
       <c r="U88" t="n">
-        <v>2.0896162135667</v>
+        <v>2.089615000005868</v>
       </c>
       <c r="V88" t="n">
-        <v>0.01079864583559203</v>
+        <v>0.01079791085738135</v>
       </c>
       <c r="W88" t="n">
-        <v>0.2133913958909061</v>
+        <v>0.2133736034431671</v>
       </c>
       <c r="X88" t="n">
         <v>0.0036</v>
       </c>
+      <c r="Y88" t="n">
+        <v>23.31766948771998</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7575,20 +7841,23 @@
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>23.76791685252277</v>
+        <v>23.76781114604884</v>
       </c>
       <c r="U89" t="n">
-        <v>2.094918164449156</v>
+        <v>2.094915694450313</v>
       </c>
       <c r="V89" t="n">
-        <v>0.01157218417979474</v>
+        <v>0.01151426144225921</v>
       </c>
       <c r="W89" t="n">
-        <v>0.230988310756996</v>
+        <v>0.2296105348160797</v>
       </c>
       <c r="X89" t="n">
         <v>0.003883333333333334</v>
       </c>
+      <c r="Y89" t="n">
+        <v>23.51196957197683</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7655,20 +7924,23 @@
         <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>23.93978428221004</v>
+        <v>23.93967898585161</v>
       </c>
       <c r="U90" t="n">
-        <v>2.09849416393484</v>
+        <v>2.098491694450313</v>
       </c>
       <c r="V90" t="n">
-        <v>0.01007979675570692</v>
+        <v>0.01007971427442612</v>
       </c>
       <c r="W90" t="n">
-        <v>0.1949533379260983</v>
+        <v>0.1949504513214563</v>
       </c>
       <c r="X90" t="n">
         <v>0.004063333333333333</v>
       </c>
+      <c r="Y90" t="n">
+        <v>23.76781114604884</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7735,20 +8007,23 @@
         <v>0.06375494686076261</v>
       </c>
       <c r="T91" t="n">
-        <v>24.22825041445948</v>
+        <v>24.22814583641843</v>
       </c>
       <c r="U91" t="n">
-        <v>2.104523719490396</v>
+        <v>2.104521250005869</v>
       </c>
       <c r="V91" t="n">
-        <v>0.01063206856027901</v>
+        <v>0.01063211796426457</v>
       </c>
       <c r="W91" t="n">
-        <v>0.2075172075993081</v>
+        <v>0.2075174500820442</v>
       </c>
       <c r="X91" t="n">
         <v>0.00435</v>
       </c>
+      <c r="Y91" t="n">
+        <v>23.93967898585161</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7815,20 +8090,23 @@
         <v>0.1716212668026328</v>
       </c>
       <c r="T92" t="n">
-        <v>24.54922625090641</v>
+        <v>24.54912557034737</v>
       </c>
       <c r="U92" t="n">
-        <v>2.111273719490396</v>
+        <v>2.111271250005868</v>
       </c>
       <c r="V92" t="n">
-        <v>0.01118066179690937</v>
+        <v>0.01118089966425217</v>
       </c>
       <c r="W92" t="n">
-        <v>0.2204078597538168</v>
+        <v>0.22041273201674</v>
       </c>
       <c r="X92" t="n">
         <v>0.00465</v>
       </c>
+      <c r="Y92" t="n">
+        <v>24.22814583641843</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7895,20 +8173,23 @@
         <v>0.2547670720457892</v>
       </c>
       <c r="T93" t="n">
-        <v>25.0069068659276</v>
+        <v>25.00680786787553</v>
       </c>
       <c r="U93" t="n">
-        <v>2.120973719490396</v>
+        <v>2.120971250005868</v>
       </c>
       <c r="V93" t="n">
-        <v>0.01186491756366023</v>
+        <v>0.0118658838353382</v>
       </c>
       <c r="W93" t="n">
-        <v>0.2371638962937377</v>
+        <v>0.2371870514484175</v>
       </c>
       <c r="X93" t="n">
         <v>0.005050000000000001</v>
       </c>
+      <c r="Y93" t="n">
+        <v>24.54912557034737</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7975,20 +8256,23 @@
         <v>0.3345630000595383</v>
       </c>
       <c r="T94" t="n">
-        <v>26.11055105190514</v>
+        <v>26.11045456428113</v>
       </c>
       <c r="U94" t="n">
-        <v>2.144734830601506</v>
+        <v>2.14473236111698</v>
       </c>
       <c r="V94" t="n">
-        <v>0.01316719187898204</v>
+        <v>0.01316721393135566</v>
       </c>
       <c r="W94" t="n">
-        <v>0.2717716206251032</v>
+        <v>0.2717711091938156</v>
       </c>
       <c r="X94" t="n">
         <v>0.005916666666666667</v>
       </c>
+      <c r="Y94" t="n">
+        <v>25.00680786787553</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8055,20 +8339,23 @@
         <v>0.4114676331552647</v>
       </c>
       <c r="T95" t="n">
-        <v>26.57406864027899</v>
+        <v>26.57397314631664</v>
       </c>
       <c r="U95" t="n">
-        <v>2.154873719490395</v>
+        <v>2.154871250005869</v>
       </c>
       <c r="V95" t="n">
-        <v>0.01360386665824679</v>
+        <v>0.01360205894586814</v>
       </c>
       <c r="W95" t="n">
-        <v>0.2844346050813339</v>
+        <v>0.2843854565366162</v>
       </c>
       <c r="X95" t="n">
         <v>0.00625</v>
       </c>
+      <c r="Y95" t="n">
+        <v>26.11045456428113</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8135,20 +8422,23 @@
         <v>0.4067877264015557</v>
       </c>
       <c r="T96" t="n">
-        <v>27.30793717444327</v>
+        <v>27.30784322886136</v>
       </c>
       <c r="U96" t="n">
-        <v>2.171123719490395</v>
+        <v>2.171121250005869</v>
       </c>
       <c r="V96" t="n">
-        <v>0.0141875669288309</v>
+        <v>0.01418844280408847</v>
       </c>
       <c r="W96" t="n">
-        <v>0.302533107063322</v>
+        <v>0.302555887977083</v>
       </c>
       <c r="X96" t="n">
         <v>0.006750000000000001</v>
       </c>
+      <c r="Y96" t="n">
+        <v>26.57397314631664</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8215,20 +8505,23 @@
         <v>0.4021708299263646</v>
       </c>
       <c r="T97" t="n">
-        <v>27.82191919539128</v>
+        <v>27.82182632953165</v>
       </c>
       <c r="U97" t="n">
-        <v>2.182651497268173</v>
+        <v>2.182649027783647</v>
       </c>
       <c r="V97" t="n">
-        <v>0.01453694131186329</v>
+        <v>0.01453702929851717</v>
       </c>
       <c r="W97" t="n">
-        <v>0.3141554581083897</v>
+        <v>0.31415675529333</v>
       </c>
       <c r="X97" t="n">
         <v>0.007083333333333334</v>
       </c>
+      <c r="Y97" t="n">
+        <v>27.30784322886136</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8295,20 +8588,23 @@
         <v>0.3873938421634567</v>
       </c>
       <c r="T98" t="n">
-        <v>28.72218235691336</v>
+        <v>28.72212538886001</v>
       </c>
       <c r="U98" t="n">
-        <v>2.203141469490395</v>
+        <v>2.203139000005869</v>
       </c>
       <c r="V98" t="n">
-        <v>0.01504654261806108</v>
+        <v>0.01504659646470858</v>
       </c>
       <c r="W98" t="n">
-        <v>0.3325674607757125</v>
+        <v>0.3325682361029325</v>
       </c>
       <c r="X98" t="n">
         <v>0.007640000000000001</v>
       </c>
+      <c r="Y98" t="n">
+        <v>27.82182632953165</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8375,20 +8671,23 @@
         <v>0.3689307159607038</v>
       </c>
       <c r="T99" t="n">
-        <v>29.76550377987243</v>
+        <v>29.76547646662382</v>
       </c>
       <c r="U99" t="n">
-        <v>2.227373719490394</v>
+        <v>2.227371250005869</v>
       </c>
       <c r="V99" t="n">
-        <v>0.0155073882925051</v>
+        <v>0.01550780134710743</v>
       </c>
       <c r="W99" t="n">
-        <v>0.3513363680617561</v>
+        <v>0.3513482182048674</v>
       </c>
       <c r="X99" t="n">
         <v>0.00825</v>
       </c>
+      <c r="Y99" t="n">
+        <v>28.72212538886001</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8455,20 +8754,23 @@
         <v>0.3542503465167628</v>
       </c>
       <c r="T100" t="n">
-        <v>30.84543175400328</v>
+        <v>30.84541916586719</v>
       </c>
       <c r="U100" t="n">
-        <v>2.253023719490394</v>
+        <v>2.253021250005869</v>
       </c>
       <c r="V100" t="n">
-        <v>0.0158706878671298</v>
+        <v>0.01587052728317392</v>
       </c>
       <c r="W100" t="n">
-        <v>0.3683756819405863</v>
+        <v>0.3683704455222586</v>
       </c>
       <c r="X100" t="n">
         <v>0.00885</v>
       </c>
+      <c r="Y100" t="n">
+        <v>29.76547646662382</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8535,20 +8837,23 @@
         <v>0.363160750555521</v>
       </c>
       <c r="T101" t="n">
-        <v>31.81469629436059</v>
+        <v>31.81469618095175</v>
       </c>
       <c r="U101" t="n">
-        <v>2.276553580601505</v>
+        <v>2.27655111111698</v>
       </c>
       <c r="V101" t="n">
-        <v>0.01611699920377449</v>
+        <v>0.01611696629351479</v>
       </c>
       <c r="W101" t="n">
-        <v>0.3818588441723268</v>
+        <v>0.3818576537892139</v>
       </c>
       <c r="X101" t="n">
         <v>0.009366666666666667</v>
       </c>
+      <c r="Y101" t="n">
+        <v>30.84541916586719</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8629,6 +8934,9 @@
       <c r="X102" t="n">
         <v>0</v>
       </c>
+      <c r="Y102" t="n">
+        <v>0.1803571428572935</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8695,19 +9003,22 @@
         <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>0.3616860820329546</v>
+        <v>0.3616830541820591</v>
       </c>
       <c r="U103" t="n">
         <v>1.7528</v>
       </c>
       <c r="V103" t="n">
-        <v>0.8697861867646041</v>
+        <v>0.8697861867769205</v>
       </c>
       <c r="W103" t="n">
-        <v>0.3145895580972733</v>
+        <v>0.3145869245188435</v>
       </c>
       <c r="X103" t="n">
         <v>0</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0.1803571428572935</v>
       </c>
     </row>
     <row r="104">
@@ -8775,19 +9086,22 @@
         <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>0.9014947666946171</v>
+        <v>0.9014843637276995</v>
       </c>
       <c r="U104" t="n">
         <v>1.7528</v>
       </c>
       <c r="V104" t="n">
-        <v>0.8697835759328052</v>
+        <v>0.8697835759926298</v>
       </c>
       <c r="W104" t="n">
-        <v>0.7841053418603541</v>
+        <v>0.784096293584519</v>
       </c>
       <c r="X104" t="n">
         <v>0</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0.3616830541820591</v>
       </c>
     </row>
     <row r="105">
@@ -8855,19 +9169,22 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>2.523229974092039</v>
+        <v>2.523189923148073</v>
       </c>
       <c r="U105" t="n">
         <v>1.7528</v>
       </c>
       <c r="V105" t="n">
-        <v>0.8697619956803639</v>
+        <v>0.8697619969135469</v>
       </c>
       <c r="W105" t="n">
-        <v>2.194609537826805</v>
+        <v>2.194574706149407</v>
       </c>
       <c r="X105" t="n">
         <v>0</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0.9014843637276995</v>
       </c>
     </row>
     <row r="106">
@@ -8935,20 +9252,23 @@
         <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>4.83708746797703</v>
+        <v>4.83708748577785</v>
       </c>
       <c r="U106" t="n">
-        <v>1.768600015763252</v>
+        <v>1.768600015789542</v>
       </c>
       <c r="V106" t="n">
-        <v>0.604588330212485</v>
+        <v>0.6045883267935741</v>
       </c>
       <c r="W106" t="n">
-        <v>2.697443211029507</v>
+        <v>2.69744320442209</v>
       </c>
       <c r="X106" t="n">
         <v>0.08300000000000002</v>
       </c>
+      <c r="Y106" t="n">
+        <v>2.523189923148073</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9015,20 +9335,23 @@
         <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>7.795781236894084</v>
+        <v>7.795781238562347</v>
       </c>
       <c r="U107" t="n">
-        <v>1.813388949441029</v>
+        <v>1.813388949467319</v>
       </c>
       <c r="V107" t="n">
-        <v>0.4510699604215321</v>
+        <v>0.4510700731428729</v>
       </c>
       <c r="W107" t="n">
-        <v>3.076510484390964</v>
+        <v>3.076511363806615</v>
       </c>
       <c r="X107" t="n">
         <v>0.1023333333333333</v>
       </c>
+      <c r="Y107" t="n">
+        <v>4.83708748577785</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9095,20 +9418,23 @@
         <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>10.81460012405906</v>
+        <v>10.81459998566029</v>
       </c>
       <c r="U108" t="n">
-        <v>1.861488997541029</v>
+        <v>1.861488997567319</v>
       </c>
       <c r="V108" t="n">
-        <v>0.3704051150733775</v>
+        <v>0.3704055565825953</v>
       </c>
       <c r="W108" t="n">
-        <v>3.310561716814426</v>
+        <v>3.31056644920324</v>
       </c>
       <c r="X108" t="n">
         <v>0.1196666666666667</v>
       </c>
+      <c r="Y108" t="n">
+        <v>7.795781238562347</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9175,20 +9501,23 @@
         <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>14.97828030896703</v>
+        <v>14.97827937126746</v>
       </c>
       <c r="U109" t="n">
-        <v>1.932176568228529</v>
+        <v>1.932176568254819</v>
       </c>
       <c r="V109" t="n">
-        <v>0.3043054011436582</v>
+        <v>0.3043058690651666</v>
       </c>
       <c r="W109" t="n">
-        <v>3.462352119561687</v>
+        <v>3.46235891147874</v>
       </c>
       <c r="X109" t="n">
         <v>0.1413333333333333</v>
       </c>
+      <c r="Y109" t="n">
+        <v>10.81459998566029</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9255,20 +9584,23 @@
         <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>17.91703139267756</v>
+        <v>17.91702949290385</v>
       </c>
       <c r="U110" t="n">
-        <v>1.985389121441029</v>
+        <v>1.985389121467319</v>
       </c>
       <c r="V110" t="n">
-        <v>0.2726816775908876</v>
+        <v>0.272683083326469</v>
       </c>
       <c r="W110" t="n">
-        <v>3.480841183288354</v>
+        <v>3.48086600083324</v>
       </c>
       <c r="X110" t="n">
         <v>0.1556666666666667</v>
       </c>
+      <c r="Y110" t="n">
+        <v>14.97827937126746</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9335,20 +9667,23 @@
         <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>20.53315697711229</v>
+        <v>20.53315325540088</v>
       </c>
       <c r="U111" t="n">
-        <v>2.035287782450751</v>
+        <v>2.035287782477041</v>
       </c>
       <c r="V111" t="n">
-        <v>0.2504959596312035</v>
+        <v>0.2504966718976183</v>
       </c>
       <c r="W111" t="n">
-        <v>3.448591969260503</v>
+        <v>3.448605969287672</v>
       </c>
       <c r="X111" t="n">
         <v>0.168</v>
       </c>
+      <c r="Y111" t="n">
+        <v>17.91702949290385</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9415,20 +9750,23 @@
         <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>24.01327655615475</v>
+        <v>24.01327158029936</v>
       </c>
       <c r="U112" t="n">
-        <v>2.105687852850751</v>
+        <v>2.105687852877041</v>
       </c>
       <c r="V112" t="n">
-        <v>0.2267491739941146</v>
+        <v>0.226749601068703</v>
       </c>
       <c r="W112" t="n">
-        <v>3.346653550748639</v>
+        <v>3.346663112763863</v>
       </c>
       <c r="X112" t="n">
         <v>0.184</v>
       </c>
+      <c r="Y112" t="n">
+        <v>20.53315325540088</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9495,20 +9833,23 @@
         <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>28.24181435886335</v>
+        <v>28.24180486772746</v>
       </c>
       <c r="U113" t="n">
-        <v>2.19806993429644</v>
+        <v>2.198068889706438</v>
       </c>
       <c r="V113" t="n">
-        <v>0.00707998064950816</v>
+        <v>0.007062670572029382</v>
       </c>
       <c r="W113" t="n">
-        <v>0.109327025622538</v>
+        <v>0.1088380779834294</v>
       </c>
       <c r="X113" t="n">
         <v>0.007053333333333333</v>
       </c>
+      <c r="Y113" t="n">
+        <v>24.01327158029936</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9575,20 +9916,23 @@
         <v>0.05060060245371522</v>
       </c>
       <c r="T114" t="n">
-        <v>28.47192299696311</v>
+        <v>28.47191369338541</v>
       </c>
       <c r="U114" t="n">
-        <v>2.203330272890108</v>
+        <v>2.203329228300105</v>
       </c>
       <c r="V114" t="n">
-        <v>0.007575502399231828</v>
+        <v>0.007575500360812597</v>
       </c>
       <c r="W114" t="n">
-        <v>0.1171356409405757</v>
+        <v>0.1171354979034436</v>
       </c>
       <c r="X114" t="n">
         <v>0.007626666666666667</v>
       </c>
+      <c r="Y114" t="n">
+        <v>28.24180486772746</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9655,20 +9999,23 @@
         <v>0.1044036282464569</v>
       </c>
       <c r="T115" t="n">
-        <v>28.65988886456502</v>
+        <v>28.65987999470776</v>
       </c>
       <c r="U115" t="n">
-        <v>2.207645943872441</v>
+        <v>2.207644899282438</v>
       </c>
       <c r="V115" t="n">
-        <v>0.00794433763067366</v>
+        <v>0.007944459054254931</v>
       </c>
       <c r="W115" t="n">
-        <v>0.1229615293641455</v>
+        <v>0.1229649217430691</v>
       </c>
       <c r="X115" t="n">
         <v>0.008066666666666666</v>
       </c>
+      <c r="Y115" t="n">
+        <v>28.47191369338541</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9735,20 +10082,23 @@
         <v>0.1491197853115378</v>
       </c>
       <c r="T116" t="n">
-        <v>28.92564612515287</v>
+        <v>28.9256375489027</v>
       </c>
       <c r="U116" t="n">
-        <v>2.213776616669774</v>
+        <v>2.213775572079771</v>
       </c>
       <c r="V116" t="n">
-        <v>0.008420548538211437</v>
+        <v>0.008420554940521486</v>
       </c>
       <c r="W116" t="n">
-        <v>0.130503630636788</v>
+        <v>0.1305037237830004</v>
       </c>
       <c r="X116" t="n">
         <v>0.008653333333333332</v>
       </c>
+      <c r="Y116" t="n">
+        <v>28.65987999470776</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9815,20 +10165,23 @@
         <v>0.1918414613393818</v>
       </c>
       <c r="T117" t="n">
-        <v>29.46263383132069</v>
+        <v>29.46262799265684</v>
       </c>
       <c r="U117" t="n">
-        <v>2.226268768050802</v>
+        <v>2.226267723460799</v>
       </c>
       <c r="V117" t="n">
-        <v>0.009253023448474186</v>
+        <v>0.009253028607806763</v>
       </c>
       <c r="W117" t="n">
-        <v>0.1437184375107467</v>
+        <v>0.14371850055597</v>
       </c>
       <c r="X117" t="n">
         <v>0.009740000000000002</v>
       </c>
+      <c r="Y117" t="n">
+        <v>28.9256375489027</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9895,20 +10248,23 @@
         <v>0.2448076315621145</v>
       </c>
       <c r="T118" t="n">
-        <v>30.73245885393927</v>
+        <v>30.73245487163991</v>
       </c>
       <c r="U118" t="n">
-        <v>2.256377548159552</v>
+        <v>2.256376503569549</v>
       </c>
       <c r="V118" t="n">
-        <v>0.01074726375017955</v>
+        <v>0.01074722319542253</v>
       </c>
       <c r="W118" t="n">
-        <v>0.1673914784433465</v>
+        <v>0.1673901349917643</v>
       </c>
       <c r="X118" t="n">
         <v>0.01196</v>
       </c>
+      <c r="Y118" t="n">
+        <v>29.46262799265684</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9975,20 +10331,23 @@
         <v>0.2862295508009267</v>
       </c>
       <c r="T119" t="n">
-        <v>31.15248473083177</v>
+        <v>31.15248097080469</v>
       </c>
       <c r="U119" t="n">
-        <v>2.266516808298802</v>
+        <v>2.266515763708799</v>
       </c>
       <c r="V119" t="n">
-        <v>0.01113628526675103</v>
+        <v>0.01113714943474031</v>
       </c>
       <c r="W119" t="n">
-        <v>0.173465448776766</v>
+        <v>0.1734922688738111</v>
       </c>
       <c r="X119" t="n">
         <v>0.01262</v>
       </c>
+      <c r="Y119" t="n">
+        <v>30.73245487163991</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10055,20 +10414,23 @@
         <v>0.2889524121591054</v>
       </c>
       <c r="T120" t="n">
-        <v>31.55040316532968</v>
+        <v>31.55039960390232</v>
       </c>
       <c r="U120" t="n">
-        <v>2.276206817988802</v>
+        <v>2.276205773398799</v>
       </c>
       <c r="V120" t="n">
-        <v>0.0114707959356816</v>
+        <v>0.01147081403029764</v>
       </c>
       <c r="W120" t="n">
-        <v>0.1786663945102576</v>
+        <v>0.1786668611418356</v>
       </c>
       <c r="X120" t="n">
         <v>0.01322</v>
       </c>
+      <c r="Y120" t="n">
+        <v>31.15248097080469</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10135,20 +10497,23 @@
         <v>0.2916972101212668</v>
       </c>
       <c r="T121" t="n">
-        <v>31.95385657262386</v>
+        <v>31.95385449152545</v>
       </c>
       <c r="U121" t="n">
-        <v>2.286116605676357</v>
+        <v>2.286115561086354</v>
       </c>
       <c r="V121" t="n">
-        <v>0.01177718512329405</v>
+        <v>0.0117772325789504</v>
       </c>
       <c r="W121" t="n">
-        <v>0.1833458439376281</v>
+        <v>0.1833472602095393</v>
       </c>
       <c r="X121" t="n">
         <v>0.01380666666666667</v>
       </c>
+      <c r="Y121" t="n">
+        <v>31.55039960390232</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10215,20 +10580,23 @@
         <v>0.2947411967231239</v>
       </c>
       <c r="T122" t="n">
-        <v>32.83159112562513</v>
+        <v>32.83159453267135</v>
       </c>
       <c r="U122" t="n">
-        <v>2.307976849758802</v>
+        <v>2.307975805168799</v>
       </c>
       <c r="V122" t="n">
-        <v>0.01235138793668174</v>
+        <v>0.01235144894981185</v>
       </c>
       <c r="W122" t="n">
-        <v>0.1918521808461034</v>
+        <v>0.1918541072094664</v>
       </c>
       <c r="X122" t="n">
         <v>0.01502</v>
       </c>
+      <c r="Y122" t="n">
+        <v>31.95385449152545</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10295,20 +10663,23 @@
         <v>0.3061500936386944</v>
       </c>
       <c r="T123" t="n">
-        <v>33.75407862959444</v>
+        <v>33.75408934841732</v>
       </c>
       <c r="U123" t="n">
-        <v>2.331406873188802</v>
+        <v>2.331405828598798</v>
       </c>
       <c r="V123" t="n">
-        <v>0.01284377298643088</v>
+        <v>0.01284354032424172</v>
       </c>
       <c r="W123" t="n">
-        <v>0.1986967725594131</v>
+        <v>0.1986888771392174</v>
       </c>
       <c r="X123" t="n">
         <v>0.01622</v>
       </c>
+      <c r="Y123" t="n">
+        <v>32.83159453267135</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10375,20 +10746,23 @@
         <v>0.3308651428571041</v>
       </c>
       <c r="T124" t="n">
-        <v>34.61645413183646</v>
+        <v>34.61647934287152</v>
       </c>
       <c r="U124" t="n">
-        <v>2.353744673304358</v>
+        <v>2.353743628714354</v>
       </c>
       <c r="V124" t="n">
-        <v>0.01322031698823076</v>
+        <v>0.01322023279290888</v>
       </c>
       <c r="W124" t="n">
-        <v>0.2034059950960809</v>
+        <v>0.2034031158610907</v>
       </c>
       <c r="X124" t="n">
         <v>0.01728666666666667</v>
       </c>
+      <c r="Y124" t="n">
+        <v>33.75408934841732</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10455,20 +10829,23 @@
         <v>0.3724108962071924</v>
       </c>
       <c r="T125" t="n">
-        <v>35.5274297311113</v>
+        <v>35.52745852248923</v>
       </c>
       <c r="U125" t="n">
-        <v>2.377810697370358</v>
+        <v>2.377809652780353</v>
       </c>
       <c r="V125" t="n">
-        <v>0.0135475534141766</v>
+        <v>0.01354761888355979</v>
       </c>
       <c r="W125" t="n">
-        <v>0.2068890589508223</v>
+        <v>0.2068914320190024</v>
       </c>
       <c r="X125" t="n">
         <v>0.01836666666666667</v>
       </c>
+      <c r="Y125" t="n">
+        <v>34.61647934287152</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10549,6 +10926,9 @@
       <c r="X126" t="n">
         <v>0</v>
       </c>
+      <c r="Y126" t="n">
+        <v>0.2740000000001075</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10615,19 +10995,22 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>0.7342834513643361</v>
+        <v>0.7342765380101685</v>
       </c>
       <c r="U127" t="n">
         <v>1.7518</v>
       </c>
       <c r="V127" t="n">
-        <v>0.8697849399654051</v>
+        <v>0.8697849399988326</v>
       </c>
       <c r="W127" t="n">
-        <v>0.6386686876625195</v>
+        <v>0.6386626745557249</v>
       </c>
       <c r="X127" t="n">
         <v>0</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.2740000000001075</v>
       </c>
     </row>
     <row r="128">
@@ -10695,19 +11078,22 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>1.494011627633362</v>
+        <v>1.493994205998671</v>
       </c>
       <c r="U128" t="n">
         <v>1.7518</v>
       </c>
       <c r="V128" t="n">
-        <v>0.8697800814316639</v>
+        <v>0.8697800815790188</v>
       </c>
       <c r="W128" t="n">
-        <v>1.299461555142798</v>
+        <v>1.299446402372106</v>
       </c>
       <c r="X128" t="n">
         <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.7342765380101685</v>
       </c>
     </row>
     <row r="129">
@@ -10775,19 +11161,22 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>3.565219050225502</v>
+        <v>3.565168706409894</v>
       </c>
       <c r="U129" t="n">
         <v>1.7518</v>
       </c>
       <c r="V129" t="n">
-        <v>0.869634676310222</v>
+        <v>0.8696347056395528</v>
       </c>
       <c r="W129" t="n">
-        <v>3.100438114717892</v>
+        <v>3.100394438554113</v>
       </c>
       <c r="X129" t="n">
         <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>1.493994205998671</v>
       </c>
     </row>
     <row r="130">
@@ -10855,20 +11244,23 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>5.404249636012797</v>
+        <v>5.404249755435242</v>
       </c>
       <c r="U130" t="n">
-        <v>1.774655578612309</v>
+        <v>1.774655578412124</v>
       </c>
       <c r="V130" t="n">
-        <v>0.560938925629793</v>
+        <v>0.5609388354247328</v>
       </c>
       <c r="W130" t="n">
-        <v>2.768548387165481</v>
+        <v>2.768547960824193</v>
       </c>
       <c r="X130" t="n">
         <v>0.08633333333333333</v>
       </c>
+      <c r="Y130" t="n">
+        <v>3.565168706409894</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10935,20 +11327,23 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>8.441995267759996</v>
+        <v>8.441995341868045</v>
       </c>
       <c r="U131" t="n">
-        <v>1.821055625012309</v>
+        <v>1.821055624812124</v>
       </c>
       <c r="V131" t="n">
-        <v>0.4282978901368172</v>
+        <v>0.4282982624799253</v>
       </c>
       <c r="W131" t="n">
-        <v>3.125842384873646</v>
+        <v>3.125845555578787</v>
       </c>
       <c r="X131" t="n">
         <v>0.1056666666666667</v>
       </c>
+      <c r="Y131" t="n">
+        <v>5.404249755435242</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11015,20 +11410,23 @@
         <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>12.01818141756318</v>
+        <v>12.01818120752623</v>
       </c>
       <c r="U132" t="n">
-        <v>1.878889016178976</v>
+        <v>1.878889015978791</v>
       </c>
       <c r="V132" t="n">
-        <v>0.3467803359250072</v>
+        <v>0.3467808586729018</v>
       </c>
       <c r="W132" t="n">
-        <v>3.363850996144621</v>
+        <v>3.363857219749223</v>
       </c>
       <c r="X132" t="n">
         <v>0.1256666666666666</v>
       </c>
+      <c r="Y132" t="n">
+        <v>8.441995341868045</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11095,20 +11493,23 @@
         <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>15.40208456300136</v>
+        <v>15.4020836537916</v>
       </c>
       <c r="U133" t="n">
-        <v>1.937100185501198</v>
+        <v>1.937100185301013</v>
       </c>
       <c r="V133" t="n">
-        <v>0.298660020552389</v>
+        <v>0.2986612608406918</v>
       </c>
       <c r="W133" t="n">
-        <v>3.462979054856761</v>
+        <v>3.462997953338244</v>
       </c>
       <c r="X133" t="n">
         <v>0.143</v>
       </c>
+      <c r="Y133" t="n">
+        <v>12.01818120752623</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11175,20 +11576,23 @@
         <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>19.69349335006702</v>
+        <v>19.69349035513918</v>
       </c>
       <c r="U134" t="n">
-        <v>2.016322486945642</v>
+        <v>2.016322486745457</v>
       </c>
       <c r="V134" t="n">
-        <v>0.2568331762122699</v>
+        <v>0.2568334097868318</v>
       </c>
       <c r="W134" t="n">
-        <v>3.459404301015714</v>
+        <v>3.459408374659483</v>
       </c>
       <c r="X134" t="n">
         <v>0.1636666666666667</v>
       </c>
+      <c r="Y134" t="n">
+        <v>15.4020836537916</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11255,20 +11659,23 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>22.34964831385378</v>
+        <v>22.34964337139774</v>
       </c>
       <c r="U135" t="n">
-        <v>2.068687817088697</v>
+        <v>2.068687816888513</v>
       </c>
       <c r="V135" t="n">
-        <v>0.2372028938886587</v>
+        <v>0.2372035646651388</v>
       </c>
       <c r="W135" t="n">
-        <v>3.399935956225911</v>
+        <v>3.399950195786845</v>
       </c>
       <c r="X135" t="n">
         <v>0.176</v>
       </c>
+      <c r="Y135" t="n">
+        <v>19.69349035513918</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11335,20 +11742,23 @@
         <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>25.42115565142006</v>
+        <v>25.42114773996207</v>
       </c>
       <c r="U136" t="n">
-        <v>2.132737881138698</v>
+        <v>2.132737880938512</v>
       </c>
       <c r="V136" t="n">
-        <v>0.2183706943701275</v>
+        <v>0.21837105793432</v>
       </c>
       <c r="W136" t="n">
-        <v>3.286531616003448</v>
+        <v>3.286539835190304</v>
       </c>
       <c r="X136" t="n">
         <v>0.19</v>
       </c>
+      <c r="Y136" t="n">
+        <v>22.34964337139774</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11415,20 +11825,23 @@
         <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>28.31816759563745</v>
+        <v>28.31815807173002</v>
       </c>
       <c r="U137" t="n">
-        <v>2.196893200352741</v>
+        <v>2.196892806246272</v>
       </c>
       <c r="V137" t="n">
-        <v>0.007044681899702128</v>
+        <v>0.0104122458017144</v>
       </c>
       <c r="W137" t="n">
-        <v>0.1088321301297718</v>
+        <v>0.2041952841576134</v>
       </c>
       <c r="X137" t="n">
         <v>0.007033333333333333</v>
       </c>
+      <c r="Y137" t="n">
+        <v>25.42114773996207</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11495,20 +11908,23 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>28.49545451865742</v>
+        <v>28.49544506706755</v>
       </c>
       <c r="U138" t="n">
-        <v>2.20094484329327</v>
+        <v>2.2009444491868</v>
       </c>
       <c r="V138" t="n">
-        <v>0.007431766613129663</v>
+        <v>0.01098361402771199</v>
       </c>
       <c r="W138" t="n">
-        <v>0.1149286137067363</v>
+        <v>0.2161400311342437</v>
       </c>
       <c r="X138" t="n">
         <v>0.007480000000000001</v>
       </c>
+      <c r="Y138" t="n">
+        <v>28.31815807173002</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11575,20 +11991,23 @@
         <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>28.74378505976747</v>
+        <v>28.74377626810038</v>
       </c>
       <c r="U139" t="n">
-        <v>2.206645293438159</v>
+        <v>2.206644899331689</v>
       </c>
       <c r="V139" t="n">
-        <v>0.00792480721407878</v>
+        <v>0.01171779493992934</v>
       </c>
       <c r="W139" t="n">
-        <v>0.1227124694134184</v>
+        <v>0.231737203693045</v>
       </c>
       <c r="X139" t="n">
         <v>0.008066666666666666</v>
       </c>
+      <c r="Y139" t="n">
+        <v>28.49544506706755</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11655,20 +12074,23 @@
         <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>28.95677638719329</v>
+        <v>28.95676810524078</v>
       </c>
       <c r="U140" t="n">
-        <v>2.21155810390652</v>
+        <v>2.211557709800049</v>
       </c>
       <c r="V140" t="n">
-        <v>0.008309672514647912</v>
+        <v>0.01228114874974565</v>
       </c>
       <c r="W140" t="n">
-        <v>0.1288038414897075</v>
+        <v>0.2438049010993913</v>
       </c>
       <c r="X140" t="n">
         <v>0.008539999999999999</v>
       </c>
+      <c r="Y140" t="n">
+        <v>28.74377626810038</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11735,20 +12157,23 @@
         <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>29.23617425627321</v>
+        <v>29.23616617039069</v>
       </c>
       <c r="U141" t="n">
-        <v>2.218035888162076</v>
+        <v>2.218035494055605</v>
       </c>
       <c r="V141" t="n">
-        <v>0.008769849406943338</v>
+        <v>0.01296732616405267</v>
       </c>
       <c r="W141" t="n">
-        <v>0.136097251362464</v>
+        <v>0.2588153203139437</v>
       </c>
       <c r="X141" t="n">
         <v>0.009126666666666668</v>
       </c>
+      <c r="Y141" t="n">
+        <v>28.95676810524078</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11815,20 +12240,23 @@
         <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>29.78688895628814</v>
+        <v>29.78688303409221</v>
       </c>
       <c r="U142" t="n">
-        <v>2.230915901042076</v>
+        <v>2.230915506935605</v>
       </c>
       <c r="V142" t="n">
-        <v>0.009558175360894783</v>
+        <v>0.01413302613406024</v>
       </c>
       <c r="W142" t="n">
-        <v>0.1486082928760876</v>
+        <v>0.2848787841656656</v>
       </c>
       <c r="X142" t="n">
         <v>0.01019333333333333</v>
       </c>
+      <c r="Y142" t="n">
+        <v>29.23616617039069</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11895,20 +12323,23 @@
         <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>31.11036957820114</v>
+        <v>31.11037299829884</v>
       </c>
       <c r="U143" t="n">
-        <v>2.262489682615826</v>
+        <v>2.262489288509355</v>
       </c>
       <c r="V143" t="n">
-        <v>0.01100115506888931</v>
+        <v>0.01625169104512008</v>
       </c>
       <c r="W143" t="n">
-        <v>0.1713770914337036</v>
+        <v>0.3347232131708391</v>
       </c>
       <c r="X143" t="n">
         <v>0.01242666666666667</v>
       </c>
+      <c r="Y143" t="n">
+        <v>29.78688303409221</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11975,20 +12406,23 @@
         <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>31.52104214064321</v>
+        <v>31.52104556401108</v>
       </c>
       <c r="U144" t="n">
-        <v>2.272469359262159</v>
+        <v>2.272468965155688</v>
       </c>
       <c r="V144" t="n">
-        <v>0.01135506083682212</v>
+        <v>0.01678984232084768</v>
       </c>
       <c r="W144" t="n">
-        <v>0.1768627492080715</v>
+        <v>0.3481727318040841</v>
       </c>
       <c r="X144" t="n">
         <v>0.01305333333333333</v>
       </c>
+      <c r="Y144" t="n">
+        <v>31.11037299829884</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12055,20 +12489,23 @@
         <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>31.94342679182958</v>
+        <v>31.94343200681957</v>
       </c>
       <c r="U145" t="n">
-        <v>2.282825952952076</v>
+        <v>2.282825558845605</v>
       </c>
       <c r="V145" t="n">
-        <v>0.01168416897368024</v>
+        <v>0.01726821272876278</v>
       </c>
       <c r="W145" t="n">
-        <v>0.1819023818855478</v>
+        <v>0.3602759005648064</v>
       </c>
       <c r="X145" t="n">
         <v>0.01367333333333333</v>
       </c>
+      <c r="Y145" t="n">
+        <v>31.52104556401108</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12135,20 +12572,23 @@
         <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>32.3573948508518</v>
+        <v>32.35740187371602</v>
       </c>
       <c r="U146" t="n">
-        <v>2.293068185416521</v>
+        <v>2.293067791310049</v>
       </c>
       <c r="V146" t="n">
-        <v>0.01197580154919097</v>
+        <v>0.01769926545816089</v>
       </c>
       <c r="W146" t="n">
-        <v>0.1862834410193705</v>
+        <v>0.371479868678853</v>
       </c>
       <c r="X146" t="n">
         <v>0.01426</v>
       </c>
+      <c r="Y146" t="n">
+        <v>31.94343200681957</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12215,20 +12655,23 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>33.25582517483905</v>
+        <v>33.2558324964522</v>
       </c>
       <c r="U147" t="n">
-        <v>2.315615985742077</v>
+        <v>2.315615591635606</v>
       </c>
       <c r="V147" t="n">
-        <v>0.01252037905729662</v>
+        <v>0.01851302896468444</v>
       </c>
       <c r="W147" t="n">
-        <v>0.1941545507687161</v>
+        <v>0.3934451172228779</v>
       </c>
       <c r="X147" t="n">
         <v>0.01547333333333333</v>
       </c>
+      <c r="Y147" t="n">
+        <v>32.35740187371602</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12295,20 +12738,23 @@
         <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>34.1973460288418</v>
+        <v>34.19735342975477</v>
       </c>
       <c r="U148" t="n">
-        <v>2.339726009852077</v>
+        <v>2.339725615745605</v>
       </c>
       <c r="V148" t="n">
-        <v>0.01298466017321329</v>
+        <v>0.01919067788683726</v>
       </c>
       <c r="W148" t="n">
-        <v>0.2003441136011347</v>
+        <v>0.412573497054656</v>
       </c>
       <c r="X148" t="n">
         <v>0.01667333333333334</v>
       </c>
+      <c r="Y148" t="n">
+        <v>33.2558324964522</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12375,20 +12821,23 @@
         <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>34.69218483480882</v>
+        <v>34.69219227762835</v>
       </c>
       <c r="U149" t="n">
-        <v>2.352599994948271</v>
+        <v>2.3525996008418</v>
       </c>
       <c r="V149" t="n">
-        <v>0.01319326233753482</v>
+        <v>0.01948925539598507</v>
       </c>
       <c r="W149" t="n">
-        <v>0.2028867412425771</v>
+        <v>0.4213085438452883</v>
       </c>
       <c r="X149" t="n">
         <v>0.01728</v>
       </c>
+      <c r="Y149" t="n">
+        <v>34.19735342975477</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -12455,19 +12904,22 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>35.04182832112816</v>
+        <v>35.0418357938299</v>
       </c>
       <c r="U150" t="n">
-        <v>2.361782254130521</v>
+        <v>2.36178186002405</v>
       </c>
       <c r="V150" t="n">
-        <v>0.01332665791637905</v>
+        <v>0.01970497486348605</v>
       </c>
       <c r="W150" t="n">
-        <v>0.2043750715436786</v>
+        <v>0.4278830064061876</v>
       </c>
       <c r="X150" t="n">
         <v>0.0177</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>34.69219227762835</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/BR_processed.xlsx
+++ b/data/processed/BR_processed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y150"/>
+  <dimension ref="A1:AA150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,40 +516,50 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>qP_sqrt</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>rP_sqrt</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Xlag1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Plag1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>X_calc</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>V_calc</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mu_calc</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dXdt_calc</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dVdt_calc</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Xlag1_calc</t>
         </is>
@@ -608,33 +618,39 @@
         <v>2.755932637154052</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2375268817204247</v>
+        <v>0.0001</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="T2" t="n">
         <v>0.2375268817204247</v>
       </c>
       <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.2375268817204247</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.500919151193634</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>0.8697873804353808</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>0.2065978842345928</v>
       </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
         <v>0.2375268817204247</v>
       </c>
     </row>
@@ -691,33 +707,39 @@
         <v>0.7929182707910082</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T3" t="n">
         <v>0.2375268817204247</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.4903420873872533</v>
-      </c>
       <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.4903425841537391</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.500919151193634</v>
       </c>
-      <c r="V3" t="n">
-        <v>0.8697864594635797</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.4264929081145402</v>
-      </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.869786459461638</v>
       </c>
       <c r="Y3" t="n">
+        <v>0.426493340194351</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
         <v>0.2375268817204247</v>
       </c>
     </row>
@@ -774,34 +796,40 @@
         <v>0.8664928233519787</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R4" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T4" t="n">
         <v>0.758194444444397</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.9691654194616852</v>
-      </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.969166406331215</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.500919151193634</v>
       </c>
-      <c r="V4" t="n">
-        <v>0.8697842876925073</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.8429648540226919</v>
-      </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.8697842876873132</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4903420873872533</v>
+        <v>0.8429657123812689</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.4903425841537391</v>
       </c>
     </row>
     <row r="5">
@@ -857,34 +885,40 @@
         <v>0.4390733992263243</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R5" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.19599999999993</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.954474381720702</v>
-      </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3.954474381724626</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.500919151193634</v>
       </c>
-      <c r="V5" t="n">
-        <v>-4.47965964071775e-09</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-6.782512760337684e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9691654194616852</v>
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.969166406331215</v>
       </c>
     </row>
     <row r="6">
@@ -940,34 +974,40 @@
         <v>0.4900501784306472</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R6" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T6" t="n">
         <v>5.025440000000001</v>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>6.787730965875914</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.537009290079959</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.657240012143226</v>
+        <v>6.787730967098184</v>
       </c>
       <c r="W6" t="n">
-        <v>4.218204117755936</v>
+        <v>1.537009290095879</v>
       </c>
       <c r="X6" t="n">
+        <v>0.6572400071048442</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.218204084318845</v>
+      </c>
+      <c r="Z6" t="n">
         <v>0.05501666666666669</v>
       </c>
-      <c r="Y6" t="n">
-        <v>3.954474381720702</v>
+      <c r="AA6" t="n">
+        <v>3.954474381724626</v>
       </c>
     </row>
     <row r="7">
@@ -1023,34 +1063,40 @@
         <v>0.3736357386093559</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T7" t="n">
         <v>6.17500000000001</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>14.38561312952787</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.642941373413292</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4009206109703933</v>
+        <v>14.38561313863158</v>
       </c>
       <c r="W7" t="n">
-        <v>5.101740083919494</v>
+        <v>1.642941373429212</v>
       </c>
       <c r="X7" t="n">
+        <v>0.4009205679956527</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.101739468936507</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0.07603333333333334</v>
       </c>
-      <c r="Y7" t="n">
-        <v>6.787730965875914</v>
+      <c r="AA7" t="n">
+        <v>6.787730967098184</v>
       </c>
     </row>
     <row r="8">
@@ -1106,34 +1152,40 @@
         <v>0.3078573703085496</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T8" t="n">
         <v>12.87142857142852</v>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>18.58021291932988</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.707928040079959</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3394416002502794</v>
+        <v>18.58021293162739</v>
       </c>
       <c r="W8" t="n">
-        <v>5.36660598856385</v>
+        <v>1.707928040095878</v>
       </c>
       <c r="X8" t="n">
+        <v>0.339441588837832</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.366605780078858</v>
+      </c>
+      <c r="Z8" t="n">
         <v>0.08643333333333333</v>
       </c>
-      <c r="Y8" t="n">
-        <v>14.38561312952787</v>
+      <c r="AA8" t="n">
+        <v>14.38561313863158</v>
       </c>
     </row>
     <row r="9">
@@ -1189,34 +1241,40 @@
         <v>0.2585007099421947</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R9" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T9" t="n">
         <v>16.07142857142854</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>23.31328380098466</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.78771915119107</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2921430095194034</v>
+        <v>23.31328394075086</v>
       </c>
       <c r="W9" t="n">
-        <v>5.536726955787929</v>
+        <v>1.78771915120699</v>
       </c>
       <c r="X9" t="n">
+        <v>0.2921430559383309</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5.536728071170317</v>
+      </c>
+      <c r="Z9" t="n">
         <v>0.09770000000000005</v>
       </c>
-      <c r="Y9" t="n">
-        <v>18.58021291932988</v>
+      <c r="AA9" t="n">
+        <v>18.58021293162739</v>
       </c>
     </row>
     <row r="10">
@@ -1278,28 +1336,34 @@
         <v>0.03252295278732637</v>
       </c>
       <c r="R10" t="n">
+        <v>0.03754548692326653</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.1803412121156071</v>
+      </c>
+      <c r="T10" t="n">
         <v>19.55000000000009</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>26.65401311124306</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.848679151181504</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2252313546719042</v>
+        <v>26.65401336848298</v>
       </c>
       <c r="W10" t="n">
-        <v>5.970158382675687</v>
+        <v>1.848679229473595</v>
       </c>
       <c r="X10" t="n">
+        <v>0.2252279510788963</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5.970067722284991</v>
+      </c>
+      <c r="Z10" t="n">
         <v>0.0023</v>
       </c>
-      <c r="Y10" t="n">
-        <v>23.31328380098466</v>
+      <c r="AA10" t="n">
+        <v>23.31328394075086</v>
       </c>
     </row>
     <row r="11">
@@ -1361,28 +1425,34 @@
         <v>0.1065167260919373</v>
       </c>
       <c r="R11" t="n">
+        <v>0.06664459174752829</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.3263690029582119</v>
+      </c>
+      <c r="T11" t="n">
         <v>23.07142857142841</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>26.81456003824498</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.851713165069686</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.006079853433416887</v>
+        <v>26.81456869324099</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1278640288312575</v>
+        <v>1.851713413179842</v>
       </c>
       <c r="X11" t="n">
+        <v>0.006093564436306846</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.1282317294427486</v>
+      </c>
+      <c r="Z11" t="n">
         <v>0.002428333333333334</v>
       </c>
-      <c r="Y11" t="n">
-        <v>26.65401311124306</v>
+      <c r="AA11" t="n">
+        <v>26.65401336848298</v>
       </c>
     </row>
     <row r="12">
@@ -1444,28 +1514,34 @@
         <v>0.08474551698518029</v>
       </c>
       <c r="R12" t="n">
+        <v>0.0585577437900562</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2911108328200452</v>
+      </c>
+      <c r="T12" t="n">
         <v>23.9821428571428</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.1310102834270957</v>
       </c>
-      <c r="T12" t="n">
-        <v>27.04656525594052</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.856115873403019</v>
-      </c>
       <c r="V12" t="n">
-        <v>0.006462808694442893</v>
+        <v>27.04657382863489</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1368620630507388</v>
+        <v>1.856116121454714</v>
       </c>
       <c r="X12" t="n">
+        <v>0.006462750056087044</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.1368605255335975</v>
+      </c>
+      <c r="Z12" t="n">
         <v>0.002603333333333333</v>
       </c>
-      <c r="Y12" t="n">
-        <v>26.81456003824498</v>
+      <c r="AA12" t="n">
+        <v>26.81456869324099</v>
       </c>
     </row>
     <row r="13">
@@ -1527,28 +1603,34 @@
         <v>0.06448817748780201</v>
       </c>
       <c r="R13" t="n">
+        <v>0.05054056312736721</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2539452253691769</v>
+      </c>
+      <c r="T13" t="n">
         <v>24.71428571428569</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.3150449672599142</v>
       </c>
-      <c r="T13" t="n">
-        <v>27.34710021604569</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.861850276180797</v>
-      </c>
       <c r="V13" t="n">
-        <v>0.006889873878741359</v>
+        <v>27.34710868323887</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1470709834936617</v>
+        <v>1.861850524232492</v>
       </c>
       <c r="X13" t="n">
+        <v>0.006890040482292315</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.1470755906637241</v>
+      </c>
+      <c r="Z13" t="n">
         <v>0.002815</v>
       </c>
-      <c r="Y13" t="n">
-        <v>27.04656525594052</v>
+      <c r="AA13" t="n">
+        <v>27.04657382863489</v>
       </c>
     </row>
     <row r="14">
@@ -1610,28 +1692,34 @@
         <v>0.112121445976553</v>
       </c>
       <c r="R14" t="n">
+        <v>0.06466559242177924</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3348454060854844</v>
+      </c>
+      <c r="T14" t="n">
         <v>25.24642857142839</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.462353720667521</v>
       </c>
-      <c r="T14" t="n">
-        <v>27.65075345661634</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.867680276180797</v>
-      </c>
       <c r="V14" t="n">
-        <v>0.007276059687110452</v>
+        <v>27.65076181827065</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1565518660143671</v>
+        <v>1.867680524232492</v>
       </c>
       <c r="X14" t="n">
+        <v>0.007275870207412934</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.1565466800263603</v>
+      </c>
+      <c r="Z14" t="n">
         <v>0.003015</v>
       </c>
-      <c r="Y14" t="n">
-        <v>27.34710021604569</v>
+      <c r="AA14" t="n">
+        <v>27.34710868323887</v>
       </c>
     </row>
     <row r="15">
@@ -1693,28 +1781,34 @@
         <v>0.2218548813486614</v>
       </c>
       <c r="R15" t="n">
+        <v>0.0901238156173267</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.4710147358084048</v>
+      </c>
+      <c r="T15" t="n">
         <v>26.8128</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.6209461221159972</v>
       </c>
-      <c r="T15" t="n">
-        <v>27.96486690381572</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.873749651180797</v>
-      </c>
       <c r="V15" t="n">
-        <v>0.007634494500556047</v>
+        <v>27.96487515706328</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1655898230009548</v>
+        <v>1.873749899232492</v>
       </c>
       <c r="X15" t="n">
+        <v>0.007634523293687587</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.1655906834098245</v>
+      </c>
+      <c r="Z15" t="n">
         <v>0.003210000000000001</v>
       </c>
-      <c r="Y15" t="n">
-        <v>27.65075345661634</v>
+      <c r="AA15" t="n">
+        <v>27.65076181827065</v>
       </c>
     </row>
     <row r="16">
@@ -1776,28 +1870,34 @@
         <v>0.3242312467603854</v>
       </c>
       <c r="R16" t="n">
+        <v>0.1082808906095662</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.5694130721720264</v>
+      </c>
+      <c r="T16" t="n">
         <v>27.31428571428567</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.9523209449429346</v>
       </c>
-      <c r="T16" t="n">
-        <v>28.14125939280519</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.877175276180797</v>
-      </c>
       <c r="V16" t="n">
-        <v>0.007820573031697493</v>
+        <v>28.14126758547796</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1703846824654642</v>
+        <v>1.877175524232492</v>
       </c>
       <c r="X16" t="n">
+        <v>0.007820569623933762</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.1703846427370974</v>
+      </c>
+      <c r="Z16" t="n">
         <v>0.003315</v>
       </c>
-      <c r="Y16" t="n">
-        <v>27.96486690381572</v>
+      <c r="AA16" t="n">
+        <v>27.96487515706328</v>
       </c>
     </row>
     <row r="17">
@@ -1859,28 +1959,34 @@
         <v>0.4847102107155994</v>
       </c>
       <c r="R17" t="n">
+        <v>0.1314793690318168</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.6962113261902592</v>
+      </c>
+      <c r="T17" t="n">
         <v>27.65357142857139</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>1.25504016023201</v>
       </c>
-      <c r="T17" t="n">
-        <v>28.31682006754251</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.880597206736353</v>
-      </c>
       <c r="V17" t="n">
-        <v>0.007995870233119741</v>
+        <v>28.31682820030403</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1749716551880656</v>
+        <v>1.880597454788048</v>
       </c>
       <c r="X17" t="n">
+        <v>0.007995866882157202</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.1749716173380987</v>
+      </c>
+      <c r="Z17" t="n">
         <v>0.003416666666666667</v>
       </c>
-      <c r="Y17" t="n">
-        <v>28.14125939280519</v>
+      <c r="AA17" t="n">
+        <v>28.14126758547796</v>
       </c>
     </row>
     <row r="18">
@@ -1942,28 +2048,34 @@
         <v>0.6709707039456413</v>
       </c>
       <c r="R18" t="n">
+        <v>0.153658332461822</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.8191280143821486</v>
+      </c>
+      <c r="T18" t="n">
         <v>28.03928571428575</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>1.69587337268752</v>
       </c>
-      <c r="T18" t="n">
-        <v>28.48804706694351</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.883946706736353</v>
-      </c>
       <c r="V18" t="n">
-        <v>0.008158145764426144</v>
+        <v>28.48805514192954</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1792828694645364</v>
+        <v>1.883946954788048</v>
       </c>
       <c r="X18" t="n">
+        <v>0.008158142377838717</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.1792828308002749</v>
+      </c>
+      <c r="Z18" t="n">
         <v>0.003513333333333334</v>
       </c>
-      <c r="Y18" t="n">
-        <v>28.31682006754251</v>
+      <c r="AA18" t="n">
+        <v>28.31682820030403</v>
       </c>
     </row>
     <row r="19">
@@ -2019,33 +2131,39 @@
         <v>1.600786172733832</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1675555555555282</v>
+        <v>0.0001</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="T19" t="n">
         <v>0.1675555555555282</v>
       </c>
       <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.1675555555555282</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.543349336870027</v>
       </c>
-      <c r="V19" t="n">
+      <c r="X19" t="n">
         <v>0.8697884252671494</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>0.1457378828114052</v>
       </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>0.1675555555555282</v>
       </c>
     </row>
@@ -2102,33 +2220,39 @@
         <v>0.3770350248802999</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R20" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T20" t="n">
         <v>0.1675555555555282</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.4827780837741287</v>
-      </c>
       <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.4827785722691494</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.543349336870027</v>
       </c>
-      <c r="V20" t="n">
-        <v>0.8697874489981038</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.4199143179180922</v>
-      </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.8697874489964632</v>
       </c>
       <c r="Y20" t="n">
+        <v>0.4199147428041381</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>0.1675555555555282</v>
       </c>
     </row>
@@ -2185,34 +2309,40 @@
         <v>0.6434421146608056</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R21" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T21" t="n">
         <v>0.425000000000088</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.9966296871455165</v>
-      </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.9966307136161114</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.543349336870027</v>
       </c>
-      <c r="V21" t="n">
-        <v>0.8697854482402663</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.8668539991634194</v>
-      </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.8697854482356324</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.4827780837741287</v>
+        <v>0.8668548919679877</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.4827785722691494</v>
       </c>
     </row>
     <row r="22">
@@ -2268,34 +2398,40 @@
         <v>0.7999569147331987</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R22" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T22" t="n">
         <v>0.5214285714284982</v>
       </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.969843362886117</v>
-      </c>
       <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.969845422905219</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.543349336870027</v>
       </c>
-      <c r="V22" t="n">
-        <v>0.8697791547051218</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.713328695072581</v>
-      </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.8697791546860387</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.9966296871455165</v>
+        <v>1.713330486796664</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.9966307136161114</v>
       </c>
     </row>
     <row r="23">
@@ -2351,34 +2487,40 @@
         <v>0.5416439745143597</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R23" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T23" t="n">
         <v>1.003571428571421</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>6.39653778402671</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.571874336868414</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0.8643084461602091</v>
+        <v>6.396537563198554</v>
       </c>
       <c r="W23" t="n">
-        <v>5.285233325413895</v>
+        <v>1.571874336879291</v>
       </c>
       <c r="X23" t="n">
+        <v>0.8643085886630451</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>5.285234054477813</v>
+      </c>
+      <c r="Z23" t="n">
         <v>0.05979999999999999</v>
       </c>
-      <c r="Y23" t="n">
-        <v>1.969843362886117</v>
+      <c r="AA23" t="n">
+        <v>1.969845422905219</v>
       </c>
     </row>
     <row r="24">
@@ -2434,34 +2576,40 @@
         <v>0.4518573616580095</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R24" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T24" t="n">
         <v>5.957142857142867</v>
       </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>14.63100688485572</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.689429336868414</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3957858234025597</v>
+        <v>14.63100687628614</v>
       </c>
       <c r="W24" t="n">
-        <v>5.110909605641546</v>
+        <v>1.68942933687929</v>
       </c>
       <c r="X24" t="n">
+        <v>0.3957858539567146</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>5.110910049690442</v>
+      </c>
+      <c r="Z24" t="n">
         <v>0.07849999999999997</v>
       </c>
-      <c r="Y24" t="n">
-        <v>6.39653778402671</v>
+      <c r="AA24" t="n">
+        <v>6.396537563198554</v>
       </c>
     </row>
     <row r="25">
@@ -2517,34 +2665,40 @@
         <v>0.3951354990954673</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R25" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T25" t="n">
         <v>12.12857142857143</v>
       </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>18.43528574219912</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.749953781312859</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3344093586730498</v>
+        <v>18.43528574476287</v>
       </c>
       <c r="W25" t="n">
-        <v>5.252975861906697</v>
+        <v>1.749953781323735</v>
       </c>
       <c r="X25" t="n">
+        <v>0.3344093033120227</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>5.25297484204653</v>
+      </c>
+      <c r="Z25" t="n">
         <v>0.08656666666666669</v>
       </c>
-      <c r="Y25" t="n">
-        <v>14.63100688485572</v>
+      <c r="AA25" t="n">
+        <v>14.63100687628614</v>
       </c>
     </row>
     <row r="26">
@@ -2600,34 +2754,40 @@
         <v>0.3288368413306143</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R26" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T26" t="n">
         <v>16.20714285714285</v>
       </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>23.1196475823968</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.830712531312859</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0.2835003395666355</v>
+        <v>23.11964730786949</v>
       </c>
       <c r="W26" t="n">
-        <v>5.338487864124922</v>
+        <v>1.830712531323734</v>
       </c>
       <c r="X26" t="n">
+        <v>0.2835003051511213</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>5.338487005067323</v>
+      </c>
+      <c r="Z26" t="n">
         <v>0.09628333333333336</v>
       </c>
-      <c r="Y26" t="n">
-        <v>18.43528574219912</v>
+      <c r="AA26" t="n">
+        <v>18.43528574476287</v>
       </c>
     </row>
     <row r="27">
@@ -2683,34 +2843,40 @@
         <v>0.1921794536128573</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R27" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T27" t="n">
         <v>21.77499999999999</v>
       </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>26.32781437148795</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.890462531312858</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0.2576119613728513</v>
+        <v>26.32781445538231</v>
       </c>
       <c r="W27" t="n">
-        <v>5.349539487463413</v>
+        <v>1.890462531323734</v>
       </c>
       <c r="X27" t="n">
+        <v>0.2576118310996777</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>5.349536074710177</v>
+      </c>
+      <c r="Z27" t="n">
         <v>0.1028833333333333</v>
       </c>
-      <c r="Y27" t="n">
-        <v>23.1196475823968</v>
+      <c r="AA27" t="n">
+        <v>23.11964730786949</v>
       </c>
     </row>
     <row r="28">
@@ -2772,28 +2938,34 @@
         <v>0.1619956336149481</v>
       </c>
       <c r="R28" t="n">
+        <v>0.07756128526809224</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.4024868117279722</v>
+      </c>
+      <c r="T28" t="n">
         <v>26.35714285714281</v>
       </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>27.23145296079409</v>
-      </c>
       <c r="U28" t="n">
-        <v>1.90800233686873</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0.01870831010401795</v>
+        <v>27.23145296063369</v>
       </c>
       <c r="W28" t="n">
-        <v>0.3981310530798082</v>
+        <v>1.908002336883929</v>
       </c>
       <c r="X28" t="n">
+        <v>0.01870851914241778</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.3981367454977016</v>
+      </c>
+      <c r="Z28" t="n">
         <v>0.007799999999999998</v>
       </c>
-      <c r="Y28" t="n">
-        <v>26.32781437148795</v>
+      <c r="AA28" t="n">
+        <v>26.32781445538231</v>
       </c>
     </row>
     <row r="29">
@@ -2855,28 +3027,34 @@
         <v>0.0921971490896749</v>
       </c>
       <c r="R29" t="n">
+        <v>0.06022672929531771</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.3036398344909226</v>
+      </c>
+      <c r="T29" t="n">
         <v>26.92857142857148</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.1961577414134905</v>
       </c>
-      <c r="T29" t="n">
-        <v>27.96947227861317</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.92257108686873</v>
-      </c>
       <c r="V29" t="n">
-        <v>0.02051071490900611</v>
+        <v>27.9694722689493</v>
       </c>
       <c r="W29" t="n">
-        <v>0.4449244950655394</v>
+        <v>1.922571086883929</v>
       </c>
       <c r="X29" t="n">
+        <v>0.02051073157175735</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.4449249609611882</v>
+      </c>
+      <c r="Z29" t="n">
         <v>0.008849999999999998</v>
       </c>
-      <c r="Y29" t="n">
-        <v>27.23145296079409</v>
+      <c r="AA29" t="n">
+        <v>27.23145296063369</v>
       </c>
     </row>
     <row r="30">
@@ -2932,34 +3110,40 @@
         <v>0.006274829559544594</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R30" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T30" t="n">
         <v>25.41785714285721</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.4648676866334254</v>
       </c>
-      <c r="T30" t="n">
-        <v>28.96836793855088</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.942647670202063</v>
-      </c>
       <c r="V30" t="n">
-        <v>0.02241121869123013</v>
+        <v>28.96836727463392</v>
       </c>
       <c r="W30" t="n">
-        <v>0.498309042119181</v>
+        <v>1.942647670217263</v>
       </c>
       <c r="X30" t="n">
+        <v>0.02241123524433885</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.4983095102163055</v>
+      </c>
+      <c r="Z30" t="n">
         <v>0.01012</v>
       </c>
-      <c r="Y30" t="n">
-        <v>27.96947227861317</v>
+      <c r="AA30" t="n">
+        <v>27.9694722689493</v>
       </c>
     </row>
     <row r="31">
@@ -3021,28 +3205,34 @@
         <v>0.166038915540943</v>
       </c>
       <c r="R31" t="n">
+        <v>0.07737225717069976</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.4074787301699844</v>
+      </c>
+      <c r="T31" t="n">
         <v>27.31785714285721</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>0.5273275582417261</v>
       </c>
-      <c r="T31" t="n">
-        <v>30.012551032435</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.964087670202063</v>
-      </c>
       <c r="V31" t="n">
-        <v>0.02393237134192201</v>
+        <v>30.01254965667641</v>
       </c>
       <c r="W31" t="n">
-        <v>0.5452944730724245</v>
+        <v>1.964087670217262</v>
       </c>
       <c r="X31" t="n">
+        <v>0.02393238700794108</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.5452949182549442</v>
+      </c>
+      <c r="Z31" t="n">
         <v>0.01132</v>
       </c>
-      <c r="Y31" t="n">
-        <v>28.96836793855088</v>
+      <c r="AA31" t="n">
+        <v>28.96836727463392</v>
       </c>
     </row>
     <row r="32">
@@ -3104,28 +3294,34 @@
         <v>0.6940734053890505</v>
       </c>
       <c r="R32" t="n">
+        <v>0.1504129176969866</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.8331106801554344</v>
+      </c>
+      <c r="T32" t="n">
         <v>27.73571428571431</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>0.5669120469218694</v>
       </c>
-      <c r="T32" t="n">
-        <v>31.10797224513737</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.98709433686873</v>
-      </c>
       <c r="V32" t="n">
-        <v>0.02516111466725047</v>
+        <v>31.10797015051896</v>
       </c>
       <c r="W32" t="n">
-        <v>0.5873367913989104</v>
+        <v>1.987094336883929</v>
       </c>
       <c r="X32" t="n">
+        <v>0.02516114519472265</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.5873377015004719</v>
+      </c>
+      <c r="Z32" t="n">
         <v>0.01248</v>
       </c>
-      <c r="Y32" t="n">
-        <v>30.012551032435</v>
+      <c r="AA32" t="n">
+        <v>30.01254965667641</v>
       </c>
     </row>
     <row r="33">
@@ -3187,28 +3383,34 @@
         <v>1.033509465599738</v>
       </c>
       <c r="R33" t="n">
+        <v>0.1835437763974597</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.016616675841852</v>
+      </c>
+      <c r="T33" t="n">
         <v>30.67857142857135</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>1.314363106233276</v>
       </c>
-      <c r="T33" t="n">
-        <v>31.7461397651932</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.000747670202063</v>
-      </c>
       <c r="V33" t="n">
-        <v>0.02574269341415964</v>
+        <v>31.74613730418875</v>
       </c>
       <c r="W33" t="n">
-        <v>0.6090542900136535</v>
+        <v>2.000747670217262</v>
       </c>
       <c r="X33" t="n">
+        <v>0.02574269542905198</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.6090543067655569</v>
+      </c>
+      <c r="Z33" t="n">
         <v>0.01312</v>
       </c>
-      <c r="Y33" t="n">
-        <v>31.10797224513737</v>
+      <c r="AA33" t="n">
+        <v>31.10797015051896</v>
       </c>
     </row>
     <row r="34">
@@ -3264,33 +3466,39 @@
         <v>0.1410188726692848</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R34" t="n">
-        <v>0.103563218390794</v>
+        <v>0.0001</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="T34" t="n">
         <v>0.103563218390794</v>
       </c>
       <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.103563218390794</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.6359</v>
       </c>
-      <c r="V34" t="n">
+      <c r="X34" t="n">
         <v>0.8697892354884217</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Y34" t="n">
         <v>0.09007817254884913</v>
       </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
         <v>0.103563218390794</v>
       </c>
     </row>
@@ -3347,33 +3555,39 @@
         <v>0.3923394771712953</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R35" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T35" t="n">
         <v>0.103563218390794</v>
       </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0.1876424209014686</v>
-      </c>
       <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.1876426207653147</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.6359</v>
       </c>
-      <c r="V35" t="n">
-        <v>0.8697890237002148</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0.1632093180806331</v>
-      </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.8697890236997015</v>
       </c>
       <c r="Y35" t="n">
+        <v>0.1632094919199164</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
         <v>0.103563218390794</v>
       </c>
     </row>
@@ -3430,34 +3644,40 @@
         <v>0.9865765782029755</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R36" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T36" t="n">
         <v>0.1748717948718132</v>
       </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0.4609639455099775</v>
-      </c>
       <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.4609644348278589</v>
+      </c>
+      <c r="W36" t="n">
         <v>1.6359</v>
       </c>
-      <c r="V36" t="n">
-        <v>0.8697882737141917</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0.4009410344096061</v>
-      </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.8697882737127572</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.1876424209014686</v>
+        <v>0.4009414600119002</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.1876426207653147</v>
       </c>
     </row>
     <row r="37">
@@ -3513,34 +3733,40 @@
         <v>0.859897420449224</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R37" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T37" t="n">
         <v>0.5107407407407478</v>
       </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.6719795776715501</v>
-      </c>
       <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.6719802989042384</v>
+      </c>
+      <c r="W37" t="n">
         <v>1.6359</v>
       </c>
-      <c r="V37" t="n">
-        <v>0.8697876206817885</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.5844795180096907</v>
-      </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.8697876206794322</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.4609639455099775</v>
+        <v>0.5844801453273711</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.4609644348278589</v>
       </c>
     </row>
     <row r="38">
@@ -3596,34 +3822,40 @@
         <v>0.8458504575051579</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R38" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T38" t="n">
         <v>0.7643333333332928</v>
       </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.053231018727321</v>
-      </c>
       <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.053232184227429</v>
+      </c>
+      <c r="W38" t="n">
         <v>1.6359</v>
       </c>
-      <c r="V38" t="n">
-        <v>0.8697862357667031</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0.9160858431715664</v>
-      </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>0.8697862357619959</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.6719795776715501</v>
+        <v>0.9160868569025606</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.6719802989042384</v>
       </c>
     </row>
     <row r="39">
@@ -3679,34 +3911,40 @@
         <v>1.072647376108041</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R39" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T39" t="n">
         <v>1.021500000000053</v>
       </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.627028120987539</v>
-      </c>
       <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.627029941264684</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.6359</v>
       </c>
-      <c r="V39" t="n">
-        <v>0.8697834490239056</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.415162130731426</v>
-      </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>0.8697834490132752</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.053231018727321</v>
+        <v>1.415163713961063</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.053232184227429</v>
       </c>
     </row>
     <row r="40">
@@ -3762,34 +4000,40 @@
         <v>0.8721620914810805</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R40" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T40" t="n">
         <v>1.369999999999916</v>
       </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.513422373865418</v>
-      </c>
       <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2.513425212631307</v>
+      </c>
+      <c r="W40" t="n">
         <v>1.6359</v>
       </c>
-      <c r="V40" t="n">
-        <v>0.8697759166886067</v>
-      </c>
-      <c r="W40" t="n">
-        <v>2.186114249254447</v>
-      </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.8697759166535052</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.627028120987539</v>
+        <v>2.186116718256426</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.627029941264684</v>
       </c>
     </row>
     <row r="41">
@@ -3845,34 +4089,40 @@
         <v>0.7803720364651523</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R41" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T41" t="n">
         <v>2.429000000000059</v>
       </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.88267907174743</v>
-      </c>
       <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>3.882683372173928</v>
+      </c>
+      <c r="W41" t="n">
         <v>1.6359</v>
       </c>
-      <c r="V41" t="n">
-        <v>0.8697189075862428</v>
-      </c>
-      <c r="W41" t="n">
-        <v>3.376839400788142</v>
-      </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.8697189069833527</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.513422373865418</v>
+        <v>3.376843138609547</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.513425212631307</v>
       </c>
     </row>
     <row r="42">
@@ -3928,34 +4178,40 @@
         <v>0.5859915840261742</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R42" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T42" t="n">
         <v>3.654000000000046</v>
       </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>4.882614170106039</v>
-      </c>
       <c r="U42" t="n">
-        <v>1.641660000006185</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0.457110420613514</v>
+        <v>4.882615521967159</v>
       </c>
       <c r="W42" t="n">
-        <v>2.144452534020647</v>
+        <v>1.64166002228396</v>
       </c>
       <c r="X42" t="n">
+        <v>0.4571103239850599</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.144452657147387</v>
+      </c>
+      <c r="Z42" t="n">
         <v>0.02939999999999999</v>
       </c>
-      <c r="Y42" t="n">
-        <v>3.88267907174743</v>
+      <c r="AA42" t="n">
+        <v>3.882683372173928</v>
       </c>
     </row>
     <row r="43">
@@ -4011,34 +4267,40 @@
         <v>0.4918158019929457</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R43" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T43" t="n">
         <v>5.610714285714247</v>
       </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>6.953413241326642</v>
-      </c>
       <c r="U43" t="n">
-        <v>1.670550000006185</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0.3733596810734912</v>
+        <v>6.953414511085085</v>
       </c>
       <c r="W43" t="n">
-        <v>2.451274381636189</v>
+        <v>1.670550021986031</v>
       </c>
       <c r="X43" t="n">
+        <v>0.3733595947783498</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2.451274231121808</v>
+      </c>
+      <c r="Z43" t="n">
         <v>0.03479999999999999</v>
       </c>
-      <c r="Y43" t="n">
-        <v>4.882614170106039</v>
+      <c r="AA43" t="n">
+        <v>4.882615521967159</v>
       </c>
     </row>
     <row r="44">
@@ -4094,34 +4356,40 @@
         <v>0.4239703641171224</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R44" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T44" t="n">
         <v>8.060714285714278</v>
       </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>9.420021220382974</v>
-      </c>
       <c r="U44" t="n">
-        <v>1.706317500006185</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0.3140130595450921</v>
+        <v>9.420022431770047</v>
       </c>
       <c r="W44" t="n">
-        <v>2.734422421515149</v>
+        <v>1.706317521986036</v>
       </c>
       <c r="X44" t="n">
+        <v>0.314013066163396</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.734422838378545</v>
+      </c>
+      <c r="Z44" t="n">
         <v>0.04049999999999999</v>
       </c>
-      <c r="Y44" t="n">
-        <v>6.953413241326642</v>
+      <c r="AA44" t="n">
+        <v>6.953414511085085</v>
       </c>
     </row>
     <row r="45">
@@ -4177,34 +4445,40 @@
         <v>0.4001175993931018</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R45" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T45" t="n">
         <v>12.56785714285716</v>
       </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>10.82063195981635</v>
-      </c>
       <c r="U45" t="n">
-        <v>1.727317500006185</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0.2900471450746221</v>
+        <v>10.82063313860438</v>
       </c>
       <c r="W45" t="n">
-        <v>2.865991398084063</v>
+        <v>1.727317521986036</v>
       </c>
       <c r="X45" t="n">
+        <v>0.2900471432209064</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.865991693711258</v>
+      </c>
+      <c r="Z45" t="n">
         <v>0.04350000000000001</v>
       </c>
-      <c r="Y45" t="n">
-        <v>9.420021220382974</v>
+      <c r="AA45" t="n">
+        <v>9.420022431770047</v>
       </c>
     </row>
     <row r="46">
@@ -4260,34 +4534,40 @@
         <v>0.456221002086854</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R46" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T46" t="n">
         <v>15.0964285714285</v>
       </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>12.93604319285868</v>
-      </c>
       <c r="U46" t="n">
-        <v>1.760033333339518</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0.2616432243634472</v>
+        <v>12.93604424613004</v>
       </c>
       <c r="W46" t="n">
-        <v>3.033303532280296</v>
+        <v>1.760033355319369</v>
       </c>
       <c r="X46" t="n">
+        <v>0.2616431887926153</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>3.033303323497858</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0.0478</v>
       </c>
-      <c r="Y46" t="n">
-        <v>10.82063195981635</v>
+      <c r="AA46" t="n">
+        <v>10.82063313860438</v>
       </c>
     </row>
     <row r="47">
@@ -4343,34 +4623,40 @@
         <v>0.3401951848972837</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R47" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T47" t="n">
         <v>19.02857142857142</v>
       </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>14.89840119804066</v>
-      </c>
       <c r="U47" t="n">
-        <v>1.791510000006185</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>0.2409319032006425</v>
+        <v>14.89840229589674</v>
       </c>
       <c r="W47" t="n">
-        <v>3.160388678482699</v>
+        <v>1.791510021986035</v>
       </c>
       <c r="X47" t="n">
+        <v>0.2409320357844078</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>3.160390891921233</v>
+      </c>
+      <c r="Z47" t="n">
         <v>0.0516</v>
       </c>
-      <c r="Y47" t="n">
-        <v>12.93604319285868</v>
+      <c r="AA47" t="n">
+        <v>12.93604424613004</v>
       </c>
     </row>
     <row r="48">
@@ -4426,34 +4712,40 @@
         <v>0.1620066644475431</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R48" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T48" t="n">
         <v>25.25357142857137</v>
       </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>16.88071097278224</v>
-      </c>
       <c r="U48" t="n">
-        <v>1.824470833339518</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0.2237696426626202</v>
+        <v>16.88071214887976</v>
       </c>
       <c r="W48" t="n">
-        <v>3.26573363836168</v>
+        <v>1.824470855319368</v>
       </c>
       <c r="X48" t="n">
+        <v>0.2237696249091863</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>3.265733572362352</v>
+      </c>
+      <c r="Z48" t="n">
         <v>0.0553</v>
       </c>
-      <c r="Y48" t="n">
-        <v>14.89840119804066</v>
+      <c r="AA48" t="n">
+        <v>14.89840229589674</v>
       </c>
     </row>
     <row r="49">
@@ -4515,28 +4807,34 @@
         <v>0.0816312894067058</v>
       </c>
       <c r="R49" t="n">
+        <v>0.05155349562266365</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.2857118993089119</v>
+      </c>
+      <c r="T49" t="n">
         <v>29.52857142857138</v>
       </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>19.99434722561607</v>
-      </c>
       <c r="U49" t="n">
-        <v>1.878764027797204</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>0.006624136125296541</v>
+        <v>19.9943493428161</v>
       </c>
       <c r="W49" t="n">
-        <v>0.1111961767348054</v>
+        <v>1.878764110411336</v>
       </c>
       <c r="X49" t="n">
+        <v>0.006624133662702124</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.1111961402057659</v>
+      </c>
+      <c r="Z49" t="n">
         <v>0.001996666666666667</v>
       </c>
-      <c r="Y49" t="n">
-        <v>16.88071097278224</v>
+      <c r="AA49" t="n">
+        <v>16.88071214887976</v>
       </c>
     </row>
     <row r="50">
@@ -4598,28 +4896,34 @@
         <v>0.04078878183453907</v>
       </c>
       <c r="R50" t="n">
+        <v>0.0359356095867547</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.2019623277607462</v>
+      </c>
+      <c r="T50" t="n">
         <v>30.71428571428574</v>
       </c>
-      <c r="S50" t="n">
+      <c r="U50" t="n">
         <v>0.09290978010103844</v>
       </c>
-      <c r="T50" t="n">
-        <v>20.11820097131467</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.880990611130537</v>
-      </c>
       <c r="V50" t="n">
-        <v>0.006756799854998181</v>
+        <v>20.1182030731978</v>
       </c>
       <c r="W50" t="n">
-        <v>0.1139909847038225</v>
+        <v>1.88099069374467</v>
       </c>
       <c r="X50" t="n">
+        <v>0.006756696680435864</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.1139889218902052</v>
+      </c>
+      <c r="Z50" t="n">
         <v>0.002051666666666667</v>
       </c>
-      <c r="Y50" t="n">
-        <v>19.99434722561607</v>
+      <c r="AA50" t="n">
+        <v>19.9943493428161</v>
       </c>
     </row>
     <row r="51">
@@ -4681,28 +4985,34 @@
         <v>0.02413582546819065</v>
       </c>
       <c r="R51" t="n">
+        <v>0.02706031021828268</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.1553570901767623</v>
+      </c>
+      <c r="T51" t="n">
         <v>31.58571428571431</v>
       </c>
-      <c r="S51" t="n">
+      <c r="U51" t="n">
         <v>0.1714635834683609</v>
       </c>
-      <c r="T51" t="n">
-        <v>20.22568990616278</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.882927277797204</v>
-      </c>
       <c r="V51" t="n">
-        <v>0.006866587876487551</v>
+        <v>20.22569199499107</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1163419771341342</v>
+        <v>1.882927360411336</v>
       </c>
       <c r="X51" t="n">
+        <v>0.006866586904202878</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0.1163419704732665</v>
+      </c>
+      <c r="Z51" t="n">
         <v>0.002098333333333333</v>
       </c>
-      <c r="Y51" t="n">
-        <v>20.11820097131467</v>
+      <c r="AA51" t="n">
+        <v>20.1182030731978</v>
       </c>
     </row>
     <row r="52">
@@ -4764,28 +5074,34 @@
         <v>0.03974752399441857</v>
       </c>
       <c r="R52" t="n">
+        <v>0.03441311909386455</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.199367810828174</v>
+      </c>
+      <c r="T52" t="n">
         <v>32.96071428571437</v>
       </c>
-      <c r="S52" t="n">
+      <c r="U52" t="n">
         <v>0.1940649581558863</v>
       </c>
-      <c r="T52" t="n">
-        <v>20.34328539823888</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.885050611130537</v>
-      </c>
       <c r="V52" t="n">
-        <v>0.006981703852210943</v>
+        <v>20.34328747236598</v>
       </c>
       <c r="W52" t="n">
-        <v>0.1188461867469677</v>
+        <v>1.88505069374467</v>
       </c>
       <c r="X52" t="n">
+        <v>0.006981715983853094</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0.1188464466776623</v>
+      </c>
+      <c r="Z52" t="n">
         <v>0.002148333333333333</v>
       </c>
-      <c r="Y52" t="n">
-        <v>20.22568990616278</v>
+      <c r="AA52" t="n">
+        <v>20.22569199499107</v>
       </c>
     </row>
     <row r="53">
@@ -4847,28 +5163,34 @@
         <v>0.07526448485171559</v>
       </c>
       <c r="R53" t="n">
+        <v>0.04747282035761839</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.2743437348504894</v>
+      </c>
+      <c r="T53" t="n">
         <v>33.56309523809537</v>
       </c>
-      <c r="S53" t="n">
+      <c r="U53" t="n">
         <v>0.2229784488956445</v>
       </c>
-      <c r="T53" t="n">
-        <v>20.4734955867161</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.887407312519426</v>
-      </c>
       <c r="V53" t="n">
-        <v>0.007103353408241623</v>
+        <v>20.47349764508844</v>
       </c>
       <c r="W53" t="n">
-        <v>0.1215390370561618</v>
+        <v>1.887407395133558</v>
       </c>
       <c r="X53" t="n">
+        <v>0.007103342896403787</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0.1215388351071716</v>
+      </c>
+      <c r="Z53" t="n">
         <v>0.0022025</v>
       </c>
-      <c r="Y53" t="n">
-        <v>20.34328539823888</v>
+      <c r="AA53" t="n">
+        <v>20.34328747236598</v>
       </c>
     </row>
     <row r="54">
@@ -4930,28 +5252,34 @@
         <v>0.102602067198723</v>
       </c>
       <c r="R54" t="n">
+        <v>0.05491924762933701</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0.3203155743930086</v>
+      </c>
+      <c r="T54" t="n">
         <v>33.39642857142849</v>
       </c>
-      <c r="S54" t="n">
+      <c r="U54" t="n">
         <v>0.2989185664601128</v>
       </c>
-      <c r="T54" t="n">
-        <v>20.58181820907232</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.889372361130537</v>
-      </c>
       <c r="V54" t="n">
-        <v>0.007200136730610088</v>
+        <v>20.58182025443793</v>
       </c>
       <c r="W54" t="n">
-        <v>0.1237179128155578</v>
+        <v>1.889372443744669</v>
       </c>
       <c r="X54" t="n">
+        <v>0.007200135700517285</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0.1237179049792681</v>
+      </c>
+      <c r="Z54" t="n">
         <v>0.002246666666666667</v>
       </c>
-      <c r="Y54" t="n">
-        <v>20.4734955867161</v>
+      <c r="AA54" t="n">
+        <v>20.47349764508844</v>
       </c>
     </row>
     <row r="55">
@@ -5007,33 +5335,39 @@
         <v>1.241564657307359</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R55" t="n">
-        <v>0.04347826086957973</v>
+        <v>0.0001</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="T55" t="n">
         <v>0.04347826086957973</v>
       </c>
       <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.04347826086957973</v>
+      </c>
+      <c r="W55" t="n">
         <v>1.6309</v>
       </c>
-      <c r="V55" t="n">
+      <c r="X55" t="n">
         <v>0.8697886689425612</v>
       </c>
-      <c r="W55" t="n">
+      <c r="Y55" t="n">
         <v>0.0378168986496892</v>
       </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
         <v>0.04347826086957973</v>
       </c>
     </row>
@@ -5090,33 +5424,39 @@
         <v>0.4980891336844761</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R56" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T56" t="n">
         <v>0.04347826086957973</v>
       </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0.07877665028313477</v>
-      </c>
       <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.07877673908509283</v>
+      </c>
+      <c r="W56" t="n">
         <v>1.6309</v>
       </c>
-      <c r="V56" t="n">
-        <v>0.8697885714934885</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0.0685190301168099</v>
-      </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>0.8697885714932413</v>
       </c>
       <c r="Y56" t="n">
+        <v>0.06851910735571869</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
         <v>0.04347826086957973</v>
       </c>
     </row>
@@ -5173,34 +5513,40 @@
         <v>0.9497676633868221</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R57" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T57" t="n">
         <v>0.1328787878787904</v>
       </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0.1935233159348465</v>
-      </c>
       <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.1935235416547727</v>
+      </c>
+      <c r="W57" t="n">
         <v>1.6309</v>
       </c>
-      <c r="V57" t="n">
-        <v>0.8697882427959044</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0.1683243049070068</v>
-      </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>0.8697882427952393</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.07877665028313477</v>
+        <v>0.168324501235416</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.07877673908509283</v>
       </c>
     </row>
     <row r="58">
@@ -5256,34 +5602,40 @@
         <v>0.8861519348632451</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R58" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T58" t="n">
         <v>0.4653846153846239</v>
       </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0.2821125744158577</v>
-      </c>
       <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.2821129043981304</v>
+      </c>
+      <c r="W58" t="n">
         <v>1.6309</v>
       </c>
-      <c r="V58" t="n">
-        <v>0.8697879758002416</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0.2453781250489639</v>
-      </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>0.8697879757992245</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.1935233159348465</v>
+        <v>0.24537841206329</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.1935235416547727</v>
       </c>
     </row>
     <row r="59">
@@ -5339,34 +5691,40 @@
         <v>0.9252948592011343</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R59" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T59" t="n">
         <v>0.6816071428571276</v>
       </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0.4233533352689145</v>
-      </c>
       <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.4233538393371857</v>
+      </c>
+      <c r="W59" t="n">
         <v>1.6309</v>
       </c>
-      <c r="V59" t="n">
-        <v>0.8697875240992518</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0.3682274493027096</v>
-      </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>0.8697875240975792</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.2821125744158577</v>
+        <v>0.3682278877342951</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0.2821129043981304</v>
       </c>
     </row>
     <row r="60">
@@ -5422,34 +5780,40 @@
         <v>0.9349196591727447</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R60" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T60" t="n">
         <v>0.9277500000000494</v>
       </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0.6830650288966243</v>
-      </c>
       <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0.683065837977753</v>
+      </c>
+      <c r="W60" t="n">
         <v>1.6309</v>
       </c>
-      <c r="V60" t="n">
-        <v>0.8697865983701096</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0.5941208079495756</v>
-      </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>0.8697865983670118</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.4233533352689145</v>
+        <v>0.5941215116753822</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0.4233538393371857</v>
       </c>
     </row>
     <row r="61">
@@ -5505,34 +5869,40 @@
         <v>0.8688225638485592</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R61" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T61" t="n">
         <v>1.43027777777781</v>
       </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>1.055197276700928</v>
-      </c>
       <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.055198526161866</v>
+      </c>
+      <c r="W61" t="n">
         <v>1.6309</v>
       </c>
-      <c r="V61" t="n">
-        <v>0.8697850039830985</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0.9177947675182717</v>
-      </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>0.8697850039771085</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.6830650288966243</v>
+        <v>0.9177958542743375</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0.683065837977753</v>
       </c>
     </row>
     <row r="62">
@@ -5588,34 +5958,40 @@
         <v>0.6800657824740611</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R62" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T62" t="n">
         <v>2.204500000000031</v>
       </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>1.630064373644841</v>
-      </c>
       <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1.63006633649882</v>
+      </c>
+      <c r="W62" t="n">
         <v>1.6309</v>
       </c>
-      <c r="V62" t="n">
-        <v>0.8697816274052284</v>
-      </c>
-      <c r="W62" t="n">
-        <v>1.417800043684095</v>
-      </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>0.8697816273911033</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.055197276700928</v>
+        <v>1.417801750915398</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>1.055198526161866</v>
       </c>
     </row>
     <row r="63">
@@ -5671,34 +6047,40 @@
         <v>0.6441156540974313</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R63" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T63" t="n">
         <v>3.41107142857146</v>
       </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>2.48186964610957</v>
-      </c>
       <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>2.481872712794513</v>
+      </c>
+      <c r="W63" t="n">
         <v>1.6309</v>
       </c>
-      <c r="V63" t="n">
-        <v>0.8697724285645281</v>
-      </c>
-      <c r="W63" t="n">
-        <v>2.158661789477307</v>
-      </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>0.8697724285148286</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.630064373644841</v>
+        <v>2.158664456671969</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1.63006633649882</v>
       </c>
     </row>
     <row r="64">
@@ -5754,34 +6136,40 @@
         <v>0.4894339946770361</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R64" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T64" t="n">
         <v>4.485714285714332</v>
       </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>4.183103260869902</v>
-      </c>
       <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>4.183103260871403</v>
+      </c>
+      <c r="W64" t="n">
         <v>1.6309</v>
       </c>
-      <c r="V64" t="n">
-        <v>-5.168314036484844e-09</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>-2.93774096838361e-08</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.48186964610957</v>
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>2.481872712794513</v>
       </c>
     </row>
     <row r="65">
@@ -5837,34 +6225,40 @@
         <v>0.4930841029038115</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R65" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T65" t="n">
         <v>8.025000000000075</v>
       </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>6.644072702977562</v>
-      </c>
       <c r="U65" t="n">
-        <v>1.664919999994332</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>0.4562847876418082</v>
+        <v>6.644073207633276</v>
       </c>
       <c r="W65" t="n">
-        <v>2.869968957550593</v>
+        <v>1.664920009844197</v>
       </c>
       <c r="X65" t="n">
+        <v>0.4562847911293855</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>2.869969199669203</v>
+      </c>
+      <c r="Z65" t="n">
         <v>0.04049999999999999</v>
       </c>
-      <c r="Y65" t="n">
-        <v>4.183103260869902</v>
+      <c r="AA65" t="n">
+        <v>4.183103260871403</v>
       </c>
     </row>
     <row r="66">
@@ -5920,34 +6314,40 @@
         <v>0.4398139997631306</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R66" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T66" t="n">
         <v>11.51785714285718</v>
       </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>8.113663161137396</v>
-      </c>
       <c r="U66" t="n">
-        <v>1.685919999994332</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>0.3963156913428896</v>
+        <v>8.113663650919111</v>
       </c>
       <c r="W66" t="n">
-        <v>3.006223807136208</v>
+        <v>1.685920009844016</v>
       </c>
       <c r="X66" t="n">
+        <v>0.3963158641047057</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>3.006225391561416</v>
+      </c>
+      <c r="Z66" t="n">
         <v>0.04350000000000001</v>
       </c>
-      <c r="Y66" t="n">
-        <v>6.644072702977562</v>
+      <c r="AA66" t="n">
+        <v>6.644073207633276</v>
       </c>
     </row>
     <row r="67">
@@ -6003,34 +6403,40 @@
         <v>0.3354852570926234</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R67" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T67" t="n">
         <v>14.97857142857154</v>
       </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>10.33156584395486</v>
-      </c>
       <c r="U67" t="n">
-        <v>1.718635833327665</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>0.3354923777667394</v>
+        <v>10.33156631118175</v>
       </c>
       <c r="W67" t="n">
-        <v>3.178812265626877</v>
+        <v>1.718635843177344</v>
       </c>
       <c r="X67" t="n">
+        <v>0.3354923524905105</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>3.17881214988686</v>
+      </c>
+      <c r="Z67" t="n">
         <v>0.0478</v>
       </c>
-      <c r="Y67" t="n">
-        <v>8.113663161137396</v>
+      <c r="AA67" t="n">
+        <v>8.113663650919111</v>
       </c>
     </row>
     <row r="68">
@@ -6086,34 +6492,40 @@
         <v>0.3363582465062418</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R68" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T68" t="n">
         <v>19.46071428571426</v>
       </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>12.38718794333273</v>
-      </c>
       <c r="U68" t="n">
-        <v>1.750112499994332</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>0.2966300583922875</v>
+        <v>12.3871883970568</v>
       </c>
       <c r="W68" t="n">
-        <v>3.309190676977103</v>
+        <v>1.75011250984401</v>
       </c>
       <c r="X68" t="n">
+        <v>0.2966301045031565</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>3.30919137142728</v>
+      </c>
+      <c r="Z68" t="n">
         <v>0.0516</v>
       </c>
-      <c r="Y68" t="n">
-        <v>10.33156584395486</v>
+      <c r="AA68" t="n">
+        <v>10.33156631118175</v>
       </c>
     </row>
     <row r="69">
@@ -6169,34 +6581,40 @@
         <v>0.183772009728279</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R69" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T69" t="n">
         <v>22.09642857142853</v>
       </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>14.80438644777559</v>
-      </c>
       <c r="U69" t="n">
-        <v>1.788633333327665</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>0.2630897918530912</v>
+        <v>14.80438687360635</v>
       </c>
       <c r="W69" t="n">
-        <v>3.43220276357191</v>
+        <v>1.788633343177343</v>
       </c>
       <c r="X69" t="n">
+        <v>0.2630897868796421</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>3.432202791214216</v>
+      </c>
+      <c r="Z69" t="n">
         <v>0.05589999999999999</v>
       </c>
-      <c r="Y69" t="n">
-        <v>12.38718794333273</v>
+      <c r="AA69" t="n">
+        <v>12.3871883970568</v>
       </c>
     </row>
     <row r="70">
@@ -6258,28 +6676,34 @@
         <v>0.06320238611045444</v>
       </c>
       <c r="R70" t="n">
+        <v>0.0464330358326207</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0.2514008474736202</v>
+      </c>
+      <c r="T70" t="n">
         <v>28.42857142857147</v>
       </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>15.01969250760888</v>
-      </c>
       <c r="U70" t="n">
-        <v>1.792146527764305</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>0.009244326228632355</v>
+        <v>15.01969296805368</v>
       </c>
       <c r="W70" t="n">
-        <v>0.1221131944166381</v>
+        <v>1.792146539303604</v>
       </c>
       <c r="X70" t="n">
+        <v>0.00924435718584087</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0.1221136632356617</v>
+      </c>
+      <c r="Z70" t="n">
         <v>0.001996666666666667</v>
       </c>
-      <c r="Y70" t="n">
-        <v>14.80438644777559</v>
+      <c r="AA70" t="n">
+        <v>14.80438687360635</v>
       </c>
     </row>
     <row r="71">
@@ -6341,28 +6765,34 @@
         <v>0.05093049240086417</v>
       </c>
       <c r="R71" t="n">
+        <v>0.04115887469949947</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0.2256778509310654</v>
+      </c>
+      <c r="T71" t="n">
         <v>29.31428571428569</v>
       </c>
-      <c r="S71" t="n">
+      <c r="U71" t="n">
         <v>0.05810793948216079</v>
       </c>
-      <c r="T71" t="n">
-        <v>15.15569778641188</v>
-      </c>
-      <c r="U71" t="n">
-        <v>1.794373111097638</v>
-      </c>
       <c r="V71" t="n">
-        <v>0.009401995746227973</v>
+        <v>15.15569823705797</v>
       </c>
       <c r="W71" t="n">
-        <v>0.1251649463817385</v>
+        <v>1.794373122636937</v>
       </c>
       <c r="X71" t="n">
+        <v>0.00940201309158991</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0.1251652130959574</v>
+      </c>
+      <c r="Z71" t="n">
         <v>0.002051666666666667</v>
       </c>
-      <c r="Y71" t="n">
-        <v>15.01969250760888</v>
+      <c r="AA71" t="n">
+        <v>15.01969296805368</v>
       </c>
     </row>
     <row r="72">
@@ -6424,28 +6854,34 @@
         <v>0.03650228328522884</v>
       </c>
       <c r="R72" t="n">
+        <v>0.03434893131725996</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0.1910557072825328</v>
+      </c>
+      <c r="T72" t="n">
         <v>30.06428571428577</v>
       </c>
-      <c r="S72" t="n">
+      <c r="U72" t="n">
         <v>0.1219400842896329</v>
       </c>
-      <c r="T72" t="n">
-        <v>15.27797946826978</v>
-      </c>
-      <c r="U72" t="n">
-        <v>1.796379749986527</v>
-      </c>
       <c r="V72" t="n">
-        <v>0.009535924639375432</v>
+        <v>15.27797991000348</v>
       </c>
       <c r="W72" t="n">
-        <v>0.12782943008243</v>
+        <v>1.796379761525826</v>
       </c>
       <c r="X72" t="n">
+        <v>0.009535909472786619</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0.1278292021782632</v>
+      </c>
+      <c r="Z72" t="n">
         <v>0.0021</v>
       </c>
-      <c r="Y72" t="n">
-        <v>15.15569778641188</v>
+      <c r="AA72" t="n">
+        <v>15.15569823705797</v>
       </c>
     </row>
     <row r="73">
@@ -6507,28 +6943,34 @@
         <v>0.01662203559450923</v>
       </c>
       <c r="R73" t="n">
+        <v>0.02296789446903608</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0.1289264735983624</v>
+      </c>
+      <c r="T73" t="n">
         <v>30.93809523809523</v>
       </c>
-      <c r="S73" t="n">
+      <c r="U73" t="n">
         <v>0.1703755277559266</v>
       </c>
-      <c r="T73" t="n">
-        <v>15.40717642178005</v>
-      </c>
-      <c r="U73" t="n">
-        <v>1.798504749986527</v>
-      </c>
       <c r="V73" t="n">
-        <v>0.009669490718981348</v>
+        <v>15.40717685453495</v>
       </c>
       <c r="W73" t="n">
-        <v>0.1305612331413965</v>
+        <v>1.798504761525826</v>
       </c>
       <c r="X73" t="n">
+        <v>0.009669568421304507</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0.1305624341001924</v>
+      </c>
+      <c r="Z73" t="n">
         <v>0.00215</v>
       </c>
-      <c r="Y73" t="n">
-        <v>15.27797946826978</v>
+      <c r="AA73" t="n">
+        <v>15.27797991000348</v>
       </c>
     </row>
     <row r="74">
@@ -6584,34 +7026,40 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R74" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T74" t="n">
         <v>31.5095238095239</v>
       </c>
-      <c r="S74" t="n">
+      <c r="U74" t="n">
         <v>0.2036432131066642</v>
       </c>
-      <c r="T74" t="n">
-        <v>15.54576471769251</v>
-      </c>
-      <c r="U74" t="n">
-        <v>1.800789812486527</v>
-      </c>
       <c r="V74" t="n">
-        <v>0.009804969956134207</v>
+        <v>15.54576514061194</v>
       </c>
       <c r="W74" t="n">
-        <v>0.1334121284519593</v>
+        <v>1.800789824025826</v>
       </c>
       <c r="X74" t="n">
+        <v>0.009804949344494194</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0.1334118117795324</v>
+      </c>
+      <c r="Z74" t="n">
         <v>0.0022025</v>
       </c>
-      <c r="Y74" t="n">
-        <v>15.40717642178005</v>
+      <c r="AA74" t="n">
+        <v>15.40717685453495</v>
       </c>
     </row>
     <row r="75">
@@ -6667,34 +7115,40 @@
         <v>0.07036365759109456</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R75" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T75" t="n">
         <v>31.73214285714281</v>
       </c>
-      <c r="S75" t="n">
+      <c r="U75" t="n">
         <v>0.2220723133576301</v>
       </c>
-      <c r="T75" t="n">
-        <v>15.66240050531441</v>
-      </c>
-      <c r="U75" t="n">
-        <v>1.802717423597638</v>
-      </c>
       <c r="V75" t="n">
-        <v>0.009912768036938789</v>
+        <v>15.66240091965512</v>
       </c>
       <c r="W75" t="n">
-        <v>0.1357454553421338</v>
+        <v>1.802717435136937</v>
       </c>
       <c r="X75" t="n">
+        <v>0.009912767707050024</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.1357454538912589</v>
+      </c>
+      <c r="Z75" t="n">
         <v>0.002245833333333333</v>
       </c>
-      <c r="Y75" t="n">
-        <v>15.54576471769251</v>
+      <c r="AA75" t="n">
+        <v>15.54576514061194</v>
       </c>
     </row>
     <row r="76">
@@ -6750,33 +7204,39 @@
         <v>2.163724434494653</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R76" t="n">
-        <v>0.2107142857143181</v>
+        <v>0.0001</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="T76" t="n">
         <v>0.2107142857143181</v>
       </c>
       <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0.2107142857143181</v>
+      </c>
+      <c r="W76" t="n">
         <v>1.74784</v>
       </c>
-      <c r="V76" t="n">
+      <c r="X76" t="n">
         <v>0.869786710518112</v>
       </c>
-      <c r="W76" t="n">
+      <c r="Y76" t="n">
         <v>0.1832764854306303</v>
       </c>
-      <c r="X76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y76" t="n">
+      <c r="Z76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" t="n">
         <v>0.2107142857143181</v>
       </c>
     </row>
@@ -6833,33 +7293,39 @@
         <v>0.4976806198790853</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R77" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T77" t="n">
         <v>0.2107142857143181</v>
       </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0.3708747165822192</v>
-      </c>
       <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0.370875083331963</v>
+      </c>
+      <c r="W77" t="n">
         <v>1.74784</v>
       </c>
-      <c r="V77" t="n">
-        <v>0.8697860788312014</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0.3225816654736816</v>
-      </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>0.8697860788296862</v>
       </c>
       <c r="Y77" t="n">
+        <v>0.3225819844669411</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="n">
         <v>0.2107142857143181</v>
       </c>
     </row>
@@ -6916,34 +7382,40 @@
         <v>0.6434103325007062</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R78" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T78" t="n">
         <v>0.4654761904762265</v>
       </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0.7018410357461898</v>
-      </c>
       <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0.7018417604311611</v>
+      </c>
+      <c r="W78" t="n">
         <v>1.74784</v>
       </c>
-      <c r="V78" t="n">
-        <v>0.8697845624794842</v>
-      </c>
-      <c r="W78" t="n">
-        <v>0.6104504982066478</v>
-      </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>0.8697845624758024</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.3708747165822192</v>
+        <v>0.6104511285238644</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0.370875083331963</v>
       </c>
     </row>
     <row r="79">
@@ -6999,34 +7471,40 @@
         <v>0.7086782992882604</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R79" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T79" t="n">
         <v>0.6464285714286033</v>
       </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>1.367227741518679</v>
-      </c>
       <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1.36722917433076</v>
+      </c>
+      <c r="W79" t="n">
         <v>1.74784</v>
       </c>
-      <c r="V79" t="n">
-        <v>0.8697802340255848</v>
-      </c>
-      <c r="W79" t="n">
-        <v>1.189187664984388</v>
-      </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>0.8697802340136507</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.7018410357461898</v>
+        <v>1.189188911199699</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0.7018417604311611</v>
       </c>
     </row>
     <row r="80">
@@ -7082,34 +7560,40 @@
         <v>0.7081139676449741</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R80" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T80" t="n">
         <v>1.175000000000005</v>
       </c>
-      <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>2.270850112990517</v>
-      </c>
       <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>2.270852496842724</v>
+      </c>
+      <c r="W80" t="n">
         <v>1.74784</v>
       </c>
-      <c r="V80" t="n">
-        <v>0.8697680795100844</v>
-      </c>
-      <c r="W80" t="n">
-        <v>1.97511294163102</v>
-      </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>0.869768079458302</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.367227741518679</v>
+        <v>1.975115014911986</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>1.36722917433076</v>
       </c>
     </row>
     <row r="81">
@@ -7165,34 +7649,40 @@
         <v>0.5633097792025544</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R81" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T81" t="n">
         <v>1.796428571428604</v>
       </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>3.740289285714594</v>
-      </c>
       <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>3.74028928571578</v>
+      </c>
+      <c r="W81" t="n">
         <v>1.74784</v>
       </c>
-      <c r="V81" t="n">
-        <v>-4.426896485969155e-09</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0</v>
-      </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>-2.36020749497522e-08</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.270850112990517</v>
+        <v>0</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>2.270852496842724</v>
       </c>
     </row>
     <row r="82">
@@ -7248,34 +7738,40 @@
         <v>0.4665723884474225</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R82" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T82" t="n">
         <v>3.449999999999922</v>
       </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>5.780684203697608</v>
-      </c>
       <c r="U82" t="n">
-        <v>1.777849722226023</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>0.5739981969170489</v>
+        <v>5.780684204026415</v>
       </c>
       <c r="W82" t="n">
-        <v>3.164197821268447</v>
+        <v>1.777849722230804</v>
       </c>
       <c r="X82" t="n">
+        <v>0.5739981352015475</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>3.164197464691017</v>
+      </c>
+      <c r="Z82" t="n">
         <v>0.04733333333333335</v>
       </c>
-      <c r="Y82" t="n">
-        <v>3.740289285714594</v>
+      <c r="AA82" t="n">
+        <v>3.74028928571578</v>
       </c>
     </row>
     <row r="83">
@@ -7331,34 +7827,40 @@
         <v>0.4598955531383755</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R83" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T83" t="n">
         <v>5.41785714285711</v>
       </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>9.058698433022704</v>
-      </c>
       <c r="U83" t="n">
-        <v>1.828277500003801</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>0.4289169262259255</v>
+        <v>9.058698433231534</v>
       </c>
       <c r="W83" t="n">
-        <v>3.60300707515135</v>
+        <v>1.828277500008582</v>
       </c>
       <c r="X83" t="n">
+        <v>0.4289168615272934</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>3.603006489149752</v>
+      </c>
+      <c r="Z83" t="n">
         <v>0.057</v>
       </c>
-      <c r="Y83" t="n">
-        <v>5.780684203697608</v>
+      <c r="AA83" t="n">
+        <v>5.780684204026415</v>
       </c>
     </row>
     <row r="84">
@@ -7414,34 +7916,40 @@
         <v>0.435983363979242</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R84" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T84" t="n">
         <v>7.639285714285721</v>
       </c>
-      <c r="S84" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" t="n">
-        <v>11.41819283039667</v>
-      </c>
       <c r="U84" t="n">
-        <v>1.866383055559356</v>
+        <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>0.3703725849593388</v>
+        <v>11.41819282344158</v>
       </c>
       <c r="W84" t="n">
-        <v>3.841523754297543</v>
+        <v>1.866383055564137</v>
       </c>
       <c r="X84" t="n">
+        <v>0.3703727279476379</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>3.841525384626546</v>
+      </c>
+      <c r="Z84" t="n">
         <v>0.06333333333333334</v>
       </c>
-      <c r="Y84" t="n">
-        <v>9.058698433022704</v>
+      <c r="AA84" t="n">
+        <v>9.058698433231534</v>
       </c>
     </row>
     <row r="85">
@@ -7497,34 +8005,40 @@
         <v>0.3176043329592845</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R85" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T85" t="n">
         <v>9.857142857142883</v>
       </c>
-      <c r="S85" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" t="n">
-        <v>16.52906369449629</v>
-      </c>
       <c r="U85" t="n">
-        <v>1.9546275000038</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>0.2931603594131192</v>
+        <v>16.52906368661916</v>
       </c>
       <c r="W85" t="n">
-        <v>4.202981731311067</v>
+        <v>1.954627500008582</v>
       </c>
       <c r="X85" t="n">
+        <v>0.293160374987613</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>4.202981986741455</v>
+      </c>
+      <c r="Z85" t="n">
         <v>0.07599999999999998</v>
       </c>
-      <c r="Y85" t="n">
-        <v>11.41819283039667</v>
+      <c r="AA85" t="n">
+        <v>11.41819282344158</v>
       </c>
     </row>
     <row r="86">
@@ -7580,34 +8094,40 @@
         <v>0.2216739014614701</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R86" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T86" t="n">
         <v>15.67142857142846</v>
       </c>
-      <c r="S86" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" t="n">
-        <v>20.39251849328181</v>
-      </c>
       <c r="U86" t="n">
-        <v>2.027077500003801</v>
+        <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>0.2562602744628768</v>
+        <v>20.39251848523132</v>
       </c>
       <c r="W86" t="n">
-        <v>4.370687402708426</v>
+        <v>2.027077500008582</v>
       </c>
       <c r="X86" t="n">
+        <v>0.2562603568609737</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>4.370689081289711</v>
+      </c>
+      <c r="Z86" t="n">
         <v>0.08500000000000002</v>
       </c>
-      <c r="Y86" t="n">
-        <v>16.52906369449629</v>
+      <c r="AA86" t="n">
+        <v>16.52906368661916</v>
       </c>
     </row>
     <row r="87">
@@ -7663,34 +8183,40 @@
         <v>0.1419264349539861</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R87" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T87" t="n">
         <v>19.33214285714294</v>
       </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" t="n">
-        <v>23.31766948771998</v>
-      </c>
       <c r="U87" t="n">
-        <v>2.085607250005868</v>
+        <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>0.01021601143463817</v>
+        <v>23.31767048629318</v>
       </c>
       <c r="W87" t="n">
-        <v>0.200536040231481</v>
+        <v>2.085607271913489</v>
       </c>
       <c r="X87" t="n">
+        <v>0.01021561874538532</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0.2005268926165561</v>
+      </c>
+      <c r="Z87" t="n">
         <v>0.003370000000000001</v>
       </c>
-      <c r="Y87" t="n">
-        <v>20.39251849328181</v>
+      <c r="AA87" t="n">
+        <v>20.39251848523132</v>
       </c>
     </row>
     <row r="88">
@@ -7746,34 +8272,40 @@
         <v>0.07721244115214908</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R88" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T88" t="n">
         <v>21.1678571428572</v>
       </c>
-      <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>23.51196957197683</v>
-      </c>
       <c r="U88" t="n">
-        <v>2.089615000005868</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>0.01079791085738135</v>
+        <v>23.51197052130172</v>
       </c>
       <c r="W88" t="n">
-        <v>0.2133736034431671</v>
+        <v>2.089615021915349</v>
       </c>
       <c r="X88" t="n">
+        <v>0.01079783915409544</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0.2133719265975545</v>
+      </c>
+      <c r="Z88" t="n">
         <v>0.0036</v>
       </c>
-      <c r="Y88" t="n">
-        <v>23.31766948771998</v>
+      <c r="AA88" t="n">
+        <v>23.31767048629318</v>
       </c>
     </row>
     <row r="89">
@@ -7829,34 +8361,40 @@
         <v>0.03322042971089017</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R89" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T89" t="n">
         <v>23.35000000000008</v>
       </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>23.76781114604884</v>
-      </c>
       <c r="U89" t="n">
-        <v>2.094915694450313</v>
+        <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>0.01151426144225921</v>
+        <v>23.76781203213405</v>
       </c>
       <c r="W89" t="n">
-        <v>0.2296105348160797</v>
+        <v>2.094915716359793</v>
       </c>
       <c r="X89" t="n">
+        <v>0.01151014686535403</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0.2295127493464703</v>
+      </c>
+      <c r="Z89" t="n">
         <v>0.003883333333333334</v>
       </c>
-      <c r="Y89" t="n">
-        <v>23.51196957197683</v>
+      <c r="AA89" t="n">
+        <v>23.51197052130172</v>
       </c>
     </row>
     <row r="90">
@@ -7918,28 +8456,34 @@
         <v>0.07399229663180125</v>
       </c>
       <c r="R90" t="n">
+        <v>0.05414454690340646</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0.2720152507338536</v>
+      </c>
+      <c r="T90" t="n">
         <v>24.49345238095237</v>
       </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>23.93967898585161</v>
-      </c>
       <c r="U90" t="n">
-        <v>2.098491694450313</v>
+        <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>0.01007971427442612</v>
+        <v>23.93968006453909</v>
       </c>
       <c r="W90" t="n">
-        <v>0.1949504513214563</v>
+        <v>2.098491720806879</v>
       </c>
       <c r="X90" t="n">
+        <v>0.01007997637280434</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>0.194956735239167</v>
+      </c>
+      <c r="Z90" t="n">
         <v>0.004063333333333333</v>
       </c>
-      <c r="Y90" t="n">
-        <v>23.76781114604884</v>
+      <c r="AA90" t="n">
+        <v>23.76781203213405</v>
       </c>
     </row>
     <row r="91">
@@ -8001,28 +8545,34 @@
         <v>0.06485638924285067</v>
       </c>
       <c r="R91" t="n">
+        <v>0.05116644028606399</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0.2546691760752578</v>
+      </c>
+      <c r="T91" t="n">
         <v>25.23928571428564</v>
       </c>
-      <c r="S91" t="n">
+      <c r="U91" t="n">
         <v>0.06375494686076261</v>
       </c>
-      <c r="T91" t="n">
-        <v>24.22814583641843</v>
-      </c>
-      <c r="U91" t="n">
-        <v>2.104521250005869</v>
-      </c>
       <c r="V91" t="n">
-        <v>0.01063211796426457</v>
+        <v>24.22814684652792</v>
       </c>
       <c r="W91" t="n">
-        <v>0.2075174500820442</v>
+        <v>2.104521276362434</v>
       </c>
       <c r="X91" t="n">
+        <v>0.01063212456913026</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>0.207517619384608</v>
+      </c>
+      <c r="Z91" t="n">
         <v>0.00435</v>
       </c>
-      <c r="Y91" t="n">
-        <v>23.93967898585161</v>
+      <c r="AA91" t="n">
+        <v>23.93968006453909</v>
       </c>
     </row>
     <row r="92">
@@ -8084,28 +8634,34 @@
         <v>0.04872158819598323</v>
       </c>
       <c r="R92" t="n">
+        <v>0.0441207297966015</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0.2207296722146418</v>
+      </c>
+      <c r="T92" t="n">
         <v>24.77321428571426</v>
       </c>
-      <c r="S92" t="n">
+      <c r="U92" t="n">
         <v>0.1716212668026328</v>
       </c>
-      <c r="T92" t="n">
-        <v>24.54912557034737</v>
-      </c>
-      <c r="U92" t="n">
-        <v>2.111271250005868</v>
-      </c>
       <c r="V92" t="n">
-        <v>0.01118089966425217</v>
+        <v>24.54912650345894</v>
       </c>
       <c r="W92" t="n">
-        <v>0.22041273201674</v>
+        <v>2.111271276362434</v>
       </c>
       <c r="X92" t="n">
+        <v>0.01118092410442565</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0.2204133410545105</v>
+      </c>
+      <c r="Z92" t="n">
         <v>0.00465</v>
       </c>
-      <c r="Y92" t="n">
-        <v>24.22814583641843</v>
+      <c r="AA92" t="n">
+        <v>24.22814684652792</v>
       </c>
     </row>
     <row r="93">
@@ -8167,28 +8723,34 @@
         <v>0.03284030984725474</v>
       </c>
       <c r="R93" t="n">
+        <v>0.03536550708002241</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0.1812189555406794</v>
+      </c>
+      <c r="T93" t="n">
         <v>25.0285714285714</v>
       </c>
-      <c r="S93" t="n">
+      <c r="U93" t="n">
         <v>0.2547670720457892</v>
       </c>
-      <c r="T93" t="n">
-        <v>25.00680786787553</v>
-      </c>
-      <c r="U93" t="n">
-        <v>2.120971250005868</v>
-      </c>
       <c r="V93" t="n">
-        <v>0.0118658838353382</v>
+        <v>25.00680869176568</v>
       </c>
       <c r="W93" t="n">
-        <v>0.2371870514484175</v>
+        <v>2.120971276362434</v>
       </c>
       <c r="X93" t="n">
+        <v>0.01186587573608902</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0.2371868574664508</v>
+      </c>
+      <c r="Z93" t="n">
         <v>0.005050000000000001</v>
       </c>
-      <c r="Y93" t="n">
-        <v>24.54912557034737</v>
+      <c r="AA93" t="n">
+        <v>24.54912650345894</v>
       </c>
     </row>
     <row r="94">
@@ -8250,28 +8812,34 @@
         <v>0.002777158124534164</v>
       </c>
       <c r="R94" t="n">
+        <v>0.01006757845422143</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0.05269874879476897</v>
+      </c>
+      <c r="T94" t="n">
         <v>26.25714285714279</v>
       </c>
-      <c r="S94" t="n">
+      <c r="U94" t="n">
         <v>0.3345630000595383</v>
       </c>
-      <c r="T94" t="n">
-        <v>26.11045456428113</v>
-      </c>
-      <c r="U94" t="n">
-        <v>2.14473236111698</v>
-      </c>
       <c r="V94" t="n">
-        <v>0.01316721393135566</v>
+        <v>26.11045512932166</v>
       </c>
       <c r="W94" t="n">
-        <v>0.2717711091938156</v>
+        <v>2.144732387473546</v>
       </c>
       <c r="X94" t="n">
+        <v>0.01316721250280378</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>0.271771078660095</v>
+      </c>
+      <c r="Z94" t="n">
         <v>0.005916666666666667</v>
       </c>
-      <c r="Y94" t="n">
-        <v>25.00680786787553</v>
+      <c r="AA94" t="n">
+        <v>25.00680869176568</v>
       </c>
     </row>
     <row r="95">
@@ -8327,34 +8895,40 @@
         <v>0.01145255846603085</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R95" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T95" t="n">
         <v>27.40000000000004</v>
       </c>
-      <c r="S95" t="n">
+      <c r="U95" t="n">
         <v>0.4114676331552647</v>
       </c>
-      <c r="T95" t="n">
-        <v>26.57397314631664</v>
-      </c>
-      <c r="U95" t="n">
-        <v>2.154871250005869</v>
-      </c>
       <c r="V95" t="n">
-        <v>0.01360205894586814</v>
+        <v>26.57397360426178</v>
       </c>
       <c r="W95" t="n">
-        <v>0.2843854565366162</v>
+        <v>2.154871276362434</v>
       </c>
       <c r="X95" t="n">
+        <v>0.01360205481603644</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>0.2843853526340677</v>
+      </c>
+      <c r="Z95" t="n">
         <v>0.00625</v>
       </c>
-      <c r="Y95" t="n">
-        <v>26.11045456428113</v>
+      <c r="AA95" t="n">
+        <v>26.11045512932166</v>
       </c>
     </row>
     <row r="96">
@@ -8416,28 +8990,34 @@
         <v>0.001762949417501451</v>
       </c>
       <c r="R96" t="n">
+        <v>0.007839965084997607</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0.04198749120275527</v>
+      </c>
+      <c r="T96" t="n">
         <v>28.4607142857143</v>
       </c>
-      <c r="S96" t="n">
+      <c r="U96" t="n">
         <v>0.4067877264015557</v>
       </c>
-      <c r="T96" t="n">
-        <v>27.30784322886136</v>
-      </c>
-      <c r="U96" t="n">
-        <v>2.171121250005869</v>
-      </c>
       <c r="V96" t="n">
-        <v>0.01418844280408847</v>
+        <v>27.30784352193885</v>
       </c>
       <c r="W96" t="n">
-        <v>0.302555887977083</v>
+        <v>2.171121276362435</v>
       </c>
       <c r="X96" t="n">
+        <v>0.01418840491525607</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>0.3025548575925655</v>
+      </c>
+      <c r="Z96" t="n">
         <v>0.006750000000000001</v>
       </c>
-      <c r="Y96" t="n">
-        <v>26.57397314631664</v>
+      <c r="AA96" t="n">
+        <v>26.57397360426178</v>
       </c>
     </row>
     <row r="97">
@@ -8499,28 +9079,34 @@
         <v>0.001647154283060745</v>
       </c>
       <c r="R97" t="n">
+        <v>0.007564472262002585</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0.04058514855289733</v>
+      </c>
+      <c r="T97" t="n">
         <v>28.6821428571429</v>
       </c>
-      <c r="S97" t="n">
+      <c r="U97" t="n">
         <v>0.4021708299263646</v>
       </c>
-      <c r="T97" t="n">
-        <v>27.82182632953165</v>
-      </c>
-      <c r="U97" t="n">
-        <v>2.182649027783647</v>
-      </c>
       <c r="V97" t="n">
-        <v>0.01453702929851717</v>
+        <v>27.82182651078572</v>
       </c>
       <c r="W97" t="n">
-        <v>0.31415675529333</v>
+        <v>2.182649054140212</v>
       </c>
       <c r="X97" t="n">
+        <v>0.01453692586273916</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>0.3141538806580285</v>
+      </c>
+      <c r="Z97" t="n">
         <v>0.007083333333333334</v>
       </c>
-      <c r="Y97" t="n">
-        <v>27.30784322886136</v>
+      <c r="AA97" t="n">
+        <v>27.30784352193885</v>
       </c>
     </row>
     <row r="98">
@@ -8582,28 +9168,34 @@
         <v>0.0005503013934911842</v>
       </c>
       <c r="R98" t="n">
+        <v>0.004370963058975695</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0.02345850364987469</v>
+      </c>
+      <c r="T98" t="n">
         <v>28.78571428571429</v>
       </c>
-      <c r="S98" t="n">
+      <c r="U98" t="n">
         <v>0.3873938421634567</v>
       </c>
-      <c r="T98" t="n">
-        <v>28.72212538886001</v>
-      </c>
-      <c r="U98" t="n">
-        <v>2.203139000005869</v>
-      </c>
       <c r="V98" t="n">
-        <v>0.01504659646470858</v>
+        <v>28.72212537780479</v>
       </c>
       <c r="W98" t="n">
-        <v>0.3325682361029325</v>
+        <v>2.203139026362434</v>
       </c>
       <c r="X98" t="n">
+        <v>0.01504659517082482</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>0.3325682000033916</v>
+      </c>
+      <c r="Z98" t="n">
         <v>0.007640000000000001</v>
       </c>
-      <c r="Y98" t="n">
-        <v>27.82182632953165</v>
+      <c r="AA98" t="n">
+        <v>27.82182651078572</v>
       </c>
     </row>
     <row r="99">
@@ -8665,28 +9257,34 @@
         <v>0.0004247662125730495</v>
       </c>
       <c r="R99" t="n">
+        <v>0.003775433716909023</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0.02060985717012735</v>
+      </c>
+      <c r="T99" t="n">
         <v>28.80357142857139</v>
       </c>
-      <c r="S99" t="n">
+      <c r="U99" t="n">
         <v>0.3689307159607038</v>
       </c>
-      <c r="T99" t="n">
-        <v>29.76547646662382</v>
-      </c>
-      <c r="U99" t="n">
-        <v>2.227371250005869</v>
-      </c>
       <c r="V99" t="n">
-        <v>0.01550780134710743</v>
+        <v>29.76547634687633</v>
       </c>
       <c r="W99" t="n">
-        <v>0.3513482182048674</v>
+        <v>2.227371276362434</v>
       </c>
       <c r="X99" t="n">
+        <v>0.01550781476267443</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>0.3513486174167029</v>
+      </c>
+      <c r="Z99" t="n">
         <v>0.00825</v>
       </c>
-      <c r="Y99" t="n">
-        <v>28.72212538886001</v>
+      <c r="AA99" t="n">
+        <v>28.72212537780479</v>
       </c>
     </row>
     <row r="100">
@@ -8748,28 +9346,34 @@
         <v>0.008954679612111731</v>
       </c>
       <c r="R100" t="n">
+        <v>0.01696173781741488</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0.09462916892856943</v>
+      </c>
+      <c r="T100" t="n">
         <v>29.79999999999999</v>
       </c>
-      <c r="S100" t="n">
+      <c r="U100" t="n">
         <v>0.3542503465167628</v>
       </c>
-      <c r="T100" t="n">
-        <v>30.84541916586719</v>
-      </c>
-      <c r="U100" t="n">
-        <v>2.253021250005869</v>
-      </c>
       <c r="V100" t="n">
-        <v>0.01587052728317392</v>
+        <v>30.84541902494425</v>
       </c>
       <c r="W100" t="n">
-        <v>0.3683704455222586</v>
+        <v>2.253021276362434</v>
       </c>
       <c r="X100" t="n">
+        <v>0.01587053886464064</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>0.3683708024918843</v>
+      </c>
+      <c r="Z100" t="n">
         <v>0.00885</v>
       </c>
-      <c r="Y100" t="n">
-        <v>29.76547646662382</v>
+      <c r="AA100" t="n">
+        <v>29.76547634687633</v>
       </c>
     </row>
     <row r="101">
@@ -8831,28 +9435,34 @@
         <v>0.02192219084074996</v>
       </c>
       <c r="R101" t="n">
+        <v>0.02664331523520602</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0.148061442788965</v>
+      </c>
+      <c r="T101" t="n">
         <v>31.12500000000002</v>
       </c>
-      <c r="S101" t="n">
+      <c r="U101" t="n">
         <v>0.363160750555521</v>
       </c>
-      <c r="T101" t="n">
-        <v>31.81469618095175</v>
-      </c>
-      <c r="U101" t="n">
-        <v>2.27655111111698</v>
-      </c>
       <c r="V101" t="n">
-        <v>0.01611696629351479</v>
+        <v>31.8146960202547</v>
       </c>
       <c r="W101" t="n">
-        <v>0.3818576537892139</v>
+        <v>2.276551137473545</v>
       </c>
       <c r="X101" t="n">
+        <v>0.01611696618632926</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0.3818576499658321</v>
+      </c>
+      <c r="Z101" t="n">
         <v>0.009366666666666667</v>
       </c>
-      <c r="Y101" t="n">
-        <v>30.84541916586719</v>
+      <c r="AA101" t="n">
+        <v>30.84541902494425</v>
       </c>
     </row>
     <row r="102">
@@ -8908,33 +9518,39 @@
         <v>0.2993817189618296</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R102" t="n">
-        <v>0.1803571428572935</v>
+        <v>0.0001</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="T102" t="n">
         <v>0.1803571428572935</v>
       </c>
       <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0.1803571428572935</v>
+      </c>
+      <c r="W102" t="n">
         <v>1.7528</v>
       </c>
-      <c r="V102" t="n">
+      <c r="X102" t="n">
         <v>0.869786886974646</v>
       </c>
-      <c r="W102" t="n">
+      <c r="Y102" t="n">
         <v>0.1568722778294868</v>
       </c>
-      <c r="X102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="n">
+      <c r="Z102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" t="n">
         <v>0.1803571428572935</v>
       </c>
     </row>
@@ -8991,33 +9607,39 @@
         <v>1.543307739364463</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R103" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T103" t="n">
         <v>0.1803571428572935</v>
       </c>
-      <c r="S103" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" t="n">
-        <v>0.3616830541820591</v>
-      </c>
       <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0.3616834182881157</v>
+      </c>
+      <c r="W103" t="n">
         <v>1.7528</v>
       </c>
-      <c r="V103" t="n">
-        <v>0.8697861867769205</v>
-      </c>
-      <c r="W103" t="n">
-        <v>0.3145869245188435</v>
-      </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>0.8697861867754395</v>
       </c>
       <c r="Y103" t="n">
+        <v>0.3145872412127264</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" t="n">
         <v>0.1803571428572935</v>
       </c>
     </row>
@@ -9074,34 +9696,40 @@
         <v>1.03160607166846</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R104" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T104" t="n">
         <v>0.3392857142857694</v>
       </c>
-      <c r="S104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0.9014843637276995</v>
-      </c>
       <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0.9014852876337008</v>
+      </c>
+      <c r="W104" t="n">
         <v>1.7528</v>
       </c>
-      <c r="V104" t="n">
-        <v>0.8697835759926298</v>
-      </c>
-      <c r="W104" t="n">
-        <v>0.784096293584519</v>
-      </c>
       <c r="X104" t="n">
-        <v>0</v>
+        <v>0.8697835759873167</v>
       </c>
       <c r="Y104" t="n">
-        <v>0.3616830541820591</v>
+        <v>0.7840970971779951</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0.3616834182881157</v>
       </c>
     </row>
     <row r="105">
@@ -9157,34 +9785,40 @@
         <v>0.779274995510789</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R105" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T105" t="n">
         <v>0.8962500000000428</v>
       </c>
-      <c r="S105" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" t="n">
-        <v>2.523189923148073</v>
-      </c>
       <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>2.523192557199961</v>
+      </c>
+      <c r="W105" t="n">
         <v>1.7528</v>
       </c>
-      <c r="V105" t="n">
-        <v>0.8697619969135469</v>
-      </c>
-      <c r="W105" t="n">
-        <v>2.194574706149407</v>
-      </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>0.869761996832446</v>
       </c>
       <c r="Y105" t="n">
-        <v>0.9014843637276995</v>
+        <v>2.194576996943004</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0.9014852876337008</v>
       </c>
     </row>
     <row r="106">
@@ -9240,34 +9874,40 @@
         <v>0.4089904904144481</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R106" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T106" t="n">
         <v>2.504651162790685</v>
       </c>
-      <c r="S106" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" t="n">
-        <v>4.83708748577785</v>
-      </c>
       <c r="U106" t="n">
-        <v>1.768600015789542</v>
+        <v>0</v>
       </c>
       <c r="V106" t="n">
-        <v>0.6045883267935741</v>
+        <v>4.83708747819038</v>
       </c>
       <c r="W106" t="n">
-        <v>2.69744320442209</v>
+        <v>1.768600015800672</v>
       </c>
       <c r="X106" t="n">
+        <v>0.6045883159844235</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>2.697443147907494</v>
+      </c>
+      <c r="Z106" t="n">
         <v>0.08300000000000002</v>
       </c>
-      <c r="Y106" t="n">
-        <v>2.523189923148073</v>
+      <c r="AA106" t="n">
+        <v>2.523192557199961</v>
       </c>
     </row>
     <row r="107">
@@ -9323,34 +9963,40 @@
         <v>0.4130305359490459</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R107" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T107" t="n">
         <v>5.678571428571439</v>
       </c>
-      <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="n">
-        <v>7.795781238562347</v>
-      </c>
       <c r="U107" t="n">
-        <v>1.813388949467319</v>
+        <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>0.4510700731428729</v>
+        <v>7.795781230965148</v>
       </c>
       <c r="W107" t="n">
-        <v>3.076511363806615</v>
+        <v>1.81338894947845</v>
       </c>
       <c r="X107" t="n">
+        <v>0.4510700491596409</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>3.076511173843142</v>
+      </c>
+      <c r="Z107" t="n">
         <v>0.1023333333333333</v>
       </c>
-      <c r="Y107" t="n">
-        <v>4.83708748577785</v>
+      <c r="AA107" t="n">
+        <v>4.83708747819038</v>
       </c>
     </row>
     <row r="108">
@@ -9406,34 +10052,40 @@
         <v>0.4207785721774875</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R108" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T108" t="n">
         <v>7.142857142857149</v>
       </c>
-      <c r="S108" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" t="n">
-        <v>10.81459998566029</v>
-      </c>
       <c r="U108" t="n">
-        <v>1.861488997567319</v>
+        <v>0</v>
       </c>
       <c r="V108" t="n">
-        <v>0.3704055565825953</v>
+        <v>10.81459997635064</v>
       </c>
       <c r="W108" t="n">
-        <v>3.31056644920324</v>
+        <v>1.86148899757845</v>
       </c>
       <c r="X108" t="n">
+        <v>0.370405582414445</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>3.310566725718646</v>
+      </c>
+      <c r="Z108" t="n">
         <v>0.1196666666666667</v>
       </c>
-      <c r="Y108" t="n">
-        <v>7.795781238562347</v>
+      <c r="AA108" t="n">
+        <v>7.795781230965148</v>
       </c>
     </row>
     <row r="109">
@@ -9489,34 +10141,40 @@
         <v>0.3884586048784459</v>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R109" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T109" t="n">
         <v>10.17142857142859</v>
       </c>
-      <c r="S109" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" t="n">
-        <v>14.97827937126746</v>
-      </c>
       <c r="U109" t="n">
-        <v>1.932176568254819</v>
+        <v>0</v>
       </c>
       <c r="V109" t="n">
-        <v>0.3043058690651666</v>
+        <v>14.97827935787934</v>
       </c>
       <c r="W109" t="n">
-        <v>3.46235891147874</v>
+        <v>1.93217656826595</v>
       </c>
       <c r="X109" t="n">
+        <v>0.3043058654900936</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>3.462358854841829</v>
+      </c>
+      <c r="Z109" t="n">
         <v>0.1413333333333333</v>
       </c>
-      <c r="Y109" t="n">
-        <v>10.81459998566029</v>
+      <c r="AA109" t="n">
+        <v>10.81459997635064</v>
       </c>
     </row>
     <row r="110">
@@ -9572,34 +10230,40 @@
         <v>0.3668120739327594</v>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R110" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T110" t="n">
         <v>14.40357142857142</v>
       </c>
-      <c r="S110" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" t="n">
-        <v>17.91702949290385</v>
-      </c>
       <c r="U110" t="n">
-        <v>1.985389121467319</v>
+        <v>0</v>
       </c>
       <c r="V110" t="n">
-        <v>0.272683083326469</v>
+        <v>17.91702948287882</v>
       </c>
       <c r="W110" t="n">
-        <v>3.48086600083324</v>
+        <v>1.985389121478449</v>
       </c>
       <c r="X110" t="n">
+        <v>0.2726830991592711</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>3.480866282570264</v>
+      </c>
+      <c r="Z110" t="n">
         <v>0.1556666666666667</v>
       </c>
-      <c r="Y110" t="n">
-        <v>14.97827937126746</v>
+      <c r="AA110" t="n">
+        <v>14.97827935787934</v>
       </c>
     </row>
     <row r="111">
@@ -9655,34 +10319,40 @@
         <v>0.280189813438795</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R111" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T111" t="n">
         <v>17.9821428571429</v>
       </c>
-      <c r="S111" t="n">
-        <v>0</v>
-      </c>
-      <c r="T111" t="n">
-        <v>20.53315325540088</v>
-      </c>
       <c r="U111" t="n">
-        <v>2.035287782477041</v>
+        <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>0.2504966718976183</v>
+        <v>20.53315308215597</v>
       </c>
       <c r="W111" t="n">
-        <v>3.448605969287672</v>
+        <v>2.035287782488171</v>
       </c>
       <c r="X111" t="n">
+        <v>0.2504966606507561</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>3.448605709266384</v>
+      </c>
+      <c r="Z111" t="n">
         <v>0.168</v>
       </c>
-      <c r="Y111" t="n">
-        <v>17.91702949290385</v>
+      <c r="AA111" t="n">
+        <v>17.91702948287882</v>
       </c>
     </row>
     <row r="112">
@@ -9738,34 +10408,40 @@
         <v>0.1463215789183206</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R112" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T112" t="n">
         <v>22.1892857142858</v>
       </c>
-      <c r="S112" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" t="n">
-        <v>24.01327158029936</v>
-      </c>
       <c r="U112" t="n">
-        <v>2.105687852877041</v>
+        <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>0.226749601068703</v>
+        <v>24.01327122841171</v>
       </c>
       <c r="W112" t="n">
-        <v>3.346663112763863</v>
+        <v>2.105687852888171</v>
       </c>
       <c r="X112" t="n">
+        <v>0.226749609860789</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>3.346663274860094</v>
+      </c>
+      <c r="Z112" t="n">
         <v>0.184</v>
       </c>
-      <c r="Y112" t="n">
-        <v>20.53315325540088</v>
+      <c r="AA112" t="n">
+        <v>20.53315308215597</v>
       </c>
     </row>
     <row r="113">
@@ -9827,28 +10503,34 @@
         <v>0.04292053230848831</v>
       </c>
       <c r="R113" t="n">
+        <v>0.03929002064237096</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0.2071727113026431</v>
+      </c>
+      <c r="T113" t="n">
         <v>25.66428571428573</v>
       </c>
-      <c r="S113" t="n">
-        <v>0</v>
-      </c>
-      <c r="T113" t="n">
-        <v>28.24180486772746</v>
-      </c>
       <c r="U113" t="n">
-        <v>2.198068889706438</v>
+        <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>0.007062670572029382</v>
+        <v>28.24180554491312</v>
       </c>
       <c r="W113" t="n">
-        <v>0.1088380779834294</v>
+        <v>2.198068908667902</v>
       </c>
       <c r="X113" t="n">
+        <v>0.007068164159168635</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0.1089932301946586</v>
+      </c>
+      <c r="Z113" t="n">
         <v>0.007053333333333333</v>
       </c>
-      <c r="Y113" t="n">
-        <v>24.01327158029936</v>
+      <c r="AA113" t="n">
+        <v>24.01327122841171</v>
       </c>
     </row>
     <row r="114">
@@ -9910,28 +10592,34 @@
         <v>0.03670292593065684</v>
       </c>
       <c r="R114" t="n">
+        <v>0.03606976413308337</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0.1915800770713303</v>
+      </c>
+      <c r="T114" t="n">
         <v>27.80357142857142</v>
       </c>
-      <c r="S114" t="n">
+      <c r="U114" t="n">
         <v>0.05060060245371522</v>
       </c>
-      <c r="T114" t="n">
-        <v>28.47191369338541</v>
-      </c>
-      <c r="U114" t="n">
-        <v>2.203329228300105</v>
-      </c>
       <c r="V114" t="n">
-        <v>0.007575500360812597</v>
+        <v>28.47191433675219</v>
       </c>
       <c r="W114" t="n">
-        <v>0.1171354979034436</v>
+        <v>2.203329247622887</v>
       </c>
       <c r="X114" t="n">
+        <v>0.007575498547917375</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0.1171354497979989</v>
+      </c>
+      <c r="Z114" t="n">
         <v>0.007626666666666667</v>
       </c>
-      <c r="Y114" t="n">
-        <v>28.24180486772746</v>
+      <c r="AA114" t="n">
+        <v>28.24180554491312</v>
       </c>
     </row>
     <row r="115">
@@ -9993,28 +10681,34 @@
         <v>0.03226430616673658</v>
       </c>
       <c r="R115" t="n">
+        <v>0.03344169305227099</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0.1796226772062386</v>
+      </c>
+      <c r="T115" t="n">
         <v>28.21071428571433</v>
       </c>
-      <c r="S115" t="n">
+      <c r="U115" t="n">
         <v>0.1044036282464569</v>
       </c>
-      <c r="T115" t="n">
-        <v>28.65987999470776</v>
-      </c>
-      <c r="U115" t="n">
-        <v>2.207644899282438</v>
-      </c>
       <c r="V115" t="n">
-        <v>0.007944459054254931</v>
+        <v>28.65988059431129</v>
       </c>
       <c r="W115" t="n">
-        <v>0.1229649217430691</v>
+        <v>2.20764491860522</v>
       </c>
       <c r="X115" t="n">
+        <v>0.007944458816790421</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0.1229649184265571</v>
+      </c>
+      <c r="Z115" t="n">
         <v>0.008066666666666666</v>
       </c>
-      <c r="Y115" t="n">
-        <v>28.47191369338541</v>
+      <c r="AA115" t="n">
+        <v>28.47191433675219</v>
       </c>
     </row>
     <row r="116">
@@ -10076,28 +10770,34 @@
         <v>0.02491516024776152</v>
       </c>
       <c r="R116" t="n">
+        <v>0.02890464370079389</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0.1578453681542842</v>
+      </c>
+      <c r="T116" t="n">
         <v>28.84999999999995</v>
       </c>
-      <c r="S116" t="n">
+      <c r="U116" t="n">
         <v>0.1491197853115378</v>
       </c>
-      <c r="T116" t="n">
-        <v>28.9256375489027</v>
-      </c>
-      <c r="U116" t="n">
-        <v>2.213775572079771</v>
-      </c>
       <c r="V116" t="n">
-        <v>0.008420554940521486</v>
+        <v>28.92563808749308</v>
       </c>
       <c r="W116" t="n">
-        <v>0.1305037237830004</v>
+        <v>2.213775591402554</v>
       </c>
       <c r="X116" t="n">
+        <v>0.008420554709994834</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0.1305037205317169</v>
+      </c>
+      <c r="Z116" t="n">
         <v>0.008653333333333332</v>
       </c>
-      <c r="Y116" t="n">
-        <v>28.65987999470776</v>
+      <c r="AA116" t="n">
+        <v>28.65988059431129</v>
       </c>
     </row>
     <row r="117">
@@ -10159,28 +10859,34 @@
         <v>0.01583178431944987</v>
       </c>
       <c r="R117" t="n">
+        <v>0.02290151451210537</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.1258244186135977</v>
+      </c>
+      <c r="T117" t="n">
         <v>29.8214285714287</v>
       </c>
-      <c r="S117" t="n">
+      <c r="U117" t="n">
         <v>0.1918414613393818</v>
       </c>
-      <c r="T117" t="n">
-        <v>29.46262799265684</v>
-      </c>
-      <c r="U117" t="n">
-        <v>2.226267723460799</v>
-      </c>
       <c r="V117" t="n">
-        <v>0.009253028607806763</v>
+        <v>29.46262840771122</v>
       </c>
       <c r="W117" t="n">
-        <v>0.14371850055597</v>
+        <v>2.226267742783581</v>
       </c>
       <c r="X117" t="n">
+        <v>0.009253028396770656</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.1437184974817057</v>
+      </c>
+      <c r="Z117" t="n">
         <v>0.009740000000000002</v>
       </c>
-      <c r="Y117" t="n">
-        <v>28.9256375489027</v>
+      <c r="AA117" t="n">
+        <v>28.92563808749308</v>
       </c>
     </row>
     <row r="118">
@@ -10242,28 +10948,34 @@
         <v>0.003813578138281135</v>
       </c>
       <c r="R118" t="n">
+        <v>0.01083418489561089</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.0617541750676109</v>
+      </c>
+      <c r="T118" t="n">
         <v>30.18571428571434</v>
       </c>
-      <c r="S118" t="n">
+      <c r="U118" t="n">
         <v>0.2448076315621145</v>
       </c>
-      <c r="T118" t="n">
-        <v>30.73245487163991</v>
-      </c>
-      <c r="U118" t="n">
-        <v>2.256376503569549</v>
-      </c>
       <c r="V118" t="n">
-        <v>0.01074722319542253</v>
+        <v>30.73245500743434</v>
       </c>
       <c r="W118" t="n">
-        <v>0.1673901349917643</v>
+        <v>2.256376522892332</v>
       </c>
       <c r="X118" t="n">
+        <v>0.01074724495172402</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.1673908057509535</v>
+      </c>
+      <c r="Z118" t="n">
         <v>0.01196</v>
       </c>
-      <c r="Y118" t="n">
-        <v>29.46262799265684</v>
+      <c r="AA118" t="n">
+        <v>29.46262840771122</v>
       </c>
     </row>
     <row r="119">
@@ -10325,28 +11037,34 @@
         <v>0.002635143243149769</v>
       </c>
       <c r="R119" t="n">
+        <v>0.008945242501938901</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.05133364630678176</v>
+      </c>
+      <c r="T119" t="n">
         <v>32.48928571428564</v>
       </c>
-      <c r="S119" t="n">
+      <c r="U119" t="n">
         <v>0.2862295508009267</v>
       </c>
-      <c r="T119" t="n">
-        <v>31.15248097080469</v>
-      </c>
-      <c r="U119" t="n">
-        <v>2.266515763708799</v>
-      </c>
       <c r="V119" t="n">
-        <v>0.01113714943474031</v>
+        <v>31.15248101756942</v>
       </c>
       <c r="W119" t="n">
-        <v>0.1734922688738111</v>
+        <v>2.266515783031581</v>
       </c>
       <c r="X119" t="n">
+        <v>0.0111372695428132</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.1734960122774931</v>
+      </c>
+      <c r="Z119" t="n">
         <v>0.01262</v>
       </c>
-      <c r="Y119" t="n">
-        <v>30.73245487163991</v>
+      <c r="AA119" t="n">
+        <v>30.73245500743434</v>
       </c>
     </row>
     <row r="120">
@@ -10408,28 +11126,34 @@
         <v>0.003468413842637606</v>
       </c>
       <c r="R120" t="n">
+        <v>0.01023902645998351</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.05889324106073299</v>
+      </c>
+      <c r="T120" t="n">
         <v>32.9321428571429</v>
       </c>
-      <c r="S120" t="n">
+      <c r="U120" t="n">
         <v>0.2889524121591054</v>
       </c>
-      <c r="T120" t="n">
-        <v>31.55039960390232</v>
-      </c>
-      <c r="U120" t="n">
-        <v>2.276205773398799</v>
-      </c>
       <c r="V120" t="n">
-        <v>0.01147081403029764</v>
+        <v>31.55039956771036</v>
       </c>
       <c r="W120" t="n">
-        <v>0.1786668611418356</v>
+        <v>2.276205792721581</v>
       </c>
       <c r="X120" t="n">
+        <v>0.01147072886081365</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.1786641753611795</v>
+      </c>
+      <c r="Z120" t="n">
         <v>0.01322</v>
       </c>
-      <c r="Y120" t="n">
-        <v>31.15248097080469</v>
+      <c r="AA120" t="n">
+        <v>31.15248101756942</v>
       </c>
     </row>
     <row r="121">
@@ -10491,28 +11215,34 @@
         <v>0.004427144891717553</v>
       </c>
       <c r="R121" t="n">
+        <v>0.01153270065092904</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.06653679351845529</v>
+      </c>
+      <c r="T121" t="n">
         <v>33.08366238246173</v>
       </c>
-      <c r="S121" t="n">
+      <c r="U121" t="n">
         <v>0.2916972101212668</v>
       </c>
-      <c r="T121" t="n">
-        <v>31.95385449152545</v>
-      </c>
-      <c r="U121" t="n">
-        <v>2.286115561086354</v>
-      </c>
       <c r="V121" t="n">
-        <v>0.0117772325789504</v>
+        <v>31.95385437249574</v>
       </c>
       <c r="W121" t="n">
-        <v>0.1833472602095393</v>
+        <v>2.286115580409136</v>
       </c>
       <c r="X121" t="n">
+        <v>0.01177719446570448</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.1833460432925698</v>
+      </c>
+      <c r="Z121" t="n">
         <v>0.01380666666666667</v>
       </c>
-      <c r="Y121" t="n">
-        <v>31.55039960390232</v>
+      <c r="AA121" t="n">
+        <v>31.55039956771036</v>
       </c>
     </row>
     <row r="122">
@@ -10574,28 +11304,34 @@
         <v>0.006989072490978496</v>
       </c>
       <c r="R122" t="n">
+        <v>0.01414625769441237</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.08360067279022637</v>
+      </c>
+      <c r="T122" t="n">
         <v>33.286006759061</v>
       </c>
-      <c r="S122" t="n">
+      <c r="U122" t="n">
         <v>0.2947411967231239</v>
       </c>
-      <c r="T122" t="n">
-        <v>32.83159453267135</v>
-      </c>
-      <c r="U122" t="n">
-        <v>2.307975805168799</v>
-      </c>
       <c r="V122" t="n">
-        <v>0.01235144894981185</v>
+        <v>32.83159423889894</v>
       </c>
       <c r="W122" t="n">
-        <v>0.1918541072094664</v>
+        <v>2.307975824491581</v>
       </c>
       <c r="X122" t="n">
+        <v>0.01235149451992449</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.1918556034210608</v>
+      </c>
+      <c r="Z122" t="n">
         <v>0.01502</v>
       </c>
-      <c r="Y122" t="n">
-        <v>31.95385449152545</v>
+      <c r="AA122" t="n">
+        <v>31.95385437249574</v>
       </c>
     </row>
     <row r="123">
@@ -10657,28 +11393,34 @@
         <v>0.01216839656025612</v>
       </c>
       <c r="R123" t="n">
+        <v>0.01855989829652208</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.1103104553533169</v>
+      </c>
+      <c r="T123" t="n">
         <v>34.92500000000002</v>
       </c>
-      <c r="S123" t="n">
+      <c r="U123" t="n">
         <v>0.3061500936386944</v>
       </c>
-      <c r="T123" t="n">
-        <v>33.75408934841732</v>
-      </c>
-      <c r="U123" t="n">
-        <v>2.331405828598798</v>
-      </c>
       <c r="V123" t="n">
-        <v>0.01284354032424172</v>
+        <v>33.75408893078473</v>
       </c>
       <c r="W123" t="n">
-        <v>0.1986888771392174</v>
+        <v>2.331405847921581</v>
       </c>
       <c r="X123" t="n">
+        <v>0.01284345245977919</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.1986859108423037</v>
+      </c>
+      <c r="Z123" t="n">
         <v>0.01622</v>
       </c>
-      <c r="Y123" t="n">
-        <v>32.83159453267135</v>
+      <c r="AA123" t="n">
+        <v>32.83159423889894</v>
       </c>
     </row>
     <row r="124">
@@ -10740,28 +11482,34 @@
         <v>0.01961652719811411</v>
       </c>
       <c r="R124" t="n">
+        <v>0.02311497993131076</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.1400590132698146</v>
+      </c>
+      <c r="T124" t="n">
         <v>35.32500000000002</v>
       </c>
-      <c r="S124" t="n">
+      <c r="U124" t="n">
         <v>0.3308651428571041</v>
       </c>
-      <c r="T124" t="n">
-        <v>34.61647934287152</v>
-      </c>
-      <c r="U124" t="n">
-        <v>2.353743628714354</v>
-      </c>
       <c r="V124" t="n">
-        <v>0.01322023279290888</v>
+        <v>34.6164789037036</v>
       </c>
       <c r="W124" t="n">
-        <v>0.2034031158610907</v>
+        <v>2.353743648037137</v>
       </c>
       <c r="X124" t="n">
+        <v>0.01322031243075041</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.2034058721493541</v>
+      </c>
+      <c r="Z124" t="n">
         <v>0.01728666666666667</v>
       </c>
-      <c r="Y124" t="n">
-        <v>33.75408934841732</v>
+      <c r="AA124" t="n">
+        <v>33.75408893078473</v>
       </c>
     </row>
     <row r="125">
@@ -10823,28 +11571,34 @@
         <v>0.02963924799363945</v>
       </c>
       <c r="R125" t="n">
+        <v>0.0284767157115998</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.1721605297204892</v>
+      </c>
+      <c r="T125" t="n">
         <v>36.71428571428564</v>
       </c>
-      <c r="S125" t="n">
+      <c r="U125" t="n">
         <v>0.3724108962071924</v>
       </c>
-      <c r="T125" t="n">
-        <v>35.52745852248923</v>
-      </c>
-      <c r="U125" t="n">
-        <v>2.377809652780353</v>
-      </c>
       <c r="V125" t="n">
-        <v>0.01354761888355979</v>
+        <v>35.52745806381636</v>
       </c>
       <c r="W125" t="n">
-        <v>0.2068914320190024</v>
+        <v>2.377809672103136</v>
       </c>
       <c r="X125" t="n">
+        <v>0.01354761894834775</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.2068914338797341</v>
+      </c>
+      <c r="Z125" t="n">
         <v>0.01836666666666667</v>
       </c>
-      <c r="Y125" t="n">
-        <v>34.61647934287152</v>
+      <c r="AA125" t="n">
+        <v>34.6164789037036</v>
       </c>
     </row>
     <row r="126">
@@ -10900,33 +11654,39 @@
         <v>0.4637116778292156</v>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R126" t="n">
-        <v>0.2740000000001075</v>
+        <v>0.0001</v>
       </c>
       <c r="S126" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="T126" t="n">
         <v>0.2740000000001075</v>
       </c>
       <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.2740000000001075</v>
+      </c>
+      <c r="W126" t="n">
         <v>1.7518</v>
       </c>
-      <c r="V126" t="n">
+      <c r="X126" t="n">
         <v>0.8697868789829178</v>
       </c>
-      <c r="W126" t="n">
+      <c r="Y126" t="n">
         <v>0.238321604841413</v>
       </c>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="n">
+      <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
         <v>0.2740000000001075</v>
       </c>
     </row>
@@ -10983,33 +11743,39 @@
         <v>0.7453679311071638</v>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R127" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T127" t="n">
         <v>0.2740000000001075</v>
       </c>
-      <c r="S127" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" t="n">
-        <v>0.7342765380101685</v>
-      </c>
       <c r="U127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.7342772800806657</v>
+      </c>
+      <c r="W127" t="n">
         <v>1.7518</v>
       </c>
-      <c r="V127" t="n">
-        <v>0.8697849399988326</v>
-      </c>
-      <c r="W127" t="n">
-        <v>0.6386626745557249</v>
-      </c>
       <c r="X127" t="n">
-        <v>0</v>
+        <v>0.8697849399952444</v>
       </c>
       <c r="Y127" t="n">
+        <v>0.6386633199948332</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="n">
         <v>0.2740000000001075</v>
       </c>
     </row>
@@ -11066,34 +11832,40 @@
         <v>0.8971601367795489</v>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R128" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T128" t="n">
         <v>0.6966666666666418</v>
       </c>
-      <c r="S128" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" t="n">
-        <v>1.493994205998671</v>
-      </c>
       <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>1.493995772743973</v>
+      </c>
+      <c r="W128" t="n">
         <v>1.7518</v>
       </c>
-      <c r="V128" t="n">
-        <v>0.8697800815790188</v>
-      </c>
-      <c r="W128" t="n">
-        <v>1.299446402372106</v>
-      </c>
       <c r="X128" t="n">
-        <v>0</v>
+        <v>0.8697800815657671</v>
       </c>
       <c r="Y128" t="n">
-        <v>0.7342765380101685</v>
+        <v>1.299447765076164</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.7342772800806657</v>
       </c>
     </row>
     <row r="129">
@@ -11149,34 +11921,40 @@
         <v>0.6919878856836935</v>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R129" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T129" t="n">
         <v>1.346000000000203</v>
       </c>
-      <c r="S129" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" t="n">
-        <v>3.565168706409894</v>
-      </c>
       <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>3.565172253956069</v>
+      </c>
+      <c r="W129" t="n">
         <v>1.7518</v>
       </c>
-      <c r="V129" t="n">
-        <v>0.8696347056395528</v>
-      </c>
-      <c r="W129" t="n">
-        <v>3.100394438554113</v>
-      </c>
       <c r="X129" t="n">
-        <v>0</v>
+        <v>0.869634703573162</v>
       </c>
       <c r="Y129" t="n">
-        <v>1.493994205998671</v>
+        <v>3.100397516256348</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>1.493995772743973</v>
       </c>
     </row>
     <row r="130">
@@ -11232,34 +12010,40 @@
         <v>0.5026713404005696</v>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R130" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T130" t="n">
         <v>3.026136363636255</v>
       </c>
-      <c r="S130" t="n">
-        <v>0</v>
-      </c>
-      <c r="T130" t="n">
-        <v>5.404249755435242</v>
-      </c>
       <c r="U130" t="n">
-        <v>1.774655578412124</v>
+        <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>0.5609388354247328</v>
+        <v>5.404249753891331</v>
       </c>
       <c r="W130" t="n">
-        <v>2.768547960824193</v>
+        <v>1.774655578417778</v>
       </c>
       <c r="X130" t="n">
+        <v>0.5609389079826891</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>2.768548352155416</v>
+      </c>
+      <c r="Z130" t="n">
         <v>0.08633333333333333</v>
       </c>
-      <c r="Y130" t="n">
-        <v>3.565168706409894</v>
+      <c r="AA130" t="n">
+        <v>3.565172253956069</v>
       </c>
     </row>
     <row r="131">
@@ -11315,34 +12099,40 @@
         <v>0.4114966666264407</v>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R131" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T131" t="n">
         <v>5.885714285714225</v>
       </c>
-      <c r="S131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T131" t="n">
-        <v>8.441995341868045</v>
-      </c>
       <c r="U131" t="n">
-        <v>1.821055624812124</v>
+        <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>0.4282982624799253</v>
+        <v>8.441995340492889</v>
       </c>
       <c r="W131" t="n">
-        <v>3.125845555578787</v>
+        <v>1.821055624817778</v>
       </c>
       <c r="X131" t="n">
+        <v>0.4282982829519956</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>3.125845727896247</v>
+      </c>
+      <c r="Z131" t="n">
         <v>0.1056666666666667</v>
       </c>
-      <c r="Y131" t="n">
-        <v>5.404249755435242</v>
+      <c r="AA131" t="n">
+        <v>5.404249753891331</v>
       </c>
     </row>
     <row r="132">
@@ -11398,34 +12188,40 @@
         <v>0.3503266780181019</v>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R132" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T132" t="n">
         <v>8.642857142857142</v>
       </c>
-      <c r="S132" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" t="n">
-        <v>12.01818120752623</v>
-      </c>
       <c r="U132" t="n">
-        <v>1.878889015978791</v>
+        <v>0</v>
       </c>
       <c r="V132" t="n">
-        <v>0.3467808586729018</v>
+        <v>12.01818119746831</v>
       </c>
       <c r="W132" t="n">
-        <v>3.363857219749223</v>
+        <v>1.878889015984444</v>
       </c>
       <c r="X132" t="n">
+        <v>0.3467808659520568</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>3.36385730441866</v>
+      </c>
+      <c r="Z132" t="n">
         <v>0.1256666666666666</v>
       </c>
-      <c r="Y132" t="n">
-        <v>8.441995341868045</v>
+      <c r="AA132" t="n">
+        <v>8.441995340492889</v>
       </c>
     </row>
     <row r="133">
@@ -11481,34 +12277,40 @@
         <v>0.2789527328089635</v>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R133" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T133" t="n">
         <v>12.06428571428577</v>
       </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" t="n">
-        <v>15.4020836537916</v>
-      </c>
       <c r="U133" t="n">
-        <v>1.937100185301013</v>
+        <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>0.2986612608406918</v>
+        <v>15.40208363873504</v>
       </c>
       <c r="W133" t="n">
-        <v>3.462997953338244</v>
+        <v>1.937100185306666</v>
       </c>
       <c r="X133" t="n">
+        <v>0.2986612576470496</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>3.462997900767509</v>
+      </c>
+      <c r="Z133" t="n">
         <v>0.143</v>
       </c>
-      <c r="Y133" t="n">
-        <v>12.01818120752623</v>
+      <c r="AA133" t="n">
+        <v>12.01818119746831</v>
       </c>
     </row>
     <row r="134">
@@ -11564,34 +12366,40 @@
         <v>0.2084246345121031</v>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R134" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T134" t="n">
         <v>15.77142857142857</v>
       </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="n">
-        <v>19.69349035513918</v>
-      </c>
       <c r="U134" t="n">
-        <v>2.016322486745457</v>
+        <v>0</v>
       </c>
       <c r="V134" t="n">
-        <v>0.2568334097868318</v>
+        <v>19.69349055328924</v>
       </c>
       <c r="W134" t="n">
-        <v>3.459408374659483</v>
+        <v>2.016322486751111</v>
       </c>
       <c r="X134" t="n">
+        <v>0.2568335205710925</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>3.4594105912003</v>
+      </c>
+      <c r="Z134" t="n">
         <v>0.1636666666666667</v>
       </c>
-      <c r="Y134" t="n">
-        <v>15.4020836537916</v>
+      <c r="AA134" t="n">
+        <v>15.40208363873504</v>
       </c>
     </row>
     <row r="135">
@@ -11647,34 +12455,40 @@
         <v>0.1351840441944742</v>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R135" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T135" t="n">
         <v>19.10357142857136</v>
       </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>22.34964337139774</v>
-      </c>
       <c r="U135" t="n">
-        <v>2.068687816888513</v>
+        <v>0</v>
       </c>
       <c r="V135" t="n">
-        <v>0.2372035646651388</v>
+        <v>22.34964323037847</v>
       </c>
       <c r="W135" t="n">
-        <v>3.399950195786845</v>
+        <v>2.068687816894167</v>
       </c>
       <c r="X135" t="n">
+        <v>0.2372035556176595</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>3.399949972131483</v>
+      </c>
+      <c r="Z135" t="n">
         <v>0.176</v>
       </c>
-      <c r="Y135" t="n">
-        <v>19.69349035513918</v>
+      <c r="AA135" t="n">
+        <v>19.69349055328924</v>
       </c>
     </row>
     <row r="136">
@@ -11730,34 +12544,40 @@
         <v>0.06997246239386802</v>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R136" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T136" t="n">
         <v>21.08928571428573</v>
       </c>
-      <c r="S136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T136" t="n">
-        <v>25.42114773996207</v>
-      </c>
       <c r="U136" t="n">
-        <v>2.132737880938512</v>
+        <v>0</v>
       </c>
       <c r="V136" t="n">
-        <v>0.21837105793432</v>
+        <v>25.42114792085842</v>
       </c>
       <c r="W136" t="n">
-        <v>3.286539835190304</v>
+        <v>2.132737880944166</v>
       </c>
       <c r="X136" t="n">
+        <v>0.2183710079200064</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>3.28653858716199</v>
+      </c>
+      <c r="Z136" t="n">
         <v>0.19</v>
       </c>
-      <c r="Y136" t="n">
-        <v>22.34964337139774</v>
+      <c r="AA136" t="n">
+        <v>22.34964323037847</v>
       </c>
     </row>
     <row r="137">
@@ -11813,34 +12633,40 @@
         <v>0.04417757490269928</v>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R137" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T137" t="n">
         <v>21.79285714285717</v>
       </c>
-      <c r="S137" t="n">
-        <v>0</v>
-      </c>
-      <c r="T137" t="n">
-        <v>28.31815807173002</v>
-      </c>
       <c r="U137" t="n">
-        <v>2.196892806246272</v>
+        <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>0.0104122458017144</v>
+        <v>28.31816032897402</v>
       </c>
       <c r="W137" t="n">
-        <v>0.2041952841576134</v>
+        <v>2.196892860793617</v>
       </c>
       <c r="X137" t="n">
+        <v>0.01041304424064643</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2042179130067702</v>
+      </c>
+      <c r="Z137" t="n">
         <v>0.007033333333333333</v>
       </c>
-      <c r="Y137" t="n">
-        <v>25.42114773996207</v>
+      <c r="AA137" t="n">
+        <v>25.42114792085842</v>
       </c>
     </row>
     <row r="138">
@@ -11896,34 +12722,40 @@
         <v>0.02615548495855645</v>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R138" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T138" t="n">
         <v>22.74159954433088</v>
       </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="n">
-        <v>28.49544506706755</v>
-      </c>
       <c r="U138" t="n">
-        <v>2.2009444491868</v>
+        <v>0</v>
       </c>
       <c r="V138" t="n">
-        <v>0.01098361402771199</v>
+        <v>28.49544748119097</v>
       </c>
       <c r="W138" t="n">
-        <v>0.2161400311342437</v>
+        <v>2.200944508712678</v>
       </c>
       <c r="X138" t="n">
+        <v>0.01098357822667265</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.216139031898086</v>
+      </c>
+      <c r="Z138" t="n">
         <v>0.007480000000000001</v>
       </c>
-      <c r="Y138" t="n">
-        <v>28.31815807173002</v>
+      <c r="AA138" t="n">
+        <v>28.31816032897402</v>
       </c>
     </row>
     <row r="139">
@@ -11979,34 +12811,40 @@
         <v>0.02647932083128075</v>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R139" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T139" t="n">
         <v>22.97108767528296</v>
       </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>28.74377626810038</v>
-      </c>
       <c r="U139" t="n">
-        <v>2.206644899331689</v>
+        <v>0</v>
       </c>
       <c r="V139" t="n">
-        <v>0.01171779493992934</v>
+        <v>28.74377861466887</v>
       </c>
       <c r="W139" t="n">
-        <v>0.231737203693045</v>
+        <v>2.206644958857567</v>
       </c>
       <c r="X139" t="n">
+        <v>0.01171774454065133</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.2317357767803047</v>
+      </c>
+      <c r="Z139" t="n">
         <v>0.008066666666666666</v>
       </c>
-      <c r="Y139" t="n">
-        <v>28.49544506706755</v>
+      <c r="AA139" t="n">
+        <v>28.49544748119097</v>
       </c>
     </row>
     <row r="140">
@@ -12062,34 +12900,40 @@
         <v>0.02163341820285943</v>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R140" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T140" t="n">
         <v>24.12500000000008</v>
       </c>
-      <c r="S140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>28.95676810524078</v>
-      </c>
       <c r="U140" t="n">
-        <v>2.211557709800049</v>
+        <v>0</v>
       </c>
       <c r="V140" t="n">
-        <v>0.01228114874974565</v>
+        <v>28.95677039510294</v>
       </c>
       <c r="W140" t="n">
-        <v>0.2438049010993913</v>
+        <v>2.211557769325928</v>
       </c>
       <c r="X140" t="n">
+        <v>0.01228110398018093</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.2438036270068062</v>
+      </c>
+      <c r="Z140" t="n">
         <v>0.008539999999999999</v>
       </c>
-      <c r="Y140" t="n">
-        <v>28.74377626810038</v>
+      <c r="AA140" t="n">
+        <v>28.74377861466887</v>
       </c>
     </row>
     <row r="141">
@@ -12145,34 +12989,40 @@
         <v>0.01944191146369945</v>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R141" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T141" t="n">
         <v>24.57500000000017</v>
       </c>
-      <c r="S141" t="n">
-        <v>0</v>
-      </c>
-      <c r="T141" t="n">
-        <v>29.23616617039069</v>
-      </c>
       <c r="U141" t="n">
-        <v>2.218035494055605</v>
+        <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>0.01296732616405267</v>
+        <v>29.2361683854742</v>
       </c>
       <c r="W141" t="n">
-        <v>0.2588153203139437</v>
+        <v>2.218035553581483</v>
       </c>
       <c r="X141" t="n">
+        <v>0.01296734667627982</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.2588159428505661</v>
+      </c>
+      <c r="Z141" t="n">
         <v>0.009126666666666668</v>
       </c>
-      <c r="Y141" t="n">
-        <v>28.95676810524078</v>
+      <c r="AA141" t="n">
+        <v>28.95677039510294</v>
       </c>
     </row>
     <row r="142">
@@ -12228,34 +13078,40 @@
         <v>0.01658310436687791</v>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R142" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T142" t="n">
         <v>25.06785714285721</v>
       </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" t="n">
-        <v>29.78688303409221</v>
-      </c>
       <c r="U142" t="n">
-        <v>2.230915506935605</v>
+        <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>0.01413302613406024</v>
+        <v>29.78688518662393</v>
       </c>
       <c r="W142" t="n">
-        <v>0.2848787841656656</v>
+        <v>2.230915566461483</v>
       </c>
       <c r="X142" t="n">
+        <v>0.01413308769286362</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.2848806420287301</v>
+      </c>
+      <c r="Z142" t="n">
         <v>0.01019333333333333</v>
       </c>
-      <c r="Y142" t="n">
-        <v>29.23616617039069</v>
+      <c r="AA142" t="n">
+        <v>29.2361683854742</v>
       </c>
     </row>
     <row r="143">
@@ -12311,34 +13167,40 @@
         <v>0.01821926693166444</v>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R143" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T143" t="n">
         <v>25.90000000000013</v>
       </c>
-      <c r="S143" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" t="n">
-        <v>31.11037299829884</v>
-      </c>
       <c r="U143" t="n">
-        <v>2.262489288509355</v>
+        <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>0.01625169104512008</v>
+        <v>31.11037508564176</v>
       </c>
       <c r="W143" t="n">
-        <v>0.3347232131708391</v>
+        <v>2.262489348035233</v>
       </c>
       <c r="X143" t="n">
+        <v>0.01625131044668814</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3347113995646889</v>
+      </c>
+      <c r="Z143" t="n">
         <v>0.01242666666666667</v>
       </c>
-      <c r="Y143" t="n">
-        <v>29.78688303409221</v>
+      <c r="AA143" t="n">
+        <v>29.78688518662393</v>
       </c>
     </row>
     <row r="144">
@@ -12394,34 +13256,40 @@
         <v>0.01480594697664882</v>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R144" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T144" t="n">
         <v>27.37499999999996</v>
       </c>
-      <c r="S144" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" t="n">
-        <v>31.52104556401108</v>
-      </c>
       <c r="U144" t="n">
-        <v>2.272468965155688</v>
+        <v>0</v>
       </c>
       <c r="V144" t="n">
-        <v>0.01678984232084768</v>
+        <v>31.5210476313021</v>
       </c>
       <c r="W144" t="n">
-        <v>0.3481727318040841</v>
+        <v>2.272469024681567</v>
       </c>
       <c r="X144" t="n">
+        <v>0.01679001717135276</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0.3481782708526754</v>
+      </c>
+      <c r="Z144" t="n">
         <v>0.01305333333333333</v>
       </c>
-      <c r="Y144" t="n">
-        <v>31.11037299829884</v>
+      <c r="AA144" t="n">
+        <v>31.11037508564176</v>
       </c>
     </row>
     <row r="145">
@@ -12477,34 +13345,40 @@
         <v>0.01899552184075797</v>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R145" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T145" t="n">
         <v>28.11428571428576</v>
       </c>
-      <c r="S145" t="n">
-        <v>0</v>
-      </c>
-      <c r="T145" t="n">
-        <v>31.94343200681957</v>
-      </c>
       <c r="U145" t="n">
-        <v>2.282825558845605</v>
+        <v>0</v>
       </c>
       <c r="V145" t="n">
-        <v>0.01726821272876278</v>
+        <v>31.94343405366691</v>
       </c>
       <c r="W145" t="n">
-        <v>0.3602759005648064</v>
+        <v>2.282825618371483</v>
       </c>
       <c r="X145" t="n">
+        <v>0.01726817068693205</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0.3602745856788814</v>
+      </c>
+      <c r="Z145" t="n">
         <v>0.01367333333333333</v>
       </c>
-      <c r="Y145" t="n">
-        <v>31.52104556401108</v>
+      <c r="AA145" t="n">
+        <v>31.5210476313021</v>
       </c>
     </row>
     <row r="146">
@@ -12560,34 +13434,40 @@
         <v>0.02233579751349438</v>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R146" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T146" t="n">
         <v>28.14285714285706</v>
       </c>
-      <c r="S146" t="n">
-        <v>0</v>
-      </c>
-      <c r="T146" t="n">
-        <v>32.35740187371602</v>
-      </c>
       <c r="U146" t="n">
-        <v>2.293067791310049</v>
+        <v>0</v>
       </c>
       <c r="V146" t="n">
-        <v>0.01769926545816089</v>
+        <v>32.35740390067283</v>
       </c>
       <c r="W146" t="n">
-        <v>0.371479868678853</v>
+        <v>2.293067850835928</v>
       </c>
       <c r="X146" t="n">
+        <v>0.01769926548522211</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>0.3714798980485495</v>
+      </c>
+      <c r="Z146" t="n">
         <v>0.01426</v>
       </c>
-      <c r="Y146" t="n">
-        <v>31.94343200681957</v>
+      <c r="AA146" t="n">
+        <v>31.94343405366691</v>
       </c>
     </row>
     <row r="147">
@@ -12643,34 +13523,40 @@
         <v>0.01014663618242141</v>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R147" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T147" t="n">
         <v>29.46071428571427</v>
       </c>
-      <c r="S147" t="n">
-        <v>0</v>
-      </c>
-      <c r="T147" t="n">
-        <v>33.2558324964522</v>
-      </c>
       <c r="U147" t="n">
-        <v>2.315615591635606</v>
+        <v>0</v>
       </c>
       <c r="V147" t="n">
-        <v>0.01851302896468444</v>
+        <v>33.25583448054279</v>
       </c>
       <c r="W147" t="n">
-        <v>0.3934451172228779</v>
+        <v>2.315615651161483</v>
       </c>
       <c r="X147" t="n">
+        <v>0.01851307209935324</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0.3934465808882616</v>
+      </c>
+      <c r="Z147" t="n">
         <v>0.01547333333333333</v>
       </c>
-      <c r="Y147" t="n">
-        <v>32.35740187371602</v>
+      <c r="AA147" t="n">
+        <v>32.35740390067283</v>
       </c>
     </row>
     <row r="148">
@@ -12726,34 +13612,40 @@
         <v>0.00902987934884078</v>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R148" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T148" t="n">
         <v>30.54107142857147</v>
       </c>
-      <c r="S148" t="n">
-        <v>0</v>
-      </c>
-      <c r="T148" t="n">
-        <v>34.19735342975477</v>
-      </c>
       <c r="U148" t="n">
-        <v>2.339725615745605</v>
+        <v>0</v>
       </c>
       <c r="V148" t="n">
-        <v>0.01919067788683726</v>
+        <v>34.19735536914632</v>
       </c>
       <c r="W148" t="n">
-        <v>0.412573497054656</v>
+        <v>2.339725675271483</v>
       </c>
       <c r="X148" t="n">
+        <v>0.01919069898130528</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>0.4125742480274263</v>
+      </c>
+      <c r="Z148" t="n">
         <v>0.01667333333333334</v>
       </c>
-      <c r="Y148" t="n">
-        <v>33.2558324964522</v>
+      <c r="AA148" t="n">
+        <v>33.25583448054279</v>
       </c>
     </row>
     <row r="149">
@@ -12809,34 +13701,40 @@
         <v>0.01371968923896166</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R149" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S149" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T149" t="n">
         <v>30.00357142857132</v>
       </c>
-      <c r="S149" t="n">
-        <v>0</v>
-      </c>
-      <c r="T149" t="n">
-        <v>34.69219227762835</v>
-      </c>
       <c r="U149" t="n">
-        <v>2.3525996008418</v>
+        <v>0</v>
       </c>
       <c r="V149" t="n">
-        <v>0.01948925539598507</v>
+        <v>34.69219417667006</v>
       </c>
       <c r="W149" t="n">
-        <v>0.4213085438452883</v>
+        <v>2.352599660367677</v>
       </c>
       <c r="X149" t="n">
+        <v>0.01948898852875239</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>0.4212993151451641</v>
+      </c>
+      <c r="Z149" t="n">
         <v>0.01728</v>
       </c>
-      <c r="Y149" t="n">
-        <v>34.19735342975477</v>
+      <c r="AA149" t="n">
+        <v>34.19735536914632</v>
       </c>
     </row>
     <row r="150">
@@ -12892,34 +13790,40 @@
         <v>0.0224321685275548</v>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R150" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T150" t="n">
         <v>30.12857142857151</v>
       </c>
-      <c r="S150" t="n">
-        <v>0</v>
-      </c>
-      <c r="T150" t="n">
-        <v>35.0418357938299</v>
-      </c>
       <c r="U150" t="n">
-        <v>2.36178186002405</v>
+        <v>0</v>
       </c>
       <c r="V150" t="n">
-        <v>0.01970497486348605</v>
+        <v>35.04183767661643</v>
       </c>
       <c r="W150" t="n">
-        <v>0.4278830064061876</v>
+        <v>2.361781919549927</v>
       </c>
       <c r="X150" t="n">
+        <v>0.01970497329658792</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0.4278829811081218</v>
+      </c>
+      <c r="Z150" t="n">
         <v>0.0177</v>
       </c>
-      <c r="Y150" t="n">
-        <v>34.69219227762835</v>
+      <c r="AA150" t="n">
+        <v>34.69219417667006</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/BR_processed.xlsx
+++ b/data/processed/BR_processed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA150"/>
+  <dimension ref="A1:Y150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,50 +516,40 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>qP_sqrt</t>
+          <t>Xlag1</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>rP_sqrt</t>
+          <t>Plag1</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Xlag1</t>
+          <t>X_calc</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Plag1</t>
+          <t>V_calc</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>X_calc</t>
+          <t>mu_calc</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>V_calc</t>
+          <t>dXdt_calc</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mu_calc</t>
+          <t>dVdt_calc</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dXdt_calc</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dVdt_calc</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Xlag1_calc</t>
         </is>
@@ -618,39 +608,33 @@
         <v>2.755932637154052</v>
       </c>
       <c r="P2" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001</v>
+        <v>0.2375268817204247</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0.2375268817204247</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.500919151193634</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2375268817204247</v>
+        <v>0.8697873804353808</v>
       </c>
       <c r="W2" t="n">
-        <v>1.500919151193634</v>
+        <v>0.2065978842345928</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8697873804353808</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2065978842345928</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
         <v>0.2375268817204247</v>
       </c>
     </row>
@@ -707,39 +691,33 @@
         <v>0.7929182707910082</v>
       </c>
       <c r="P3" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001</v>
+        <v>0.2375268817204247</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2375268817204247</v>
+        <v>0.4903425841537391</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.500919151193634</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4903425841537391</v>
+        <v>0.869786459461638</v>
       </c>
       <c r="W3" t="n">
-        <v>1.500919151193634</v>
+        <v>0.426493340194351</v>
       </c>
       <c r="X3" t="n">
-        <v>0.869786459461638</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.426493340194351</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
         <v>0.2375268817204247</v>
       </c>
     </row>
@@ -796,39 +774,33 @@
         <v>0.8664928233519787</v>
       </c>
       <c r="P4" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001</v>
+        <v>0.758194444444397</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.758194444444397</v>
+        <v>0.969166406331215</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.500919151193634</v>
       </c>
       <c r="V4" t="n">
-        <v>0.969166406331215</v>
+        <v>0.8697842876873132</v>
       </c>
       <c r="W4" t="n">
-        <v>1.500919151193634</v>
+        <v>0.8429657123812689</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8697842876873132</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.8429657123812689</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
         <v>0.4903425841537391</v>
       </c>
     </row>
@@ -885,39 +857,33 @@
         <v>0.4390733992263243</v>
       </c>
       <c r="P5" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001</v>
+        <v>1.19599999999993</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.19599999999993</v>
+        <v>3.954474381724626</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.500919151193634</v>
       </c>
       <c r="V5" t="n">
-        <v>3.954474381724626</v>
+        <v>-6.782512760337684e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.500919151193634</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.782512760337684e-08</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
         <v>0.969166406331215</v>
       </c>
     </row>
@@ -974,39 +940,33 @@
         <v>0.4900501784306472</v>
       </c>
       <c r="P6" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001</v>
+        <v>5.025440000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>5.025440000000001</v>
+        <v>6.787730967098184</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.537009290095879</v>
       </c>
       <c r="V6" t="n">
-        <v>6.787730967098184</v>
+        <v>0.6572400071048442</v>
       </c>
       <c r="W6" t="n">
-        <v>1.537009290095879</v>
+        <v>4.218204084318845</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6572400071048442</v>
+        <v>0.05501666666666669</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.218204084318845</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.05501666666666669</v>
-      </c>
-      <c r="AA6" t="n">
         <v>3.954474381724626</v>
       </c>
     </row>
@@ -1063,39 +1023,33 @@
         <v>0.3736357386093559</v>
       </c>
       <c r="P7" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001</v>
+        <v>6.17500000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>6.17500000000001</v>
+        <v>14.38561313863158</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.642941373429212</v>
       </c>
       <c r="V7" t="n">
-        <v>14.38561313863158</v>
+        <v>0.4009205679956527</v>
       </c>
       <c r="W7" t="n">
-        <v>1.642941373429212</v>
+        <v>5.101739468936507</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4009205679956527</v>
+        <v>0.07603333333333334</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.101739468936507</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.07603333333333334</v>
-      </c>
-      <c r="AA7" t="n">
         <v>6.787730967098184</v>
       </c>
     </row>
@@ -1152,39 +1106,33 @@
         <v>0.3078573703085496</v>
       </c>
       <c r="P8" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0001</v>
+        <v>12.87142857142852</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>12.87142857142852</v>
+        <v>18.58021293162739</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.707928040095878</v>
       </c>
       <c r="V8" t="n">
-        <v>18.58021293162739</v>
+        <v>0.339441588837832</v>
       </c>
       <c r="W8" t="n">
-        <v>1.707928040095878</v>
+        <v>5.366605780078858</v>
       </c>
       <c r="X8" t="n">
-        <v>0.339441588837832</v>
+        <v>0.08643333333333333</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.366605780078858</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.08643333333333333</v>
-      </c>
-      <c r="AA8" t="n">
         <v>14.38561313863158</v>
       </c>
     </row>
@@ -1241,39 +1189,33 @@
         <v>0.2585007099421947</v>
       </c>
       <c r="P9" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0001</v>
+        <v>16.07142857142854</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>16.07142857142854</v>
+        <v>23.31328394075086</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.78771915120699</v>
       </c>
       <c r="V9" t="n">
-        <v>23.31328394075086</v>
+        <v>0.2921430559383309</v>
       </c>
       <c r="W9" t="n">
-        <v>1.78771915120699</v>
+        <v>5.536728071170317</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2921430559383309</v>
+        <v>0.09770000000000005</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.536728071170317</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.09770000000000005</v>
-      </c>
-      <c r="AA9" t="n">
         <v>18.58021293162739</v>
       </c>
     </row>
@@ -1336,33 +1278,27 @@
         <v>0.03252295278732637</v>
       </c>
       <c r="R10" t="n">
-        <v>0.03754548692326653</v>
+        <v>19.55000000000009</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1803412121156071</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>19.55000000000009</v>
+        <v>26.65401336848298</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.848679229473595</v>
       </c>
       <c r="V10" t="n">
-        <v>26.65401336848298</v>
+        <v>0.2252279510788963</v>
       </c>
       <c r="W10" t="n">
-        <v>1.848679229473595</v>
+        <v>5.970067722284991</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2252279510788963</v>
+        <v>0.0023</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.970067722284991</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="AA10" t="n">
         <v>23.31328394075086</v>
       </c>
     </row>
@@ -1425,33 +1361,27 @@
         <v>0.1065167260919373</v>
       </c>
       <c r="R11" t="n">
-        <v>0.06664459174752829</v>
+        <v>23.07142857142841</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3263690029582119</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>23.07142857142841</v>
+        <v>26.81456869324099</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.851713413179842</v>
       </c>
       <c r="V11" t="n">
-        <v>26.81456869324099</v>
+        <v>0.006093564436306846</v>
       </c>
       <c r="W11" t="n">
-        <v>1.851713413179842</v>
+        <v>0.1282317294427486</v>
       </c>
       <c r="X11" t="n">
-        <v>0.006093564436306846</v>
+        <v>0.002428333333333334</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1282317294427486</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.002428333333333334</v>
-      </c>
-      <c r="AA11" t="n">
         <v>26.65401336848298</v>
       </c>
     </row>
@@ -1514,33 +1444,27 @@
         <v>0.08474551698518029</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0585577437900562</v>
+        <v>23.9821428571428</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2911108328200452</v>
+        <v>0.1310102834270957</v>
       </c>
       <c r="T12" t="n">
-        <v>23.9821428571428</v>
+        <v>27.04657382863489</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1310102834270957</v>
+        <v>1.856116121454714</v>
       </c>
       <c r="V12" t="n">
-        <v>27.04657382863489</v>
+        <v>0.006462750056087044</v>
       </c>
       <c r="W12" t="n">
-        <v>1.856116121454714</v>
+        <v>0.1368605255335975</v>
       </c>
       <c r="X12" t="n">
-        <v>0.006462750056087044</v>
+        <v>0.002603333333333333</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1368605255335975</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.002603333333333333</v>
-      </c>
-      <c r="AA12" t="n">
         <v>26.81456869324099</v>
       </c>
     </row>
@@ -1603,33 +1527,27 @@
         <v>0.06448817748780201</v>
       </c>
       <c r="R13" t="n">
-        <v>0.05054056312736721</v>
+        <v>24.71428571428569</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2539452253691769</v>
+        <v>0.3150449672599142</v>
       </c>
       <c r="T13" t="n">
-        <v>24.71428571428569</v>
+        <v>27.34710868323887</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3150449672599142</v>
+        <v>1.861850524232492</v>
       </c>
       <c r="V13" t="n">
-        <v>27.34710868323887</v>
+        <v>0.006890040482292315</v>
       </c>
       <c r="W13" t="n">
-        <v>1.861850524232492</v>
+        <v>0.1470755906637241</v>
       </c>
       <c r="X13" t="n">
-        <v>0.006890040482292315</v>
+        <v>0.002815</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1470755906637241</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.002815</v>
-      </c>
-      <c r="AA13" t="n">
         <v>27.04657382863489</v>
       </c>
     </row>
@@ -1692,33 +1610,27 @@
         <v>0.112121445976553</v>
       </c>
       <c r="R14" t="n">
-        <v>0.06466559242177924</v>
+        <v>25.24642857142839</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3348454060854844</v>
+        <v>0.462353720667521</v>
       </c>
       <c r="T14" t="n">
-        <v>25.24642857142839</v>
+        <v>27.65076181827065</v>
       </c>
       <c r="U14" t="n">
-        <v>0.462353720667521</v>
+        <v>1.867680524232492</v>
       </c>
       <c r="V14" t="n">
-        <v>27.65076181827065</v>
+        <v>0.007275870207412934</v>
       </c>
       <c r="W14" t="n">
-        <v>1.867680524232492</v>
+        <v>0.1565466800263603</v>
       </c>
       <c r="X14" t="n">
-        <v>0.007275870207412934</v>
+        <v>0.003015</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1565466800263603</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.003015</v>
-      </c>
-      <c r="AA14" t="n">
         <v>27.34710868323887</v>
       </c>
     </row>
@@ -1781,33 +1693,27 @@
         <v>0.2218548813486614</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0901238156173267</v>
+        <v>26.8128</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4710147358084048</v>
+        <v>0.6209461221159972</v>
       </c>
       <c r="T15" t="n">
-        <v>26.8128</v>
+        <v>27.96487515706328</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6209461221159972</v>
+        <v>1.873749899232492</v>
       </c>
       <c r="V15" t="n">
-        <v>27.96487515706328</v>
+        <v>0.007634523293687587</v>
       </c>
       <c r="W15" t="n">
-        <v>1.873749899232492</v>
+        <v>0.1655906834098245</v>
       </c>
       <c r="X15" t="n">
-        <v>0.007634523293687587</v>
+        <v>0.003210000000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1655906834098245</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0.003210000000000001</v>
-      </c>
-      <c r="AA15" t="n">
         <v>27.65076181827065</v>
       </c>
     </row>
@@ -1870,33 +1776,27 @@
         <v>0.3242312467603854</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1082808906095662</v>
+        <v>27.31428571428567</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5694130721720264</v>
+        <v>0.9523209449429346</v>
       </c>
       <c r="T16" t="n">
-        <v>27.31428571428567</v>
+        <v>28.14126758547796</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9523209449429346</v>
+        <v>1.877175524232492</v>
       </c>
       <c r="V16" t="n">
-        <v>28.14126758547796</v>
+        <v>0.007820569623933762</v>
       </c>
       <c r="W16" t="n">
-        <v>1.877175524232492</v>
+        <v>0.1703846427370974</v>
       </c>
       <c r="X16" t="n">
-        <v>0.007820569623933762</v>
+        <v>0.003315</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1703846427370974</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0.003315</v>
-      </c>
-      <c r="AA16" t="n">
         <v>27.96487515706328</v>
       </c>
     </row>
@@ -1959,33 +1859,27 @@
         <v>0.4847102107155994</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1314793690318168</v>
+        <v>27.65357142857139</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6962113261902592</v>
+        <v>1.25504016023201</v>
       </c>
       <c r="T17" t="n">
-        <v>27.65357142857139</v>
+        <v>28.31682820030403</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25504016023201</v>
+        <v>1.880597454788048</v>
       </c>
       <c r="V17" t="n">
-        <v>28.31682820030403</v>
+        <v>0.007995866882157202</v>
       </c>
       <c r="W17" t="n">
-        <v>1.880597454788048</v>
+        <v>0.1749716173380987</v>
       </c>
       <c r="X17" t="n">
-        <v>0.007995866882157202</v>
+        <v>0.003416666666666667</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1749716173380987</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0.003416666666666667</v>
-      </c>
-      <c r="AA17" t="n">
         <v>28.14126758547796</v>
       </c>
     </row>
@@ -2048,33 +1942,27 @@
         <v>0.6709707039456413</v>
       </c>
       <c r="R18" t="n">
-        <v>0.153658332461822</v>
+        <v>28.03928571428575</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8191280143821486</v>
+        <v>1.69587337268752</v>
       </c>
       <c r="T18" t="n">
-        <v>28.03928571428575</v>
+        <v>28.48805514192954</v>
       </c>
       <c r="U18" t="n">
-        <v>1.69587337268752</v>
+        <v>1.883946954788048</v>
       </c>
       <c r="V18" t="n">
-        <v>28.48805514192954</v>
+        <v>0.008158142377838717</v>
       </c>
       <c r="W18" t="n">
-        <v>1.883946954788048</v>
+        <v>0.1792828308002749</v>
       </c>
       <c r="X18" t="n">
-        <v>0.008158142377838717</v>
+        <v>0.003513333333333334</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1792828308002749</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0.003513333333333334</v>
-      </c>
-      <c r="AA18" t="n">
         <v>28.31682820030403</v>
       </c>
     </row>
@@ -2131,39 +2019,33 @@
         <v>1.600786172733832</v>
       </c>
       <c r="P19" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0001</v>
+        <v>0.1675555555555282</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0.1675555555555282</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.543349336870027</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1675555555555282</v>
+        <v>0.8697884252671494</v>
       </c>
       <c r="W19" t="n">
-        <v>1.543349336870027</v>
+        <v>0.1457378828114052</v>
       </c>
       <c r="X19" t="n">
-        <v>0.8697884252671494</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1457378828114052</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
         <v>0.1675555555555282</v>
       </c>
     </row>
@@ -2220,39 +2102,33 @@
         <v>0.3770350248802999</v>
       </c>
       <c r="P20" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0001</v>
+        <v>0.1675555555555282</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1675555555555282</v>
+        <v>0.4827785722691494</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.543349336870027</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4827785722691494</v>
+        <v>0.8697874489964632</v>
       </c>
       <c r="W20" t="n">
-        <v>1.543349336870027</v>
+        <v>0.4199147428041381</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8697874489964632</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.4199147428041381</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
         <v>0.1675555555555282</v>
       </c>
     </row>
@@ -2309,39 +2185,33 @@
         <v>0.6434421146608056</v>
       </c>
       <c r="P21" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0001</v>
+        <v>0.425000000000088</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.425000000000088</v>
+        <v>0.9966307136161114</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.543349336870027</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9966307136161114</v>
+        <v>0.8697854482356324</v>
       </c>
       <c r="W21" t="n">
-        <v>1.543349336870027</v>
+        <v>0.8668548919679877</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8697854482356324</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.8668548919679877</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
         <v>0.4827785722691494</v>
       </c>
     </row>
@@ -2398,39 +2268,33 @@
         <v>0.7999569147331987</v>
       </c>
       <c r="P22" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0001</v>
+        <v>0.5214285714284982</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5214285714284982</v>
+        <v>1.969845422905219</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.543349336870027</v>
       </c>
       <c r="V22" t="n">
-        <v>1.969845422905219</v>
+        <v>0.8697791546860387</v>
       </c>
       <c r="W22" t="n">
-        <v>1.543349336870027</v>
+        <v>1.713330486796664</v>
       </c>
       <c r="X22" t="n">
-        <v>0.8697791546860387</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.713330486796664</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
         <v>0.9966307136161114</v>
       </c>
     </row>
@@ -2487,39 +2351,33 @@
         <v>0.5416439745143597</v>
       </c>
       <c r="P23" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0001</v>
+        <v>1.003571428571421</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.003571428571421</v>
+        <v>6.396537563198554</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.571874336879291</v>
       </c>
       <c r="V23" t="n">
-        <v>6.396537563198554</v>
+        <v>0.8643085886630451</v>
       </c>
       <c r="W23" t="n">
-        <v>1.571874336879291</v>
+        <v>5.285234054477813</v>
       </c>
       <c r="X23" t="n">
-        <v>0.8643085886630451</v>
+        <v>0.05979999999999999</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.285234054477813</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.05979999999999999</v>
-      </c>
-      <c r="AA23" t="n">
         <v>1.969845422905219</v>
       </c>
     </row>
@@ -2576,39 +2434,33 @@
         <v>0.4518573616580095</v>
       </c>
       <c r="P24" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0001</v>
+        <v>5.957142857142867</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>5.957142857142867</v>
+        <v>14.63100687628614</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.68942933687929</v>
       </c>
       <c r="V24" t="n">
-        <v>14.63100687628614</v>
+        <v>0.3957858539567146</v>
       </c>
       <c r="W24" t="n">
-        <v>1.68942933687929</v>
+        <v>5.110910049690442</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3957858539567146</v>
+        <v>0.07849999999999997</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.110910049690442</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0.07849999999999997</v>
-      </c>
-      <c r="AA24" t="n">
         <v>6.396537563198554</v>
       </c>
     </row>
@@ -2665,39 +2517,33 @@
         <v>0.3951354990954673</v>
       </c>
       <c r="P25" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0001</v>
+        <v>12.12857142857143</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>12.12857142857143</v>
+        <v>18.43528574476287</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.749953781323735</v>
       </c>
       <c r="V25" t="n">
-        <v>18.43528574476287</v>
+        <v>0.3344093033120227</v>
       </c>
       <c r="W25" t="n">
-        <v>1.749953781323735</v>
+        <v>5.25297484204653</v>
       </c>
       <c r="X25" t="n">
-        <v>0.3344093033120227</v>
+        <v>0.08656666666666669</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.25297484204653</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0.08656666666666669</v>
-      </c>
-      <c r="AA25" t="n">
         <v>14.63100687628614</v>
       </c>
     </row>
@@ -2754,39 +2600,33 @@
         <v>0.3288368413306143</v>
       </c>
       <c r="P26" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0001</v>
+        <v>16.20714285714285</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>16.20714285714285</v>
+        <v>23.11964730786949</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.830712531323734</v>
       </c>
       <c r="V26" t="n">
-        <v>23.11964730786949</v>
+        <v>0.2835003051511213</v>
       </c>
       <c r="W26" t="n">
-        <v>1.830712531323734</v>
+        <v>5.338487005067323</v>
       </c>
       <c r="X26" t="n">
-        <v>0.2835003051511213</v>
+        <v>0.09628333333333336</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.338487005067323</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0.09628333333333336</v>
-      </c>
-      <c r="AA26" t="n">
         <v>18.43528574476287</v>
       </c>
     </row>
@@ -2843,39 +2683,33 @@
         <v>0.1921794536128573</v>
       </c>
       <c r="P27" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0001</v>
+        <v>21.77499999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>21.77499999999999</v>
+        <v>26.32781445538231</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.890462531323734</v>
       </c>
       <c r="V27" t="n">
-        <v>26.32781445538231</v>
+        <v>0.2576118310996777</v>
       </c>
       <c r="W27" t="n">
-        <v>1.890462531323734</v>
+        <v>5.349536074710177</v>
       </c>
       <c r="X27" t="n">
-        <v>0.2576118310996777</v>
+        <v>0.1028833333333333</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.349536074710177</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0.1028833333333333</v>
-      </c>
-      <c r="AA27" t="n">
         <v>23.11964730786949</v>
       </c>
     </row>
@@ -2938,33 +2772,27 @@
         <v>0.1619956336149481</v>
       </c>
       <c r="R28" t="n">
-        <v>0.07756128526809224</v>
+        <v>26.35714285714281</v>
       </c>
       <c r="S28" t="n">
-        <v>0.4024868117279722</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>26.35714285714281</v>
+        <v>27.23145296063369</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.908002336883929</v>
       </c>
       <c r="V28" t="n">
-        <v>27.23145296063369</v>
+        <v>0.01870851914241778</v>
       </c>
       <c r="W28" t="n">
-        <v>1.908002336883929</v>
+        <v>0.3981367454977016</v>
       </c>
       <c r="X28" t="n">
-        <v>0.01870851914241778</v>
+        <v>0.007799999999999998</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.3981367454977016</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0.007799999999999998</v>
-      </c>
-      <c r="AA28" t="n">
         <v>26.32781445538231</v>
       </c>
     </row>
@@ -3027,33 +2855,27 @@
         <v>0.0921971490896749</v>
       </c>
       <c r="R29" t="n">
-        <v>0.06022672929531771</v>
+        <v>26.92857142857148</v>
       </c>
       <c r="S29" t="n">
-        <v>0.3036398344909226</v>
+        <v>0.1961577414134905</v>
       </c>
       <c r="T29" t="n">
-        <v>26.92857142857148</v>
+        <v>27.9694722689493</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1961577414134905</v>
+        <v>1.922571086883929</v>
       </c>
       <c r="V29" t="n">
-        <v>27.9694722689493</v>
+        <v>0.02051073157175735</v>
       </c>
       <c r="W29" t="n">
-        <v>1.922571086883929</v>
+        <v>0.4449249609611882</v>
       </c>
       <c r="X29" t="n">
-        <v>0.02051073157175735</v>
+        <v>0.008849999999999998</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.4449249609611882</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0.008849999999999998</v>
-      </c>
-      <c r="AA29" t="n">
         <v>27.23145296063369</v>
       </c>
     </row>
@@ -3110,39 +2932,33 @@
         <v>0.006274829559544594</v>
       </c>
       <c r="P30" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0001</v>
+        <v>25.41785714285721</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0001</v>
+        <v>0.4648676866334254</v>
       </c>
       <c r="T30" t="n">
-        <v>25.41785714285721</v>
+        <v>28.96836727463392</v>
       </c>
       <c r="U30" t="n">
-        <v>0.4648676866334254</v>
+        <v>1.942647670217263</v>
       </c>
       <c r="V30" t="n">
-        <v>28.96836727463392</v>
+        <v>0.02241123524433885</v>
       </c>
       <c r="W30" t="n">
-        <v>1.942647670217263</v>
+        <v>0.4983095102163055</v>
       </c>
       <c r="X30" t="n">
-        <v>0.02241123524433885</v>
+        <v>0.01012</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.4983095102163055</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0.01012</v>
-      </c>
-      <c r="AA30" t="n">
         <v>27.9694722689493</v>
       </c>
     </row>
@@ -3205,33 +3021,27 @@
         <v>0.166038915540943</v>
       </c>
       <c r="R31" t="n">
-        <v>0.07737225717069976</v>
+        <v>27.31785714285721</v>
       </c>
       <c r="S31" t="n">
-        <v>0.4074787301699844</v>
+        <v>0.5273275582417261</v>
       </c>
       <c r="T31" t="n">
-        <v>27.31785714285721</v>
+        <v>30.01254965667641</v>
       </c>
       <c r="U31" t="n">
-        <v>0.5273275582417261</v>
+        <v>1.964087670217262</v>
       </c>
       <c r="V31" t="n">
-        <v>30.01254965667641</v>
+        <v>0.02393238700794108</v>
       </c>
       <c r="W31" t="n">
-        <v>1.964087670217262</v>
+        <v>0.5452949182549442</v>
       </c>
       <c r="X31" t="n">
-        <v>0.02393238700794108</v>
+        <v>0.01132</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.5452949182549442</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0.01132</v>
-      </c>
-      <c r="AA31" t="n">
         <v>28.96836727463392</v>
       </c>
     </row>
@@ -3294,33 +3104,27 @@
         <v>0.6940734053890505</v>
       </c>
       <c r="R32" t="n">
-        <v>0.1504129176969866</v>
+        <v>27.73571428571431</v>
       </c>
       <c r="S32" t="n">
-        <v>0.8331106801554344</v>
+        <v>0.5669120469218694</v>
       </c>
       <c r="T32" t="n">
-        <v>27.73571428571431</v>
+        <v>31.10797015051896</v>
       </c>
       <c r="U32" t="n">
-        <v>0.5669120469218694</v>
+        <v>1.987094336883929</v>
       </c>
       <c r="V32" t="n">
-        <v>31.10797015051896</v>
+        <v>0.02516114519472265</v>
       </c>
       <c r="W32" t="n">
-        <v>1.987094336883929</v>
+        <v>0.5873377015004719</v>
       </c>
       <c r="X32" t="n">
-        <v>0.02516114519472265</v>
+        <v>0.01248</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.5873377015004719</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0.01248</v>
-      </c>
-      <c r="AA32" t="n">
         <v>30.01254965667641</v>
       </c>
     </row>
@@ -3383,33 +3187,27 @@
         <v>1.033509465599738</v>
       </c>
       <c r="R33" t="n">
-        <v>0.1835437763974597</v>
+        <v>30.67857142857135</v>
       </c>
       <c r="S33" t="n">
-        <v>1.016616675841852</v>
+        <v>1.314363106233276</v>
       </c>
       <c r="T33" t="n">
-        <v>30.67857142857135</v>
+        <v>31.74613730418875</v>
       </c>
       <c r="U33" t="n">
-        <v>1.314363106233276</v>
+        <v>2.000747670217262</v>
       </c>
       <c r="V33" t="n">
-        <v>31.74613730418875</v>
+        <v>0.02574269542905198</v>
       </c>
       <c r="W33" t="n">
-        <v>2.000747670217262</v>
+        <v>0.6090543067655569</v>
       </c>
       <c r="X33" t="n">
-        <v>0.02574269542905198</v>
+        <v>0.01312</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.6090543067655569</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0.01312</v>
-      </c>
-      <c r="AA33" t="n">
         <v>31.10797015051896</v>
       </c>
     </row>
@@ -3466,39 +3264,33 @@
         <v>0.1410188726692848</v>
       </c>
       <c r="P34" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0001</v>
+        <v>0.103563218390794</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0.103563218390794</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.6359</v>
       </c>
       <c r="V34" t="n">
-        <v>0.103563218390794</v>
+        <v>0.8697892354884217</v>
       </c>
       <c r="W34" t="n">
-        <v>1.6359</v>
+        <v>0.09007817254884913</v>
       </c>
       <c r="X34" t="n">
-        <v>0.8697892354884217</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.09007817254884913</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
         <v>0.103563218390794</v>
       </c>
     </row>
@@ -3555,39 +3347,33 @@
         <v>0.3923394771712953</v>
       </c>
       <c r="P35" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0001</v>
+        <v>0.103563218390794</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.103563218390794</v>
+        <v>0.1876426207653147</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.6359</v>
       </c>
       <c r="V35" t="n">
-        <v>0.1876426207653147</v>
+        <v>0.8697890236997015</v>
       </c>
       <c r="W35" t="n">
-        <v>1.6359</v>
+        <v>0.1632094919199164</v>
       </c>
       <c r="X35" t="n">
-        <v>0.8697890236997015</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.1632094919199164</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
         <v>0.103563218390794</v>
       </c>
     </row>
@@ -3644,39 +3430,33 @@
         <v>0.9865765782029755</v>
       </c>
       <c r="P36" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0001</v>
+        <v>0.1748717948718132</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0.1748717948718132</v>
+        <v>0.4609644348278589</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.6359</v>
       </c>
       <c r="V36" t="n">
-        <v>0.4609644348278589</v>
+        <v>0.8697882737127572</v>
       </c>
       <c r="W36" t="n">
-        <v>1.6359</v>
+        <v>0.4009414600119002</v>
       </c>
       <c r="X36" t="n">
-        <v>0.8697882737127572</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.4009414600119002</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
         <v>0.1876426207653147</v>
       </c>
     </row>
@@ -3733,39 +3513,33 @@
         <v>0.859897420449224</v>
       </c>
       <c r="P37" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0001</v>
+        <v>0.5107407407407478</v>
       </c>
       <c r="S37" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0.5107407407407478</v>
+        <v>0.6719802989042384</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.6359</v>
       </c>
       <c r="V37" t="n">
-        <v>0.6719802989042384</v>
+        <v>0.8697876206794322</v>
       </c>
       <c r="W37" t="n">
-        <v>1.6359</v>
+        <v>0.5844801453273711</v>
       </c>
       <c r="X37" t="n">
-        <v>0.8697876206794322</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.5844801453273711</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
         <v>0.4609644348278589</v>
       </c>
     </row>
@@ -3822,39 +3596,33 @@
         <v>0.8458504575051579</v>
       </c>
       <c r="P38" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0001</v>
+        <v>0.7643333333332928</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0.7643333333332928</v>
+        <v>1.053232184227429</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.6359</v>
       </c>
       <c r="V38" t="n">
-        <v>1.053232184227429</v>
+        <v>0.8697862357619959</v>
       </c>
       <c r="W38" t="n">
-        <v>1.6359</v>
+        <v>0.9160868569025606</v>
       </c>
       <c r="X38" t="n">
-        <v>0.8697862357619959</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.9160868569025606</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
         <v>0.6719802989042384</v>
       </c>
     </row>
@@ -3911,39 +3679,33 @@
         <v>1.072647376108041</v>
       </c>
       <c r="P39" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0.0001</v>
+        <v>1.021500000000053</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>1.021500000000053</v>
+        <v>1.627029941264684</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.6359</v>
       </c>
       <c r="V39" t="n">
-        <v>1.627029941264684</v>
+        <v>0.8697834490132752</v>
       </c>
       <c r="W39" t="n">
-        <v>1.6359</v>
+        <v>1.415163713961063</v>
       </c>
       <c r="X39" t="n">
-        <v>0.8697834490132752</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.415163713961063</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
         <v>1.053232184227429</v>
       </c>
     </row>
@@ -4000,39 +3762,33 @@
         <v>0.8721620914810805</v>
       </c>
       <c r="P40" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0001</v>
+        <v>1.369999999999916</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1.369999999999916</v>
+        <v>2.513425212631307</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.6359</v>
       </c>
       <c r="V40" t="n">
-        <v>2.513425212631307</v>
+        <v>0.8697759166535052</v>
       </c>
       <c r="W40" t="n">
-        <v>1.6359</v>
+        <v>2.186116718256426</v>
       </c>
       <c r="X40" t="n">
-        <v>0.8697759166535052</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.186116718256426</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
         <v>1.627029941264684</v>
       </c>
     </row>
@@ -4089,39 +3845,33 @@
         <v>0.7803720364651523</v>
       </c>
       <c r="P41" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0001</v>
+        <v>2.429000000000059</v>
       </c>
       <c r="S41" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.429000000000059</v>
+        <v>3.882683372173928</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.6359</v>
       </c>
       <c r="V41" t="n">
-        <v>3.882683372173928</v>
+        <v>0.8697189069833527</v>
       </c>
       <c r="W41" t="n">
-        <v>1.6359</v>
+        <v>3.376843138609547</v>
       </c>
       <c r="X41" t="n">
-        <v>0.8697189069833527</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>3.376843138609547</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
         <v>2.513425212631307</v>
       </c>
     </row>
@@ -4178,39 +3928,33 @@
         <v>0.5859915840261742</v>
       </c>
       <c r="P42" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.0001</v>
+        <v>3.654000000000046</v>
       </c>
       <c r="S42" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3.654000000000046</v>
+        <v>4.882615521967159</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.64166002228396</v>
       </c>
       <c r="V42" t="n">
-        <v>4.882615521967159</v>
+        <v>0.4571103239850599</v>
       </c>
       <c r="W42" t="n">
-        <v>1.64166002228396</v>
+        <v>2.144452657147387</v>
       </c>
       <c r="X42" t="n">
-        <v>0.4571103239850599</v>
+        <v>0.02939999999999999</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.144452657147387</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0.02939999999999999</v>
-      </c>
-      <c r="AA42" t="n">
         <v>3.882683372173928</v>
       </c>
     </row>
@@ -4267,39 +4011,33 @@
         <v>0.4918158019929457</v>
       </c>
       <c r="P43" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0001</v>
+        <v>5.610714285714247</v>
       </c>
       <c r="S43" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>5.610714285714247</v>
+        <v>6.953414511085085</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.670550021986031</v>
       </c>
       <c r="V43" t="n">
-        <v>6.953414511085085</v>
+        <v>0.3733595947783498</v>
       </c>
       <c r="W43" t="n">
-        <v>1.670550021986031</v>
+        <v>2.451274231121808</v>
       </c>
       <c r="X43" t="n">
-        <v>0.3733595947783498</v>
+        <v>0.03479999999999999</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.451274231121808</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0.03479999999999999</v>
-      </c>
-      <c r="AA43" t="n">
         <v>4.882615521967159</v>
       </c>
     </row>
@@ -4356,39 +4094,33 @@
         <v>0.4239703641171224</v>
       </c>
       <c r="P44" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.0001</v>
+        <v>8.060714285714278</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>8.060714285714278</v>
+        <v>9.420022431770047</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.706317521986036</v>
       </c>
       <c r="V44" t="n">
-        <v>9.420022431770047</v>
+        <v>0.314013066163396</v>
       </c>
       <c r="W44" t="n">
-        <v>1.706317521986036</v>
+        <v>2.734422838378545</v>
       </c>
       <c r="X44" t="n">
-        <v>0.314013066163396</v>
+        <v>0.04049999999999999</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.734422838378545</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0.04049999999999999</v>
-      </c>
-      <c r="AA44" t="n">
         <v>6.953414511085085</v>
       </c>
     </row>
@@ -4445,39 +4177,33 @@
         <v>0.4001175993931018</v>
       </c>
       <c r="P45" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0.0001</v>
+        <v>12.56785714285716</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>12.56785714285716</v>
+        <v>10.82063313860438</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.727317521986036</v>
       </c>
       <c r="V45" t="n">
-        <v>10.82063313860438</v>
+        <v>0.2900471432209064</v>
       </c>
       <c r="W45" t="n">
-        <v>1.727317521986036</v>
+        <v>2.865991693711258</v>
       </c>
       <c r="X45" t="n">
-        <v>0.2900471432209064</v>
+        <v>0.04350000000000001</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.865991693711258</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0.04350000000000001</v>
-      </c>
-      <c r="AA45" t="n">
         <v>9.420022431770047</v>
       </c>
     </row>
@@ -4534,39 +4260,33 @@
         <v>0.456221002086854</v>
       </c>
       <c r="P46" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0001</v>
+        <v>15.0964285714285</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>15.0964285714285</v>
+        <v>12.93604424613004</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.760033355319369</v>
       </c>
       <c r="V46" t="n">
-        <v>12.93604424613004</v>
+        <v>0.2616431887926153</v>
       </c>
       <c r="W46" t="n">
-        <v>1.760033355319369</v>
+        <v>3.033303323497858</v>
       </c>
       <c r="X46" t="n">
-        <v>0.2616431887926153</v>
+        <v>0.0478</v>
       </c>
       <c r="Y46" t="n">
-        <v>3.033303323497858</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0.0478</v>
-      </c>
-      <c r="AA46" t="n">
         <v>10.82063313860438</v>
       </c>
     </row>
@@ -4623,39 +4343,33 @@
         <v>0.3401951848972837</v>
       </c>
       <c r="P47" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0001</v>
+        <v>19.02857142857142</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>19.02857142857142</v>
+        <v>14.89840229589674</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.791510021986035</v>
       </c>
       <c r="V47" t="n">
-        <v>14.89840229589674</v>
+        <v>0.2409320357844078</v>
       </c>
       <c r="W47" t="n">
-        <v>1.791510021986035</v>
+        <v>3.160390891921233</v>
       </c>
       <c r="X47" t="n">
-        <v>0.2409320357844078</v>
+        <v>0.0516</v>
       </c>
       <c r="Y47" t="n">
-        <v>3.160390891921233</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0.0516</v>
-      </c>
-      <c r="AA47" t="n">
         <v>12.93604424613004</v>
       </c>
     </row>
@@ -4712,39 +4426,33 @@
         <v>0.1620066644475431</v>
       </c>
       <c r="P48" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.0001</v>
+        <v>25.25357142857137</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>25.25357142857137</v>
+        <v>16.88071214887976</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.824470855319368</v>
       </c>
       <c r="V48" t="n">
-        <v>16.88071214887976</v>
+        <v>0.2237696249091863</v>
       </c>
       <c r="W48" t="n">
-        <v>1.824470855319368</v>
+        <v>3.265733572362352</v>
       </c>
       <c r="X48" t="n">
-        <v>0.2237696249091863</v>
+        <v>0.0553</v>
       </c>
       <c r="Y48" t="n">
-        <v>3.265733572362352</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0.0553</v>
-      </c>
-      <c r="AA48" t="n">
         <v>14.89840229589674</v>
       </c>
     </row>
@@ -4807,33 +4515,27 @@
         <v>0.0816312894067058</v>
       </c>
       <c r="R49" t="n">
-        <v>0.05155349562266365</v>
+        <v>29.52857142857138</v>
       </c>
       <c r="S49" t="n">
-        <v>0.2857118993089119</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>29.52857142857138</v>
+        <v>19.99434821018733</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.878764049847864</v>
       </c>
       <c r="V49" t="n">
-        <v>19.9943493428161</v>
+        <v>0.006623948324800732</v>
       </c>
       <c r="W49" t="n">
-        <v>1.878764110411336</v>
+        <v>0.11119242751127</v>
       </c>
       <c r="X49" t="n">
-        <v>0.006624133662702124</v>
+        <v>0.001996666666666667</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.1111961402057659</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0.001996666666666667</v>
-      </c>
-      <c r="AA49" t="n">
         <v>16.88071214887976</v>
       </c>
     </row>
@@ -4896,34 +4598,28 @@
         <v>0.04078878183453907</v>
       </c>
       <c r="R50" t="n">
-        <v>0.0359356095867547</v>
+        <v>30.71428571428574</v>
       </c>
       <c r="S50" t="n">
-        <v>0.2019623277607462</v>
+        <v>0.09290978010103844</v>
       </c>
       <c r="T50" t="n">
-        <v>30.71428571428574</v>
+        <v>20.11820220859315</v>
       </c>
       <c r="U50" t="n">
-        <v>0.09290978010103844</v>
+        <v>1.880990638206213</v>
       </c>
       <c r="V50" t="n">
-        <v>20.1182030731978</v>
+        <v>0.006756705910393339</v>
       </c>
       <c r="W50" t="n">
-        <v>1.88099069374467</v>
+        <v>0.1139891020336284</v>
       </c>
       <c r="X50" t="n">
-        <v>0.006756696680435864</v>
+        <v>0.002051666666666667</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.1139889218902052</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0.002051666666666667</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>19.9943493428161</v>
+        <v>19.99434821018733</v>
       </c>
     </row>
     <row r="51">
@@ -4985,34 +4681,28 @@
         <v>0.02413582546819065</v>
       </c>
       <c r="R51" t="n">
-        <v>0.02706031021828268</v>
+        <v>31.58571428571431</v>
       </c>
       <c r="S51" t="n">
-        <v>0.1553570901767623</v>
+        <v>0.1714635834683609</v>
       </c>
       <c r="T51" t="n">
-        <v>31.58571428571431</v>
+        <v>20.22569114062808</v>
       </c>
       <c r="U51" t="n">
-        <v>0.1714635834683609</v>
+        <v>1.88292730487288</v>
       </c>
       <c r="V51" t="n">
-        <v>20.22569199499107</v>
+        <v>0.006866587396872273</v>
       </c>
       <c r="W51" t="n">
-        <v>1.882927360411336</v>
+        <v>0.1163419748585688</v>
       </c>
       <c r="X51" t="n">
-        <v>0.006866586904202878</v>
+        <v>0.002098333333333333</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.1163419704732665</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0.002098333333333333</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>20.1182030731978</v>
+        <v>20.11820220859315</v>
       </c>
     </row>
     <row r="52">
@@ -5074,34 +4764,28 @@
         <v>0.03974752399441857</v>
       </c>
       <c r="R52" t="n">
-        <v>0.03441311909386455</v>
+        <v>32.96071428571437</v>
       </c>
       <c r="S52" t="n">
-        <v>0.199367810828174</v>
+        <v>0.1940649581558863</v>
       </c>
       <c r="T52" t="n">
-        <v>32.96071428571437</v>
+        <v>20.34328662960689</v>
       </c>
       <c r="U52" t="n">
-        <v>0.1940649581558863</v>
+        <v>1.885050638206214</v>
       </c>
       <c r="V52" t="n">
-        <v>20.34328747236598</v>
+        <v>0.006981721188787508</v>
       </c>
       <c r="W52" t="n">
-        <v>1.88505069374467</v>
+        <v>0.1188465469566182</v>
       </c>
       <c r="X52" t="n">
-        <v>0.006981715983853094</v>
+        <v>0.002148333333333333</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.1188464466776623</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0.002148333333333333</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>20.22569199499107</v>
+        <v>20.22569114062808</v>
       </c>
     </row>
     <row r="53">
@@ -5163,34 +4847,28 @@
         <v>0.07526448485171559</v>
       </c>
       <c r="R53" t="n">
-        <v>0.04747282035761839</v>
+        <v>33.56309523809537</v>
       </c>
       <c r="S53" t="n">
-        <v>0.2743437348504894</v>
+        <v>0.2229784488956445</v>
       </c>
       <c r="T53" t="n">
-        <v>33.56309523809537</v>
+        <v>20.47349681467529</v>
       </c>
       <c r="U53" t="n">
-        <v>0.2229784488956445</v>
+        <v>1.887407339595103</v>
       </c>
       <c r="V53" t="n">
-        <v>20.47349764508844</v>
+        <v>0.007103361739172312</v>
       </c>
       <c r="W53" t="n">
-        <v>1.887407395133558</v>
+        <v>0.1215392152518453</v>
       </c>
       <c r="X53" t="n">
-        <v>0.007103342896403787</v>
+        <v>0.0022025</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.1215388351071716</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0.0022025</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>20.34328747236598</v>
+        <v>20.34328662960689</v>
       </c>
     </row>
     <row r="54">
@@ -5252,34 +4930,28 @@
         <v>0.102602067198723</v>
       </c>
       <c r="R54" t="n">
-        <v>0.05491924762933701</v>
+        <v>33.39642857142849</v>
       </c>
       <c r="S54" t="n">
-        <v>0.3203155743930086</v>
+        <v>0.2989185664601128</v>
       </c>
       <c r="T54" t="n">
-        <v>33.39642857142849</v>
+        <v>20.58181943419975</v>
       </c>
       <c r="U54" t="n">
-        <v>0.2989185664601128</v>
+        <v>1.889372388206214</v>
       </c>
       <c r="V54" t="n">
-        <v>20.58182025443793</v>
+        <v>0.007200136199108651</v>
       </c>
       <c r="W54" t="n">
-        <v>1.889372443744669</v>
+        <v>0.1237179095912931</v>
       </c>
       <c r="X54" t="n">
-        <v>0.007200135700517285</v>
+        <v>0.002246666666666667</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.1237179049792681</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0.002246666666666667</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>20.47349764508844</v>
+        <v>20.47349681467529</v>
       </c>
     </row>
     <row r="55">
@@ -5335,39 +5007,33 @@
         <v>1.241564657307359</v>
       </c>
       <c r="P55" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.0001</v>
+        <v>0.04347826086957973</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
         <v>0.04347826086957973</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.6309</v>
       </c>
       <c r="V55" t="n">
-        <v>0.04347826086957973</v>
+        <v>0.8697886689425612</v>
       </c>
       <c r="W55" t="n">
-        <v>1.6309</v>
+        <v>0.0378168986496892</v>
       </c>
       <c r="X55" t="n">
-        <v>0.8697886689425612</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.0378168986496892</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
         <v>0.04347826086957973</v>
       </c>
     </row>
@@ -5424,39 +5090,33 @@
         <v>0.4980891336844761</v>
       </c>
       <c r="P56" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.0001</v>
+        <v>0.04347826086957973</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0.04347826086957973</v>
+        <v>0.07877673908509283</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.6309</v>
       </c>
       <c r="V56" t="n">
-        <v>0.07877673908509283</v>
+        <v>0.8697885714932413</v>
       </c>
       <c r="W56" t="n">
-        <v>1.6309</v>
+        <v>0.06851910735571869</v>
       </c>
       <c r="X56" t="n">
-        <v>0.8697885714932413</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.06851910735571869</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
         <v>0.04347826086957973</v>
       </c>
     </row>
@@ -5513,39 +5173,33 @@
         <v>0.9497676633868221</v>
       </c>
       <c r="P57" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0.0001</v>
+        <v>0.1328787878787904</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>0.1328787878787904</v>
+        <v>0.1935235416547727</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.6309</v>
       </c>
       <c r="V57" t="n">
-        <v>0.1935235416547727</v>
+        <v>0.8697882427952393</v>
       </c>
       <c r="W57" t="n">
-        <v>1.6309</v>
+        <v>0.168324501235416</v>
       </c>
       <c r="X57" t="n">
-        <v>0.8697882427952393</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.168324501235416</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
         <v>0.07877673908509283</v>
       </c>
     </row>
@@ -5602,39 +5256,33 @@
         <v>0.8861519348632451</v>
       </c>
       <c r="P58" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.0001</v>
+        <v>0.4653846153846239</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>0.4653846153846239</v>
+        <v>0.2821129043981304</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.6309</v>
       </c>
       <c r="V58" t="n">
-        <v>0.2821129043981304</v>
+        <v>0.8697879757992245</v>
       </c>
       <c r="W58" t="n">
-        <v>1.6309</v>
+        <v>0.24537841206329</v>
       </c>
       <c r="X58" t="n">
-        <v>0.8697879757992245</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.24537841206329</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
         <v>0.1935235416547727</v>
       </c>
     </row>
@@ -5691,39 +5339,33 @@
         <v>0.9252948592011343</v>
       </c>
       <c r="P59" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.0001</v>
+        <v>0.6816071428571276</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.6816071428571276</v>
+        <v>0.4233538393371857</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.6309</v>
       </c>
       <c r="V59" t="n">
-        <v>0.4233538393371857</v>
+        <v>0.8697875240975792</v>
       </c>
       <c r="W59" t="n">
-        <v>1.6309</v>
+        <v>0.3682278877342951</v>
       </c>
       <c r="X59" t="n">
-        <v>0.8697875240975792</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.3682278877342951</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
         <v>0.2821129043981304</v>
       </c>
     </row>
@@ -5780,39 +5422,33 @@
         <v>0.9349196591727447</v>
       </c>
       <c r="P60" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0.0001</v>
+        <v>0.9277500000000494</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0.9277500000000494</v>
+        <v>0.683065837977753</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.6309</v>
       </c>
       <c r="V60" t="n">
-        <v>0.683065837977753</v>
+        <v>0.8697865983670118</v>
       </c>
       <c r="W60" t="n">
-        <v>1.6309</v>
+        <v>0.5941215116753822</v>
       </c>
       <c r="X60" t="n">
-        <v>0.8697865983670118</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.5941215116753822</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="n">
         <v>0.4233538393371857</v>
       </c>
     </row>
@@ -5869,39 +5505,33 @@
         <v>0.8688225638485592</v>
       </c>
       <c r="P61" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0001</v>
+        <v>1.43027777777781</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>1.43027777777781</v>
+        <v>1.055198526161866</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.6309</v>
       </c>
       <c r="V61" t="n">
-        <v>1.055198526161866</v>
+        <v>0.8697850039771085</v>
       </c>
       <c r="W61" t="n">
-        <v>1.6309</v>
+        <v>0.9177958542743375</v>
       </c>
       <c r="X61" t="n">
-        <v>0.8697850039771085</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.9177958542743375</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
         <v>0.683065837977753</v>
       </c>
     </row>
@@ -5958,39 +5588,33 @@
         <v>0.6800657824740611</v>
       </c>
       <c r="P62" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.0001</v>
+        <v>2.204500000000031</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.204500000000031</v>
+        <v>1.63006633649882</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.6309</v>
       </c>
       <c r="V62" t="n">
-        <v>1.63006633649882</v>
+        <v>0.8697816273911033</v>
       </c>
       <c r="W62" t="n">
-        <v>1.6309</v>
+        <v>1.417801750915398</v>
       </c>
       <c r="X62" t="n">
-        <v>0.8697816273911033</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.417801750915398</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
         <v>1.055198526161866</v>
       </c>
     </row>
@@ -6047,39 +5671,33 @@
         <v>0.6441156540974313</v>
       </c>
       <c r="P63" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>0.0001</v>
+        <v>3.41107142857146</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>3.41107142857146</v>
+        <v>2.481872712794513</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.6309</v>
       </c>
       <c r="V63" t="n">
-        <v>2.481872712794513</v>
+        <v>0.8697724285148286</v>
       </c>
       <c r="W63" t="n">
-        <v>1.6309</v>
+        <v>2.158664456671969</v>
       </c>
       <c r="X63" t="n">
-        <v>0.8697724285148286</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.158664456671969</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA63" t="n">
         <v>1.63006633649882</v>
       </c>
     </row>
@@ -6136,39 +5754,33 @@
         <v>0.4894339946770361</v>
       </c>
       <c r="P64" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0001</v>
+        <v>4.485714285714332</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>4.485714285714332</v>
+        <v>4.183103260871403</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.6309</v>
       </c>
       <c r="V64" t="n">
-        <v>4.183103260871403</v>
+        <v>-2.93774096838361e-08</v>
       </c>
       <c r="W64" t="n">
-        <v>1.6309</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>-2.93774096838361e-08</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="n">
         <v>2.481872712794513</v>
       </c>
     </row>
@@ -6225,39 +5837,33 @@
         <v>0.4930841029038115</v>
       </c>
       <c r="P65" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0001</v>
+        <v>8.025000000000075</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>8.025000000000075</v>
+        <v>6.644073207633276</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.664920009844197</v>
       </c>
       <c r="V65" t="n">
-        <v>6.644073207633276</v>
+        <v>0.4562847911293855</v>
       </c>
       <c r="W65" t="n">
-        <v>1.664920009844197</v>
+        <v>2.869969199669203</v>
       </c>
       <c r="X65" t="n">
-        <v>0.4562847911293855</v>
+        <v>0.04049999999999999</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.869969199669203</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0.04049999999999999</v>
-      </c>
-      <c r="AA65" t="n">
         <v>4.183103260871403</v>
       </c>
     </row>
@@ -6314,39 +5920,33 @@
         <v>0.4398139997631306</v>
       </c>
       <c r="P66" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.0001</v>
+        <v>11.51785714285718</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>11.51785714285718</v>
+        <v>8.113663650919111</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.685920009844016</v>
       </c>
       <c r="V66" t="n">
-        <v>8.113663650919111</v>
+        <v>0.3963158641047057</v>
       </c>
       <c r="W66" t="n">
-        <v>1.685920009844016</v>
+        <v>3.006225391561416</v>
       </c>
       <c r="X66" t="n">
-        <v>0.3963158641047057</v>
+        <v>0.04350000000000001</v>
       </c>
       <c r="Y66" t="n">
-        <v>3.006225391561416</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0.04350000000000001</v>
-      </c>
-      <c r="AA66" t="n">
         <v>6.644073207633276</v>
       </c>
     </row>
@@ -6403,39 +6003,33 @@
         <v>0.3354852570926234</v>
       </c>
       <c r="P67" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0.0001</v>
+        <v>14.97857142857154</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>14.97857142857154</v>
+        <v>10.33156631118175</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.718635843177344</v>
       </c>
       <c r="V67" t="n">
-        <v>10.33156631118175</v>
+        <v>0.3354923524905105</v>
       </c>
       <c r="W67" t="n">
-        <v>1.718635843177344</v>
+        <v>3.17881214988686</v>
       </c>
       <c r="X67" t="n">
-        <v>0.3354923524905105</v>
+        <v>0.0478</v>
       </c>
       <c r="Y67" t="n">
-        <v>3.17881214988686</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>0.0478</v>
-      </c>
-      <c r="AA67" t="n">
         <v>8.113663650919111</v>
       </c>
     </row>
@@ -6492,39 +6086,33 @@
         <v>0.3363582465062418</v>
       </c>
       <c r="P68" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>0.0001</v>
+        <v>19.46071428571426</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>19.46071428571426</v>
+        <v>12.3871883970568</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.75011250984401</v>
       </c>
       <c r="V68" t="n">
-        <v>12.3871883970568</v>
+        <v>0.2966301045031565</v>
       </c>
       <c r="W68" t="n">
-        <v>1.75011250984401</v>
+        <v>3.30919137142728</v>
       </c>
       <c r="X68" t="n">
-        <v>0.2966301045031565</v>
+        <v>0.0516</v>
       </c>
       <c r="Y68" t="n">
-        <v>3.30919137142728</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0.0516</v>
-      </c>
-      <c r="AA68" t="n">
         <v>10.33156631118175</v>
       </c>
     </row>
@@ -6581,39 +6169,33 @@
         <v>0.183772009728279</v>
       </c>
       <c r="P69" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0.0001</v>
+        <v>22.09642857142853</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>22.09642857142853</v>
+        <v>14.80438687360635</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.788633343177343</v>
       </c>
       <c r="V69" t="n">
-        <v>14.80438687360635</v>
+        <v>0.2630897868796421</v>
       </c>
       <c r="W69" t="n">
-        <v>1.788633343177343</v>
+        <v>3.432202791214216</v>
       </c>
       <c r="X69" t="n">
-        <v>0.2630897868796421</v>
+        <v>0.05589999999999999</v>
       </c>
       <c r="Y69" t="n">
-        <v>3.432202791214216</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>0.05589999999999999</v>
-      </c>
-      <c r="AA69" t="n">
         <v>12.3871883970568</v>
       </c>
     </row>
@@ -6676,33 +6258,27 @@
         <v>0.06320238611045444</v>
       </c>
       <c r="R70" t="n">
-        <v>0.0464330358326207</v>
+        <v>28.42857142857147</v>
       </c>
       <c r="S70" t="n">
-        <v>0.2514008474736202</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>28.42857142857147</v>
+        <v>15.01969296805368</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.792146539303604</v>
       </c>
       <c r="V70" t="n">
-        <v>15.01969296805368</v>
+        <v>0.00924435718584087</v>
       </c>
       <c r="W70" t="n">
-        <v>1.792146539303604</v>
+        <v>0.1221136632356617</v>
       </c>
       <c r="X70" t="n">
-        <v>0.00924435718584087</v>
+        <v>0.001996666666666667</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.1221136632356617</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>0.001996666666666667</v>
-      </c>
-      <c r="AA70" t="n">
         <v>14.80438687360635</v>
       </c>
     </row>
@@ -6765,33 +6341,27 @@
         <v>0.05093049240086417</v>
       </c>
       <c r="R71" t="n">
-        <v>0.04115887469949947</v>
+        <v>29.31428571428569</v>
       </c>
       <c r="S71" t="n">
-        <v>0.2256778509310654</v>
+        <v>0.05810793948216079</v>
       </c>
       <c r="T71" t="n">
-        <v>29.31428571428569</v>
+        <v>15.15569823705797</v>
       </c>
       <c r="U71" t="n">
-        <v>0.05810793948216079</v>
+        <v>1.794373122636937</v>
       </c>
       <c r="V71" t="n">
-        <v>15.15569823705797</v>
+        <v>0.00940201309158991</v>
       </c>
       <c r="W71" t="n">
-        <v>1.794373122636937</v>
+        <v>0.1251652130959574</v>
       </c>
       <c r="X71" t="n">
-        <v>0.00940201309158991</v>
+        <v>0.002051666666666667</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.1251652130959574</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>0.002051666666666667</v>
-      </c>
-      <c r="AA71" t="n">
         <v>15.01969296805368</v>
       </c>
     </row>
@@ -6854,33 +6424,27 @@
         <v>0.03650228328522884</v>
       </c>
       <c r="R72" t="n">
-        <v>0.03434893131725996</v>
+        <v>30.06428571428577</v>
       </c>
       <c r="S72" t="n">
-        <v>0.1910557072825328</v>
+        <v>0.1219400842896329</v>
       </c>
       <c r="T72" t="n">
-        <v>30.06428571428577</v>
+        <v>15.27797991000348</v>
       </c>
       <c r="U72" t="n">
-        <v>0.1219400842896329</v>
+        <v>1.796379761525826</v>
       </c>
       <c r="V72" t="n">
-        <v>15.27797991000348</v>
+        <v>0.009535909472786619</v>
       </c>
       <c r="W72" t="n">
-        <v>1.796379761525826</v>
+        <v>0.1278292021782632</v>
       </c>
       <c r="X72" t="n">
-        <v>0.009535909472786619</v>
+        <v>0.0021</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.1278292021782632</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="AA72" t="n">
         <v>15.15569823705797</v>
       </c>
     </row>
@@ -6943,33 +6507,27 @@
         <v>0.01662203559450923</v>
       </c>
       <c r="R73" t="n">
-        <v>0.02296789446903608</v>
+        <v>30.93809523809523</v>
       </c>
       <c r="S73" t="n">
-        <v>0.1289264735983624</v>
+        <v>0.1703755277559266</v>
       </c>
       <c r="T73" t="n">
-        <v>30.93809523809523</v>
+        <v>15.40717685453495</v>
       </c>
       <c r="U73" t="n">
-        <v>0.1703755277559266</v>
+        <v>1.798504761525826</v>
       </c>
       <c r="V73" t="n">
-        <v>15.40717685453495</v>
+        <v>0.009669568421304507</v>
       </c>
       <c r="W73" t="n">
-        <v>1.798504761525826</v>
+        <v>0.1305624341001924</v>
       </c>
       <c r="X73" t="n">
-        <v>0.009669568421304507</v>
+        <v>0.00215</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.1305624341001924</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>0.00215</v>
-      </c>
-      <c r="AA73" t="n">
         <v>15.27797991000348</v>
       </c>
     </row>
@@ -7026,39 +6584,33 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>0.0001</v>
+        <v>31.5095238095239</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0001</v>
+        <v>0.2036432131066642</v>
       </c>
       <c r="T74" t="n">
-        <v>31.5095238095239</v>
+        <v>15.54576514061194</v>
       </c>
       <c r="U74" t="n">
-        <v>0.2036432131066642</v>
+        <v>1.800789824025826</v>
       </c>
       <c r="V74" t="n">
-        <v>15.54576514061194</v>
+        <v>0.009804949344494194</v>
       </c>
       <c r="W74" t="n">
-        <v>1.800789824025826</v>
+        <v>0.1334118117795324</v>
       </c>
       <c r="X74" t="n">
-        <v>0.009804949344494194</v>
+        <v>0.0022025</v>
       </c>
       <c r="Y74" t="n">
-        <v>0.1334118117795324</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>0.0022025</v>
-      </c>
-      <c r="AA74" t="n">
         <v>15.40717685453495</v>
       </c>
     </row>
@@ -7115,39 +6667,33 @@
         <v>0.07036365759109456</v>
       </c>
       <c r="P75" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0.0001</v>
+        <v>31.73214285714281</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0001</v>
+        <v>0.2220723133576301</v>
       </c>
       <c r="T75" t="n">
-        <v>31.73214285714281</v>
+        <v>15.66240091965512</v>
       </c>
       <c r="U75" t="n">
-        <v>0.2220723133576301</v>
+        <v>1.802717435136937</v>
       </c>
       <c r="V75" t="n">
-        <v>15.66240091965512</v>
+        <v>0.009912767707050024</v>
       </c>
       <c r="W75" t="n">
-        <v>1.802717435136937</v>
+        <v>0.1357454538912589</v>
       </c>
       <c r="X75" t="n">
-        <v>0.009912767707050024</v>
+        <v>0.002245833333333333</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.1357454538912589</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>0.002245833333333333</v>
-      </c>
-      <c r="AA75" t="n">
         <v>15.54576514061194</v>
       </c>
     </row>
@@ -7204,39 +6750,33 @@
         <v>2.163724434494653</v>
       </c>
       <c r="P76" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0.0001</v>
+        <v>0.2107142857143181</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
         <v>0.2107142857143181</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1.74784</v>
       </c>
       <c r="V76" t="n">
-        <v>0.2107142857143181</v>
+        <v>0.869786710518112</v>
       </c>
       <c r="W76" t="n">
-        <v>1.74784</v>
+        <v>0.1832764854306303</v>
       </c>
       <c r="X76" t="n">
-        <v>0.869786710518112</v>
+        <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.1832764854306303</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA76" t="n">
         <v>0.2107142857143181</v>
       </c>
     </row>
@@ -7293,39 +6833,33 @@
         <v>0.4976806198790853</v>
       </c>
       <c r="P77" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0001</v>
+        <v>0.2107142857143181</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>0.2107142857143181</v>
+        <v>0.370875083331963</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.74784</v>
       </c>
       <c r="V77" t="n">
-        <v>0.370875083331963</v>
+        <v>0.8697860788296862</v>
       </c>
       <c r="W77" t="n">
-        <v>1.74784</v>
+        <v>0.3225819844669411</v>
       </c>
       <c r="X77" t="n">
-        <v>0.8697860788296862</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.3225819844669411</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA77" t="n">
         <v>0.2107142857143181</v>
       </c>
     </row>
@@ -7382,39 +6916,33 @@
         <v>0.6434103325007062</v>
       </c>
       <c r="P78" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0001</v>
+        <v>0.4654761904762265</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>0.4654761904762265</v>
+        <v>0.7018417604311611</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1.74784</v>
       </c>
       <c r="V78" t="n">
-        <v>0.7018417604311611</v>
+        <v>0.8697845624758024</v>
       </c>
       <c r="W78" t="n">
-        <v>1.74784</v>
+        <v>0.6104511285238644</v>
       </c>
       <c r="X78" t="n">
-        <v>0.8697845624758024</v>
+        <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.6104511285238644</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA78" t="n">
         <v>0.370875083331963</v>
       </c>
     </row>
@@ -7471,39 +6999,33 @@
         <v>0.7086782992882604</v>
       </c>
       <c r="P79" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0001</v>
+        <v>0.6464285714286033</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>0.6464285714286033</v>
+        <v>1.36722917433076</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1.74784</v>
       </c>
       <c r="V79" t="n">
-        <v>1.36722917433076</v>
+        <v>0.8697802340136507</v>
       </c>
       <c r="W79" t="n">
-        <v>1.74784</v>
+        <v>1.189188911199699</v>
       </c>
       <c r="X79" t="n">
-        <v>0.8697802340136507</v>
+        <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.189188911199699</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA79" t="n">
         <v>0.7018417604311611</v>
       </c>
     </row>
@@ -7560,39 +7082,33 @@
         <v>0.7081139676449741</v>
       </c>
       <c r="P80" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>0.0001</v>
+        <v>1.175000000000005</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>1.175000000000005</v>
+        <v>2.270852496842724</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.74784</v>
       </c>
       <c r="V80" t="n">
-        <v>2.270852496842724</v>
+        <v>0.869768079458302</v>
       </c>
       <c r="W80" t="n">
-        <v>1.74784</v>
+        <v>1.975115014911986</v>
       </c>
       <c r="X80" t="n">
-        <v>0.869768079458302</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.975115014911986</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA80" t="n">
         <v>1.36722917433076</v>
       </c>
     </row>
@@ -7649,39 +7165,33 @@
         <v>0.5633097792025544</v>
       </c>
       <c r="P81" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>0.0001</v>
+        <v>1.796428571428604</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>1.796428571428604</v>
+        <v>3.74028928571578</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.74784</v>
       </c>
       <c r="V81" t="n">
-        <v>3.74028928571578</v>
+        <v>-2.36020749497522e-08</v>
       </c>
       <c r="W81" t="n">
-        <v>1.74784</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>-2.36020749497522e-08</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA81" t="n">
         <v>2.270852496842724</v>
       </c>
     </row>
@@ -7738,39 +7248,33 @@
         <v>0.4665723884474225</v>
       </c>
       <c r="P82" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.0001</v>
+        <v>3.449999999999922</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>3.449999999999922</v>
+        <v>5.780684204026415</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.777849722230804</v>
       </c>
       <c r="V82" t="n">
-        <v>5.780684204026415</v>
+        <v>0.5739981352015475</v>
       </c>
       <c r="W82" t="n">
-        <v>1.777849722230804</v>
+        <v>3.164197464691017</v>
       </c>
       <c r="X82" t="n">
-        <v>0.5739981352015475</v>
+        <v>0.04733333333333335</v>
       </c>
       <c r="Y82" t="n">
-        <v>3.164197464691017</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>0.04733333333333335</v>
-      </c>
-      <c r="AA82" t="n">
         <v>3.74028928571578</v>
       </c>
     </row>
@@ -7827,39 +7331,33 @@
         <v>0.4598955531383755</v>
       </c>
       <c r="P83" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.0001</v>
+        <v>5.41785714285711</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>5.41785714285711</v>
+        <v>9.058698433231534</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.828277500008582</v>
       </c>
       <c r="V83" t="n">
-        <v>9.058698433231534</v>
+        <v>0.4289168615272934</v>
       </c>
       <c r="W83" t="n">
-        <v>1.828277500008582</v>
+        <v>3.603006489149752</v>
       </c>
       <c r="X83" t="n">
-        <v>0.4289168615272934</v>
+        <v>0.057</v>
       </c>
       <c r="Y83" t="n">
-        <v>3.603006489149752</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="AA83" t="n">
         <v>5.780684204026415</v>
       </c>
     </row>
@@ -7916,39 +7414,33 @@
         <v>0.435983363979242</v>
       </c>
       <c r="P84" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.0001</v>
+        <v>7.639285714285721</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>7.639285714285721</v>
+        <v>11.41819282344158</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1.866383055564137</v>
       </c>
       <c r="V84" t="n">
-        <v>11.41819282344158</v>
+        <v>0.3703727279476379</v>
       </c>
       <c r="W84" t="n">
-        <v>1.866383055564137</v>
+        <v>3.841525384626546</v>
       </c>
       <c r="X84" t="n">
-        <v>0.3703727279476379</v>
+        <v>0.06333333333333334</v>
       </c>
       <c r="Y84" t="n">
-        <v>3.841525384626546</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>0.06333333333333334</v>
-      </c>
-      <c r="AA84" t="n">
         <v>9.058698433231534</v>
       </c>
     </row>
@@ -8005,39 +7497,33 @@
         <v>0.3176043329592845</v>
       </c>
       <c r="P85" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.0001</v>
+        <v>9.857142857142883</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>9.857142857142883</v>
+        <v>16.52906368661916</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>1.954627500008582</v>
       </c>
       <c r="V85" t="n">
-        <v>16.52906368661916</v>
+        <v>0.293160374987613</v>
       </c>
       <c r="W85" t="n">
-        <v>1.954627500008582</v>
+        <v>4.202981986741455</v>
       </c>
       <c r="X85" t="n">
-        <v>0.293160374987613</v>
+        <v>0.07599999999999998</v>
       </c>
       <c r="Y85" t="n">
-        <v>4.202981986741455</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>0.07599999999999998</v>
-      </c>
-      <c r="AA85" t="n">
         <v>11.41819282344158</v>
       </c>
     </row>
@@ -8094,39 +7580,33 @@
         <v>0.2216739014614701</v>
       </c>
       <c r="P86" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.0001</v>
+        <v>15.67142857142846</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>15.67142857142846</v>
+        <v>20.39251848523132</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>2.027077500008582</v>
       </c>
       <c r="V86" t="n">
-        <v>20.39251848523132</v>
+        <v>0.2562603568609737</v>
       </c>
       <c r="W86" t="n">
-        <v>2.027077500008582</v>
+        <v>4.370689081289711</v>
       </c>
       <c r="X86" t="n">
-        <v>0.2562603568609737</v>
+        <v>0.08500000000000002</v>
       </c>
       <c r="Y86" t="n">
-        <v>4.370689081289711</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>0.08500000000000002</v>
-      </c>
-      <c r="AA86" t="n">
         <v>16.52906368661916</v>
       </c>
     </row>
@@ -8183,39 +7663,33 @@
         <v>0.1419264349539861</v>
       </c>
       <c r="P87" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0.0001</v>
+        <v>19.33214285714294</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>19.33214285714294</v>
+        <v>23.31767048629318</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>2.085607271913489</v>
       </c>
       <c r="V87" t="n">
-        <v>23.31767048629318</v>
+        <v>0.01021561874538532</v>
       </c>
       <c r="W87" t="n">
-        <v>2.085607271913489</v>
+        <v>0.2005268926165561</v>
       </c>
       <c r="X87" t="n">
-        <v>0.01021561874538532</v>
+        <v>0.003370000000000001</v>
       </c>
       <c r="Y87" t="n">
-        <v>0.2005268926165561</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>0.003370000000000001</v>
-      </c>
-      <c r="AA87" t="n">
         <v>20.39251848523132</v>
       </c>
     </row>
@@ -8272,39 +7746,33 @@
         <v>0.07721244115214908</v>
       </c>
       <c r="P88" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0.0001</v>
+        <v>21.1678571428572</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>21.1678571428572</v>
+        <v>23.51197052130172</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>2.089615021915349</v>
       </c>
       <c r="V88" t="n">
-        <v>23.51197052130172</v>
+        <v>0.01079783915409544</v>
       </c>
       <c r="W88" t="n">
-        <v>2.089615021915349</v>
+        <v>0.2133719265975545</v>
       </c>
       <c r="X88" t="n">
-        <v>0.01079783915409544</v>
+        <v>0.0036</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.2133719265975545</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="AA88" t="n">
         <v>23.31767048629318</v>
       </c>
     </row>
@@ -8361,39 +7829,33 @@
         <v>0.03322042971089017</v>
       </c>
       <c r="P89" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0.0001</v>
+        <v>23.35000000000008</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>23.35000000000008</v>
+        <v>23.76781203213405</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>2.094915716359793</v>
       </c>
       <c r="V89" t="n">
-        <v>23.76781203213405</v>
+        <v>0.01151014686535403</v>
       </c>
       <c r="W89" t="n">
-        <v>2.094915716359793</v>
+        <v>0.2295127493464703</v>
       </c>
       <c r="X89" t="n">
-        <v>0.01151014686535403</v>
+        <v>0.003883333333333334</v>
       </c>
       <c r="Y89" t="n">
-        <v>0.2295127493464703</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>0.003883333333333334</v>
-      </c>
-      <c r="AA89" t="n">
         <v>23.51197052130172</v>
       </c>
     </row>
@@ -8456,33 +7918,27 @@
         <v>0.07399229663180125</v>
       </c>
       <c r="R90" t="n">
-        <v>0.05414454690340646</v>
+        <v>24.49345238095237</v>
       </c>
       <c r="S90" t="n">
-        <v>0.2720152507338536</v>
+        <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>24.49345238095237</v>
+        <v>23.93968006453909</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>2.098491720806879</v>
       </c>
       <c r="V90" t="n">
-        <v>23.93968006453909</v>
+        <v>0.01007997637280434</v>
       </c>
       <c r="W90" t="n">
-        <v>2.098491720806879</v>
+        <v>0.194956735239167</v>
       </c>
       <c r="X90" t="n">
-        <v>0.01007997637280434</v>
+        <v>0.004063333333333333</v>
       </c>
       <c r="Y90" t="n">
-        <v>0.194956735239167</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>0.004063333333333333</v>
-      </c>
-      <c r="AA90" t="n">
         <v>23.76781203213405</v>
       </c>
     </row>
@@ -8545,33 +8001,27 @@
         <v>0.06485638924285067</v>
       </c>
       <c r="R91" t="n">
-        <v>0.05116644028606399</v>
+        <v>25.23928571428564</v>
       </c>
       <c r="S91" t="n">
-        <v>0.2546691760752578</v>
+        <v>0.06375494686076261</v>
       </c>
       <c r="T91" t="n">
-        <v>25.23928571428564</v>
+        <v>24.22814684652792</v>
       </c>
       <c r="U91" t="n">
-        <v>0.06375494686076261</v>
+        <v>2.104521276362434</v>
       </c>
       <c r="V91" t="n">
-        <v>24.22814684652792</v>
+        <v>0.01063212456913026</v>
       </c>
       <c r="W91" t="n">
-        <v>2.104521276362434</v>
+        <v>0.207517619384608</v>
       </c>
       <c r="X91" t="n">
-        <v>0.01063212456913026</v>
+        <v>0.00435</v>
       </c>
       <c r="Y91" t="n">
-        <v>0.207517619384608</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>0.00435</v>
-      </c>
-      <c r="AA91" t="n">
         <v>23.93968006453909</v>
       </c>
     </row>
@@ -8634,33 +8084,27 @@
         <v>0.04872158819598323</v>
       </c>
       <c r="R92" t="n">
-        <v>0.0441207297966015</v>
+        <v>24.77321428571426</v>
       </c>
       <c r="S92" t="n">
-        <v>0.2207296722146418</v>
+        <v>0.1716212668026328</v>
       </c>
       <c r="T92" t="n">
-        <v>24.77321428571426</v>
+        <v>24.54912650345894</v>
       </c>
       <c r="U92" t="n">
-        <v>0.1716212668026328</v>
+        <v>2.111271276362434</v>
       </c>
       <c r="V92" t="n">
-        <v>24.54912650345894</v>
+        <v>0.01118092410442565</v>
       </c>
       <c r="W92" t="n">
-        <v>2.111271276362434</v>
+        <v>0.2204133410545105</v>
       </c>
       <c r="X92" t="n">
-        <v>0.01118092410442565</v>
+        <v>0.00465</v>
       </c>
       <c r="Y92" t="n">
-        <v>0.2204133410545105</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>0.00465</v>
-      </c>
-      <c r="AA92" t="n">
         <v>24.22814684652792</v>
       </c>
     </row>
@@ -8723,33 +8167,27 @@
         <v>0.03284030984725474</v>
       </c>
       <c r="R93" t="n">
-        <v>0.03536550708002241</v>
+        <v>25.0285714285714</v>
       </c>
       <c r="S93" t="n">
-        <v>0.1812189555406794</v>
+        <v>0.2547670720457892</v>
       </c>
       <c r="T93" t="n">
-        <v>25.0285714285714</v>
+        <v>25.00680869176568</v>
       </c>
       <c r="U93" t="n">
-        <v>0.2547670720457892</v>
+        <v>2.120971276362434</v>
       </c>
       <c r="V93" t="n">
-        <v>25.00680869176568</v>
+        <v>0.01186587573608902</v>
       </c>
       <c r="W93" t="n">
-        <v>2.120971276362434</v>
+        <v>0.2371868574664508</v>
       </c>
       <c r="X93" t="n">
-        <v>0.01186587573608902</v>
+        <v>0.005050000000000001</v>
       </c>
       <c r="Y93" t="n">
-        <v>0.2371868574664508</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>0.005050000000000001</v>
-      </c>
-      <c r="AA93" t="n">
         <v>24.54912650345894</v>
       </c>
     </row>
@@ -8812,33 +8250,27 @@
         <v>0.002777158124534164</v>
       </c>
       <c r="R94" t="n">
-        <v>0.01006757845422143</v>
+        <v>26.25714285714279</v>
       </c>
       <c r="S94" t="n">
-        <v>0.05269874879476897</v>
+        <v>0.3345630000595383</v>
       </c>
       <c r="T94" t="n">
-        <v>26.25714285714279</v>
+        <v>26.11045512932166</v>
       </c>
       <c r="U94" t="n">
-        <v>0.3345630000595383</v>
+        <v>2.144732387473546</v>
       </c>
       <c r="V94" t="n">
-        <v>26.11045512932166</v>
+        <v>0.01316721250280378</v>
       </c>
       <c r="W94" t="n">
-        <v>2.144732387473546</v>
+        <v>0.271771078660095</v>
       </c>
       <c r="X94" t="n">
-        <v>0.01316721250280378</v>
+        <v>0.005916666666666667</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.271771078660095</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>0.005916666666666667</v>
-      </c>
-      <c r="AA94" t="n">
         <v>25.00680869176568</v>
       </c>
     </row>
@@ -8895,39 +8327,33 @@
         <v>0.01145255846603085</v>
       </c>
       <c r="P95" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.0001</v>
+        <v>27.40000000000004</v>
       </c>
       <c r="S95" t="n">
-        <v>0.0001</v>
+        <v>0.4114676331552647</v>
       </c>
       <c r="T95" t="n">
-        <v>27.40000000000004</v>
+        <v>26.57397360426178</v>
       </c>
       <c r="U95" t="n">
-        <v>0.4114676331552647</v>
+        <v>2.154871276362434</v>
       </c>
       <c r="V95" t="n">
-        <v>26.57397360426178</v>
+        <v>0.01360205481603644</v>
       </c>
       <c r="W95" t="n">
-        <v>2.154871276362434</v>
+        <v>0.2843853526340677</v>
       </c>
       <c r="X95" t="n">
-        <v>0.01360205481603644</v>
+        <v>0.00625</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.2843853526340677</v>
-      </c>
-      <c r="Z95" t="n">
-        <v>0.00625</v>
-      </c>
-      <c r="AA95" t="n">
         <v>26.11045512932166</v>
       </c>
     </row>
@@ -8990,33 +8416,27 @@
         <v>0.001762949417501451</v>
       </c>
       <c r="R96" t="n">
-        <v>0.007839965084997607</v>
+        <v>28.4607142857143</v>
       </c>
       <c r="S96" t="n">
-        <v>0.04198749120275527</v>
+        <v>0.4067877264015557</v>
       </c>
       <c r="T96" t="n">
-        <v>28.4607142857143</v>
+        <v>27.30784352193885</v>
       </c>
       <c r="U96" t="n">
-        <v>0.4067877264015557</v>
+        <v>2.171121276362435</v>
       </c>
       <c r="V96" t="n">
-        <v>27.30784352193885</v>
+        <v>0.01418840491525607</v>
       </c>
       <c r="W96" t="n">
-        <v>2.171121276362435</v>
+        <v>0.3025548575925655</v>
       </c>
       <c r="X96" t="n">
-        <v>0.01418840491525607</v>
+        <v>0.006750000000000001</v>
       </c>
       <c r="Y96" t="n">
-        <v>0.3025548575925655</v>
-      </c>
-      <c r="Z96" t="n">
-        <v>0.006750000000000001</v>
-      </c>
-      <c r="AA96" t="n">
         <v>26.57397360426178</v>
       </c>
     </row>
@@ -9079,33 +8499,27 @@
         <v>0.001647154283060745</v>
       </c>
       <c r="R97" t="n">
-        <v>0.007564472262002585</v>
+        <v>28.6821428571429</v>
       </c>
       <c r="S97" t="n">
-        <v>0.04058514855289733</v>
+        <v>0.4021708299263646</v>
       </c>
       <c r="T97" t="n">
-        <v>28.6821428571429</v>
+        <v>27.82182651078572</v>
       </c>
       <c r="U97" t="n">
-        <v>0.4021708299263646</v>
+        <v>2.182649054140212</v>
       </c>
       <c r="V97" t="n">
-        <v>27.82182651078572</v>
+        <v>0.01453692586273916</v>
       </c>
       <c r="W97" t="n">
-        <v>2.182649054140212</v>
+        <v>0.3141538806580285</v>
       </c>
       <c r="X97" t="n">
-        <v>0.01453692586273916</v>
+        <v>0.007083333333333334</v>
       </c>
       <c r="Y97" t="n">
-        <v>0.3141538806580285</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>0.007083333333333334</v>
-      </c>
-      <c r="AA97" t="n">
         <v>27.30784352193885</v>
       </c>
     </row>
@@ -9168,33 +8582,27 @@
         <v>0.0005503013934911842</v>
       </c>
       <c r="R98" t="n">
-        <v>0.004370963058975695</v>
+        <v>28.78571428571429</v>
       </c>
       <c r="S98" t="n">
-        <v>0.02345850364987469</v>
+        <v>0.3873938421634567</v>
       </c>
       <c r="T98" t="n">
-        <v>28.78571428571429</v>
+        <v>28.72212537780479</v>
       </c>
       <c r="U98" t="n">
-        <v>0.3873938421634567</v>
+        <v>2.203139026362434</v>
       </c>
       <c r="V98" t="n">
-        <v>28.72212537780479</v>
+        <v>0.01504659517082482</v>
       </c>
       <c r="W98" t="n">
-        <v>2.203139026362434</v>
+        <v>0.3325682000033916</v>
       </c>
       <c r="X98" t="n">
-        <v>0.01504659517082482</v>
+        <v>0.007640000000000001</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.3325682000033916</v>
-      </c>
-      <c r="Z98" t="n">
-        <v>0.007640000000000001</v>
-      </c>
-      <c r="AA98" t="n">
         <v>27.82182651078572</v>
       </c>
     </row>
@@ -9257,33 +8665,27 @@
         <v>0.0004247662125730495</v>
       </c>
       <c r="R99" t="n">
-        <v>0.003775433716909023</v>
+        <v>28.80357142857139</v>
       </c>
       <c r="S99" t="n">
-        <v>0.02060985717012735</v>
+        <v>0.3689307159607038</v>
       </c>
       <c r="T99" t="n">
-        <v>28.80357142857139</v>
+        <v>29.76547634687633</v>
       </c>
       <c r="U99" t="n">
-        <v>0.3689307159607038</v>
+        <v>2.227371276362434</v>
       </c>
       <c r="V99" t="n">
-        <v>29.76547634687633</v>
+        <v>0.01550781476267443</v>
       </c>
       <c r="W99" t="n">
-        <v>2.227371276362434</v>
+        <v>0.3513486174167029</v>
       </c>
       <c r="X99" t="n">
-        <v>0.01550781476267443</v>
+        <v>0.00825</v>
       </c>
       <c r="Y99" t="n">
-        <v>0.3513486174167029</v>
-      </c>
-      <c r="Z99" t="n">
-        <v>0.00825</v>
-      </c>
-      <c r="AA99" t="n">
         <v>28.72212537780479</v>
       </c>
     </row>
@@ -9346,33 +8748,27 @@
         <v>0.008954679612111731</v>
       </c>
       <c r="R100" t="n">
-        <v>0.01696173781741488</v>
+        <v>29.79999999999999</v>
       </c>
       <c r="S100" t="n">
-        <v>0.09462916892856943</v>
+        <v>0.3542503465167628</v>
       </c>
       <c r="T100" t="n">
-        <v>29.79999999999999</v>
+        <v>30.84541902494425</v>
       </c>
       <c r="U100" t="n">
-        <v>0.3542503465167628</v>
+        <v>2.253021276362434</v>
       </c>
       <c r="V100" t="n">
-        <v>30.84541902494425</v>
+        <v>0.01587053886464064</v>
       </c>
       <c r="W100" t="n">
-        <v>2.253021276362434</v>
+        <v>0.3683708024918843</v>
       </c>
       <c r="X100" t="n">
-        <v>0.01587053886464064</v>
+        <v>0.00885</v>
       </c>
       <c r="Y100" t="n">
-        <v>0.3683708024918843</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>0.00885</v>
-      </c>
-      <c r="AA100" t="n">
         <v>29.76547634687633</v>
       </c>
     </row>
@@ -9435,33 +8831,27 @@
         <v>0.02192219084074996</v>
       </c>
       <c r="R101" t="n">
-        <v>0.02664331523520602</v>
+        <v>31.12500000000002</v>
       </c>
       <c r="S101" t="n">
-        <v>0.148061442788965</v>
+        <v>0.363160750555521</v>
       </c>
       <c r="T101" t="n">
-        <v>31.12500000000002</v>
+        <v>31.8146960202547</v>
       </c>
       <c r="U101" t="n">
-        <v>0.363160750555521</v>
+        <v>2.276551137473545</v>
       </c>
       <c r="V101" t="n">
-        <v>31.8146960202547</v>
+        <v>0.01611696618632926</v>
       </c>
       <c r="W101" t="n">
-        <v>2.276551137473545</v>
+        <v>0.3818576499658321</v>
       </c>
       <c r="X101" t="n">
-        <v>0.01611696618632926</v>
+        <v>0.009366666666666667</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.3818576499658321</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>0.009366666666666667</v>
-      </c>
-      <c r="AA101" t="n">
         <v>30.84541902494425</v>
       </c>
     </row>
@@ -9518,39 +8908,33 @@
         <v>0.2993817189618296</v>
       </c>
       <c r="P102" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>0.0001</v>
+        <v>0.1803571428572935</v>
       </c>
       <c r="S102" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
         <v>0.1803571428572935</v>
       </c>
       <c r="U102" t="n">
-        <v>0</v>
+        <v>1.7528</v>
       </c>
       <c r="V102" t="n">
-        <v>0.1803571428572935</v>
+        <v>0.869786886974646</v>
       </c>
       <c r="W102" t="n">
-        <v>1.7528</v>
+        <v>0.1568722778294868</v>
       </c>
       <c r="X102" t="n">
-        <v>0.869786886974646</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0.1568722778294868</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA102" t="n">
         <v>0.1803571428572935</v>
       </c>
     </row>
@@ -9607,39 +8991,33 @@
         <v>1.543307739364463</v>
       </c>
       <c r="P103" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0.0001</v>
+        <v>0.1803571428572935</v>
       </c>
       <c r="S103" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>0.1803571428572935</v>
+        <v>0.3616834182881157</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>1.7528</v>
       </c>
       <c r="V103" t="n">
-        <v>0.3616834182881157</v>
+        <v>0.8697861867754395</v>
       </c>
       <c r="W103" t="n">
-        <v>1.7528</v>
+        <v>0.3145872412127264</v>
       </c>
       <c r="X103" t="n">
-        <v>0.8697861867754395</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.3145872412127264</v>
-      </c>
-      <c r="Z103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA103" t="n">
         <v>0.1803571428572935</v>
       </c>
     </row>
@@ -9696,39 +9074,33 @@
         <v>1.03160607166846</v>
       </c>
       <c r="P104" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>0.0001</v>
+        <v>0.3392857142857694</v>
       </c>
       <c r="S104" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>0.3392857142857694</v>
+        <v>0.9014852876337008</v>
       </c>
       <c r="U104" t="n">
-        <v>0</v>
+        <v>1.7528</v>
       </c>
       <c r="V104" t="n">
-        <v>0.9014852876337008</v>
+        <v>0.8697835759873167</v>
       </c>
       <c r="W104" t="n">
-        <v>1.7528</v>
+        <v>0.7840970971779951</v>
       </c>
       <c r="X104" t="n">
-        <v>0.8697835759873167</v>
+        <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0.7840970971779951</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA104" t="n">
         <v>0.3616834182881157</v>
       </c>
     </row>
@@ -9785,39 +9157,33 @@
         <v>0.779274995510789</v>
       </c>
       <c r="P105" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>0.0001</v>
+        <v>0.8962500000000428</v>
       </c>
       <c r="S105" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>0.8962500000000428</v>
+        <v>2.523192557199961</v>
       </c>
       <c r="U105" t="n">
-        <v>0</v>
+        <v>1.7528</v>
       </c>
       <c r="V105" t="n">
-        <v>2.523192557199961</v>
+        <v>0.869761996832446</v>
       </c>
       <c r="W105" t="n">
-        <v>1.7528</v>
+        <v>2.194576996943004</v>
       </c>
       <c r="X105" t="n">
-        <v>0.869761996832446</v>
+        <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.194576996943004</v>
-      </c>
-      <c r="Z105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA105" t="n">
         <v>0.9014852876337008</v>
       </c>
     </row>
@@ -9874,39 +9240,33 @@
         <v>0.4089904904144481</v>
       </c>
       <c r="P106" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0.0001</v>
+        <v>2.504651162790685</v>
       </c>
       <c r="S106" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>2.504651162790685</v>
+        <v>4.83708747819038</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>1.768600015800672</v>
       </c>
       <c r="V106" t="n">
-        <v>4.83708747819038</v>
+        <v>0.6045883159844235</v>
       </c>
       <c r="W106" t="n">
-        <v>1.768600015800672</v>
+        <v>2.697443147907494</v>
       </c>
       <c r="X106" t="n">
-        <v>0.6045883159844235</v>
+        <v>0.08300000000000002</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.697443147907494</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>0.08300000000000002</v>
-      </c>
-      <c r="AA106" t="n">
         <v>2.523192557199961</v>
       </c>
     </row>
@@ -9963,39 +9323,33 @@
         <v>0.4130305359490459</v>
       </c>
       <c r="P107" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>0.0001</v>
+        <v>5.678571428571439</v>
       </c>
       <c r="S107" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>5.678571428571439</v>
+        <v>7.795781230965148</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>1.81338894947845</v>
       </c>
       <c r="V107" t="n">
-        <v>7.795781230965148</v>
+        <v>0.4510700491596409</v>
       </c>
       <c r="W107" t="n">
-        <v>1.81338894947845</v>
+        <v>3.076511173843142</v>
       </c>
       <c r="X107" t="n">
-        <v>0.4510700491596409</v>
+        <v>0.1023333333333333</v>
       </c>
       <c r="Y107" t="n">
-        <v>3.076511173843142</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>0.1023333333333333</v>
-      </c>
-      <c r="AA107" t="n">
         <v>4.83708747819038</v>
       </c>
     </row>
@@ -10052,39 +9406,33 @@
         <v>0.4207785721774875</v>
       </c>
       <c r="P108" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>0.0001</v>
+        <v>7.142857142857149</v>
       </c>
       <c r="S108" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>7.142857142857149</v>
+        <v>10.81459997635064</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
+        <v>1.86148899757845</v>
       </c>
       <c r="V108" t="n">
-        <v>10.81459997635064</v>
+        <v>0.370405582414445</v>
       </c>
       <c r="W108" t="n">
-        <v>1.86148899757845</v>
+        <v>3.310566725718646</v>
       </c>
       <c r="X108" t="n">
-        <v>0.370405582414445</v>
+        <v>0.1196666666666667</v>
       </c>
       <c r="Y108" t="n">
-        <v>3.310566725718646</v>
-      </c>
-      <c r="Z108" t="n">
-        <v>0.1196666666666667</v>
-      </c>
-      <c r="AA108" t="n">
         <v>7.795781230965148</v>
       </c>
     </row>
@@ -10141,39 +9489,33 @@
         <v>0.3884586048784459</v>
       </c>
       <c r="P109" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>0.0001</v>
+        <v>10.17142857142859</v>
       </c>
       <c r="S109" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>10.17142857142859</v>
+        <v>14.97827935787934</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
+        <v>1.93217656826595</v>
       </c>
       <c r="V109" t="n">
-        <v>14.97827935787934</v>
+        <v>0.3043058654900936</v>
       </c>
       <c r="W109" t="n">
-        <v>1.93217656826595</v>
+        <v>3.462358854841829</v>
       </c>
       <c r="X109" t="n">
-        <v>0.3043058654900936</v>
+        <v>0.1413333333333333</v>
       </c>
       <c r="Y109" t="n">
-        <v>3.462358854841829</v>
-      </c>
-      <c r="Z109" t="n">
-        <v>0.1413333333333333</v>
-      </c>
-      <c r="AA109" t="n">
         <v>10.81459997635064</v>
       </c>
     </row>
@@ -10230,39 +9572,33 @@
         <v>0.3668120739327594</v>
       </c>
       <c r="P110" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0.0001</v>
+        <v>14.40357142857142</v>
       </c>
       <c r="S110" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>14.40357142857142</v>
+        <v>17.91702948287882</v>
       </c>
       <c r="U110" t="n">
-        <v>0</v>
+        <v>1.985389121478449</v>
       </c>
       <c r="V110" t="n">
-        <v>17.91702948287882</v>
+        <v>0.2726830991592711</v>
       </c>
       <c r="W110" t="n">
-        <v>1.985389121478449</v>
+        <v>3.480866282570264</v>
       </c>
       <c r="X110" t="n">
-        <v>0.2726830991592711</v>
+        <v>0.1556666666666667</v>
       </c>
       <c r="Y110" t="n">
-        <v>3.480866282570264</v>
-      </c>
-      <c r="Z110" t="n">
-        <v>0.1556666666666667</v>
-      </c>
-      <c r="AA110" t="n">
         <v>14.97827935787934</v>
       </c>
     </row>
@@ -10319,39 +9655,33 @@
         <v>0.280189813438795</v>
       </c>
       <c r="P111" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>0.0001</v>
+        <v>17.9821428571429</v>
       </c>
       <c r="S111" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>17.9821428571429</v>
+        <v>20.53315308215597</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>2.035287782488171</v>
       </c>
       <c r="V111" t="n">
-        <v>20.53315308215597</v>
+        <v>0.2504966606507561</v>
       </c>
       <c r="W111" t="n">
-        <v>2.035287782488171</v>
+        <v>3.448605709266384</v>
       </c>
       <c r="X111" t="n">
-        <v>0.2504966606507561</v>
+        <v>0.168</v>
       </c>
       <c r="Y111" t="n">
-        <v>3.448605709266384</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="AA111" t="n">
         <v>17.91702948287882</v>
       </c>
     </row>
@@ -10408,39 +9738,33 @@
         <v>0.1463215789183206</v>
       </c>
       <c r="P112" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>0.0001</v>
+        <v>22.1892857142858</v>
       </c>
       <c r="S112" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>22.1892857142858</v>
+        <v>24.01327122841171</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
+        <v>2.105687852888171</v>
       </c>
       <c r="V112" t="n">
-        <v>24.01327122841171</v>
+        <v>0.226749609860789</v>
       </c>
       <c r="W112" t="n">
-        <v>2.105687852888171</v>
+        <v>3.346663274860094</v>
       </c>
       <c r="X112" t="n">
-        <v>0.226749609860789</v>
+        <v>0.184</v>
       </c>
       <c r="Y112" t="n">
-        <v>3.346663274860094</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="AA112" t="n">
         <v>20.53315308215597</v>
       </c>
     </row>
@@ -10503,33 +9827,27 @@
         <v>0.04292053230848831</v>
       </c>
       <c r="R113" t="n">
-        <v>0.03929002064237096</v>
+        <v>25.66428571428573</v>
       </c>
       <c r="S113" t="n">
-        <v>0.2071727113026431</v>
+        <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>25.66428571428573</v>
+        <v>28.24180554491312</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>2.198068908667902</v>
       </c>
       <c r="V113" t="n">
-        <v>28.24180554491312</v>
+        <v>0.007068164159168635</v>
       </c>
       <c r="W113" t="n">
-        <v>2.198068908667902</v>
+        <v>0.1089932301946586</v>
       </c>
       <c r="X113" t="n">
-        <v>0.007068164159168635</v>
+        <v>0.007053333333333333</v>
       </c>
       <c r="Y113" t="n">
-        <v>0.1089932301946586</v>
-      </c>
-      <c r="Z113" t="n">
-        <v>0.007053333333333333</v>
-      </c>
-      <c r="AA113" t="n">
         <v>24.01327122841171</v>
       </c>
     </row>
@@ -10592,33 +9910,27 @@
         <v>0.03670292593065684</v>
       </c>
       <c r="R114" t="n">
-        <v>0.03606976413308337</v>
+        <v>27.80357142857142</v>
       </c>
       <c r="S114" t="n">
-        <v>0.1915800770713303</v>
+        <v>0.05060060245371522</v>
       </c>
       <c r="T114" t="n">
-        <v>27.80357142857142</v>
+        <v>28.47191433675219</v>
       </c>
       <c r="U114" t="n">
-        <v>0.05060060245371522</v>
+        <v>2.203329247622887</v>
       </c>
       <c r="V114" t="n">
-        <v>28.47191433675219</v>
+        <v>0.007575498547917375</v>
       </c>
       <c r="W114" t="n">
-        <v>2.203329247622887</v>
+        <v>0.1171354497979989</v>
       </c>
       <c r="X114" t="n">
-        <v>0.007575498547917375</v>
+        <v>0.007626666666666667</v>
       </c>
       <c r="Y114" t="n">
-        <v>0.1171354497979989</v>
-      </c>
-      <c r="Z114" t="n">
-        <v>0.007626666666666667</v>
-      </c>
-      <c r="AA114" t="n">
         <v>28.24180554491312</v>
       </c>
     </row>
@@ -10681,33 +9993,27 @@
         <v>0.03226430616673658</v>
       </c>
       <c r="R115" t="n">
-        <v>0.03344169305227099</v>
+        <v>28.21071428571433</v>
       </c>
       <c r="S115" t="n">
-        <v>0.1796226772062386</v>
+        <v>0.1044036282464569</v>
       </c>
       <c r="T115" t="n">
-        <v>28.21071428571433</v>
+        <v>28.65988059431129</v>
       </c>
       <c r="U115" t="n">
-        <v>0.1044036282464569</v>
+        <v>2.20764491860522</v>
       </c>
       <c r="V115" t="n">
-        <v>28.65988059431129</v>
+        <v>0.007944458816790421</v>
       </c>
       <c r="W115" t="n">
-        <v>2.20764491860522</v>
+        <v>0.1229649184265571</v>
       </c>
       <c r="X115" t="n">
-        <v>0.007944458816790421</v>
+        <v>0.008066666666666666</v>
       </c>
       <c r="Y115" t="n">
-        <v>0.1229649184265571</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>0.008066666666666666</v>
-      </c>
-      <c r="AA115" t="n">
         <v>28.47191433675219</v>
       </c>
     </row>
@@ -10770,33 +10076,27 @@
         <v>0.02491516024776152</v>
       </c>
       <c r="R116" t="n">
-        <v>0.02890464370079389</v>
+        <v>28.84999999999995</v>
       </c>
       <c r="S116" t="n">
-        <v>0.1578453681542842</v>
+        <v>0.1491197853115378</v>
       </c>
       <c r="T116" t="n">
-        <v>28.84999999999995</v>
+        <v>28.92563808749308</v>
       </c>
       <c r="U116" t="n">
-        <v>0.1491197853115378</v>
+        <v>2.213775591402554</v>
       </c>
       <c r="V116" t="n">
-        <v>28.92563808749308</v>
+        <v>0.008420554709994834</v>
       </c>
       <c r="W116" t="n">
-        <v>2.213775591402554</v>
+        <v>0.1305037205317169</v>
       </c>
       <c r="X116" t="n">
-        <v>0.008420554709994834</v>
+        <v>0.008653333333333332</v>
       </c>
       <c r="Y116" t="n">
-        <v>0.1305037205317169</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>0.008653333333333332</v>
-      </c>
-      <c r="AA116" t="n">
         <v>28.65988059431129</v>
       </c>
     </row>
@@ -10859,33 +10159,27 @@
         <v>0.01583178431944987</v>
       </c>
       <c r="R117" t="n">
-        <v>0.02290151451210537</v>
+        <v>29.8214285714287</v>
       </c>
       <c r="S117" t="n">
-        <v>0.1258244186135977</v>
+        <v>0.1918414613393818</v>
       </c>
       <c r="T117" t="n">
-        <v>29.8214285714287</v>
+        <v>29.46262840771122</v>
       </c>
       <c r="U117" t="n">
-        <v>0.1918414613393818</v>
+        <v>2.226267742783581</v>
       </c>
       <c r="V117" t="n">
-        <v>29.46262840771122</v>
+        <v>0.009253028396770656</v>
       </c>
       <c r="W117" t="n">
-        <v>2.226267742783581</v>
+        <v>0.1437184974817057</v>
       </c>
       <c r="X117" t="n">
-        <v>0.009253028396770656</v>
+        <v>0.009740000000000002</v>
       </c>
       <c r="Y117" t="n">
-        <v>0.1437184974817057</v>
-      </c>
-      <c r="Z117" t="n">
-        <v>0.009740000000000002</v>
-      </c>
-      <c r="AA117" t="n">
         <v>28.92563808749308</v>
       </c>
     </row>
@@ -10948,33 +10242,27 @@
         <v>0.003813578138281135</v>
       </c>
       <c r="R118" t="n">
-        <v>0.01083418489561089</v>
+        <v>30.18571428571434</v>
       </c>
       <c r="S118" t="n">
-        <v>0.0617541750676109</v>
+        <v>0.2448076315621145</v>
       </c>
       <c r="T118" t="n">
-        <v>30.18571428571434</v>
+        <v>30.73245500743434</v>
       </c>
       <c r="U118" t="n">
-        <v>0.2448076315621145</v>
+        <v>2.256376522892332</v>
       </c>
       <c r="V118" t="n">
-        <v>30.73245500743434</v>
+        <v>0.01074724495172402</v>
       </c>
       <c r="W118" t="n">
-        <v>2.256376522892332</v>
+        <v>0.1673908057509535</v>
       </c>
       <c r="X118" t="n">
-        <v>0.01074724495172402</v>
+        <v>0.01196</v>
       </c>
       <c r="Y118" t="n">
-        <v>0.1673908057509535</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>0.01196</v>
-      </c>
-      <c r="AA118" t="n">
         <v>29.46262840771122</v>
       </c>
     </row>
@@ -11037,33 +10325,27 @@
         <v>0.002635143243149769</v>
       </c>
       <c r="R119" t="n">
-        <v>0.008945242501938901</v>
+        <v>32.48928571428564</v>
       </c>
       <c r="S119" t="n">
-        <v>0.05133364630678176</v>
+        <v>0.2862295508009267</v>
       </c>
       <c r="T119" t="n">
-        <v>32.48928571428564</v>
+        <v>31.15248101756942</v>
       </c>
       <c r="U119" t="n">
-        <v>0.2862295508009267</v>
+        <v>2.266515783031581</v>
       </c>
       <c r="V119" t="n">
-        <v>31.15248101756942</v>
+        <v>0.0111372695428132</v>
       </c>
       <c r="W119" t="n">
-        <v>2.266515783031581</v>
+        <v>0.1734960122774931</v>
       </c>
       <c r="X119" t="n">
-        <v>0.0111372695428132</v>
+        <v>0.01262</v>
       </c>
       <c r="Y119" t="n">
-        <v>0.1734960122774931</v>
-      </c>
-      <c r="Z119" t="n">
-        <v>0.01262</v>
-      </c>
-      <c r="AA119" t="n">
         <v>30.73245500743434</v>
       </c>
     </row>
@@ -11126,33 +10408,27 @@
         <v>0.003468413842637606</v>
       </c>
       <c r="R120" t="n">
-        <v>0.01023902645998351</v>
+        <v>32.9321428571429</v>
       </c>
       <c r="S120" t="n">
-        <v>0.05889324106073299</v>
+        <v>0.2889524121591054</v>
       </c>
       <c r="T120" t="n">
-        <v>32.9321428571429</v>
+        <v>31.55039956771036</v>
       </c>
       <c r="U120" t="n">
-        <v>0.2889524121591054</v>
+        <v>2.276205792721581</v>
       </c>
       <c r="V120" t="n">
-        <v>31.55039956771036</v>
+        <v>0.01147072886081365</v>
       </c>
       <c r="W120" t="n">
-        <v>2.276205792721581</v>
+        <v>0.1786641753611795</v>
       </c>
       <c r="X120" t="n">
-        <v>0.01147072886081365</v>
+        <v>0.01322</v>
       </c>
       <c r="Y120" t="n">
-        <v>0.1786641753611795</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>0.01322</v>
-      </c>
-      <c r="AA120" t="n">
         <v>31.15248101756942</v>
       </c>
     </row>
@@ -11215,33 +10491,27 @@
         <v>0.004427144891717553</v>
       </c>
       <c r="R121" t="n">
-        <v>0.01153270065092904</v>
+        <v>33.08366238246173</v>
       </c>
       <c r="S121" t="n">
-        <v>0.06653679351845529</v>
+        <v>0.2916972101212668</v>
       </c>
       <c r="T121" t="n">
-        <v>33.08366238246173</v>
+        <v>31.95385437249574</v>
       </c>
       <c r="U121" t="n">
-        <v>0.2916972101212668</v>
+        <v>2.286115580409136</v>
       </c>
       <c r="V121" t="n">
-        <v>31.95385437249574</v>
+        <v>0.01177719446570448</v>
       </c>
       <c r="W121" t="n">
-        <v>2.286115580409136</v>
+        <v>0.1833460432925698</v>
       </c>
       <c r="X121" t="n">
-        <v>0.01177719446570448</v>
+        <v>0.01380666666666667</v>
       </c>
       <c r="Y121" t="n">
-        <v>0.1833460432925698</v>
-      </c>
-      <c r="Z121" t="n">
-        <v>0.01380666666666667</v>
-      </c>
-      <c r="AA121" t="n">
         <v>31.55039956771036</v>
       </c>
     </row>
@@ -11304,33 +10574,27 @@
         <v>0.006989072490978496</v>
       </c>
       <c r="R122" t="n">
-        <v>0.01414625769441237</v>
+        <v>33.286006759061</v>
       </c>
       <c r="S122" t="n">
-        <v>0.08360067279022637</v>
+        <v>0.2947411967231239</v>
       </c>
       <c r="T122" t="n">
-        <v>33.286006759061</v>
+        <v>32.83159423889894</v>
       </c>
       <c r="U122" t="n">
-        <v>0.2947411967231239</v>
+        <v>2.307975824491581</v>
       </c>
       <c r="V122" t="n">
-        <v>32.83159423889894</v>
+        <v>0.01235149451992449</v>
       </c>
       <c r="W122" t="n">
-        <v>2.307975824491581</v>
+        <v>0.1918556034210608</v>
       </c>
       <c r="X122" t="n">
-        <v>0.01235149451992449</v>
+        <v>0.01502</v>
       </c>
       <c r="Y122" t="n">
-        <v>0.1918556034210608</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>0.01502</v>
-      </c>
-      <c r="AA122" t="n">
         <v>31.95385437249574</v>
       </c>
     </row>
@@ -11393,33 +10657,27 @@
         <v>0.01216839656025612</v>
       </c>
       <c r="R123" t="n">
-        <v>0.01855989829652208</v>
+        <v>34.92500000000002</v>
       </c>
       <c r="S123" t="n">
-        <v>0.1103104553533169</v>
+        <v>0.3061500936386944</v>
       </c>
       <c r="T123" t="n">
-        <v>34.92500000000002</v>
+        <v>33.75408893078473</v>
       </c>
       <c r="U123" t="n">
-        <v>0.3061500936386944</v>
+        <v>2.331405847921581</v>
       </c>
       <c r="V123" t="n">
-        <v>33.75408893078473</v>
+        <v>0.01284345245977919</v>
       </c>
       <c r="W123" t="n">
-        <v>2.331405847921581</v>
+        <v>0.1986859108423037</v>
       </c>
       <c r="X123" t="n">
-        <v>0.01284345245977919</v>
+        <v>0.01622</v>
       </c>
       <c r="Y123" t="n">
-        <v>0.1986859108423037</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>0.01622</v>
-      </c>
-      <c r="AA123" t="n">
         <v>32.83159423889894</v>
       </c>
     </row>
@@ -11482,33 +10740,27 @@
         <v>0.01961652719811411</v>
       </c>
       <c r="R124" t="n">
-        <v>0.02311497993131076</v>
+        <v>35.32500000000002</v>
       </c>
       <c r="S124" t="n">
-        <v>0.1400590132698146</v>
+        <v>0.3308651428571041</v>
       </c>
       <c r="T124" t="n">
-        <v>35.32500000000002</v>
+        <v>34.6164789037036</v>
       </c>
       <c r="U124" t="n">
-        <v>0.3308651428571041</v>
+        <v>2.353743648037137</v>
       </c>
       <c r="V124" t="n">
-        <v>34.6164789037036</v>
+        <v>0.01322031243075041</v>
       </c>
       <c r="W124" t="n">
-        <v>2.353743648037137</v>
+        <v>0.2034058721493541</v>
       </c>
       <c r="X124" t="n">
-        <v>0.01322031243075041</v>
+        <v>0.01728666666666667</v>
       </c>
       <c r="Y124" t="n">
-        <v>0.2034058721493541</v>
-      </c>
-      <c r="Z124" t="n">
-        <v>0.01728666666666667</v>
-      </c>
-      <c r="AA124" t="n">
         <v>33.75408893078473</v>
       </c>
     </row>
@@ -11571,33 +10823,27 @@
         <v>0.02963924799363945</v>
       </c>
       <c r="R125" t="n">
-        <v>0.0284767157115998</v>
+        <v>36.71428571428564</v>
       </c>
       <c r="S125" t="n">
-        <v>0.1721605297204892</v>
+        <v>0.3724108962071924</v>
       </c>
       <c r="T125" t="n">
-        <v>36.71428571428564</v>
+        <v>35.52745806381636</v>
       </c>
       <c r="U125" t="n">
-        <v>0.3724108962071924</v>
+        <v>2.377809672103136</v>
       </c>
       <c r="V125" t="n">
-        <v>35.52745806381636</v>
+        <v>0.01354761894834775</v>
       </c>
       <c r="W125" t="n">
-        <v>2.377809672103136</v>
+        <v>0.2068914338797341</v>
       </c>
       <c r="X125" t="n">
-        <v>0.01354761894834775</v>
+        <v>0.01836666666666667</v>
       </c>
       <c r="Y125" t="n">
-        <v>0.2068914338797341</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>0.01836666666666667</v>
-      </c>
-      <c r="AA125" t="n">
         <v>34.6164789037036</v>
       </c>
     </row>
@@ -11654,39 +10900,33 @@
         <v>0.4637116778292156</v>
       </c>
       <c r="P126" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>0.0001</v>
+        <v>0.2740000000001075</v>
       </c>
       <c r="S126" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T126" t="n">
         <v>0.2740000000001075</v>
       </c>
       <c r="U126" t="n">
-        <v>0</v>
+        <v>1.7518</v>
       </c>
       <c r="V126" t="n">
-        <v>0.2740000000001075</v>
+        <v>0.8697868789829178</v>
       </c>
       <c r="W126" t="n">
-        <v>1.7518</v>
+        <v>0.238321604841413</v>
       </c>
       <c r="X126" t="n">
-        <v>0.8697868789829178</v>
+        <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0.238321604841413</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA126" t="n">
         <v>0.2740000000001075</v>
       </c>
     </row>
@@ -11743,39 +10983,33 @@
         <v>0.7453679311071638</v>
       </c>
       <c r="P127" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0.0001</v>
+        <v>0.2740000000001075</v>
       </c>
       <c r="S127" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>0.2740000000001075</v>
+        <v>0.7342772800806657</v>
       </c>
       <c r="U127" t="n">
-        <v>0</v>
+        <v>1.7518</v>
       </c>
       <c r="V127" t="n">
-        <v>0.7342772800806657</v>
+        <v>0.8697849399952444</v>
       </c>
       <c r="W127" t="n">
-        <v>1.7518</v>
+        <v>0.6386633199948332</v>
       </c>
       <c r="X127" t="n">
-        <v>0.8697849399952444</v>
+        <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0.6386633199948332</v>
-      </c>
-      <c r="Z127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA127" t="n">
         <v>0.2740000000001075</v>
       </c>
     </row>
@@ -11832,39 +11066,33 @@
         <v>0.8971601367795489</v>
       </c>
       <c r="P128" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>0.0001</v>
+        <v>0.6966666666666418</v>
       </c>
       <c r="S128" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>0.6966666666666418</v>
+        <v>1.493995772743973</v>
       </c>
       <c r="U128" t="n">
-        <v>0</v>
+        <v>1.7518</v>
       </c>
       <c r="V128" t="n">
-        <v>1.493995772743973</v>
+        <v>0.8697800815657671</v>
       </c>
       <c r="W128" t="n">
-        <v>1.7518</v>
+        <v>1.299447765076164</v>
       </c>
       <c r="X128" t="n">
-        <v>0.8697800815657671</v>
+        <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.299447765076164</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA128" t="n">
         <v>0.7342772800806657</v>
       </c>
     </row>
@@ -11921,39 +11149,33 @@
         <v>0.6919878856836935</v>
       </c>
       <c r="P129" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>0.0001</v>
+        <v>1.346000000000203</v>
       </c>
       <c r="S129" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>1.346000000000203</v>
+        <v>3.565172253956069</v>
       </c>
       <c r="U129" t="n">
-        <v>0</v>
+        <v>1.7518</v>
       </c>
       <c r="V129" t="n">
-        <v>3.565172253956069</v>
+        <v>0.869634703573162</v>
       </c>
       <c r="W129" t="n">
-        <v>1.7518</v>
+        <v>3.100397516256348</v>
       </c>
       <c r="X129" t="n">
-        <v>0.869634703573162</v>
+        <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>3.100397516256348</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" t="n">
         <v>1.493995772743973</v>
       </c>
     </row>
@@ -12010,39 +11232,33 @@
         <v>0.5026713404005696</v>
       </c>
       <c r="P130" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>0.0001</v>
+        <v>3.026136363636255</v>
       </c>
       <c r="S130" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>3.026136363636255</v>
+        <v>5.404249753891331</v>
       </c>
       <c r="U130" t="n">
-        <v>0</v>
+        <v>1.774655578417778</v>
       </c>
       <c r="V130" t="n">
-        <v>5.404249753891331</v>
+        <v>0.5609389079826891</v>
       </c>
       <c r="W130" t="n">
-        <v>1.774655578417778</v>
+        <v>2.768548352155416</v>
       </c>
       <c r="X130" t="n">
-        <v>0.5609389079826891</v>
+        <v>0.08633333333333333</v>
       </c>
       <c r="Y130" t="n">
-        <v>2.768548352155416</v>
-      </c>
-      <c r="Z130" t="n">
-        <v>0.08633333333333333</v>
-      </c>
-      <c r="AA130" t="n">
         <v>3.565172253956069</v>
       </c>
     </row>
@@ -12099,39 +11315,33 @@
         <v>0.4114966666264407</v>
       </c>
       <c r="P131" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>0.0001</v>
+        <v>5.885714285714225</v>
       </c>
       <c r="S131" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>5.885714285714225</v>
+        <v>8.441995340492889</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>1.821055624817778</v>
       </c>
       <c r="V131" t="n">
-        <v>8.441995340492889</v>
+        <v>0.4282982829519956</v>
       </c>
       <c r="W131" t="n">
-        <v>1.821055624817778</v>
+        <v>3.125845727896247</v>
       </c>
       <c r="X131" t="n">
-        <v>0.4282982829519956</v>
+        <v>0.1056666666666667</v>
       </c>
       <c r="Y131" t="n">
-        <v>3.125845727896247</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>0.1056666666666667</v>
-      </c>
-      <c r="AA131" t="n">
         <v>5.404249753891331</v>
       </c>
     </row>
@@ -12188,39 +11398,33 @@
         <v>0.3503266780181019</v>
       </c>
       <c r="P132" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>0.0001</v>
+        <v>8.642857142857142</v>
       </c>
       <c r="S132" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>8.642857142857142</v>
+        <v>12.01818119746831</v>
       </c>
       <c r="U132" t="n">
-        <v>0</v>
+        <v>1.878889015984444</v>
       </c>
       <c r="V132" t="n">
-        <v>12.01818119746831</v>
+        <v>0.3467808659520568</v>
       </c>
       <c r="W132" t="n">
-        <v>1.878889015984444</v>
+        <v>3.36385730441866</v>
       </c>
       <c r="X132" t="n">
-        <v>0.3467808659520568</v>
+        <v>0.1256666666666666</v>
       </c>
       <c r="Y132" t="n">
-        <v>3.36385730441866</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>0.1256666666666666</v>
-      </c>
-      <c r="AA132" t="n">
         <v>8.441995340492889</v>
       </c>
     </row>
@@ -12277,39 +11481,33 @@
         <v>0.2789527328089635</v>
       </c>
       <c r="P133" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>0.0001</v>
+        <v>12.06428571428577</v>
       </c>
       <c r="S133" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>12.06428571428577</v>
+        <v>15.40208363873504</v>
       </c>
       <c r="U133" t="n">
-        <v>0</v>
+        <v>1.937100185306666</v>
       </c>
       <c r="V133" t="n">
-        <v>15.40208363873504</v>
+        <v>0.2986612576470496</v>
       </c>
       <c r="W133" t="n">
-        <v>1.937100185306666</v>
+        <v>3.462997900767509</v>
       </c>
       <c r="X133" t="n">
-        <v>0.2986612576470496</v>
+        <v>0.143</v>
       </c>
       <c r="Y133" t="n">
-        <v>3.462997900767509</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AA133" t="n">
         <v>12.01818119746831</v>
       </c>
     </row>
@@ -12366,39 +11564,33 @@
         <v>0.2084246345121031</v>
       </c>
       <c r="P134" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>0.0001</v>
+        <v>15.77142857142857</v>
       </c>
       <c r="S134" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>15.77142857142857</v>
+        <v>19.69349055328924</v>
       </c>
       <c r="U134" t="n">
-        <v>0</v>
+        <v>2.016322486751111</v>
       </c>
       <c r="V134" t="n">
-        <v>19.69349055328924</v>
+        <v>0.2568335205710925</v>
       </c>
       <c r="W134" t="n">
-        <v>2.016322486751111</v>
+        <v>3.4594105912003</v>
       </c>
       <c r="X134" t="n">
-        <v>0.2568335205710925</v>
+        <v>0.1636666666666667</v>
       </c>
       <c r="Y134" t="n">
-        <v>3.4594105912003</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>0.1636666666666667</v>
-      </c>
-      <c r="AA134" t="n">
         <v>15.40208363873504</v>
       </c>
     </row>
@@ -12455,39 +11647,33 @@
         <v>0.1351840441944742</v>
       </c>
       <c r="P135" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>0.0001</v>
+        <v>19.10357142857136</v>
       </c>
       <c r="S135" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>19.10357142857136</v>
+        <v>22.34964323037847</v>
       </c>
       <c r="U135" t="n">
-        <v>0</v>
+        <v>2.068687816894167</v>
       </c>
       <c r="V135" t="n">
-        <v>22.34964323037847</v>
+        <v>0.2372035556176595</v>
       </c>
       <c r="W135" t="n">
-        <v>2.068687816894167</v>
+        <v>3.399949972131483</v>
       </c>
       <c r="X135" t="n">
-        <v>0.2372035556176595</v>
+        <v>0.176</v>
       </c>
       <c r="Y135" t="n">
-        <v>3.399949972131483</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="AA135" t="n">
         <v>19.69349055328924</v>
       </c>
     </row>
@@ -12544,39 +11730,33 @@
         <v>0.06997246239386802</v>
       </c>
       <c r="P136" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>0.0001</v>
+        <v>21.08928571428573</v>
       </c>
       <c r="S136" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>21.08928571428573</v>
+        <v>25.42114792085842</v>
       </c>
       <c r="U136" t="n">
-        <v>0</v>
+        <v>2.132737880944166</v>
       </c>
       <c r="V136" t="n">
-        <v>25.42114792085842</v>
+        <v>0.2183710079200064</v>
       </c>
       <c r="W136" t="n">
-        <v>2.132737880944166</v>
+        <v>3.28653858716199</v>
       </c>
       <c r="X136" t="n">
-        <v>0.2183710079200064</v>
+        <v>0.19</v>
       </c>
       <c r="Y136" t="n">
-        <v>3.28653858716199</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AA136" t="n">
         <v>22.34964323037847</v>
       </c>
     </row>
@@ -12633,39 +11813,33 @@
         <v>0.04417757490269928</v>
       </c>
       <c r="P137" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>0.0001</v>
+        <v>21.79285714285717</v>
       </c>
       <c r="S137" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>21.79285714285717</v>
+        <v>28.31816032897402</v>
       </c>
       <c r="U137" t="n">
-        <v>0</v>
+        <v>2.196892860793617</v>
       </c>
       <c r="V137" t="n">
-        <v>28.31816032897402</v>
+        <v>0.01041304424064643</v>
       </c>
       <c r="W137" t="n">
-        <v>2.196892860793617</v>
+        <v>0.2042179130067702</v>
       </c>
       <c r="X137" t="n">
-        <v>0.01041304424064643</v>
+        <v>0.007033333333333333</v>
       </c>
       <c r="Y137" t="n">
-        <v>0.2042179130067702</v>
-      </c>
-      <c r="Z137" t="n">
-        <v>0.007033333333333333</v>
-      </c>
-      <c r="AA137" t="n">
         <v>25.42114792085842</v>
       </c>
     </row>
@@ -12722,39 +11896,33 @@
         <v>0.02615548495855645</v>
       </c>
       <c r="P138" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>0.0001</v>
+        <v>22.74159954433088</v>
       </c>
       <c r="S138" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>22.74159954433088</v>
+        <v>28.49544748119097</v>
       </c>
       <c r="U138" t="n">
-        <v>0</v>
+        <v>2.200944508712678</v>
       </c>
       <c r="V138" t="n">
-        <v>28.49544748119097</v>
+        <v>0.01098357822667265</v>
       </c>
       <c r="W138" t="n">
-        <v>2.200944508712678</v>
+        <v>0.216139031898086</v>
       </c>
       <c r="X138" t="n">
-        <v>0.01098357822667265</v>
+        <v>0.007480000000000001</v>
       </c>
       <c r="Y138" t="n">
-        <v>0.216139031898086</v>
-      </c>
-      <c r="Z138" t="n">
-        <v>0.007480000000000001</v>
-      </c>
-      <c r="AA138" t="n">
         <v>28.31816032897402</v>
       </c>
     </row>
@@ -12811,39 +11979,33 @@
         <v>0.02647932083128075</v>
       </c>
       <c r="P139" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>0.0001</v>
+        <v>22.97108767528296</v>
       </c>
       <c r="S139" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>22.97108767528296</v>
+        <v>28.74377861466887</v>
       </c>
       <c r="U139" t="n">
-        <v>0</v>
+        <v>2.206644958857567</v>
       </c>
       <c r="V139" t="n">
-        <v>28.74377861466887</v>
+        <v>0.01171774454065133</v>
       </c>
       <c r="W139" t="n">
-        <v>2.206644958857567</v>
+        <v>0.2317357767803047</v>
       </c>
       <c r="X139" t="n">
-        <v>0.01171774454065133</v>
+        <v>0.008066666666666666</v>
       </c>
       <c r="Y139" t="n">
-        <v>0.2317357767803047</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>0.008066666666666666</v>
-      </c>
-      <c r="AA139" t="n">
         <v>28.49544748119097</v>
       </c>
     </row>
@@ -12900,39 +12062,33 @@
         <v>0.02163341820285943</v>
       </c>
       <c r="P140" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>0.0001</v>
+        <v>24.12500000000008</v>
       </c>
       <c r="S140" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>24.12500000000008</v>
+        <v>28.95677039510294</v>
       </c>
       <c r="U140" t="n">
-        <v>0</v>
+        <v>2.211557769325928</v>
       </c>
       <c r="V140" t="n">
-        <v>28.95677039510294</v>
+        <v>0.01228110398018093</v>
       </c>
       <c r="W140" t="n">
-        <v>2.211557769325928</v>
+        <v>0.2438036270068062</v>
       </c>
       <c r="X140" t="n">
-        <v>0.01228110398018093</v>
+        <v>0.008539999999999999</v>
       </c>
       <c r="Y140" t="n">
-        <v>0.2438036270068062</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>0.008539999999999999</v>
-      </c>
-      <c r="AA140" t="n">
         <v>28.74377861466887</v>
       </c>
     </row>
@@ -12989,39 +12145,33 @@
         <v>0.01944191146369945</v>
       </c>
       <c r="P141" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0.0001</v>
+        <v>24.57500000000017</v>
       </c>
       <c r="S141" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>24.57500000000017</v>
+        <v>29.2361683854742</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
+        <v>2.218035553581483</v>
       </c>
       <c r="V141" t="n">
-        <v>29.2361683854742</v>
+        <v>0.01296734667627982</v>
       </c>
       <c r="W141" t="n">
-        <v>2.218035553581483</v>
+        <v>0.2588159428505661</v>
       </c>
       <c r="X141" t="n">
-        <v>0.01296734667627982</v>
+        <v>0.009126666666666668</v>
       </c>
       <c r="Y141" t="n">
-        <v>0.2588159428505661</v>
-      </c>
-      <c r="Z141" t="n">
-        <v>0.009126666666666668</v>
-      </c>
-      <c r="AA141" t="n">
         <v>28.95677039510294</v>
       </c>
     </row>
@@ -13078,39 +12228,33 @@
         <v>0.01658310436687791</v>
       </c>
       <c r="P142" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>0.0001</v>
+        <v>25.06785714285721</v>
       </c>
       <c r="S142" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>25.06785714285721</v>
+        <v>29.78688518662393</v>
       </c>
       <c r="U142" t="n">
-        <v>0</v>
+        <v>2.230915566461483</v>
       </c>
       <c r="V142" t="n">
-        <v>29.78688518662393</v>
+        <v>0.01413308769286362</v>
       </c>
       <c r="W142" t="n">
-        <v>2.230915566461483</v>
+        <v>0.2848806420287301</v>
       </c>
       <c r="X142" t="n">
-        <v>0.01413308769286362</v>
+        <v>0.01019333333333333</v>
       </c>
       <c r="Y142" t="n">
-        <v>0.2848806420287301</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>0.01019333333333333</v>
-      </c>
-      <c r="AA142" t="n">
         <v>29.2361683854742</v>
       </c>
     </row>
@@ -13167,39 +12311,33 @@
         <v>0.01821926693166444</v>
       </c>
       <c r="P143" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>0.0001</v>
+        <v>25.90000000000013</v>
       </c>
       <c r="S143" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>25.90000000000013</v>
+        <v>31.11037508564176</v>
       </c>
       <c r="U143" t="n">
-        <v>0</v>
+        <v>2.262489348035233</v>
       </c>
       <c r="V143" t="n">
-        <v>31.11037508564176</v>
+        <v>0.01625131044668814</v>
       </c>
       <c r="W143" t="n">
-        <v>2.262489348035233</v>
+        <v>0.3347113995646889</v>
       </c>
       <c r="X143" t="n">
-        <v>0.01625131044668814</v>
+        <v>0.01242666666666667</v>
       </c>
       <c r="Y143" t="n">
-        <v>0.3347113995646889</v>
-      </c>
-      <c r="Z143" t="n">
-        <v>0.01242666666666667</v>
-      </c>
-      <c r="AA143" t="n">
         <v>29.78688518662393</v>
       </c>
     </row>
@@ -13256,39 +12394,33 @@
         <v>0.01480594697664882</v>
       </c>
       <c r="P144" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>0.0001</v>
+        <v>27.37499999999996</v>
       </c>
       <c r="S144" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>27.37499999999996</v>
+        <v>31.5210476313021</v>
       </c>
       <c r="U144" t="n">
-        <v>0</v>
+        <v>2.272469024681567</v>
       </c>
       <c r="V144" t="n">
-        <v>31.5210476313021</v>
+        <v>0.01679001717135276</v>
       </c>
       <c r="W144" t="n">
-        <v>2.272469024681567</v>
+        <v>0.3481782708526754</v>
       </c>
       <c r="X144" t="n">
-        <v>0.01679001717135276</v>
+        <v>0.01305333333333333</v>
       </c>
       <c r="Y144" t="n">
-        <v>0.3481782708526754</v>
-      </c>
-      <c r="Z144" t="n">
-        <v>0.01305333333333333</v>
-      </c>
-      <c r="AA144" t="n">
         <v>31.11037508564176</v>
       </c>
     </row>
@@ -13345,39 +12477,33 @@
         <v>0.01899552184075797</v>
       </c>
       <c r="P145" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>0.0001</v>
+        <v>28.11428571428576</v>
       </c>
       <c r="S145" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>28.11428571428576</v>
+        <v>31.94343405366691</v>
       </c>
       <c r="U145" t="n">
-        <v>0</v>
+        <v>2.282825618371483</v>
       </c>
       <c r="V145" t="n">
-        <v>31.94343405366691</v>
+        <v>0.01726817068693205</v>
       </c>
       <c r="W145" t="n">
-        <v>2.282825618371483</v>
+        <v>0.3602745856788814</v>
       </c>
       <c r="X145" t="n">
-        <v>0.01726817068693205</v>
+        <v>0.01367333333333333</v>
       </c>
       <c r="Y145" t="n">
-        <v>0.3602745856788814</v>
-      </c>
-      <c r="Z145" t="n">
-        <v>0.01367333333333333</v>
-      </c>
-      <c r="AA145" t="n">
         <v>31.5210476313021</v>
       </c>
     </row>
@@ -13434,39 +12560,33 @@
         <v>0.02233579751349438</v>
       </c>
       <c r="P146" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>0.0001</v>
+        <v>28.14285714285706</v>
       </c>
       <c r="S146" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>28.14285714285706</v>
+        <v>32.35740390067283</v>
       </c>
       <c r="U146" t="n">
-        <v>0</v>
+        <v>2.293067850835928</v>
       </c>
       <c r="V146" t="n">
-        <v>32.35740390067283</v>
+        <v>0.01769926548522211</v>
       </c>
       <c r="W146" t="n">
-        <v>2.293067850835928</v>
+        <v>0.3714798980485495</v>
       </c>
       <c r="X146" t="n">
-        <v>0.01769926548522211</v>
+        <v>0.01426</v>
       </c>
       <c r="Y146" t="n">
-        <v>0.3714798980485495</v>
-      </c>
-      <c r="Z146" t="n">
-        <v>0.01426</v>
-      </c>
-      <c r="AA146" t="n">
         <v>31.94343405366691</v>
       </c>
     </row>
@@ -13523,39 +12643,33 @@
         <v>0.01014663618242141</v>
       </c>
       <c r="P147" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>0.0001</v>
+        <v>29.46071428571427</v>
       </c>
       <c r="S147" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>29.46071428571427</v>
+        <v>33.25583448054279</v>
       </c>
       <c r="U147" t="n">
-        <v>0</v>
+        <v>2.315615651161483</v>
       </c>
       <c r="V147" t="n">
-        <v>33.25583448054279</v>
+        <v>0.01851307209935324</v>
       </c>
       <c r="W147" t="n">
-        <v>2.315615651161483</v>
+        <v>0.3934465808882616</v>
       </c>
       <c r="X147" t="n">
-        <v>0.01851307209935324</v>
+        <v>0.01547333333333333</v>
       </c>
       <c r="Y147" t="n">
-        <v>0.3934465808882616</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>0.01547333333333333</v>
-      </c>
-      <c r="AA147" t="n">
         <v>32.35740390067283</v>
       </c>
     </row>
@@ -13612,39 +12726,33 @@
         <v>0.00902987934884078</v>
       </c>
       <c r="P148" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>0.0001</v>
+        <v>30.54107142857147</v>
       </c>
       <c r="S148" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>30.54107142857147</v>
+        <v>34.19735536914632</v>
       </c>
       <c r="U148" t="n">
-        <v>0</v>
+        <v>2.339725675271483</v>
       </c>
       <c r="V148" t="n">
-        <v>34.19735536914632</v>
+        <v>0.01919069898130528</v>
       </c>
       <c r="W148" t="n">
-        <v>2.339725675271483</v>
+        <v>0.4125742480274263</v>
       </c>
       <c r="X148" t="n">
-        <v>0.01919069898130528</v>
+        <v>0.01667333333333334</v>
       </c>
       <c r="Y148" t="n">
-        <v>0.4125742480274263</v>
-      </c>
-      <c r="Z148" t="n">
-        <v>0.01667333333333334</v>
-      </c>
-      <c r="AA148" t="n">
         <v>33.25583448054279</v>
       </c>
     </row>
@@ -13701,39 +12809,33 @@
         <v>0.01371968923896166</v>
       </c>
       <c r="P149" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>0.0001</v>
+        <v>30.00357142857132</v>
       </c>
       <c r="S149" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>30.00357142857132</v>
+        <v>34.69219417667006</v>
       </c>
       <c r="U149" t="n">
-        <v>0</v>
+        <v>2.352599660367677</v>
       </c>
       <c r="V149" t="n">
-        <v>34.69219417667006</v>
+        <v>0.01948898852875239</v>
       </c>
       <c r="W149" t="n">
-        <v>2.352599660367677</v>
+        <v>0.4212993151451641</v>
       </c>
       <c r="X149" t="n">
-        <v>0.01948898852875239</v>
+        <v>0.01728</v>
       </c>
       <c r="Y149" t="n">
-        <v>0.4212993151451641</v>
-      </c>
-      <c r="Z149" t="n">
-        <v>0.01728</v>
-      </c>
-      <c r="AA149" t="n">
         <v>34.19735536914632</v>
       </c>
     </row>
@@ -13790,39 +12892,33 @@
         <v>0.0224321685275548</v>
       </c>
       <c r="P150" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>0.0001</v>
+        <v>30.12857142857151</v>
       </c>
       <c r="S150" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>30.12857142857151</v>
+        <v>35.04183767661643</v>
       </c>
       <c r="U150" t="n">
-        <v>0</v>
+        <v>2.361781919549927</v>
       </c>
       <c r="V150" t="n">
-        <v>35.04183767661643</v>
+        <v>0.01970497329658792</v>
       </c>
       <c r="W150" t="n">
-        <v>2.361781919549927</v>
+        <v>0.4278829811081218</v>
       </c>
       <c r="X150" t="n">
-        <v>0.01970497329658792</v>
+        <v>0.0177</v>
       </c>
       <c r="Y150" t="n">
-        <v>0.4278829811081218</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="AA150" t="n">
         <v>34.69219417667006</v>
       </c>
     </row>

--- a/data/processed/BR_processed.xlsx
+++ b/data/processed/BR_processed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB152"/>
+  <dimension ref="A1:AB150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1392,7 +1392,7 @@
         <v>0.03252295278732637</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001220189719696315</v>
+        <v>0.001220189719696316</v>
       </c>
       <c r="AB10" t="n">
         <v>0.03252295278732637</v>
@@ -2036,7 +2036,7 @@
         <v>0.4847102107155994</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.01902416488705139</v>
+        <v>0.0190241648870514</v>
       </c>
       <c r="AB17" t="n">
         <v>0.5387038540642539</v>
@@ -3042,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.006015752972438382</v>
+        <v>0.006015752972438381</v>
       </c>
       <c r="Z28" t="n">
         <v>0.1619956336149481</v>
@@ -3140,7 +3140,7 @@
         <v>0.0921971490896749</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.003588200271870521</v>
+        <v>0.003588200271870522</v>
       </c>
       <c r="AB29" t="n">
         <v>0.1003600680355974</v>
@@ -3318,13 +3318,13 @@
         <v>0.02643890324335607</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.0059864661796889</v>
+        <v>0.005986466179688899</v>
       </c>
       <c r="Z31" t="n">
         <v>0.166038915540943</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.005834624532342146</v>
+        <v>0.005834624532342147</v>
       </c>
       <c r="AB31" t="n">
         <v>0.1751119665341944</v>
@@ -4974,13 +4974,13 @@
         <v>0.04062202704143002</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.002657762910916001</v>
+        <v>0.002657762910916</v>
       </c>
       <c r="Z49" t="n">
         <v>0.0816312894067058</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.004090749458226509</v>
+        <v>0.00409074945822651</v>
       </c>
       <c r="AB49" t="n">
         <v>0.08179186507452586</v>
@@ -5342,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.002253668672706708</v>
+        <v>0.002253668672706707</v>
       </c>
       <c r="Z53" t="n">
         <v>0.07526448485171559</v>
@@ -6912,7 +6912,7 @@
         <v>0.06320238611045444</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.004235445898201378</v>
+        <v>0.004235445898201379</v>
       </c>
       <c r="AB70" t="n">
         <v>0.06361509502651258</v>
@@ -7004,7 +7004,7 @@
         <v>0.05093049240086417</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.003538733655060629</v>
+        <v>0.003538733655060628</v>
       </c>
       <c r="AB71" t="n">
         <v>0.0536319778251635</v>
@@ -7280,7 +7280,7 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.0006703122036587194</v>
+        <v>0.0006703122036587193</v>
       </c>
       <c r="AB74" t="n">
         <v>0.01042051580594177</v>
@@ -8936,7 +8936,7 @@
         <v>0.04872158819598323</v>
       </c>
       <c r="AA92" t="n">
-        <v>0.002019535772512294</v>
+        <v>0.002019535772512295</v>
       </c>
       <c r="AB92" t="n">
         <v>0.0495778372711814</v>
@@ -9390,7 +9390,7 @@
         <v>0.00813246080612828</v>
       </c>
       <c r="Y97" t="n">
-        <v>5.72212406026065e-05</v>
+        <v>5.722124060260651e-05</v>
       </c>
       <c r="Z97" t="n">
         <v>0.001647154283060745</v>
@@ -9773,93 +9773,93 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>46.93333333333334</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>31.93571428571439</v>
+        <v>0.1803571428572935</v>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>8.209</v>
       </c>
       <c r="G102" t="n">
-        <v>2.515307377137465</v>
+        <v>1.7528</v>
       </c>
       <c r="H102" t="n">
-        <v>0.7360300997802449</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>32.01</v>
+        <v>37.26</v>
       </c>
       <c r="J102" t="n">
-        <v>0.3122489136229731</v>
+        <v>0.05518764938391202</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>-0.4529858429858447</v>
       </c>
       <c r="L102" t="n">
-        <v>0.02633606438824609</v>
+        <v>-0.01158462033462093</v>
       </c>
       <c r="M102" t="n">
-        <v>0.06894461020814052</v>
+        <v>0</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="O102" t="n">
-        <v>30.88214285714287</v>
+        <v>0.1803571428572935</v>
       </c>
       <c r="P102" t="n">
-        <v>0.3954213588988506</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>34.84968576356186</v>
+        <v>0.1803571428572935</v>
       </c>
       <c r="R102" t="n">
-        <v>2.35351377776252</v>
+        <v>1.7528</v>
       </c>
       <c r="S102" t="n">
-        <v>0.01654179887468221</v>
+        <v>0.8697868869746461</v>
       </c>
       <c r="T102" t="n">
-        <v>0.4152720349990039</v>
+        <v>0.1568722778294868</v>
       </c>
       <c r="U102" t="n">
-        <v>0.01088666666666667</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>0.01088666666666667</v>
+        <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>31.81469618008588</v>
+        <v>0.1803571428572935</v>
       </c>
       <c r="X102" t="n">
-        <v>0.02024773721229721</v>
+        <v>0.2993817189618296</v>
       </c>
       <c r="Y102" t="n">
-        <v>0.002400167963573594</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>0.07665107832241122</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0.002076037952137571</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>0.07234927026522282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -9874,34 +9874,34 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="D103" t="n">
-        <v>0.1803571428572935</v>
+        <v>0.3392857142857694</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>8.209</v>
+        <v>7.657</v>
       </c>
       <c r="G103" t="n">
-        <v>1.7528</v>
+        <v>1.7438</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>37.26</v>
+        <v>36.98999999999999</v>
       </c>
       <c r="J103" t="n">
-        <v>0.05518764938391202</v>
+        <v>0.5253847655919646</v>
       </c>
       <c r="K103" t="n">
-        <v>-0.4529858429858447</v>
+        <v>-0.9401929156479114</v>
       </c>
       <c r="L103" t="n">
-        <v>-0.01158462033462093</v>
+        <v>-0.009058566064178136</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -9918,16 +9918,16 @@
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.1803571428572935</v>
+        <v>0.3616830505930247</v>
       </c>
       <c r="R103" t="n">
         <v>1.7528</v>
       </c>
       <c r="S103" t="n">
-        <v>0.8697868869746461</v>
+        <v>0.8697861867769351</v>
       </c>
       <c r="T103" t="n">
-        <v>0.1568722778294868</v>
+        <v>0.3145869213971563</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>0.1803571428572935</v>
       </c>
       <c r="X103" t="n">
-        <v>0.2993817189618296</v>
+        <v>1.543307739364463</v>
       </c>
       <c r="Y103" t="n">
         <v>0</v>
@@ -9966,19 +9966,19 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.7999999999999998</v>
+        <v>1.85</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3392857142857694</v>
+        <v>0.8962500000000428</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>7.657</v>
+        <v>6.357</v>
       </c>
       <c r="G104" t="n">
-        <v>1.7438</v>
+        <v>1.7328</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -9987,13 +9987,13 @@
         <v>36.98999999999999</v>
       </c>
       <c r="J104" t="n">
-        <v>0.5253847655919646</v>
+        <v>0.9312803307915893</v>
       </c>
       <c r="K104" t="n">
-        <v>-0.9401929156479114</v>
+        <v>-2.013263232635963</v>
       </c>
       <c r="L104" t="n">
-        <v>-0.009058566064178136</v>
+        <v>-0.01296025948216898</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
@@ -10004,22 +10004,22 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>0.1803571428572935</v>
+        <v>0.3392857142857694</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.3616830505930247</v>
+        <v>0.9014843522334873</v>
       </c>
       <c r="R104" t="n">
         <v>1.7528</v>
       </c>
       <c r="S104" t="n">
-        <v>0.8697861867769351</v>
+        <v>0.869783575992696</v>
       </c>
       <c r="T104" t="n">
-        <v>0.3145869213971563</v>
+        <v>0.7840962835871017</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10028,10 +10028,10 @@
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>0.1803571428572935</v>
+        <v>0.3616830505930247</v>
       </c>
       <c r="X104" t="n">
-        <v>1.543307739364463</v>
+        <v>1.03160607166846</v>
       </c>
       <c r="Y104" t="n">
         <v>0</v>
@@ -10058,60 +10058,60 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1.85</v>
+        <v>3.033333333333333</v>
       </c>
       <c r="D105" t="n">
+        <v>2.504651162790685</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1.7228</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1.960777481350042</v>
+      </c>
+      <c r="K105" t="n">
+        <v>-3.002449655113146</v>
+      </c>
+      <c r="L105" t="n">
+        <v>-0.006166803095242269</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O105" t="n">
         <v>0.8962500000000428</v>
       </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>6.357</v>
-      </c>
-      <c r="G105" t="n">
-        <v>1.7328</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="n">
-        <v>36.98999999999999</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0.9312803307915893</v>
-      </c>
-      <c r="K105" t="n">
-        <v>-2.013263232635963</v>
-      </c>
-      <c r="L105" t="n">
-        <v>-0.01296025948216898</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O105" t="n">
-        <v>0.3392857142857694</v>
-      </c>
       <c r="P105" t="n">
         <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.9014843522334873</v>
+        <v>2.523189877060152</v>
       </c>
       <c r="R105" t="n">
         <v>1.7528</v>
       </c>
       <c r="S105" t="n">
-        <v>0.869783575992696</v>
+        <v>0.869761996914966</v>
       </c>
       <c r="T105" t="n">
-        <v>0.7840962835871017</v>
+        <v>2.194574666067465</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -10120,10 +10120,10 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>0.3616830505930247</v>
+        <v>0.9014843522334873</v>
       </c>
       <c r="X105" t="n">
-        <v>1.03160607166846</v>
+        <v>0.779274995510789</v>
       </c>
       <c r="Y105" t="n">
         <v>0</v>
@@ -10150,72 +10150,72 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3.033333333333333</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="D106" t="n">
+        <v>5.678571428571439</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1.728574534971083</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>36.98999999999999</v>
+      </c>
+      <c r="J106" t="n">
+        <v>2.297172439252865</v>
+      </c>
+      <c r="K106" t="n">
+        <v>-1.5801724137931</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.007704220574257453</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O106" t="n">
         <v>2.504651162790685</v>
       </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" t="n">
-        <v>3.055</v>
-      </c>
-      <c r="G106" t="n">
-        <v>1.7228</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" t="n">
-        <v>37.02</v>
-      </c>
-      <c r="J106" t="n">
-        <v>1.960777481350042</v>
-      </c>
-      <c r="K106" t="n">
-        <v>-3.002449655113146</v>
-      </c>
-      <c r="L106" t="n">
-        <v>-0.006166803095242269</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O106" t="n">
-        <v>0.8962500000000428</v>
-      </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
+        <v>4.837087486134564</v>
+      </c>
+      <c r="R106" t="n">
+        <v>1.768600015796089</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0.6045883105005354</v>
+      </c>
+      <c r="T106" t="n">
+        <v>2.697443125811001</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0.08300000000000002</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0.04150000000000001</v>
+      </c>
+      <c r="W106" t="n">
         <v>2.523189877060152</v>
       </c>
-      <c r="R106" t="n">
-        <v>1.7528</v>
-      </c>
-      <c r="S106" t="n">
-        <v>0.869761996914966</v>
-      </c>
-      <c r="T106" t="n">
-        <v>2.194574666067465</v>
-      </c>
-      <c r="U106" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" t="n">
-        <v>0</v>
-      </c>
-      <c r="W106" t="n">
-        <v>0.9014843522334873</v>
-      </c>
       <c r="X106" t="n">
-        <v>0.779274995510789</v>
+        <v>0.4089904904144481</v>
       </c>
       <c r="Y106" t="n">
         <v>0</v>
@@ -10242,72 +10242,72 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4.000000000000001</v>
+        <v>4.966666666666666</v>
       </c>
       <c r="D107" t="n">
+        <v>7.142857142857149</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1.741722990771442</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>37.005</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2.828057552126018</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.02978778026632769</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O107" t="n">
         <v>5.678571428571439</v>
       </c>
-      <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" t="n">
-        <v>1.728574534971083</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="n">
-        <v>36.98999999999999</v>
-      </c>
-      <c r="J107" t="n">
-        <v>2.297172439252865</v>
-      </c>
-      <c r="K107" t="n">
-        <v>-1.5801724137931</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0.007704220574257453</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O107" t="n">
-        <v>2.504651162790685</v>
-      </c>
       <c r="P107" t="n">
         <v>0</v>
       </c>
       <c r="Q107" t="n">
+        <v>7.795781238820468</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1.813388949473866</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0.4510700441714365</v>
+      </c>
+      <c r="T107" t="n">
+        <v>3.076511138055088</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0.1023333333333333</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0.05116666666666666</v>
+      </c>
+      <c r="W107" t="n">
         <v>4.837087486134564</v>
       </c>
-      <c r="R107" t="n">
-        <v>1.768600015796089</v>
-      </c>
-      <c r="S107" t="n">
-        <v>0.6045883105005354</v>
-      </c>
-      <c r="T107" t="n">
-        <v>2.697443125811001</v>
-      </c>
-      <c r="U107" t="n">
-        <v>0.08300000000000002</v>
-      </c>
-      <c r="V107" t="n">
-        <v>0.04150000000000001</v>
-      </c>
-      <c r="W107" t="n">
-        <v>2.523189877060152</v>
-      </c>
       <c r="X107" t="n">
-        <v>0.4089904904144481</v>
+        <v>0.4130305359490459</v>
       </c>
       <c r="Y107" t="n">
         <v>0</v>
@@ -10334,72 +10334,72 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4.966666666666666</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="D108" t="n">
+        <v>10.17142857142859</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1.76736773586597</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>37.035</v>
+      </c>
+      <c r="J108" t="n">
+        <v>3.881380064666679</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.06924938703837771</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O108" t="n">
         <v>7.142857142857149</v>
       </c>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" t="n">
-        <v>1.741722990771442</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="n">
-        <v>37.005</v>
-      </c>
-      <c r="J108" t="n">
-        <v>2.828057552126018</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="n">
-        <v>0.02978778026632769</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O108" t="n">
-        <v>5.678571428571439</v>
-      </c>
       <c r="P108" t="n">
         <v>0</v>
       </c>
       <c r="Q108" t="n">
+        <v>10.81459998402953</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1.861488997573866</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0.3704055830971815</v>
+      </c>
+      <c r="T108" t="n">
+        <v>3.310566735451119</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0.1196666666666667</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0.05983333333333334</v>
+      </c>
+      <c r="W108" t="n">
         <v>7.795781238820468</v>
       </c>
-      <c r="R108" t="n">
-        <v>1.813388949473866</v>
-      </c>
-      <c r="S108" t="n">
-        <v>0.4510700441714365</v>
-      </c>
-      <c r="T108" t="n">
-        <v>3.076511138055088</v>
-      </c>
-      <c r="U108" t="n">
-        <v>0.1023333333333333</v>
-      </c>
-      <c r="V108" t="n">
-        <v>0.05116666666666666</v>
-      </c>
-      <c r="W108" t="n">
-        <v>4.837087486134564</v>
-      </c>
       <c r="X108" t="n">
-        <v>0.4130305359490459</v>
+        <v>0.4207785721774875</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
@@ -10426,72 +10426,72 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5.833333333333333</v>
+        <v>6.916666666666667</v>
       </c>
       <c r="D109" t="n">
+        <v>14.40357142857142</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1.873606104027935</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="J109" t="n">
+        <v>4.804965048714049</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.1027920516023208</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O109" t="n">
         <v>10.17142857142859</v>
       </c>
-      <c r="E109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" t="n">
-        <v>1.76736773586597</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" t="n">
-        <v>37.035</v>
-      </c>
-      <c r="J109" t="n">
-        <v>3.881380064666679</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" t="n">
-        <v>0.06924938703837771</v>
-      </c>
-      <c r="M109" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O109" t="n">
-        <v>7.142857142857149</v>
-      </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
+        <v>14.97827936533493</v>
+      </c>
+      <c r="R109" t="n">
+        <v>1.932176568261367</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0.3043058652189708</v>
+      </c>
+      <c r="T109" t="n">
+        <v>3.4623588525017</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0.1413333333333333</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0.07066666666666667</v>
+      </c>
+      <c r="W109" t="n">
         <v>10.81459998402953</v>
       </c>
-      <c r="R109" t="n">
-        <v>1.861488997573866</v>
-      </c>
-      <c r="S109" t="n">
-        <v>0.3704055830971815</v>
-      </c>
-      <c r="T109" t="n">
-        <v>3.310566735451119</v>
-      </c>
-      <c r="U109" t="n">
-        <v>0.1196666666666667</v>
-      </c>
-      <c r="V109" t="n">
-        <v>0.05983333333333334</v>
-      </c>
-      <c r="W109" t="n">
-        <v>7.795781238820468</v>
-      </c>
       <c r="X109" t="n">
-        <v>0.4207785721774875</v>
+        <v>0.3884586048784459</v>
       </c>
       <c r="Y109" t="n">
         <v>0</v>
@@ -10518,72 +10518,72 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6.916666666666667</v>
+        <v>7.633333333333334</v>
       </c>
       <c r="D110" t="n">
+        <v>17.9821428571429</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1.940578415365944</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>37.035</v>
+      </c>
+      <c r="J110" t="n">
+        <v>5.625141208026163</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.1047793843769387</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O110" t="n">
         <v>14.40357142857142</v>
       </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="n">
-        <v>1.873606104027935</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" t="n">
-        <v>37.02</v>
-      </c>
-      <c r="J110" t="n">
-        <v>4.804965048714049</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" t="n">
-        <v>0.1027920516023208</v>
-      </c>
-      <c r="M110" t="n">
-        <v>0</v>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O110" t="n">
-        <v>10.17142857142859</v>
-      </c>
       <c r="P110" t="n">
         <v>0</v>
       </c>
       <c r="Q110" t="n">
+        <v>17.91702948957649</v>
+      </c>
+      <c r="R110" t="n">
+        <v>1.985389121473867</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0.2726830989271983</v>
+      </c>
+      <c r="T110" t="n">
+        <v>3.480866279710169</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0.1556666666666667</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0.07783333333333334</v>
+      </c>
+      <c r="W110" t="n">
         <v>14.97827936533493</v>
       </c>
-      <c r="R110" t="n">
-        <v>1.932176568261367</v>
-      </c>
-      <c r="S110" t="n">
-        <v>0.3043058652189708</v>
-      </c>
-      <c r="T110" t="n">
-        <v>3.4623588525017</v>
-      </c>
-      <c r="U110" t="n">
-        <v>0.1413333333333333</v>
-      </c>
-      <c r="V110" t="n">
-        <v>0.07066666666666667</v>
-      </c>
-      <c r="W110" t="n">
-        <v>10.81459998402953</v>
-      </c>
       <c r="X110" t="n">
-        <v>0.3884586048784459</v>
+        <v>0.3668120739327594</v>
       </c>
       <c r="Y110" t="n">
         <v>0</v>
@@ -10610,72 +10610,72 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>7.633333333333334</v>
+        <v>8.25</v>
       </c>
       <c r="D111" t="n">
+        <v>22.1892857142858</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2.0142889853048</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="J111" t="n">
+        <v>5.155508911897284</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.09637878885836956</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O111" t="n">
         <v>17.9821428571429</v>
       </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" t="n">
-        <v>1.940578415365944</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" t="n">
-        <v>37.035</v>
-      </c>
-      <c r="J111" t="n">
-        <v>5.625141208026163</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" t="n">
-        <v>0.1047793843769387</v>
-      </c>
-      <c r="M111" t="n">
-        <v>0</v>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O111" t="n">
-        <v>14.40357142857142</v>
-      </c>
       <c r="P111" t="n">
         <v>0</v>
       </c>
       <c r="Q111" t="n">
+        <v>20.53315308798466</v>
+      </c>
+      <c r="R111" t="n">
+        <v>2.035287782483589</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0.2504966616746517</v>
+      </c>
+      <c r="T111" t="n">
+        <v>3.448605731265319</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="W111" t="n">
         <v>17.91702948957649</v>
       </c>
-      <c r="R111" t="n">
-        <v>1.985389121473867</v>
-      </c>
-      <c r="S111" t="n">
-        <v>0.2726830989271983</v>
-      </c>
-      <c r="T111" t="n">
-        <v>3.480866279710169</v>
-      </c>
-      <c r="U111" t="n">
-        <v>0.1556666666666667</v>
-      </c>
-      <c r="V111" t="n">
-        <v>0.07783333333333334</v>
-      </c>
-      <c r="W111" t="n">
-        <v>14.97827936533493</v>
-      </c>
       <c r="X111" t="n">
-        <v>0.3668120739327594</v>
+        <v>0.280189813438795</v>
       </c>
       <c r="Y111" t="n">
         <v>0</v>
@@ -10702,72 +10702,72 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>8.25</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="D112" t="n">
+        <v>25.66428571428573</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2.104115150425559</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="J112" t="n">
+        <v>3.114902635128286</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.05249867682683448</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.01984067189471752</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O112" t="n">
         <v>22.1892857142858</v>
       </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" t="n">
-        <v>2.0142889853048</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="n">
-        <v>36.96</v>
-      </c>
-      <c r="J112" t="n">
-        <v>5.155508911897284</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" t="n">
-        <v>0.09637878885836956</v>
-      </c>
-      <c r="M112" t="n">
-        <v>0</v>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O112" t="n">
-        <v>17.9821428571429</v>
-      </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
+        <v>24.01327123307239</v>
+      </c>
+      <c r="R112" t="n">
+        <v>2.10568785288359</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0.2267496097821178</v>
+      </c>
+      <c r="T112" t="n">
+        <v>3.346663273615921</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0.09200000000000001</v>
+      </c>
+      <c r="W112" t="n">
         <v>20.53315308798466</v>
       </c>
-      <c r="R112" t="n">
-        <v>2.035287782483589</v>
-      </c>
-      <c r="S112" t="n">
-        <v>0.2504966616746517</v>
-      </c>
-      <c r="T112" t="n">
-        <v>3.448605731265319</v>
-      </c>
-      <c r="U112" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="V112" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="W112" t="n">
-        <v>17.91702948957649</v>
-      </c>
       <c r="X112" t="n">
-        <v>0.280189813438795</v>
+        <v>0.1463215789183206</v>
       </c>
       <c r="Y112" t="n">
         <v>0</v>
@@ -10794,84 +10794,84 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>9.050000000000001</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="D113" t="n">
+        <v>27.80357142857142</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2.111411826295212</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.05060060245371522</v>
+      </c>
+      <c r="I113" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1.292833793699242</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.0006879481871742564</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.04290404542881167</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O113" t="n">
         <v>25.66428571428573</v>
       </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="n">
-        <v>2.104115150425559</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" t="n">
-        <v>37.02</v>
-      </c>
-      <c r="J113" t="n">
-        <v>3.114902635128286</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0.05249867682683448</v>
-      </c>
-      <c r="M113" t="n">
-        <v>0.01984067189471752</v>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O113" t="n">
-        <v>22.1892857142858</v>
-      </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
+        <v>28.24180486689044</v>
+      </c>
+      <c r="R113" t="n">
+        <v>2.198068889704303</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0.007073425374068638</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0.1091418130006905</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0.007053333333333333</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0.003526666666666667</v>
+      </c>
+      <c r="W113" t="n">
         <v>24.01327123307239</v>
       </c>
-      <c r="R113" t="n">
-        <v>2.10568785288359</v>
-      </c>
-      <c r="S113" t="n">
-        <v>0.2267496097821178</v>
-      </c>
-      <c r="T113" t="n">
-        <v>3.346663273615921</v>
-      </c>
-      <c r="U113" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="V113" t="n">
-        <v>0.09200000000000001</v>
-      </c>
-      <c r="W113" t="n">
-        <v>20.53315308798466</v>
-      </c>
       <c r="X113" t="n">
-        <v>0.1463215789183206</v>
+        <v>0.04682466286201208</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>0.001543705722077936</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>0.04292053230848831</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>0.001524917290366768</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>0.04306641655268557</v>
       </c>
     </row>
     <row r="114">
@@ -10886,10 +10886,10 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>10.13333333333333</v>
+        <v>11.56666666666667</v>
       </c>
       <c r="D114" t="n">
-        <v>27.80357142857142</v>
+        <v>28.21071428571433</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
@@ -10898,72 +10898,72 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>2.111411826295212</v>
+        <v>2.092706775844421</v>
       </c>
       <c r="H114" t="n">
+        <v>0.1044036282464569</v>
+      </c>
+      <c r="I114" t="n">
+        <v>28.995</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.4995599667938492</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>-0.01656280347506739</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.03752923222291429</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O114" t="n">
+        <v>27.80357142857142</v>
+      </c>
+      <c r="P114" t="n">
         <v>0.05060060245371522</v>
       </c>
-      <c r="I114" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="J114" t="n">
-        <v>1.292833793699242</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" t="n">
-        <v>0.0006879481871742564</v>
-      </c>
-      <c r="M114" t="n">
-        <v>0.04290404542881167</v>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O114" t="n">
-        <v>25.66428571428573</v>
-      </c>
-      <c r="P114" t="n">
-        <v>0</v>
-      </c>
       <c r="Q114" t="n">
+        <v>28.4719136932896</v>
+      </c>
+      <c r="R114" t="n">
+        <v>2.20332922829797</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0.007575517607850952</v>
+      </c>
+      <c r="T114" t="n">
+        <v>0.1171359889591415</v>
+      </c>
+      <c r="U114" t="n">
+        <v>0.007626666666666667</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0.003813333333333334</v>
+      </c>
+      <c r="W114" t="n">
         <v>28.24180486689044</v>
       </c>
-      <c r="R114" t="n">
-        <v>2.198068889704303</v>
-      </c>
-      <c r="S114" t="n">
-        <v>0.007073425374068638</v>
-      </c>
-      <c r="T114" t="n">
-        <v>0.1091418130006905</v>
-      </c>
-      <c r="U114" t="n">
-        <v>0.007053333333333333</v>
-      </c>
-      <c r="V114" t="n">
-        <v>0.003526666666666667</v>
-      </c>
-      <c r="W114" t="n">
-        <v>24.01327123307239</v>
-      </c>
       <c r="X114" t="n">
-        <v>0.04682466286201208</v>
+        <v>0.009793628241382288</v>
       </c>
       <c r="Y114" t="n">
-        <v>0.001543705722077936</v>
+        <v>0.001301027884616268</v>
       </c>
       <c r="Z114" t="n">
-        <v>0.04292053230848831</v>
+        <v>0.03670292593065684</v>
       </c>
       <c r="AA114" t="n">
-        <v>0.001524917290366768</v>
+        <v>0.001330806855107746</v>
       </c>
       <c r="AB114" t="n">
-        <v>0.04306641655268557</v>
+        <v>0.03789061792106591</v>
       </c>
     </row>
     <row r="115">
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>11.56666666666667</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="D115" t="n">
-        <v>28.21071428571433</v>
+        <v>28.84999999999995</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
@@ -10990,25 +10990,25 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>2.092706775844421</v>
+        <v>2.059106202419109</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1044036282464569</v>
+        <v>0.1491197853115378</v>
       </c>
       <c r="I115" t="n">
         <v>28.995</v>
       </c>
       <c r="J115" t="n">
-        <v>0.4995599667938492</v>
+        <v>0.5552285401125786</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>-0.01656280347506739</v>
+        <v>-0.01268043122870065</v>
       </c>
       <c r="M115" t="n">
-        <v>0.03752923222291429</v>
+        <v>0.03318261877259444</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
@@ -11016,46 +11016,46 @@
         </is>
       </c>
       <c r="O115" t="n">
-        <v>27.80357142857142</v>
+        <v>28.21071428571433</v>
       </c>
       <c r="P115" t="n">
-        <v>0.05060060245371522</v>
+        <v>0.1044036282464569</v>
       </c>
       <c r="Q115" t="n">
+        <v>28.65987999487133</v>
+      </c>
+      <c r="R115" t="n">
+        <v>2.207644899280303</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0.00794445905433588</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0.1229649217459896</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0.008066666666666666</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0.004033333333333333</v>
+      </c>
+      <c r="W115" t="n">
         <v>28.4719136932896</v>
       </c>
-      <c r="R115" t="n">
-        <v>2.20332922829797</v>
-      </c>
-      <c r="S115" t="n">
-        <v>0.007575517607850952</v>
-      </c>
-      <c r="T115" t="n">
-        <v>0.1171359889591415</v>
-      </c>
-      <c r="U115" t="n">
-        <v>0.007626666666666667</v>
-      </c>
-      <c r="V115" t="n">
-        <v>0.003813333333333334</v>
-      </c>
-      <c r="W115" t="n">
-        <v>28.24180486689044</v>
-      </c>
       <c r="X115" t="n">
-        <v>0.009793628241382288</v>
+        <v>0.01308713559294417</v>
       </c>
       <c r="Y115" t="n">
-        <v>0.001301027884616268</v>
+        <v>0.00111834683420231</v>
       </c>
       <c r="Z115" t="n">
-        <v>0.03670292593065684</v>
+        <v>0.03226430616673658</v>
       </c>
       <c r="AA115" t="n">
-        <v>0.001330806855107746</v>
+        <v>0.001176819229347405</v>
       </c>
       <c r="AB115" t="n">
-        <v>0.03789061792106591</v>
+        <v>0.03372749788875357</v>
       </c>
     </row>
     <row r="116">
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>12.66666666666667</v>
+        <v>14.13333333333333</v>
       </c>
       <c r="D116" t="n">
-        <v>28.84999999999995</v>
+        <v>29.8214285714287</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -11082,25 +11082,25 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>2.059106202419109</v>
+        <v>2.054382414798483</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1491197853115378</v>
+        <v>0.1918414613393818</v>
       </c>
       <c r="I116" t="n">
         <v>28.995</v>
       </c>
       <c r="J116" t="n">
-        <v>0.5552285401125786</v>
+        <v>0.4551298135529764</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>-0.01268043122870065</v>
+        <v>-0.00225385966014273</v>
       </c>
       <c r="M116" t="n">
-        <v>0.03318261877259444</v>
+        <v>0.02512562920803933</v>
       </c>
       <c r="N116" t="inlineStr">
         <is>
@@ -11108,46 +11108,46 @@
         </is>
       </c>
       <c r="O116" t="n">
-        <v>28.21071428571433</v>
+        <v>28.84999999999995</v>
       </c>
       <c r="P116" t="n">
-        <v>0.1044036282464569</v>
+        <v>0.1491197853115378</v>
       </c>
       <c r="Q116" t="n">
+        <v>28.92563754904613</v>
+      </c>
+      <c r="R116" t="n">
+        <v>2.213775572077636</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0.008420554940362099</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0.1305037237789281</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0.008653333333333332</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0.004326666666666666</v>
+      </c>
+      <c r="W116" t="n">
         <v>28.65987999487133</v>
       </c>
-      <c r="R116" t="n">
-        <v>2.207644899280303</v>
-      </c>
-      <c r="S116" t="n">
-        <v>0.00794445905433588</v>
-      </c>
-      <c r="T116" t="n">
-        <v>0.1229649217459896</v>
-      </c>
-      <c r="U116" t="n">
-        <v>0.008066666666666666</v>
-      </c>
-      <c r="V116" t="n">
-        <v>0.004033333333333333</v>
-      </c>
-      <c r="W116" t="n">
-        <v>28.4719136932896</v>
-      </c>
       <c r="X116" t="n">
-        <v>0.01308713559294417</v>
+        <v>0.01416473965932023</v>
       </c>
       <c r="Y116" t="n">
-        <v>0.00111834683420231</v>
+        <v>0.0008354784274698437</v>
       </c>
       <c r="Z116" t="n">
-        <v>0.03226430616673658</v>
+        <v>0.02491516024776152</v>
       </c>
       <c r="AA116" t="n">
-        <v>0.001176819229347405</v>
+        <v>0.0008945528030802108</v>
       </c>
       <c r="AB116" t="n">
-        <v>0.03372749788875357</v>
+        <v>0.02587551015038141</v>
       </c>
     </row>
     <row r="117">
@@ -11162,10 +11162,10 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>14.13333333333333</v>
+        <v>16.85</v>
       </c>
       <c r="D117" t="n">
-        <v>29.8214285714287</v>
+        <v>30.18571428571434</v>
       </c>
       <c r="E117" t="n">
         <v>1</v>
@@ -11174,25 +11174,25 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>2.054382414798483</v>
+        <v>2.052763135178324</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1918414613393818</v>
+        <v>0.2448076315621145</v>
       </c>
       <c r="I117" t="n">
         <v>28.995</v>
       </c>
       <c r="J117" t="n">
-        <v>0.4551298135529764</v>
+        <v>0.2858643792140457</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>-0.00225385966014273</v>
+        <v>0.004342262917761283</v>
       </c>
       <c r="M117" t="n">
-        <v>0.02512562920803933</v>
+        <v>0.01531393640884581</v>
       </c>
       <c r="N117" t="inlineStr">
         <is>
@@ -11200,46 +11200,46 @@
         </is>
       </c>
       <c r="O117" t="n">
-        <v>28.84999999999995</v>
+        <v>29.8214285714287</v>
       </c>
       <c r="P117" t="n">
-        <v>0.1491197853115378</v>
+        <v>0.1918414613393818</v>
       </c>
       <c r="Q117" t="n">
+        <v>29.46262799242935</v>
+      </c>
+      <c r="R117" t="n">
+        <v>2.226267723458665</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.009253028608468959</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.1437185005742468</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.009740000000000002</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.004870000000000001</v>
+      </c>
+      <c r="W117" t="n">
         <v>28.92563754904613</v>
       </c>
-      <c r="R117" t="n">
-        <v>2.213775572077636</v>
-      </c>
-      <c r="S117" t="n">
-        <v>0.008420554940362099</v>
-      </c>
-      <c r="T117" t="n">
-        <v>0.1305037237789281</v>
-      </c>
-      <c r="U117" t="n">
-        <v>0.008653333333333332</v>
-      </c>
-      <c r="V117" t="n">
-        <v>0.004326666666666666</v>
-      </c>
-      <c r="W117" t="n">
-        <v>28.65987999487133</v>
-      </c>
       <c r="X117" t="n">
-        <v>0.01416473965932023</v>
+        <v>0.01158551351625574</v>
       </c>
       <c r="Y117" t="n">
-        <v>0.0008354784274698437</v>
+        <v>0.0005244793669481728</v>
       </c>
       <c r="Z117" t="n">
-        <v>0.02491516024776152</v>
+        <v>0.01583178431944987</v>
       </c>
       <c r="AA117" t="n">
-        <v>0.0008945528030802108</v>
+        <v>0.0005561275272637983</v>
       </c>
       <c r="AB117" t="n">
-        <v>0.02587551015038141</v>
+        <v>0.0163849784521229</v>
       </c>
     </row>
     <row r="118">
@@ -11254,10 +11254,10 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>16.85</v>
+        <v>22.4</v>
       </c>
       <c r="D118" t="n">
-        <v>30.18571428571434</v>
+        <v>32.48928571428564</v>
       </c>
       <c r="E118" t="n">
         <v>1</v>
@@ -11266,25 +11266,25 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>2.052763135178324</v>
+        <v>2.136378998440389</v>
       </c>
       <c r="H118" t="n">
-        <v>0.2448076315621145</v>
+        <v>0.2862295508009267</v>
       </c>
       <c r="I118" t="n">
         <v>28.995</v>
       </c>
       <c r="J118" t="n">
-        <v>0.2858643792140457</v>
+        <v>0.2861652497401637</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>0.004342262917761283</v>
+        <v>0.002939955113684175</v>
       </c>
       <c r="M118" t="n">
-        <v>0.01531393640884581</v>
+        <v>0.003419686402695349</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -11292,46 +11292,46 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>29.8214285714287</v>
+        <v>30.18571428571434</v>
       </c>
       <c r="P118" t="n">
-        <v>0.1918414613393818</v>
+        <v>0.2448076315621145</v>
       </c>
       <c r="Q118" t="n">
+        <v>30.73245487142585</v>
+      </c>
+      <c r="R118" t="n">
+        <v>2.256376503567415</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.01074722783805307</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.1673902776698777</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.01196</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.005979999999999999</v>
+      </c>
+      <c r="W118" t="n">
         <v>29.46262799242935</v>
       </c>
-      <c r="R118" t="n">
-        <v>2.226267723458665</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0.009253028608468959</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0.1437185005742468</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0.009740000000000002</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0.004870000000000001</v>
-      </c>
-      <c r="W118" t="n">
-        <v>28.92563754904613</v>
-      </c>
       <c r="X118" t="n">
-        <v>0.01158551351625574</v>
+        <v>0.01018412764647287</v>
       </c>
       <c r="Y118" t="n">
-        <v>0.0005244793669481729</v>
+        <v>0.0001173795623522832</v>
       </c>
       <c r="Z118" t="n">
-        <v>0.01583178431944987</v>
+        <v>0.003813578138281135</v>
       </c>
       <c r="AA118" t="n">
-        <v>0.0005561275272637982</v>
+        <v>0.000160639813569606</v>
       </c>
       <c r="AB118" t="n">
-        <v>0.0163849784521229</v>
+        <v>0.004936855821082178</v>
       </c>
     </row>
     <row r="119">
@@ -11346,10 +11346,10 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>22.4</v>
+        <v>24.05</v>
       </c>
       <c r="D119" t="n">
-        <v>32.48928571428564</v>
+        <v>32.9321428571429</v>
       </c>
       <c r="E119" t="n">
         <v>1</v>
@@ -11358,72 +11358,72 @@
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>2.136378998440389</v>
+        <v>2.119328558258994</v>
       </c>
       <c r="H119" t="n">
+        <v>0.2889524121591054</v>
+      </c>
+      <c r="I119" t="n">
+        <v>28.98962893733009</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.2278965996953445</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.003428148603602897</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.002167744356653061</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O119" t="n">
+        <v>32.48928571428564</v>
+      </c>
+      <c r="P119" t="n">
         <v>0.2862295508009267</v>
       </c>
-      <c r="I119" t="n">
-        <v>28.995</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0.2861652497401637</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" t="n">
-        <v>0.002939955113684175</v>
-      </c>
-      <c r="M119" t="n">
-        <v>0.003419686402695349</v>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O119" t="n">
-        <v>30.18571428571434</v>
-      </c>
-      <c r="P119" t="n">
-        <v>0.2448076315621145</v>
-      </c>
       <c r="Q119" t="n">
+        <v>31.15248097069052</v>
+      </c>
+      <c r="R119" t="n">
+        <v>2.266515763706664</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.01113732683946593</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.173497795470351</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.01262</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.00631</v>
+      </c>
+      <c r="W119" t="n">
         <v>30.73245487142585</v>
       </c>
-      <c r="R119" t="n">
-        <v>2.256376503567415</v>
-      </c>
-      <c r="S119" t="n">
-        <v>0.01074722783805307</v>
-      </c>
-      <c r="T119" t="n">
-        <v>0.1673902776698777</v>
-      </c>
-      <c r="U119" t="n">
-        <v>0.01196</v>
-      </c>
-      <c r="V119" t="n">
-        <v>0.005979999999999999</v>
-      </c>
-      <c r="W119" t="n">
-        <v>29.46262799242935</v>
-      </c>
       <c r="X119" t="n">
-        <v>0.01018412764647287</v>
+        <v>0.0085377509283628</v>
       </c>
       <c r="Y119" t="n">
-        <v>0.0001173795623522832</v>
+        <v>8.001736341849413e-05</v>
       </c>
       <c r="Z119" t="n">
-        <v>0.003813578138281135</v>
+        <v>0.002635143243149769</v>
       </c>
       <c r="AA119" t="n">
-        <v>0.000160639813569606</v>
+        <v>0.000121230682064597</v>
       </c>
       <c r="AB119" t="n">
-        <v>0.004936855821082178</v>
+        <v>0.003776636516081191</v>
       </c>
     </row>
     <row r="120">
@@ -11438,10 +11438,10 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>24.05</v>
+        <v>25.55</v>
       </c>
       <c r="D120" t="n">
-        <v>32.9321428571429</v>
+        <v>33.08366238246173</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
@@ -11450,72 +11450,72 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>2.119328558258994</v>
+        <v>2.122927932215827</v>
       </c>
       <c r="H120" t="n">
+        <v>0.2916972101212668</v>
+      </c>
+      <c r="I120" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.2049207718657497</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.01007802025635504</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.002083661045468459</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O120" t="n">
+        <v>32.9321428571429</v>
+      </c>
+      <c r="P120" t="n">
         <v>0.2889524121591054</v>
       </c>
-      <c r="I120" t="n">
-        <v>28.98962893733009</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0.2278965996953445</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0.003428148603602897</v>
-      </c>
-      <c r="M120" t="n">
-        <v>0.002167744356653061</v>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O120" t="n">
-        <v>32.48928571428564</v>
-      </c>
-      <c r="P120" t="n">
-        <v>0.2862295508009267</v>
-      </c>
       <c r="Q120" t="n">
+        <v>31.55039960381771</v>
+      </c>
+      <c r="R120" t="n">
+        <v>2.276205773396665</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.01147068869907342</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.1786629068909775</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.01322</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.00661</v>
+      </c>
+      <c r="W120" t="n">
         <v>31.15248097069052</v>
       </c>
-      <c r="R120" t="n">
-        <v>2.266515763706664</v>
-      </c>
-      <c r="S120" t="n">
-        <v>0.01113732683946593</v>
-      </c>
-      <c r="T120" t="n">
-        <v>0.173497795470351</v>
-      </c>
-      <c r="U120" t="n">
-        <v>0.01262</v>
-      </c>
-      <c r="V120" t="n">
-        <v>0.00631</v>
-      </c>
-      <c r="W120" t="n">
-        <v>30.73245487142585</v>
-      </c>
       <c r="X120" t="n">
-        <v>0.0085377509283628</v>
+        <v>0.01094124388489767</v>
       </c>
       <c r="Y120" t="n">
-        <v>8.001736341849413e-05</v>
+        <v>0.0001048376628482425</v>
       </c>
       <c r="Z120" t="n">
-        <v>0.002635143243149769</v>
+        <v>0.003468413842637606</v>
       </c>
       <c r="AA120" t="n">
-        <v>0.000121230682064597</v>
+        <v>0.0001197389718612531</v>
       </c>
       <c r="AB120" t="n">
-        <v>0.003776636516081191</v>
+        <v>0.003777812410372821</v>
       </c>
     </row>
     <row r="121">
@@ -11530,10 +11530,10 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>25.55</v>
+        <v>27.01666666666667</v>
       </c>
       <c r="D121" t="n">
-        <v>33.08366238246173</v>
+        <v>33.286006759061</v>
       </c>
       <c r="E121" t="n">
         <v>1</v>
@@ -11542,25 +11542,25 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>2.122927932215827</v>
+        <v>2.149102129882635</v>
       </c>
       <c r="H121" t="n">
-        <v>0.2916972101212668</v>
+        <v>0.2947411967231239</v>
       </c>
       <c r="I121" t="n">
         <v>29.01</v>
       </c>
       <c r="J121" t="n">
-        <v>0.2049207718657497</v>
+        <v>0.2878082500112895</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>0.01007802025635504</v>
+        <v>0.01358415797906408</v>
       </c>
       <c r="M121" t="n">
-        <v>0.002083661045468459</v>
+        <v>0.002564129205513765</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -11568,46 +11568,46 @@
         </is>
       </c>
       <c r="O121" t="n">
-        <v>32.9321428571429</v>
+        <v>33.08366238246173</v>
       </c>
       <c r="P121" t="n">
-        <v>0.2889524121591054</v>
+        <v>0.2916972101212668</v>
       </c>
       <c r="Q121" t="n">
+        <v>31.95385449141564</v>
+      </c>
+      <c r="R121" t="n">
+        <v>2.28611556108422</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.01177718080478872</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.1833456058247001</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.01380666666666667</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.006903333333333334</v>
+      </c>
+      <c r="W121" t="n">
         <v>31.55039960381771</v>
       </c>
-      <c r="R121" t="n">
-        <v>2.276205773396665</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0.01147068869907342</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0.1786629068909775</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0.01322</v>
-      </c>
-      <c r="V121" t="n">
-        <v>0.00661</v>
-      </c>
-      <c r="W121" t="n">
-        <v>31.15248097069052</v>
-      </c>
       <c r="X121" t="n">
-        <v>0.01094124388489767</v>
+        <v>0.01496737650102324</v>
       </c>
       <c r="Y121" t="n">
-        <v>0.0001048376628482425</v>
+        <v>0.0001330031843039391</v>
       </c>
       <c r="Z121" t="n">
-        <v>0.003468413842637606</v>
+        <v>0.004427144891717553</v>
       </c>
       <c r="AA121" t="n">
-        <v>0.0001197389718612531</v>
+        <v>0.0001359515592164663</v>
       </c>
       <c r="AB121" t="n">
-        <v>0.003777812410372821</v>
+        <v>0.004344176341084041</v>
       </c>
     </row>
     <row r="122">
@@ -11622,10 +11622,10 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>27.01666666666667</v>
+        <v>30.05</v>
       </c>
       <c r="D122" t="n">
-        <v>33.286006759061</v>
+        <v>34.92500000000002</v>
       </c>
       <c r="E122" t="n">
         <v>1</v>
@@ -11634,72 +11634,72 @@
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>2.149102129882635</v>
+        <v>2.204791765804646</v>
       </c>
       <c r="H122" t="n">
+        <v>0.3061500936386944</v>
+      </c>
+      <c r="I122" t="n">
+        <v>28.995</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3273118051359381</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.01005866658037854</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.005592359312335324</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O122" t="n">
+        <v>33.286006759061</v>
+      </c>
+      <c r="P122" t="n">
         <v>0.2947411967231239</v>
       </c>
-      <c r="I122" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0.2878082500112895</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="n">
-        <v>0.01358415797906408</v>
-      </c>
-      <c r="M122" t="n">
-        <v>0.002564129205513765</v>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O122" t="n">
-        <v>33.08366238246173</v>
-      </c>
-      <c r="P122" t="n">
-        <v>0.2916972101212668</v>
-      </c>
       <c r="Q122" t="n">
+        <v>32.83159453257404</v>
+      </c>
+      <c r="R122" t="n">
+        <v>2.307975805166664</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.01235151587956077</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.1918563046190789</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.01502</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.007509999999999999</v>
+      </c>
+      <c r="W122" t="n">
         <v>31.95385449141564</v>
       </c>
-      <c r="R122" t="n">
-        <v>2.28611556108422</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0.01177718080478872</v>
-      </c>
-      <c r="T122" t="n">
-        <v>0.1833456058247001</v>
-      </c>
-      <c r="U122" t="n">
-        <v>0.01380666666666667</v>
-      </c>
-      <c r="V122" t="n">
-        <v>0.006903333333333334</v>
-      </c>
-      <c r="W122" t="n">
-        <v>31.55039960381771</v>
-      </c>
       <c r="X122" t="n">
-        <v>0.01496737650102324</v>
+        <v>0.01393403278476044</v>
       </c>
       <c r="Y122" t="n">
-        <v>0.0001330031843039391</v>
+        <v>0.0002001166067567213</v>
       </c>
       <c r="Z122" t="n">
-        <v>0.004427144891717553</v>
+        <v>0.006989072490978496</v>
       </c>
       <c r="AA122" t="n">
-        <v>0.0001359515592164663</v>
+        <v>0.0002310196494435016</v>
       </c>
       <c r="AB122" t="n">
-        <v>0.004344176341084041</v>
+        <v>0.007584743459586439</v>
       </c>
     </row>
     <row r="123">
@@ -11714,10 +11714,10 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>30.05</v>
+        <v>33.05</v>
       </c>
       <c r="D123" t="n">
-        <v>34.92500000000002</v>
+        <v>35.32500000000002</v>
       </c>
       <c r="E123" t="n">
         <v>1</v>
@@ -11726,72 +11726,72 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>2.204791765804646</v>
+        <v>2.222071473920533</v>
       </c>
       <c r="H123" t="n">
+        <v>0.3308651428571041</v>
+      </c>
+      <c r="I123" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3206543266788474</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.005559533698940396</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.01134058524405515</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O123" t="n">
+        <v>34.92500000000002</v>
+      </c>
+      <c r="P123" t="n">
         <v>0.3061500936386944</v>
       </c>
-      <c r="I123" t="n">
-        <v>28.995</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0.3273118051359381</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" t="n">
-        <v>0.01005866658037854</v>
-      </c>
-      <c r="M123" t="n">
-        <v>0.005592359312335324</v>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O123" t="n">
-        <v>33.286006759061</v>
-      </c>
-      <c r="P123" t="n">
-        <v>0.2947411967231239</v>
-      </c>
       <c r="Q123" t="n">
+        <v>33.75408934834007</v>
+      </c>
+      <c r="R123" t="n">
+        <v>2.331405828596664</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.01284342625596111</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1986850268676124</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.008110000000000001</v>
+      </c>
+      <c r="W123" t="n">
         <v>32.83159453257404</v>
       </c>
-      <c r="R123" t="n">
-        <v>2.307975805166664</v>
-      </c>
-      <c r="S123" t="n">
-        <v>0.01235151587956077</v>
-      </c>
-      <c r="T123" t="n">
-        <v>0.1918563046190789</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0.01502</v>
-      </c>
-      <c r="V123" t="n">
-        <v>0.007509999999999999</v>
-      </c>
-      <c r="W123" t="n">
-        <v>31.95385449141564</v>
-      </c>
       <c r="X123" t="n">
-        <v>0.01393403278476044</v>
+        <v>0.01157922320647989</v>
       </c>
       <c r="Y123" t="n">
-        <v>0.0002001166067567213</v>
+        <v>0.0003444698247772432</v>
       </c>
       <c r="Z123" t="n">
-        <v>0.006989072490978496</v>
+        <v>0.01216839656025612</v>
       </c>
       <c r="AA123" t="n">
-        <v>0.0002310196494435016</v>
+        <v>0.0004041724259930121</v>
       </c>
       <c r="AB123" t="n">
-        <v>0.007584743459586439</v>
+        <v>0.0136424721791035</v>
       </c>
     </row>
     <row r="124">
@@ -11806,10 +11806,10 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>33.05</v>
+        <v>35.71666666666666</v>
       </c>
       <c r="D124" t="n">
-        <v>35.32500000000002</v>
+        <v>36.71428571428564</v>
       </c>
       <c r="E124" t="n">
         <v>1</v>
@@ -11818,72 +11818,72 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>2.222071473920533</v>
+        <v>2.225119195750334</v>
       </c>
       <c r="H124" t="n">
+        <v>0.3724108962071924</v>
+      </c>
+      <c r="I124" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.2482560989697474</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.005575616292307751</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.01868335460030837</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O124" t="n">
+        <v>35.32500000000002</v>
+      </c>
+      <c r="P124" t="n">
         <v>0.3308651428571041</v>
       </c>
-      <c r="I124" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="J124" t="n">
-        <v>0.3206543266788474</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" t="n">
-        <v>0.005559533698940396</v>
-      </c>
-      <c r="M124" t="n">
-        <v>0.01134058524405515</v>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O124" t="n">
-        <v>34.92500000000002</v>
-      </c>
-      <c r="P124" t="n">
-        <v>0.3061500936386944</v>
-      </c>
       <c r="Q124" t="n">
+        <v>34.61647934279934</v>
+      </c>
+      <c r="R124" t="n">
+        <v>2.35374362871222</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.0132203465779301</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.2034070546972727</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.01728666666666667</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.008643333333333333</v>
+      </c>
+      <c r="W124" t="n">
         <v>33.75408934834007</v>
       </c>
-      <c r="R124" t="n">
-        <v>2.331405828596664</v>
-      </c>
-      <c r="S124" t="n">
-        <v>0.01284342625596111</v>
-      </c>
-      <c r="T124" t="n">
-        <v>0.1986850268676124</v>
-      </c>
-      <c r="U124" t="n">
-        <v>0.01622</v>
-      </c>
-      <c r="V124" t="n">
-        <v>0.008110000000000001</v>
-      </c>
-      <c r="W124" t="n">
-        <v>32.83159453257404</v>
-      </c>
       <c r="X124" t="n">
-        <v>0.01157922320647989</v>
+        <v>0.009267599997966548</v>
       </c>
       <c r="Y124" t="n">
-        <v>0.0003444698247772432</v>
+        <v>0.0005343022972248991</v>
       </c>
       <c r="Z124" t="n">
-        <v>0.01216839656025612</v>
+        <v>0.01961652719811411</v>
       </c>
       <c r="AA124" t="n">
-        <v>0.000404172425993012</v>
+        <v>0.0006187360183830693</v>
       </c>
       <c r="AB124" t="n">
-        <v>0.0136424721791035</v>
+        <v>0.02141846259900343</v>
       </c>
     </row>
     <row r="125">
@@ -11898,10 +11898,10 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>35.71666666666666</v>
+        <v>38.41666666666666</v>
       </c>
       <c r="D125" t="n">
-        <v>36.71428571428564</v>
+        <v>36.54999999999995</v>
       </c>
       <c r="E125" t="n">
         <v>1</v>
@@ -11910,25 +11910,25 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>2.225119195750334</v>
+        <v>2.238126974352284</v>
       </c>
       <c r="H125" t="n">
-        <v>0.3724108962071924</v>
+        <v>0.4370511859323505</v>
       </c>
       <c r="I125" t="n">
         <v>28.98</v>
       </c>
       <c r="J125" t="n">
-        <v>0.2482560989697474</v>
+        <v>0.09314611508350956</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>0.005575616292307751</v>
+        <v>0.008164208448361089</v>
       </c>
       <c r="M125" t="n">
-        <v>0.01868335460030837</v>
+        <v>0.02804497875626173</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
@@ -11936,91 +11936,91 @@
         </is>
       </c>
       <c r="O125" t="n">
-        <v>35.32500000000002</v>
+        <v>36.71428571428564</v>
       </c>
       <c r="P125" t="n">
-        <v>0.3308651428571041</v>
+        <v>0.3724108962071924</v>
       </c>
       <c r="Q125" t="n">
+        <v>35.52745852239729</v>
+      </c>
+      <c r="R125" t="n">
+        <v>2.377809652778219</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.013547618883582</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.2068914320190097</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.01836666666666667</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.009183333333333333</v>
+      </c>
+      <c r="W125" t="n">
         <v>34.61647934279934</v>
       </c>
-      <c r="R125" t="n">
-        <v>2.35374362871222</v>
-      </c>
-      <c r="S125" t="n">
-        <v>0.0132203465779301</v>
-      </c>
-      <c r="T125" t="n">
-        <v>0.2034070546972727</v>
-      </c>
-      <c r="U125" t="n">
-        <v>0.01728666666666667</v>
-      </c>
-      <c r="V125" t="n">
-        <v>0.008643333333333333</v>
-      </c>
-      <c r="W125" t="n">
-        <v>33.75408934834007</v>
-      </c>
       <c r="X125" t="n">
-        <v>0.009267599997966548</v>
+        <v>0.006196243412663805</v>
       </c>
       <c r="Y125" t="n">
-        <v>0.0005343022972248991</v>
+        <v>0.0008109233377192746</v>
       </c>
       <c r="Z125" t="n">
-        <v>0.01961652719811411</v>
+        <v>0.02963924799363945</v>
       </c>
       <c r="AA125" t="n">
-        <v>0.0006187360183830692</v>
+        <v>0.0008844102245227442</v>
       </c>
       <c r="AB125" t="n">
-        <v>0.02141846259900343</v>
+        <v>0.03142084756851587</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>38.41666666666666</v>
+        <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>36.54999999999995</v>
+        <v>0.2740000000001075</v>
       </c>
       <c r="E126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>8.204000000000001</v>
       </c>
       <c r="G126" t="n">
-        <v>2.238126974352284</v>
+        <v>1.7518</v>
       </c>
       <c r="H126" t="n">
-        <v>0.4370511859323505</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>28.98</v>
+        <v>36.98999999999999</v>
       </c>
       <c r="J126" t="n">
-        <v>0.09314611508350956</v>
+        <v>0.1275827253975047</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>-1.730777080062796</v>
       </c>
       <c r="L126" t="n">
-        <v>0.008164208448361089</v>
+        <v>-0.003361190630097877</v>
       </c>
       <c r="M126" t="n">
-        <v>0.02804497875626173</v>
+        <v>0</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
@@ -12028,91 +12028,91 @@
         </is>
       </c>
       <c r="O126" t="n">
-        <v>36.71428571428564</v>
+        <v>0.2740000000001075</v>
       </c>
       <c r="P126" t="n">
-        <v>0.3724108962071924</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>35.52745852239729</v>
+        <v>0.2740000000001075</v>
       </c>
       <c r="R126" t="n">
-        <v>2.377809652778219</v>
+        <v>1.7518</v>
       </c>
       <c r="S126" t="n">
-        <v>0.013547618883582</v>
+        <v>0.8697868789829178</v>
       </c>
       <c r="T126" t="n">
-        <v>0.2068914320190097</v>
+        <v>0.238321604841413</v>
       </c>
       <c r="U126" t="n">
-        <v>0.01836666666666667</v>
+        <v>0</v>
       </c>
       <c r="V126" t="n">
-        <v>0.009183333333333333</v>
+        <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>34.61647934279934</v>
+        <v>0.2740000000001075</v>
       </c>
       <c r="X126" t="n">
-        <v>0.006196243412663805</v>
+        <v>0.4637116778292156</v>
       </c>
       <c r="Y126" t="n">
-        <v>0.0008109233377192746</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>0.02963924799363945</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0.0008844102245227442</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>0.03142084756851587</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>46.41666666666666</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="D127" t="n">
-        <v>37.45357142857144</v>
+        <v>0.6966666666666418</v>
       </c>
       <c r="E127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>7.269</v>
       </c>
       <c r="G127" t="n">
-        <v>2.350696964539372</v>
+        <v>1.7448</v>
       </c>
       <c r="H127" t="n">
-        <v>0.792026695150037</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>28.98</v>
+        <v>36.98999999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>0.2428851122484339</v>
+        <v>0.523999870603825</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>0.02098979306862803</v>
+        <v>-0.01183845614334009</v>
       </c>
       <c r="M127" t="n">
-        <v>0.05964752041359847</v>
+        <v>0</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -12120,46 +12120,46 @@
         </is>
       </c>
       <c r="O127" t="n">
-        <v>36.54999999999995</v>
+        <v>0.2740000000001075</v>
       </c>
       <c r="P127" t="n">
-        <v>0.4370511859323505</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>38.42283179751898</v>
+        <v>0.734276524839871</v>
       </c>
       <c r="R127" t="n">
-        <v>2.457676399311553</v>
+        <v>1.7518</v>
       </c>
       <c r="S127" t="n">
-        <v>0.01423124238248942</v>
+        <v>0.8697849399988962</v>
       </c>
       <c r="T127" t="n">
-        <v>0.2096355868065863</v>
+        <v>0.6386626631004453</v>
       </c>
       <c r="U127" t="n">
-        <v>0.02156666666666666</v>
+        <v>0</v>
       </c>
       <c r="V127" t="n">
-        <v>0.01078333333333333</v>
+        <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>35.52745852239729</v>
+        <v>0.2740000000001075</v>
       </c>
       <c r="X127" t="n">
-        <v>0.01541414394739185</v>
+        <v>0.7453679311071638</v>
       </c>
       <c r="Y127" t="n">
-        <v>0.001781396691915808</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>0.06671966824328958</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0.001733285414237975</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>0.06659773392835872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -12174,34 +12174,34 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="D128" t="n">
-        <v>0.2740000000001075</v>
+        <v>1.346000000000203</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>8.204000000000001</v>
+        <v>7.868</v>
       </c>
       <c r="G128" t="n">
-        <v>1.7518</v>
+        <v>1.7358</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>36.98999999999999</v>
+        <v>37.005</v>
       </c>
       <c r="J128" t="n">
-        <v>0.1275827253975047</v>
+        <v>1.213494776126425</v>
       </c>
       <c r="K128" t="n">
-        <v>-1.730777080062796</v>
+        <v>-2.370705657339377</v>
       </c>
       <c r="L128" t="n">
-        <v>-0.003361190630097877</v>
+        <v>-0.007630855380385202</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
@@ -12212,22 +12212,22 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>0.2740000000001075</v>
+        <v>0.6966666666666418</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.2740000000001075</v>
+        <v>1.493994212599856</v>
       </c>
       <c r="R128" t="n">
         <v>1.7518</v>
       </c>
       <c r="S128" t="n">
-        <v>0.8697868789829178</v>
+        <v>0.8697800815789629</v>
       </c>
       <c r="T128" t="n">
-        <v>0.238321604841413</v>
+        <v>1.299446408113601</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -12236,10 +12236,10 @@
         <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>0.2740000000001075</v>
+        <v>0.734276524839871</v>
       </c>
       <c r="X128" t="n">
-        <v>0.4637116778292156</v>
+        <v>0.8971601367795489</v>
       </c>
       <c r="Y128" t="n">
         <v>0</v>
@@ -12266,34 +12266,34 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1.133333333333333</v>
+        <v>2.95</v>
       </c>
       <c r="D129" t="n">
-        <v>0.6966666666666418</v>
+        <v>3.026136363636255</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>7.269</v>
+        <v>2.283</v>
       </c>
       <c r="G129" t="n">
-        <v>1.7448</v>
+        <v>1.729919363395226</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>36.98999999999999</v>
+        <v>37.02</v>
       </c>
       <c r="J129" t="n">
-        <v>0.523999870603825</v>
+        <v>2.081851096411961</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>-4.448165488022615</v>
       </c>
       <c r="L129" t="n">
-        <v>-0.01183845614334009</v>
+        <v>0.006973448994535756</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
@@ -12304,22 +12304,22 @@
         </is>
       </c>
       <c r="O129" t="n">
-        <v>0.2740000000001075</v>
+        <v>1.346000000000203</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.734276524839871</v>
+        <v>3.5651687097501</v>
       </c>
       <c r="R129" t="n">
         <v>1.7518</v>
       </c>
       <c r="S129" t="n">
-        <v>0.8697849399988962</v>
+        <v>0.8696347056376073</v>
       </c>
       <c r="T129" t="n">
-        <v>0.6386626631004453</v>
+        <v>3.100394441451936</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -12328,10 +12328,10 @@
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>0.2740000000001075</v>
+        <v>1.493994212599856</v>
       </c>
       <c r="X129" t="n">
-        <v>0.7453679311071638</v>
+        <v>0.6919878856836935</v>
       </c>
       <c r="Y129" t="n">
         <v>0</v>
@@ -12358,34 +12358,34 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1.95</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="D130" t="n">
-        <v>1.346000000000203</v>
+        <v>5.885714285714225</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>7.868</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>1.7358</v>
+        <v>1.755331166511884</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>37.005</v>
+        <v>36.98999999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>1.213494776126425</v>
+        <v>2.855802075840205</v>
       </c>
       <c r="K130" t="n">
-        <v>-2.370705657339377</v>
+        <v>-0.8307895012025531</v>
       </c>
       <c r="L130" t="n">
-        <v>-0.007630855380385202</v>
+        <v>0.03065203139067928</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
@@ -12396,34 +12396,34 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>0.6966666666666418</v>
+        <v>3.026136363636255</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>1.493994212599856</v>
+        <v>5.404249754812128</v>
       </c>
       <c r="R130" t="n">
-        <v>1.7518</v>
+        <v>1.774655578403517</v>
       </c>
       <c r="S130" t="n">
-        <v>0.8697800815789629</v>
+        <v>0.5609388874953546</v>
       </c>
       <c r="T130" t="n">
-        <v>1.299446408113601</v>
+        <v>2.768548241906347</v>
       </c>
       <c r="U130" t="n">
-        <v>0</v>
+        <v>0.08633333333333333</v>
       </c>
       <c r="V130" t="n">
-        <v>0</v>
+        <v>0.04316666666666667</v>
       </c>
       <c r="W130" t="n">
-        <v>0.734276524839871</v>
+        <v>3.5651687097501</v>
       </c>
       <c r="X130" t="n">
-        <v>0.8971601367795489</v>
+        <v>0.5026713404005696</v>
       </c>
       <c r="Y130" t="n">
         <v>0</v>
@@ -12450,34 +12450,34 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2.95</v>
+        <v>5.133333333333335</v>
       </c>
       <c r="D131" t="n">
-        <v>3.026136363636255</v>
+        <v>8.642857142857142</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>2.283</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>1.729919363395226</v>
+        <v>1.790807714034016</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>37.02</v>
+        <v>36.98999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>2.081851096411961</v>
+        <v>3.302799915871411</v>
       </c>
       <c r="K131" t="n">
-        <v>-4.448165488022615</v>
+        <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>0.006973448994535756</v>
+        <v>0.05256831446789809</v>
       </c>
       <c r="M131" t="n">
         <v>0</v>
@@ -12488,34 +12488,34 @@
         </is>
       </c>
       <c r="O131" t="n">
-        <v>1.346000000000203</v>
+        <v>5.885714285714225</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.5651687097501</v>
+        <v>8.441995341407473</v>
       </c>
       <c r="R131" t="n">
-        <v>1.7518</v>
+        <v>1.821055624803517</v>
       </c>
       <c r="S131" t="n">
-        <v>0.8696347056376073</v>
+        <v>0.4282982830769928</v>
       </c>
       <c r="T131" t="n">
-        <v>3.100394441451936</v>
+        <v>3.125845729286283</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>0.1056666666666667</v>
       </c>
       <c r="V131" t="n">
-        <v>0</v>
+        <v>0.05283333333333335</v>
       </c>
       <c r="W131" t="n">
-        <v>1.493994212599856</v>
+        <v>5.404249754812128</v>
       </c>
       <c r="X131" t="n">
-        <v>0.6919878856836935</v>
+        <v>0.4114966666264407</v>
       </c>
       <c r="Y131" t="n">
         <v>0</v>
@@ -12542,10 +12542,10 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>4.166666666666666</v>
+        <v>6.133333333333333</v>
       </c>
       <c r="D132" t="n">
-        <v>5.885714285714225</v>
+        <v>12.06428571428577</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -12554,7 +12554,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>1.755331166511884</v>
+        <v>1.853612941241087</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -12563,13 +12563,13 @@
         <v>36.98999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>2.855802075840205</v>
+        <v>3.728918538617804</v>
       </c>
       <c r="K132" t="n">
-        <v>-0.8307895012025531</v>
+        <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>0.03065203139067928</v>
+        <v>0.07644168487578316</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
@@ -12580,34 +12580,34 @@
         </is>
       </c>
       <c r="O132" t="n">
-        <v>3.026136363636255</v>
+        <v>8.642857142857142</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>5.404249754812128</v>
+        <v>12.01818119841178</v>
       </c>
       <c r="R132" t="n">
-        <v>1.774655578403517</v>
+        <v>1.878889015970184</v>
       </c>
       <c r="S132" t="n">
-        <v>0.5609388874953546</v>
+        <v>0.3467808654092747</v>
       </c>
       <c r="T132" t="n">
-        <v>2.768548241906347</v>
+        <v>3.363857298153381</v>
       </c>
       <c r="U132" t="n">
-        <v>0.08633333333333333</v>
+        <v>0.1256666666666666</v>
       </c>
       <c r="V132" t="n">
-        <v>0.04316666666666667</v>
+        <v>0.06283333333333332</v>
       </c>
       <c r="W132" t="n">
-        <v>3.5651687097501</v>
+        <v>8.441995341407473</v>
       </c>
       <c r="X132" t="n">
-        <v>0.5026713404005696</v>
+        <v>0.3503266780181019</v>
       </c>
       <c r="Y132" t="n">
         <v>0</v>
@@ -12634,10 +12634,10 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>5.133333333333335</v>
+        <v>7</v>
       </c>
       <c r="D133" t="n">
-        <v>8.642857142857142</v>
+        <v>15.77142857142857</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -12646,22 +12646,22 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>1.790807714034016</v>
+        <v>1.916039061041396</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>36.98999999999999</v>
+        <v>37.035</v>
       </c>
       <c r="J133" t="n">
-        <v>3.302799915871411</v>
+        <v>3.583234336617672</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0.05256831446789809</v>
+        <v>0.0991644166957692</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
@@ -12672,34 +12672,34 @@
         </is>
       </c>
       <c r="O133" t="n">
-        <v>5.885714285714225</v>
+        <v>12.06428571428577</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>8.441995341407473</v>
+        <v>15.40208363976879</v>
       </c>
       <c r="R133" t="n">
-        <v>1.821055624803517</v>
+        <v>1.937100185292406</v>
       </c>
       <c r="S133" t="n">
-        <v>0.4282982830769928</v>
+        <v>0.2986612582351104</v>
       </c>
       <c r="T133" t="n">
-        <v>3.125845729286283</v>
+        <v>3.462997910048928</v>
       </c>
       <c r="U133" t="n">
-        <v>0.1056666666666667</v>
+        <v>0.143</v>
       </c>
       <c r="V133" t="n">
-        <v>0.05283333333333335</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="W133" t="n">
-        <v>5.404249754812128</v>
+        <v>12.01818119841178</v>
       </c>
       <c r="X133" t="n">
-        <v>0.4114966666264407</v>
+        <v>0.2789527328089635</v>
       </c>
       <c r="Y133" t="n">
         <v>0</v>
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>6.133333333333333</v>
+        <v>8.033333333333335</v>
       </c>
       <c r="D134" t="n">
-        <v>12.06428571428577</v>
+        <v>19.10357142857136</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
@@ -12738,22 +12738,22 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>1.853612941241087</v>
+        <v>2.047561806578555</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>36.98999999999999</v>
+        <v>36.975</v>
       </c>
       <c r="J134" t="n">
-        <v>3.728918538617804</v>
+        <v>2.954048730035644</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>0.07644168487578316</v>
+        <v>0.1101410350993035</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
@@ -12764,34 +12764,34 @@
         </is>
       </c>
       <c r="O134" t="n">
-        <v>8.642857142857142</v>
+        <v>15.77142857142857</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>12.01818119841178</v>
+        <v>19.69349055319588</v>
       </c>
       <c r="R134" t="n">
-        <v>1.878889015970184</v>
+        <v>2.016322486736851</v>
       </c>
       <c r="S134" t="n">
-        <v>0.3467808654092747</v>
+        <v>0.2568335199339056</v>
       </c>
       <c r="T134" t="n">
-        <v>3.363857298153381</v>
+        <v>3.459410578624159</v>
       </c>
       <c r="U134" t="n">
-        <v>0.1256666666666666</v>
+        <v>0.1636666666666667</v>
       </c>
       <c r="V134" t="n">
-        <v>0.06283333333333332</v>
+        <v>0.08183333333333336</v>
       </c>
       <c r="W134" t="n">
-        <v>8.441995341407473</v>
+        <v>15.40208363976879</v>
       </c>
       <c r="X134" t="n">
-        <v>0.3503266780181019</v>
+        <v>0.2084246345121031</v>
       </c>
       <c r="Y134" t="n">
         <v>0</v>
@@ -12818,10 +12818,10 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>7</v>
+        <v>8.649999999999999</v>
       </c>
       <c r="D135" t="n">
-        <v>15.77142857142857</v>
+        <v>21.08928571428573</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -12830,22 +12830,22 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>1.916039061041396</v>
+        <v>2.129469939500608</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>37.035</v>
+        <v>36.98999999999999</v>
       </c>
       <c r="J135" t="n">
-        <v>3.583234336617672</v>
+        <v>2.118204178435278</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>0.0991644166957692</v>
+        <v>0.07398676914270308</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -12856,34 +12856,34 @@
         </is>
       </c>
       <c r="O135" t="n">
-        <v>12.06428571428577</v>
+        <v>19.10357142857136</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>15.40208363976879</v>
+        <v>22.34964322948165</v>
       </c>
       <c r="R135" t="n">
-        <v>1.937100185292406</v>
+        <v>2.068687816879906</v>
       </c>
       <c r="S135" t="n">
-        <v>0.2986612582351104</v>
+        <v>0.2372035556461162</v>
       </c>
       <c r="T135" t="n">
-        <v>3.462997910048928</v>
+        <v>3.399949972617945</v>
       </c>
       <c r="U135" t="n">
-        <v>0.143</v>
+        <v>0.176</v>
       </c>
       <c r="V135" t="n">
-        <v>0.07150000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="W135" t="n">
-        <v>12.01818119841178</v>
+        <v>19.69349055319588</v>
       </c>
       <c r="X135" t="n">
-        <v>0.2789527328089635</v>
+        <v>0.1351840441944742</v>
       </c>
       <c r="Y135" t="n">
         <v>0</v>
@@ -12910,10 +12910,10 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>8.033333333333335</v>
+        <v>9.35</v>
       </c>
       <c r="D136" t="n">
-        <v>19.10357142857136</v>
+        <v>21.79285714285717</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
@@ -12922,22 +12922,22 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>2.047561806578555</v>
+        <v>2.145294715651962</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>36.975</v>
+        <v>28.02500000000001</v>
       </c>
       <c r="J136" t="n">
-        <v>2.954048730035644</v>
+        <v>1.247543009697327</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
       </c>
       <c r="L136" t="n">
-        <v>0.1101410350993035</v>
+        <v>0.02730308456683142</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
@@ -12948,34 +12948,34 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>15.77142857142857</v>
+        <v>21.08928571428573</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>19.69349055319588</v>
+        <v>25.42114791934122</v>
       </c>
       <c r="R136" t="n">
-        <v>2.016322486736851</v>
+        <v>2.132737880929906</v>
       </c>
       <c r="S136" t="n">
-        <v>0.2568335199339056</v>
+        <v>0.2183710078857313</v>
       </c>
       <c r="T136" t="n">
-        <v>3.459410578624159</v>
+        <v>3.286538586079387</v>
       </c>
       <c r="U136" t="n">
-        <v>0.1636666666666667</v>
+        <v>0.19</v>
       </c>
       <c r="V136" t="n">
-        <v>0.08183333333333336</v>
+        <v>0.095</v>
       </c>
       <c r="W136" t="n">
-        <v>15.40208363976879</v>
+        <v>22.34964322948165</v>
       </c>
       <c r="X136" t="n">
-        <v>0.2084246345121031</v>
+        <v>0.06997246239386802</v>
       </c>
       <c r="Y136" t="n">
         <v>0</v>
@@ -13002,10 +13002,10 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>8.649999999999999</v>
+        <v>10.08333333333333</v>
       </c>
       <c r="D137" t="n">
-        <v>21.08928571428573</v>
+        <v>22.74159954433088</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
@@ -13014,22 +13014,22 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>2.129469939500608</v>
+        <v>2.151754877317993</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>36.98999999999999</v>
+        <v>28.995</v>
       </c>
       <c r="J137" t="n">
-        <v>2.118204178435278</v>
+        <v>0.8532992157616837</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>0.07398676914270308</v>
+        <v>0.0143222143423807</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -13040,34 +13040,34 @@
         </is>
       </c>
       <c r="O137" t="n">
-        <v>19.10357142857136</v>
+        <v>21.79285714285717</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>22.34964322948165</v>
+        <v>28.31815807004039</v>
       </c>
       <c r="R137" t="n">
-        <v>2.068687816879906</v>
+        <v>2.196892806206484</v>
       </c>
       <c r="S137" t="n">
-        <v>0.2372035556461162</v>
+        <v>0.01041196717294989</v>
       </c>
       <c r="T137" t="n">
-        <v>3.399949972617945</v>
+        <v>0.2041873938903916</v>
       </c>
       <c r="U137" t="n">
-        <v>0.176</v>
+        <v>0.007033333333333333</v>
       </c>
       <c r="V137" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.003516666666666667</v>
       </c>
       <c r="W137" t="n">
-        <v>19.69349055319588</v>
+        <v>25.42114791934122</v>
       </c>
       <c r="X137" t="n">
-        <v>0.1351840441944742</v>
+        <v>0.04417757490269928</v>
       </c>
       <c r="Y137" t="n">
         <v>0</v>
@@ -13094,10 +13094,10 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>9.35</v>
+        <v>11.2</v>
       </c>
       <c r="D138" t="n">
-        <v>21.79285714285717</v>
+        <v>22.97108767528296</v>
       </c>
       <c r="E138" t="n">
         <v>0</v>
@@ -13106,22 +13106,22 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>2.145294715651962</v>
+        <v>2.163697271557409</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>28.02500000000001</v>
+        <v>28.995</v>
       </c>
       <c r="J138" t="n">
-        <v>1.247543009697327</v>
+        <v>0.4955894525174036</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
       </c>
       <c r="L138" t="n">
-        <v>0.02730308456683142</v>
+        <v>0.00991189089150895</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -13132,34 +13132,34 @@
         </is>
       </c>
       <c r="O138" t="n">
-        <v>21.08928571428573</v>
+        <v>22.74159954433088</v>
       </c>
       <c r="P138" t="n">
         <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>25.42114791934122</v>
+        <v>28.49544506515976</v>
       </c>
       <c r="R138" t="n">
-        <v>2.132737880929906</v>
+        <v>2.200944449147011</v>
       </c>
       <c r="S138" t="n">
-        <v>0.2183710078857313</v>
+        <v>0.01098357032200971</v>
       </c>
       <c r="T138" t="n">
-        <v>3.286538586079387</v>
+        <v>0.2161387857045839</v>
       </c>
       <c r="U138" t="n">
-        <v>0.19</v>
+        <v>0.007480000000000001</v>
       </c>
       <c r="V138" t="n">
-        <v>0.095</v>
+        <v>0.00374</v>
       </c>
       <c r="W138" t="n">
-        <v>22.34964322948165</v>
+        <v>28.31815807004039</v>
       </c>
       <c r="X138" t="n">
-        <v>0.06997246239386802</v>
+        <v>0.02615548495855645</v>
       </c>
       <c r="Y138" t="n">
         <v>0</v>
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>10.08333333333333</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="D139" t="n">
-        <v>22.74159954433088</v>
+        <v>24.12500000000008</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -13198,22 +13198,22 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>2.151754877317993</v>
+        <v>2.18231465451585</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>28.995</v>
+        <v>28.98790163201834</v>
       </c>
       <c r="J139" t="n">
-        <v>0.8532992157616837</v>
+        <v>0.527194572758186</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>0.0143222143423807</v>
+        <v>0.01009690660006621</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -13224,34 +13224,34 @@
         </is>
       </c>
       <c r="O139" t="n">
-        <v>21.79285714285717</v>
+        <v>22.97108767528296</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>28.31815807004039</v>
+        <v>28.74377626618266</v>
       </c>
       <c r="R139" t="n">
-        <v>2.196892806206484</v>
+        <v>2.2066448992919</v>
       </c>
       <c r="S139" t="n">
-        <v>0.01041196717294989</v>
+        <v>0.01171780391374263</v>
       </c>
       <c r="T139" t="n">
-        <v>0.2041873938903916</v>
+        <v>0.2317374616169707</v>
       </c>
       <c r="U139" t="n">
-        <v>0.007033333333333333</v>
+        <v>0.008066666666666666</v>
       </c>
       <c r="V139" t="n">
-        <v>0.003516666666666667</v>
+        <v>0.004033333333333333</v>
       </c>
       <c r="W139" t="n">
-        <v>25.42114791934122</v>
+        <v>28.49544506515976</v>
       </c>
       <c r="X139" t="n">
-        <v>0.04417757490269928</v>
+        <v>0.02647932083128075</v>
       </c>
       <c r="Y139" t="n">
         <v>0</v>
@@ -13278,10 +13278,10 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>11.2</v>
+        <v>13.85</v>
       </c>
       <c r="D140" t="n">
-        <v>22.97108767528296</v>
+        <v>24.57500000000017</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -13290,22 +13290,22 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>2.163697271557409</v>
+        <v>2.193791961026335</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>28.995</v>
+        <v>28.98710002854261</v>
       </c>
       <c r="J140" t="n">
-        <v>0.4955894525174036</v>
+        <v>0.4106539365163594</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
       </c>
       <c r="L140" t="n">
-        <v>0.00991189089150895</v>
+        <v>0.01080044764312056</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -13316,34 +13316,34 @@
         </is>
       </c>
       <c r="O140" t="n">
-        <v>22.74159954433088</v>
+        <v>24.12500000000008</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>28.49544506515976</v>
+        <v>28.95676810363952</v>
       </c>
       <c r="R140" t="n">
-        <v>2.200944449147011</v>
+        <v>2.211557709760262</v>
       </c>
       <c r="S140" t="n">
-        <v>0.01098357032200971</v>
+        <v>0.01228108243496568</v>
       </c>
       <c r="T140" t="n">
-        <v>0.2161387857045839</v>
+        <v>0.2438029808221922</v>
       </c>
       <c r="U140" t="n">
-        <v>0.007480000000000001</v>
+        <v>0.008539999999999999</v>
       </c>
       <c r="V140" t="n">
-        <v>0.00374</v>
+        <v>0.004269999999999999</v>
       </c>
       <c r="W140" t="n">
-        <v>28.31815807004039</v>
+        <v>28.74377626618266</v>
       </c>
       <c r="X140" t="n">
-        <v>0.02615548495855645</v>
+        <v>0.02163341820285943</v>
       </c>
       <c r="Y140" t="n">
         <v>0</v>
@@ -13370,10 +13370,10 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>12.66666666666667</v>
+        <v>15.31666666666667</v>
       </c>
       <c r="D141" t="n">
-        <v>24.12500000000008</v>
+        <v>25.06785714285721</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -13382,22 +13382,22 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>2.18231465451585</v>
+        <v>2.214828125862959</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>28.98790163201834</v>
+        <v>28.98</v>
       </c>
       <c r="J141" t="n">
-        <v>0.527194572758186</v>
+        <v>0.3756303196153055</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>0.01009690660006621</v>
+        <v>0.009872310665280869</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -13408,34 +13408,34 @@
         </is>
       </c>
       <c r="O141" t="n">
-        <v>22.97108767528296</v>
+        <v>24.57500000000017</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>28.74377626618266</v>
+        <v>29.2361661686984</v>
       </c>
       <c r="R141" t="n">
-        <v>2.2066448992919</v>
+        <v>2.218035494015818</v>
       </c>
       <c r="S141" t="n">
-        <v>0.01171780391374263</v>
+        <v>0.01296737669517052</v>
       </c>
       <c r="T141" t="n">
-        <v>0.2317374616169707</v>
+        <v>0.2588167976329628</v>
       </c>
       <c r="U141" t="n">
-        <v>0.008066666666666666</v>
+        <v>0.009126666666666668</v>
       </c>
       <c r="V141" t="n">
-        <v>0.004033333333333333</v>
+        <v>0.004563333333333334</v>
       </c>
       <c r="W141" t="n">
-        <v>28.49544506515976</v>
+        <v>28.95676810363952</v>
       </c>
       <c r="X141" t="n">
-        <v>0.02647932083128075</v>
+        <v>0.01944191146369945</v>
       </c>
       <c r="Y141" t="n">
         <v>0</v>
@@ -13462,10 +13462,10 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>13.85</v>
+        <v>17.98333333333333</v>
       </c>
       <c r="D142" t="n">
-        <v>24.57500000000017</v>
+        <v>25.90000000000013</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -13474,22 +13474,22 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>2.193791961026335</v>
+        <v>2.214024096070052</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>28.98710002854261</v>
+        <v>28.98</v>
       </c>
       <c r="J142" t="n">
-        <v>0.4106539365163594</v>
+        <v>0.3298559424945083</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>0.01080044764312056</v>
+        <v>0.008518133778895404</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -13500,34 +13500,34 @@
         </is>
       </c>
       <c r="O142" t="n">
-        <v>24.12500000000008</v>
+        <v>25.06785714285721</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>28.95676810363952</v>
+        <v>29.78688303253967</v>
       </c>
       <c r="R142" t="n">
-        <v>2.211557709760262</v>
+        <v>2.230915506895817</v>
       </c>
       <c r="S142" t="n">
-        <v>0.01228108243496568</v>
+        <v>0.01413309295165512</v>
       </c>
       <c r="T142" t="n">
-        <v>0.2438029808221922</v>
+        <v>0.2848807744362734</v>
       </c>
       <c r="U142" t="n">
-        <v>0.008539999999999999</v>
+        <v>0.01019333333333333</v>
       </c>
       <c r="V142" t="n">
-        <v>0.004269999999999999</v>
+        <v>0.005096666666666667</v>
       </c>
       <c r="W142" t="n">
-        <v>28.74377626618266</v>
+        <v>29.2361661686984</v>
       </c>
       <c r="X142" t="n">
-        <v>0.02163341820285943</v>
+        <v>0.01658310436687791</v>
       </c>
       <c r="Y142" t="n">
         <v>0</v>
@@ -13554,10 +13554,10 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>15.31666666666667</v>
+        <v>23.56666666666667</v>
       </c>
       <c r="D143" t="n">
-        <v>25.06785714285721</v>
+        <v>27.37499999999996</v>
       </c>
       <c r="E143" t="n">
         <v>0</v>
@@ -13566,22 +13566,22 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>2.214828125862959</v>
+        <v>2.307573593937551</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>28.98</v>
+        <v>28.99338819905182</v>
       </c>
       <c r="J143" t="n">
-        <v>0.3756303196153055</v>
+        <v>0.3454451519070621</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
       </c>
       <c r="L143" t="n">
-        <v>0.009872310665280869</v>
+        <v>0.0129230258223817</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
@@ -13592,34 +13592,34 @@
         </is>
       </c>
       <c r="O143" t="n">
-        <v>24.57500000000017</v>
+        <v>25.90000000000013</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>29.2361661686984</v>
+        <v>31.11037299665006</v>
       </c>
       <c r="R143" t="n">
-        <v>2.218035494015818</v>
+        <v>2.262489288469567</v>
       </c>
       <c r="S143" t="n">
-        <v>0.01296737669517052</v>
+        <v>0.01625124162510059</v>
       </c>
       <c r="T143" t="n">
-        <v>0.2588167976329628</v>
+        <v>0.3347092315256564</v>
       </c>
       <c r="U143" t="n">
-        <v>0.009126666666666668</v>
+        <v>0.01242666666666667</v>
       </c>
       <c r="V143" t="n">
-        <v>0.004563333333333334</v>
+        <v>0.006213333333333333</v>
       </c>
       <c r="W143" t="n">
-        <v>28.95676810363952</v>
+        <v>29.78688303253967</v>
       </c>
       <c r="X143" t="n">
-        <v>0.01944191146369945</v>
+        <v>0.01821926693166444</v>
       </c>
       <c r="Y143" t="n">
         <v>0</v>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>17.98333333333333</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="D144" t="n">
-        <v>25.90000000000013</v>
+        <v>28.11428571428576</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
@@ -13658,22 +13658,22 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>2.214024096070052</v>
+        <v>2.324643491537374</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>28.98</v>
+        <v>28.98907356082457</v>
       </c>
       <c r="J144" t="n">
-        <v>0.3298559424945083</v>
+        <v>0.2438328224960159</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>0.008518133778895404</v>
+        <v>0.01425711185829255</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -13684,34 +13684,34 @@
         </is>
       </c>
       <c r="O144" t="n">
-        <v>25.06785714285721</v>
+        <v>27.37499999999996</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>29.78688303253967</v>
+        <v>31.52104556228423</v>
       </c>
       <c r="R144" t="n">
-        <v>2.230915506895817</v>
+        <v>2.272468965115901</v>
       </c>
       <c r="S144" t="n">
-        <v>0.01413309295165512</v>
+        <v>0.01679004299276455</v>
       </c>
       <c r="T144" t="n">
-        <v>0.2848807744362734</v>
+        <v>0.3481790571704745</v>
       </c>
       <c r="U144" t="n">
-        <v>0.01019333333333333</v>
+        <v>0.01305333333333333</v>
       </c>
       <c r="V144" t="n">
-        <v>0.005096666666666667</v>
+        <v>0.006526666666666667</v>
       </c>
       <c r="W144" t="n">
-        <v>29.2361661686984</v>
+        <v>31.11037299665006</v>
       </c>
       <c r="X144" t="n">
-        <v>0.01658310436687791</v>
+        <v>0.01480594697664882</v>
       </c>
       <c r="Y144" t="n">
         <v>0</v>
@@ -13738,10 +13738,10 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>23.56666666666667</v>
+        <v>26.68333333333333</v>
       </c>
       <c r="D145" t="n">
-        <v>27.37499999999996</v>
+        <v>28.14285714285706</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -13750,22 +13750,22 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>2.307573593937551</v>
+        <v>2.352668497327067</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>28.99338819905182</v>
+        <v>28.995</v>
       </c>
       <c r="J145" t="n">
-        <v>0.3454451519070621</v>
+        <v>0.3483746225501007</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>0.0129230258223817</v>
+        <v>0.01556696786466986</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -13776,34 +13776,34 @@
         </is>
       </c>
       <c r="O145" t="n">
-        <v>25.90000000000013</v>
+        <v>28.11428571428576</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>31.11037299665006</v>
+        <v>31.94343200509588</v>
       </c>
       <c r="R145" t="n">
-        <v>2.262489288469567</v>
+        <v>2.282825558805818</v>
       </c>
       <c r="S145" t="n">
-        <v>0.01625124162510059</v>
+        <v>0.01726816390210312</v>
       </c>
       <c r="T145" t="n">
-        <v>0.3347092315256564</v>
+        <v>0.360274340850948</v>
       </c>
       <c r="U145" t="n">
-        <v>0.01242666666666667</v>
+        <v>0.01367333333333333</v>
       </c>
       <c r="V145" t="n">
-        <v>0.006213333333333333</v>
+        <v>0.006836666666666666</v>
       </c>
       <c r="W145" t="n">
-        <v>29.78688303253967</v>
+        <v>31.52104556228423</v>
       </c>
       <c r="X145" t="n">
-        <v>0.01821926693166444</v>
+        <v>0.01899552184075797</v>
       </c>
       <c r="Y145" t="n">
         <v>0</v>
@@ -13830,10 +13830,10 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>25.13333333333333</v>
+        <v>28.15</v>
       </c>
       <c r="D146" t="n">
-        <v>28.11428571428576</v>
+        <v>29.46071428571427</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
@@ -13842,22 +13842,22 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>2.324643491537374</v>
+        <v>2.375720882565579</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>28.98907356082457</v>
+        <v>28.995</v>
       </c>
       <c r="J146" t="n">
-        <v>0.2438328224960159</v>
+        <v>0.4669603785258343</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>0.01425711185829255</v>
+        <v>0.01540779486614794</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -13868,34 +13868,34 @@
         </is>
       </c>
       <c r="O146" t="n">
-        <v>27.37499999999996</v>
+        <v>28.14285714285706</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>31.52104556228423</v>
+        <v>32.3574018720367</v>
       </c>
       <c r="R146" t="n">
-        <v>2.272468965115901</v>
+        <v>2.293067791270262</v>
       </c>
       <c r="S146" t="n">
-        <v>0.01679004299276455</v>
+        <v>0.01769926440963473</v>
       </c>
       <c r="T146" t="n">
-        <v>0.3481790571704745</v>
+        <v>0.3714798347284995</v>
       </c>
       <c r="U146" t="n">
-        <v>0.01305333333333333</v>
+        <v>0.01426</v>
       </c>
       <c r="V146" t="n">
-        <v>0.006526666666666667</v>
+        <v>0.007129999999999999</v>
       </c>
       <c r="W146" t="n">
-        <v>31.11037299665006</v>
+        <v>31.94343200509588</v>
       </c>
       <c r="X146" t="n">
-        <v>0.01480594697664882</v>
+        <v>0.02233579751349438</v>
       </c>
       <c r="Y146" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>26.68333333333333</v>
+        <v>31.18333333333333</v>
       </c>
       <c r="D147" t="n">
-        <v>28.14285714285706</v>
+        <v>30.54107142857147</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
@@ -13934,22 +13934,22 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>2.352668497327067</v>
+        <v>2.429480867954015</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>28.995</v>
+        <v>28.98</v>
       </c>
       <c r="J147" t="n">
-        <v>0.3483746225501007</v>
+        <v>0.1393496146836234</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>0.01556696786466986</v>
+        <v>0.01356607661731992</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -13960,34 +13960,34 @@
         </is>
       </c>
       <c r="O147" t="n">
-        <v>28.11428571428576</v>
+        <v>29.46071428571427</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>31.94343200509588</v>
+        <v>33.25583249482232</v>
       </c>
       <c r="R147" t="n">
-        <v>2.282825558805818</v>
+        <v>2.315615591595817</v>
       </c>
       <c r="S147" t="n">
-        <v>0.01726816390210312</v>
+        <v>0.01851308273432502</v>
       </c>
       <c r="T147" t="n">
-        <v>0.360274340850948</v>
+        <v>0.3934469053539372</v>
       </c>
       <c r="U147" t="n">
-        <v>0.01367333333333333</v>
+        <v>0.01547333333333333</v>
       </c>
       <c r="V147" t="n">
-        <v>0.006836666666666666</v>
+        <v>0.007736666666666666</v>
       </c>
       <c r="W147" t="n">
-        <v>31.52104556228423</v>
+        <v>32.3574018720367</v>
       </c>
       <c r="X147" t="n">
-        <v>0.01899552184075797</v>
+        <v>0.01014663618242141</v>
       </c>
       <c r="Y147" t="n">
         <v>0</v>
@@ -14014,10 +14014,10 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>28.15</v>
+        <v>34.18333333333334</v>
       </c>
       <c r="D148" t="n">
-        <v>29.46071428571427</v>
+        <v>30.00357142857132</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
@@ -14026,7 +14026,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>2.375720882565579</v>
+        <v>2.451704147576396</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -14035,13 +14035,13 @@
         <v>28.995</v>
       </c>
       <c r="J148" t="n">
-        <v>0.4669603785258343</v>
+        <v>0.08855763882758942</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>0.01540779486614794</v>
+        <v>0.01490221644458623</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -14052,34 +14052,34 @@
         </is>
       </c>
       <c r="O148" t="n">
-        <v>28.14285714285706</v>
+        <v>30.54107142857147</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>32.3574018720367</v>
+        <v>34.19735342816631</v>
       </c>
       <c r="R148" t="n">
-        <v>2.293067791270262</v>
+        <v>2.339725615705817</v>
       </c>
       <c r="S148" t="n">
-        <v>0.01769926440963473</v>
+        <v>0.01919070522193477</v>
       </c>
       <c r="T148" t="n">
-        <v>0.3714798347284995</v>
+        <v>0.4125744318193387</v>
       </c>
       <c r="U148" t="n">
-        <v>0.01426</v>
+        <v>0.01667333333333334</v>
       </c>
       <c r="V148" t="n">
-        <v>0.007129999999999999</v>
+        <v>0.008336666666666668</v>
       </c>
       <c r="W148" t="n">
-        <v>31.94343200509588</v>
+        <v>33.25583249482232</v>
       </c>
       <c r="X148" t="n">
-        <v>0.02233579751349438</v>
+        <v>0.00902987934884078</v>
       </c>
       <c r="Y148" t="n">
         <v>0</v>
@@ -14106,10 +14106,10 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>31.18333333333333</v>
+        <v>35.7</v>
       </c>
       <c r="D149" t="n">
-        <v>30.54107142857147</v>
+        <v>30.12857142857151</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -14118,22 +14118,22 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>2.429480867954015</v>
+        <v>2.481063784627632</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>28.98</v>
+        <v>29.01</v>
       </c>
       <c r="J149" t="n">
-        <v>0.1393496146836234</v>
+        <v>0.2239877292055531</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>0.01356607661731992</v>
+        <v>0.01559421357166551</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
@@ -14144,34 +14144,34 @@
         </is>
       </c>
       <c r="O149" t="n">
-        <v>29.46071428571427</v>
+        <v>30.00357142857132</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>33.25583249482232</v>
+        <v>34.69219227608998</v>
       </c>
       <c r="R149" t="n">
-        <v>2.315615591595817</v>
+        <v>2.352599600802012</v>
       </c>
       <c r="S149" t="n">
-        <v>0.01851308273432502</v>
+        <v>0.01948896483444288</v>
       </c>
       <c r="T149" t="n">
-        <v>0.3934469053539372</v>
+        <v>0.4212984636054069</v>
       </c>
       <c r="U149" t="n">
-        <v>0.01547333333333333</v>
+        <v>0.01728</v>
       </c>
       <c r="V149" t="n">
-        <v>0.007736666666666666</v>
+        <v>0.00864</v>
       </c>
       <c r="W149" t="n">
-        <v>32.3574018720367</v>
+        <v>34.19735342816631</v>
       </c>
       <c r="X149" t="n">
-        <v>0.01014663618242141</v>
+        <v>0.01371968923896166</v>
       </c>
       <c r="Y149" t="n">
         <v>0</v>
@@ -14198,10 +14198,10 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>34.18333333333334</v>
+        <v>36.75</v>
       </c>
       <c r="D150" t="n">
-        <v>30.00357142857132</v>
+        <v>30.54107142857147</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -14210,22 +14210,22 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>2.451704147576396</v>
+        <v>2.497032422101453</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>28.995</v>
+        <v>28.98</v>
       </c>
       <c r="J150" t="n">
-        <v>0.08855763882758942</v>
+        <v>0.5198551448550432</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
       </c>
       <c r="L150" t="n">
-        <v>0.01490221644458623</v>
+        <v>0.01351059041225433</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -14236,34 +14236,34 @@
         </is>
       </c>
       <c r="O150" t="n">
-        <v>30.54107142857147</v>
+        <v>30.12857142857151</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>34.19735342816631</v>
+        <v>35.04183579224857</v>
       </c>
       <c r="R150" t="n">
-        <v>2.339725615705817</v>
+        <v>2.361781859984262</v>
       </c>
       <c r="S150" t="n">
-        <v>0.01919070522193477</v>
+        <v>0.01970497485318354</v>
       </c>
       <c r="T150" t="n">
-        <v>0.4125744318193387</v>
+        <v>0.4278830060214355</v>
       </c>
       <c r="U150" t="n">
-        <v>0.01667333333333334</v>
+        <v>0.0177</v>
       </c>
       <c r="V150" t="n">
-        <v>0.008336666666666668</v>
+        <v>0.00885</v>
       </c>
       <c r="W150" t="n">
-        <v>33.25583249482232</v>
+        <v>34.69219227608998</v>
       </c>
       <c r="X150" t="n">
-        <v>0.00902987934884078</v>
+        <v>0.0224321685275548</v>
       </c>
       <c r="Y150" t="n">
         <v>0</v>
@@ -14275,190 +14275,6 @@
         <v>0</v>
       </c>
       <c r="AB150" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="D151" t="n">
-        <v>30.12857142857151</v>
-      </c>
-      <c r="E151" t="n">
-        <v>0</v>
-      </c>
-      <c r="F151" t="n">
-        <v>0</v>
-      </c>
-      <c r="G151" t="n">
-        <v>2.481063784627632</v>
-      </c>
-      <c r="H151" t="n">
-        <v>0</v>
-      </c>
-      <c r="I151" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="J151" t="n">
-        <v>0.2239877292055531</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" t="n">
-        <v>0.01559421357166551</v>
-      </c>
-      <c r="M151" t="n">
-        <v>0</v>
-      </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O151" t="n">
-        <v>30.00357142857132</v>
-      </c>
-      <c r="P151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q151" t="n">
-        <v>34.69219227608998</v>
-      </c>
-      <c r="R151" t="n">
-        <v>2.352599600802012</v>
-      </c>
-      <c r="S151" t="n">
-        <v>0.01948896483444288</v>
-      </c>
-      <c r="T151" t="n">
-        <v>0.4212984636054069</v>
-      </c>
-      <c r="U151" t="n">
-        <v>0.01728</v>
-      </c>
-      <c r="V151" t="n">
-        <v>0.00864</v>
-      </c>
-      <c r="W151" t="n">
-        <v>34.19735342816631</v>
-      </c>
-      <c r="X151" t="n">
-        <v>0.01371968923896166</v>
-      </c>
-      <c r="Y151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB151" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>36.75</v>
-      </c>
-      <c r="D152" t="n">
-        <v>30.54107142857147</v>
-      </c>
-      <c r="E152" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" t="n">
-        <v>2.497032422101453</v>
-      </c>
-      <c r="H152" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" t="n">
-        <v>28.98</v>
-      </c>
-      <c r="J152" t="n">
-        <v>0.5198551448550432</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" t="n">
-        <v>0.01351059041225433</v>
-      </c>
-      <c r="M152" t="n">
-        <v>0</v>
-      </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O152" t="n">
-        <v>30.12857142857151</v>
-      </c>
-      <c r="P152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>35.04183579224857</v>
-      </c>
-      <c r="R152" t="n">
-        <v>2.361781859984262</v>
-      </c>
-      <c r="S152" t="n">
-        <v>0.01970497485318354</v>
-      </c>
-      <c r="T152" t="n">
-        <v>0.4278830060214355</v>
-      </c>
-      <c r="U152" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="V152" t="n">
-        <v>0.00885</v>
-      </c>
-      <c r="W152" t="n">
-        <v>34.69219227608998</v>
-      </c>
-      <c r="X152" t="n">
-        <v>0.0224321685275548</v>
-      </c>
-      <c r="Y152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB152" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/processed/BR_processed.xlsx
+++ b/data/processed/BR_processed.xlsx
@@ -1454,16 +1454,16 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>26.81456003797826</v>
+        <v>26.81456003794531</v>
       </c>
       <c r="R11" t="n">
         <v>1.851713165092423</v>
       </c>
       <c r="S11" t="n">
-        <v>0.006094311842885767</v>
+        <v>0.006094652876519476</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1282517247191745</v>
+        <v>0.1282608693858629</v>
       </c>
       <c r="U11" t="n">
         <v>0.002428333333333334</v>
@@ -1484,7 +1484,7 @@
         <v>0.1065167260919373</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.004012411300951165</v>
+        <v>0.004012411300956096</v>
       </c>
       <c r="AB11" t="n">
         <v>0.1075910437264175</v>
@@ -1546,16 +1546,16 @@
         <v>0.1310102834270957</v>
       </c>
       <c r="Q12" t="n">
-        <v>27.04656525722977</v>
+        <v>27.04656525722954</v>
       </c>
       <c r="R12" t="n">
         <v>1.856115873425756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.006462731911821826</v>
+        <v>0.006462734694132884</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1368599863515561</v>
+        <v>0.1368600616035126</v>
       </c>
       <c r="U12" t="n">
         <v>0.002603333333333333</v>
@@ -1564,7 +1564,7 @@
         <v>0.002603333333333333</v>
       </c>
       <c r="W12" t="n">
-        <v>26.81456003797826</v>
+        <v>26.81456003794531</v>
       </c>
       <c r="X12" t="n">
         <v>5.19473822208176e-05</v>
@@ -1576,7 +1576,7 @@
         <v>0.08474551698518029</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.003294261940258428</v>
+        <v>0.003294261940258456</v>
       </c>
       <c r="AB12" t="n">
         <v>0.08909847054160794</v>
@@ -1638,16 +1638,16 @@
         <v>0.3150449672599142</v>
       </c>
       <c r="Q13" t="n">
-        <v>27.34710021724289</v>
+        <v>27.34710021724216</v>
       </c>
       <c r="R13" t="n">
         <v>1.861850276203534</v>
       </c>
       <c r="S13" t="n">
-        <v>0.006890081998479314</v>
+        <v>0.006890089633184113</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1470766749719362</v>
+        <v>0.1470768837589695</v>
       </c>
       <c r="U13" t="n">
         <v>0.002815</v>
@@ -1656,7 +1656,7 @@
         <v>0.002815</v>
       </c>
       <c r="W13" t="n">
-        <v>27.04656525722977</v>
+        <v>27.04656525722954</v>
       </c>
       <c r="X13" t="n">
         <v>0.009247963860255975</v>
@@ -1668,10 +1668,10 @@
         <v>0.06448817748780201</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.002529907594138891</v>
+        <v>0.002529907594138958</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.06918563651728009</v>
+        <v>0.0691856365172801</v>
       </c>
     </row>
     <row r="14">
@@ -1730,16 +1730,16 @@
         <v>0.462353720667521</v>
       </c>
       <c r="Q14" t="n">
-        <v>27.65075345784634</v>
+        <v>27.65075345784807</v>
       </c>
       <c r="R14" t="n">
         <v>1.867680276203534</v>
       </c>
       <c r="S14" t="n">
-        <v>0.007275831136120344</v>
+        <v>0.007275813451270728</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1565455464147945</v>
+        <v>0.1565450574153875</v>
       </c>
       <c r="U14" t="n">
         <v>0.003015</v>
@@ -1748,7 +1748,7 @@
         <v>0.003015</v>
       </c>
       <c r="W14" t="n">
-        <v>27.34710021724289</v>
+        <v>27.34710021724216</v>
       </c>
       <c r="X14" t="n">
         <v>0.00709381743588283</v>
@@ -1760,7 +1760,7 @@
         <v>0.112121445976553</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.004332845827375171</v>
+        <v>0.004332845827374901</v>
       </c>
       <c r="AB14" t="n">
         <v>0.1198064517436091</v>
@@ -1822,16 +1822,16 @@
         <v>0.6209461221159972</v>
       </c>
       <c r="Q15" t="n">
-        <v>27.96486690504897</v>
+        <v>27.96486690504821</v>
       </c>
       <c r="R15" t="n">
         <v>1.873749651203534</v>
       </c>
       <c r="S15" t="n">
-        <v>0.007634549004260692</v>
+        <v>0.007634557258848181</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1655913471976849</v>
+        <v>0.1655915780361208</v>
       </c>
       <c r="U15" t="n">
         <v>0.003210000000000001</v>
@@ -1840,7 +1840,7 @@
         <v>0.003210000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>27.65075345784634</v>
+        <v>27.65075345784807</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>0.2218548813486614</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.008700430054214071</v>
+        <v>0.008700430054214307</v>
       </c>
       <c r="AB15" t="n">
         <v>0.2433063684827845</v>
@@ -1914,16 +1914,16 @@
         <v>0.9523209449429346</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.1412593939992</v>
+        <v>28.14125939399926</v>
       </c>
       <c r="R16" t="n">
         <v>1.877175276203534</v>
       </c>
       <c r="S16" t="n">
-        <v>0.007820572933980103</v>
+        <v>0.007820572933980101</v>
       </c>
       <c r="T16" t="n">
-        <v>0.170384679723405</v>
+        <v>0.1703846797234053</v>
       </c>
       <c r="U16" t="n">
         <v>0.003315</v>
@@ -1932,7 +1932,7 @@
         <v>0.003315</v>
       </c>
       <c r="W16" t="n">
-        <v>27.96486690504897</v>
+        <v>27.96486690504821</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>0.3242312467603854</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.01278089828636537</v>
+        <v>0.01278089828636535</v>
       </c>
       <c r="AB16" t="n">
         <v>0.3596705739649278</v>
@@ -2006,16 +2006,16 @@
         <v>1.25504016023201</v>
       </c>
       <c r="Q17" t="n">
-        <v>28.31682006871782</v>
+        <v>28.31682006871788</v>
       </c>
       <c r="R17" t="n">
         <v>1.880597206759089</v>
       </c>
       <c r="S17" t="n">
-        <v>0.007995870233005839</v>
+        <v>0.007995870233005813</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1749716551927246</v>
+        <v>0.1749716551927243</v>
       </c>
       <c r="U17" t="n">
         <v>0.003416666666666667</v>
@@ -2024,7 +2024,7 @@
         <v>0.003416666666666667</v>
       </c>
       <c r="W17" t="n">
-        <v>28.1412593939992</v>
+        <v>28.14125939399926</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2036,7 +2036,7 @@
         <v>0.4847102107155994</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0190241648870514</v>
+        <v>0.01902416488705136</v>
       </c>
       <c r="AB17" t="n">
         <v>0.5387038540642539</v>
@@ -2098,16 +2098,16 @@
         <v>1.69587337268752</v>
       </c>
       <c r="Q18" t="n">
-        <v>28.48804706810432</v>
+        <v>28.48804706810439</v>
       </c>
       <c r="R18" t="n">
-        <v>1.88394670675909</v>
+        <v>1.883946706759089</v>
       </c>
       <c r="S18" t="n">
-        <v>0.00815814576399599</v>
+        <v>0.008158145763995973</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1792828694602287</v>
+        <v>0.1792828694602286</v>
       </c>
       <c r="U18" t="n">
         <v>0.003513333333333334</v>
@@ -2116,7 +2116,7 @@
         <v>0.003513333333333334</v>
       </c>
       <c r="W18" t="n">
-        <v>28.31682006871782</v>
+        <v>28.31682006871788</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
         <v>0.6709707039456413</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.02637900208746056</v>
+        <v>0.0263790020874605</v>
       </c>
       <c r="AB18" t="n">
         <v>0.7514862530771985</v>
@@ -3024,10 +3024,10 @@
         <v>1.908002336876444</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0187088218943581</v>
+        <v>0.01870882202496487</v>
       </c>
       <c r="T28" t="n">
-        <v>0.3981449898798762</v>
+        <v>0.3981449934364881</v>
       </c>
       <c r="U28" t="n">
         <v>0.007799999999999998</v>
@@ -3048,7 +3048,7 @@
         <v>0.1619956336149481</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.006010640046182783</v>
+        <v>0.006010640046182784</v>
       </c>
       <c r="AB28" t="n">
         <v>0.1636784616839654</v>
@@ -3110,16 +3110,16 @@
         <v>0.1961577414134905</v>
       </c>
       <c r="Q29" t="n">
-        <v>27.96947227900406</v>
+        <v>27.96947227900407</v>
       </c>
       <c r="R29" t="n">
         <v>1.922571086876444</v>
       </c>
       <c r="S29" t="n">
-        <v>0.02051067907382667</v>
+        <v>0.02051067912378411</v>
       </c>
       <c r="T29" t="n">
-        <v>0.4449234927812163</v>
+        <v>0.4449234941784995</v>
       </c>
       <c r="U29" t="n">
         <v>0.008849999999999998</v>
@@ -3140,7 +3140,7 @@
         <v>0.0921971490896749</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.003588200271870522</v>
+        <v>0.003588200271870521</v>
       </c>
       <c r="AB29" t="n">
         <v>0.1003600680355974</v>
@@ -3202,16 +3202,16 @@
         <v>0.4648676866334254</v>
       </c>
       <c r="Q30" t="n">
-        <v>28.9683679389311</v>
+        <v>28.96836793893106</v>
       </c>
       <c r="R30" t="n">
-        <v>1.942647670209778</v>
+        <v>1.942647670209777</v>
       </c>
       <c r="S30" t="n">
-        <v>0.02241122155096527</v>
+        <v>0.022411221550434</v>
       </c>
       <c r="T30" t="n">
-        <v>0.4983091249681805</v>
+        <v>0.4983091249527896</v>
       </c>
       <c r="U30" t="n">
         <v>0.01012</v>
@@ -3220,7 +3220,7 @@
         <v>0.01012</v>
       </c>
       <c r="W30" t="n">
-        <v>27.96947227900406</v>
+        <v>27.96947227900407</v>
       </c>
       <c r="X30" t="n">
         <v>0.006274829559544594</v>
@@ -3232,10 +3232,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.0001765021936132476</v>
+        <v>0.000176502193613248</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.005112980486617013</v>
+        <v>0.005112980486617014</v>
       </c>
     </row>
     <row r="31">
@@ -3294,16 +3294,16 @@
         <v>0.5273275582417261</v>
       </c>
       <c r="Q31" t="n">
-        <v>30.01255103280837</v>
+        <v>30.0125510328083</v>
       </c>
       <c r="R31" t="n">
         <v>1.964087670209778</v>
       </c>
       <c r="S31" t="n">
-        <v>0.02393237056821312</v>
+        <v>0.02393237056755607</v>
       </c>
       <c r="T31" t="n">
-        <v>0.5452944498589103</v>
+        <v>0.545294449839189</v>
       </c>
       <c r="U31" t="n">
         <v>0.01132</v>
@@ -3312,7 +3312,7 @@
         <v>0.01132</v>
       </c>
       <c r="W31" t="n">
-        <v>28.9683679389311</v>
+        <v>28.96836793893106</v>
       </c>
       <c r="X31" t="n">
         <v>0.02643890324335607</v>
@@ -3324,7 +3324,7 @@
         <v>0.166038915540943</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.005834624532342147</v>
+        <v>0.00583462453234216</v>
       </c>
       <c r="AB31" t="n">
         <v>0.1751119665341944</v>
@@ -3386,16 +3386,16 @@
         <v>0.5669120469218694</v>
       </c>
       <c r="Q32" t="n">
-        <v>31.10797224550702</v>
+        <v>31.10797224550694</v>
       </c>
       <c r="R32" t="n">
         <v>1.987094336876444</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0251610435573475</v>
+        <v>0.02516104333188622</v>
       </c>
       <c r="T32" t="n">
-        <v>0.5873345793217604</v>
+        <v>0.5873345723081156</v>
       </c>
       <c r="U32" t="n">
         <v>0.01248</v>
@@ -3404,7 +3404,7 @@
         <v>0.01248</v>
       </c>
       <c r="W32" t="n">
-        <v>30.01255103280837</v>
+        <v>30.0125510328083</v>
       </c>
       <c r="X32" t="n">
         <v>0.00455350837092449</v>
@@ -3416,7 +3416,7 @@
         <v>0.6940734053890505</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.02327612397420667</v>
+        <v>0.02327612397420674</v>
       </c>
       <c r="AB32" t="n">
         <v>0.7240730185726018</v>
@@ -3478,16 +3478,16 @@
         <v>1.314363106233276</v>
       </c>
       <c r="Q33" t="n">
-        <v>31.74613976555075</v>
+        <v>31.74613976555108</v>
       </c>
       <c r="R33" t="n">
         <v>2.000747670209778</v>
       </c>
       <c r="S33" t="n">
-        <v>0.02574269343420042</v>
+        <v>0.02574269343420017</v>
       </c>
       <c r="T33" t="n">
-        <v>0.6090542906575334</v>
+        <v>0.6090542906575316</v>
       </c>
       <c r="U33" t="n">
         <v>0.01312</v>
@@ -3496,7 +3496,7 @@
         <v>0.01312</v>
       </c>
       <c r="W33" t="n">
-        <v>31.10797224550702</v>
+        <v>31.10797224550694</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>1.033509465599738</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.03569355102898607</v>
+        <v>0.0356935510289857</v>
       </c>
       <c r="AB33" t="n">
         <v>1.133132459695009</v>
@@ -4950,16 +4950,16 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>19.99434722408682</v>
+        <v>19.99434722414867</v>
       </c>
       <c r="R49" t="n">
-        <v>1.87876402776961</v>
+        <v>1.878764027770175</v>
       </c>
       <c r="S49" t="n">
-        <v>0.006624041782399131</v>
+        <v>0.00662367589221488</v>
       </c>
       <c r="T49" t="n">
-        <v>0.1111942904013396</v>
+        <v>0.1111869746663001</v>
       </c>
       <c r="U49" t="n">
         <v>0.001996666666666667</v>
@@ -4980,10 +4980,10 @@
         <v>0.0816312894067058</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.00409074945822651</v>
+        <v>0.004090749458213853</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.08179186507452586</v>
+        <v>0.08179186507452584</v>
       </c>
     </row>
     <row r="50">
@@ -5042,16 +5042,16 @@
         <v>0.09290978010103844</v>
       </c>
       <c r="Q50" t="n">
-        <v>20.11820096978532</v>
+        <v>20.11820096981678</v>
       </c>
       <c r="R50" t="n">
-        <v>1.880990611102943</v>
+        <v>1.880990611103508</v>
       </c>
       <c r="S50" t="n">
-        <v>0.006756702796297812</v>
+        <v>0.006756701709062598</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1139890320483953</v>
+        <v>0.1139890101753636</v>
       </c>
       <c r="U50" t="n">
         <v>0.002051666666666667</v>
@@ -5060,7 +5060,7 @@
         <v>0.002051666666666667</v>
       </c>
       <c r="W50" t="n">
-        <v>19.99434722408682</v>
+        <v>19.99434722414867</v>
       </c>
       <c r="X50" t="n">
         <v>0.01789804707363351</v>
@@ -5072,10 +5072,10 @@
         <v>0.04078878183453907</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.002159985784733604</v>
+        <v>0.002159985784730224</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.04345502810915009</v>
+        <v>0.04345502810915004</v>
       </c>
     </row>
     <row r="51">
@@ -5134,16 +5134,16 @@
         <v>0.1714635834683609</v>
       </c>
       <c r="Q51" t="n">
-        <v>20.22568990464505</v>
+        <v>20.22568990467636</v>
       </c>
       <c r="R51" t="n">
-        <v>1.88292727776961</v>
+        <v>1.882927277770174</v>
       </c>
       <c r="S51" t="n">
-        <v>0.006866587915325191</v>
+        <v>0.006866587915312488</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1163419779105917</v>
+        <v>0.1163419779105216</v>
       </c>
       <c r="U51" t="n">
         <v>0.002098333333333333</v>
@@ -5152,7 +5152,7 @@
         <v>0.002098333333333333</v>
       </c>
       <c r="W51" t="n">
-        <v>20.11820096978532</v>
+        <v>20.11820096981678</v>
       </c>
       <c r="X51" t="n">
         <v>0.001401645203937436</v>
@@ -5164,10 +5164,10 @@
         <v>0.02413582546819065</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.001421388845636275</v>
+        <v>0.001421388845634071</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.02874857002576069</v>
+        <v>0.02874857002576062</v>
       </c>
     </row>
     <row r="52">
@@ -5226,16 +5226,16 @@
         <v>0.1940649581558863</v>
       </c>
       <c r="Q52" t="n">
-        <v>20.34328539671193</v>
+        <v>20.34328539674237</v>
       </c>
       <c r="R52" t="n">
-        <v>1.885050611102943</v>
+        <v>1.885050611103508</v>
       </c>
       <c r="S52" t="n">
-        <v>0.006981708507962712</v>
+        <v>0.006981718078190372</v>
       </c>
       <c r="T52" t="n">
-        <v>0.1188462814509948</v>
+        <v>0.1188464761410522</v>
       </c>
       <c r="U52" t="n">
         <v>0.002148333333333333</v>
@@ -5244,7 +5244,7 @@
         <v>0.002148333333333333</v>
       </c>
       <c r="W52" t="n">
-        <v>20.22568990464505</v>
+        <v>20.22568990467636</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
@@ -5256,10 +5256,10 @@
         <v>0.03974752399441857</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.002253972861086382</v>
+        <v>0.002253972861083005</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.0458532131895236</v>
+        <v>0.04585321318952352</v>
       </c>
     </row>
     <row r="53">
@@ -5318,16 +5318,16 @@
         <v>0.2229784488956445</v>
       </c>
       <c r="Q53" t="n">
-        <v>20.47349558519533</v>
+        <v>20.47349558522638</v>
       </c>
       <c r="R53" t="n">
-        <v>1.887407312491832</v>
+        <v>1.887407312492397</v>
       </c>
       <c r="S53" t="n">
-        <v>0.007103330707160857</v>
+        <v>0.007103332026096677</v>
       </c>
       <c r="T53" t="n">
-        <v>0.1215385722763077</v>
+        <v>0.1215385992797259</v>
       </c>
       <c r="U53" t="n">
         <v>0.0022025</v>
@@ -5336,7 +5336,7 @@
         <v>0.0022025</v>
       </c>
       <c r="W53" t="n">
-        <v>20.34328539671193</v>
+        <v>20.34328539674237</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
@@ -5348,10 +5348,10 @@
         <v>0.07526448485171559</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.004133579428144476</v>
+        <v>0.0041335794281382</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.08462882017317015</v>
+        <v>0.08462882017317004</v>
       </c>
     </row>
     <row r="54">
@@ -5410,16 +5410,16 @@
         <v>0.2989185664601128</v>
       </c>
       <c r="Q54" t="n">
-        <v>20.58181820755303</v>
+        <v>20.58181820758407</v>
       </c>
       <c r="R54" t="n">
-        <v>1.889372361102943</v>
+        <v>1.889372361103508</v>
       </c>
       <c r="S54" t="n">
-        <v>0.007200136731513198</v>
+        <v>0.007200136731500186</v>
       </c>
       <c r="T54" t="n">
-        <v>0.1237179128246555</v>
+        <v>0.1237179128245816</v>
       </c>
       <c r="U54" t="n">
         <v>0.002246666666666667</v>
@@ -5428,7 +5428,7 @@
         <v>0.002246666666666667</v>
       </c>
       <c r="W54" t="n">
-        <v>20.47349558519533</v>
+        <v>20.47349558522638</v>
       </c>
       <c r="X54" t="n">
         <v>0.00396735495458923</v>
@@ -5440,10 +5440,10 @@
         <v>0.102602067198723</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.00553492897706259</v>
+        <v>0.005534928977054236</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.1139189019976197</v>
+        <v>0.1139189019976196</v>
       </c>
     </row>
     <row r="55">
@@ -6882,16 +6882,16 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>15.01969250829702</v>
+        <v>15.01969250829701</v>
       </c>
       <c r="R70" t="n">
         <v>1.792146527775721</v>
       </c>
       <c r="S70" t="n">
-        <v>0.009244457711781045</v>
+        <v>0.009244457741737573</v>
       </c>
       <c r="T70" t="n">
-        <v>0.1221151692588028</v>
+        <v>0.1221151697087406</v>
       </c>
       <c r="U70" t="n">
         <v>0.001996666666666667</v>
@@ -6912,7 +6912,7 @@
         <v>0.06320238611045444</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.004235445898201379</v>
+        <v>0.00423544589820138</v>
       </c>
       <c r="AB70" t="n">
         <v>0.06361509502651258</v>
@@ -6980,10 +6980,10 @@
         <v>1.794373111109054</v>
       </c>
       <c r="S71" t="n">
-        <v>0.009402010871868823</v>
+        <v>0.009402010873351092</v>
       </c>
       <c r="T71" t="n">
-        <v>0.1251651756272311</v>
+        <v>0.1251651756496959</v>
       </c>
       <c r="U71" t="n">
         <v>0.002051666666666667</v>
@@ -6992,7 +6992,7 @@
         <v>0.002051666666666667</v>
       </c>
       <c r="W71" t="n">
-        <v>15.01969250829702</v>
+        <v>15.01969250829701</v>
       </c>
       <c r="X71" t="n">
         <v>0.00139773628339818</v>
@@ -7072,10 +7072,10 @@
         <v>1.796379749997943</v>
       </c>
       <c r="S72" t="n">
-        <v>0.009535870585130196</v>
+        <v>0.00953587058164054</v>
       </c>
       <c r="T72" t="n">
-        <v>0.1278286042487415</v>
+        <v>0.1278286041954265</v>
       </c>
       <c r="U72" t="n">
         <v>0.0021</v>
@@ -7096,7 +7096,7 @@
         <v>0.03650228328522884</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.00273972621461791</v>
+        <v>0.002739726214617911</v>
       </c>
       <c r="AB72" t="n">
         <v>0.04185748085752747</v>
@@ -7158,16 +7158,16 @@
         <v>0.1703755277559266</v>
       </c>
       <c r="Q73" t="n">
-        <v>15.40717642247016</v>
+        <v>15.40717642247015</v>
       </c>
       <c r="R73" t="n">
         <v>1.798504749997943</v>
       </c>
       <c r="S73" t="n">
-        <v>0.009669531240909355</v>
+        <v>0.009669531246993858</v>
       </c>
       <c r="T73" t="n">
-        <v>0.1305618574758552</v>
+        <v>0.1305618575696002</v>
       </c>
       <c r="U73" t="n">
         <v>0.00215</v>
@@ -7188,7 +7188,7 @@
         <v>0.01662203559450923</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.001732058081469854</v>
+        <v>0.001732058081469855</v>
       </c>
       <c r="AB73" t="n">
         <v>0.02668612443517123</v>
@@ -7250,16 +7250,16 @@
         <v>0.2036432131066642</v>
       </c>
       <c r="Q74" t="n">
-        <v>15.54576471838672</v>
+        <v>15.54576471838671</v>
       </c>
       <c r="R74" t="n">
-        <v>1.800789812497943</v>
+        <v>1.800789812497944</v>
       </c>
       <c r="S74" t="n">
-        <v>0.009804928460793325</v>
+        <v>0.009804928460010224</v>
       </c>
       <c r="T74" t="n">
-        <v>0.1334114833812312</v>
+        <v>0.1334114833690572</v>
       </c>
       <c r="U74" t="n">
         <v>0.0022025</v>
@@ -7268,7 +7268,7 @@
         <v>0.0022025</v>
       </c>
       <c r="W74" t="n">
-        <v>15.40717642247016</v>
+        <v>15.40717642247015</v>
       </c>
       <c r="X74" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.0006703122036587193</v>
+        <v>0.0006703122036587197</v>
       </c>
       <c r="AB74" t="n">
         <v>0.01042051580594177</v>
@@ -7345,13 +7345,13 @@
         <v>15.66240050600434</v>
       </c>
       <c r="R75" t="n">
-        <v>1.802717423609054</v>
+        <v>1.802717423609055</v>
       </c>
       <c r="S75" t="n">
-        <v>0.009912768032329064</v>
+        <v>0.009912768032329062</v>
       </c>
       <c r="T75" t="n">
-        <v>0.1357454552760377</v>
+        <v>0.1357454552760376</v>
       </c>
       <c r="U75" t="n">
         <v>0.002245833333333333</v>
@@ -7360,7 +7360,7 @@
         <v>0.002245833333333333</v>
       </c>
       <c r="W75" t="n">
-        <v>15.54576471838672</v>
+        <v>15.54576471838671</v>
       </c>
       <c r="X75" t="n">
         <v>0.07036365759109456</v>
@@ -8725,13 +8725,13 @@
         <v>23.93967898481781</v>
       </c>
       <c r="R90" t="n">
-        <v>2.098491694429186</v>
+        <v>2.098491694429187</v>
       </c>
       <c r="S90" t="n">
-        <v>0.01007990385835065</v>
+        <v>0.01007990389195562</v>
       </c>
       <c r="T90" t="n">
-        <v>0.1949549898908649</v>
+        <v>0.194954990695357</v>
       </c>
       <c r="U90" t="n">
         <v>0.004063333333333333</v>
@@ -8814,16 +8814,16 @@
         <v>0.06375494686076261</v>
       </c>
       <c r="Q91" t="n">
-        <v>24.2281458354068</v>
+        <v>24.22814583540682</v>
       </c>
       <c r="R91" t="n">
-        <v>2.104521249984742</v>
+        <v>2.104521249984743</v>
       </c>
       <c r="S91" t="n">
-        <v>0.01063211161318078</v>
+        <v>0.01063211162014986</v>
       </c>
       <c r="T91" t="n">
-        <v>0.2075172961978925</v>
+        <v>0.2075172963667405</v>
       </c>
       <c r="U91" t="n">
         <v>0.00435</v>
@@ -8844,7 +8844,7 @@
         <v>0.06485638924285067</v>
       </c>
       <c r="AA91" t="n">
-        <v>0.002715697513538642</v>
+        <v>0.00271569751353864</v>
       </c>
       <c r="AB91" t="n">
         <v>0.06579631540286586</v>
@@ -8906,16 +8906,16 @@
         <v>0.1716212668026328</v>
       </c>
       <c r="Q92" t="n">
-        <v>24.54912556934149</v>
+        <v>24.54912556934151</v>
       </c>
       <c r="R92" t="n">
-        <v>2.111271249984742</v>
+        <v>2.111271249984743</v>
       </c>
       <c r="S92" t="n">
-        <v>0.01118090176887276</v>
+        <v>0.01118090177937685</v>
       </c>
       <c r="T92" t="n">
-        <v>0.220412783673763</v>
+        <v>0.2204127839316294</v>
       </c>
       <c r="U92" t="n">
         <v>0.00465</v>
@@ -8924,7 +8924,7 @@
         <v>0.00465</v>
       </c>
       <c r="W92" t="n">
-        <v>24.2281458354068</v>
+        <v>24.22814583540682</v>
       </c>
       <c r="X92" t="n">
         <v>0.01411667984325947</v>
@@ -8936,7 +8936,7 @@
         <v>0.04872158819598323</v>
       </c>
       <c r="AA92" t="n">
-        <v>0.002019535772512295</v>
+        <v>0.002019535772512294</v>
       </c>
       <c r="AB92" t="n">
         <v>0.0495778372711814</v>
@@ -8998,16 +8998,16 @@
         <v>0.2547670720457892</v>
       </c>
       <c r="Q93" t="n">
-        <v>25.00680786687654</v>
+        <v>25.00680786687655</v>
       </c>
       <c r="R93" t="n">
-        <v>2.120971249984742</v>
+        <v>2.120971249984743</v>
       </c>
       <c r="S93" t="n">
-        <v>0.01186590941261322</v>
+        <v>0.01186590939888761</v>
       </c>
       <c r="T93" t="n">
-        <v>0.2371876910443514</v>
+        <v>0.2371876907011177</v>
       </c>
       <c r="U93" t="n">
         <v>0.005050000000000001</v>
@@ -9016,7 +9016,7 @@
         <v>0.005050000000000001</v>
       </c>
       <c r="W93" t="n">
-        <v>24.54912556934149</v>
+        <v>24.54912556934151</v>
       </c>
       <c r="X93" t="n">
         <v>0.01729347944990734</v>
@@ -9090,16 +9090,16 @@
         <v>0.3345630000595383</v>
       </c>
       <c r="Q94" t="n">
-        <v>26.11045456330865</v>
+        <v>26.11045456330866</v>
       </c>
       <c r="R94" t="n">
-        <v>2.144732361095853</v>
+        <v>2.144732361095854</v>
       </c>
       <c r="S94" t="n">
-        <v>0.01316720048945217</v>
+        <v>0.01316720038405787</v>
       </c>
       <c r="T94" t="n">
-        <v>0.2717707582087737</v>
+        <v>0.2717707554568806</v>
       </c>
       <c r="U94" t="n">
         <v>0.005916666666666667</v>
@@ -9108,7 +9108,7 @@
         <v>0.005916666666666667</v>
       </c>
       <c r="W94" t="n">
-        <v>25.00680786687654</v>
+        <v>25.00680786687655</v>
       </c>
       <c r="X94" t="n">
         <v>0.01396089162246411</v>
@@ -9120,10 +9120,10 @@
         <v>0.002777158124534164</v>
       </c>
       <c r="AA94" t="n">
-        <v>0.0001589641491270463</v>
+        <v>0.0001589641491270462</v>
       </c>
       <c r="AB94" t="n">
-        <v>0.004150626192976762</v>
+        <v>0.004150626192976761</v>
       </c>
     </row>
     <row r="95">
@@ -9182,16 +9182,16 @@
         <v>0.4114676331552647</v>
       </c>
       <c r="Q95" t="n">
-        <v>26.57397314534753</v>
+        <v>26.57397314534754</v>
       </c>
       <c r="R95" t="n">
-        <v>2.154871249984741</v>
+        <v>2.154871249984743</v>
       </c>
       <c r="S95" t="n">
-        <v>0.01360207801067354</v>
+        <v>0.01360207800305404</v>
       </c>
       <c r="T95" t="n">
-        <v>0.284385963153116</v>
+        <v>0.2843859629506359</v>
       </c>
       <c r="U95" t="n">
         <v>0.00625</v>
@@ -9200,7 +9200,7 @@
         <v>0.00625</v>
       </c>
       <c r="W95" t="n">
-        <v>26.11045456330865</v>
+        <v>26.11045456330866</v>
       </c>
       <c r="X95" t="n">
         <v>0.01145255846603085</v>
@@ -9212,10 +9212,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>4.439867806962225e-05</v>
+        <v>4.43986780696222e-05</v>
       </c>
       <c r="AB95" t="n">
-        <v>0.001179849278711072</v>
+        <v>0.001179849278711071</v>
       </c>
     </row>
     <row r="96">
@@ -9277,13 +9277,13 @@
         <v>27.30784322790872</v>
       </c>
       <c r="R96" t="n">
-        <v>2.171121249984742</v>
+        <v>2.171121249984743</v>
       </c>
       <c r="S96" t="n">
-        <v>0.0141884524772847</v>
+        <v>0.01418845246147928</v>
       </c>
       <c r="T96" t="n">
-        <v>0.3025561521198283</v>
+        <v>0.3025561516882164</v>
       </c>
       <c r="U96" t="n">
         <v>0.006750000000000001</v>
@@ -9292,7 +9292,7 @@
         <v>0.006750000000000001</v>
       </c>
       <c r="W96" t="n">
-        <v>26.57397314534753</v>
+        <v>26.57397314534754</v>
       </c>
       <c r="X96" t="n">
         <v>0.009152735978746178</v>
@@ -9304,10 +9304,10 @@
         <v>0.001762949417501451</v>
       </c>
       <c r="AA96" t="n">
-        <v>4.578707085297216e-05</v>
+        <v>4.578707085297215e-05</v>
       </c>
       <c r="AB96" t="n">
-        <v>0.001250346152718113</v>
+        <v>0.001250346152718112</v>
       </c>
     </row>
     <row r="97">
@@ -9366,16 +9366,16 @@
         <v>0.4021708299263646</v>
       </c>
       <c r="Q97" t="n">
-        <v>27.82182632859926</v>
+        <v>27.82182632859923</v>
       </c>
       <c r="R97" t="n">
-        <v>2.182649027762519</v>
+        <v>2.182649027762521</v>
       </c>
       <c r="S97" t="n">
-        <v>0.01453689713190097</v>
+        <v>0.01453689738861425</v>
       </c>
       <c r="T97" t="n">
-        <v>0.3141530781652856</v>
+        <v>0.3141530853075174</v>
       </c>
       <c r="U97" t="n">
         <v>0.007083333333333334</v>
@@ -9396,7 +9396,7 @@
         <v>0.001647154283060745</v>
       </c>
       <c r="AA97" t="n">
-        <v>4.518776391829951e-05</v>
+        <v>4.518776391829954e-05</v>
       </c>
       <c r="AB97" t="n">
         <v>0.001257206119912673</v>
@@ -9458,16 +9458,16 @@
         <v>0.3873938421634567</v>
       </c>
       <c r="Q98" t="n">
-        <v>28.72212538793306</v>
+        <v>28.72212538793305</v>
       </c>
       <c r="R98" t="n">
-        <v>2.203138999984742</v>
+        <v>2.203138999984743</v>
       </c>
       <c r="S98" t="n">
-        <v>0.01504659661368045</v>
+        <v>0.01504659661323521</v>
       </c>
       <c r="T98" t="n">
-        <v>0.332568240370033</v>
+        <v>0.3325682403572446</v>
       </c>
       <c r="U98" t="n">
         <v>0.007640000000000001</v>
@@ -9476,7 +9476,7 @@
         <v>0.007640000000000001</v>
       </c>
       <c r="W98" t="n">
-        <v>27.82182632859926</v>
+        <v>27.82182632859923</v>
       </c>
       <c r="X98" t="n">
         <v>0.007018151213335786</v>
@@ -9488,10 +9488,10 @@
         <v>0.0005503013934911842</v>
       </c>
       <c r="AA98" t="n">
-        <v>4.454302433905063e-05</v>
+        <v>4.454302433905062e-05</v>
       </c>
       <c r="AB98" t="n">
-        <v>0.001279370330223966</v>
+        <v>0.001279370330223965</v>
       </c>
     </row>
     <row r="99">
@@ -9550,16 +9550,16 @@
         <v>0.3689307159607038</v>
       </c>
       <c r="Q99" t="n">
-        <v>29.76547646571372</v>
+        <v>29.76547646571371</v>
       </c>
       <c r="R99" t="n">
-        <v>2.227371249984742</v>
+        <v>2.227371249984743</v>
       </c>
       <c r="S99" t="n">
-        <v>0.01550784152635049</v>
+        <v>0.0155078415118352</v>
       </c>
       <c r="T99" t="n">
-        <v>0.3513494141473926</v>
+        <v>0.3513494137153382</v>
       </c>
       <c r="U99" t="n">
         <v>0.00825</v>
@@ -9568,7 +9568,7 @@
         <v>0.00825</v>
       </c>
       <c r="W99" t="n">
-        <v>28.72212538793306</v>
+        <v>28.72212538793305</v>
       </c>
       <c r="X99" t="n">
         <v>0.01009923569250023</v>
@@ -9580,10 +9580,10 @@
         <v>0.0004247662125730495</v>
       </c>
       <c r="AA99" t="n">
-        <v>4.408174559026024e-05</v>
+        <v>4.408174559026023e-05</v>
       </c>
       <c r="AB99" t="n">
-        <v>0.001312114160934471</v>
+        <v>0.00131211416093447</v>
       </c>
     </row>
     <row r="100">
@@ -9642,16 +9642,16 @@
         <v>0.3542503465167628</v>
       </c>
       <c r="Q100" t="n">
-        <v>30.84541916498261</v>
+        <v>30.84541916498249</v>
       </c>
       <c r="R100" t="n">
-        <v>2.253021249984741</v>
+        <v>2.253021249984743</v>
       </c>
       <c r="S100" t="n">
-        <v>0.01587051772024678</v>
+        <v>0.01587051773015364</v>
       </c>
       <c r="T100" t="n">
-        <v>0.3683701505380624</v>
+        <v>0.3683701508436424</v>
       </c>
       <c r="U100" t="n">
         <v>0.00885</v>
@@ -9660,7 +9660,7 @@
         <v>0.00885</v>
       </c>
       <c r="W100" t="n">
-        <v>29.76547646571372</v>
+        <v>29.76547646571371</v>
       </c>
       <c r="X100" t="n">
         <v>0.007799312579268405</v>
@@ -9672,10 +9672,10 @@
         <v>0.008954679612111731</v>
       </c>
       <c r="AA100" t="n">
-        <v>0.0003012099228746787</v>
+        <v>0.0003012099228746798</v>
       </c>
       <c r="AB100" t="n">
-        <v>0.009290946327721547</v>
+        <v>0.009290946327721546</v>
       </c>
     </row>
     <row r="101">
@@ -9737,13 +9737,13 @@
         <v>31.81469618008588</v>
       </c>
       <c r="R101" t="n">
-        <v>2.276551111095853</v>
+        <v>2.276551111095854</v>
       </c>
       <c r="S101" t="n">
-        <v>0.0161169662921108</v>
+        <v>0.01611696629211079</v>
       </c>
       <c r="T101" t="n">
-        <v>0.381857653732939</v>
+        <v>0.3818576537329387</v>
       </c>
       <c r="U101" t="n">
         <v>0.009366666666666667</v>
@@ -9752,7 +9752,7 @@
         <v>0.009366666666666667</v>
       </c>
       <c r="W101" t="n">
-        <v>30.84541916498261</v>
+        <v>30.84541916498249</v>
       </c>
       <c r="X101" t="n">
         <v>0.006429284455135683</v>
@@ -10838,16 +10838,16 @@
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>28.24180486689044</v>
+        <v>28.24180486627348</v>
       </c>
       <c r="R113" t="n">
-        <v>2.198068889704303</v>
+        <v>2.198068889704301</v>
       </c>
       <c r="S113" t="n">
-        <v>0.007073425374068638</v>
+        <v>0.007080000683784983</v>
       </c>
       <c r="T113" t="n">
-        <v>0.1091418130006905</v>
+        <v>0.1093275116122504</v>
       </c>
       <c r="U113" t="n">
         <v>0.007053333333333333</v>
@@ -10868,7 +10868,7 @@
         <v>0.04292053230848831</v>
       </c>
       <c r="AA113" t="n">
-        <v>0.001524917290366768</v>
+        <v>0.00152491729040008</v>
       </c>
       <c r="AB113" t="n">
         <v>0.04306641655268557</v>
@@ -10930,16 +10930,16 @@
         <v>0.05060060245371522</v>
       </c>
       <c r="Q114" t="n">
-        <v>28.4719136932896</v>
+        <v>28.47191369328903</v>
       </c>
       <c r="R114" t="n">
-        <v>2.20332922829797</v>
+        <v>2.203329228297967</v>
       </c>
       <c r="S114" t="n">
-        <v>0.007575517607850952</v>
+        <v>0.00757552039323006</v>
       </c>
       <c r="T114" t="n">
-        <v>0.1171359889591415</v>
+        <v>0.1171360682642126</v>
       </c>
       <c r="U114" t="n">
         <v>0.007626666666666667</v>
@@ -10948,7 +10948,7 @@
         <v>0.003813333333333334</v>
       </c>
       <c r="W114" t="n">
-        <v>28.24180486689044</v>
+        <v>28.24180486627348</v>
       </c>
       <c r="X114" t="n">
         <v>0.009793628241382288</v>
@@ -10960,7 +10960,7 @@
         <v>0.03670292593065684</v>
       </c>
       <c r="AA114" t="n">
-        <v>0.001330806855107746</v>
+        <v>0.001330806855107773</v>
       </c>
       <c r="AB114" t="n">
         <v>0.03789061792106591</v>
@@ -11022,16 +11022,16 @@
         <v>0.1044036282464569</v>
       </c>
       <c r="Q115" t="n">
-        <v>28.65987999487133</v>
+        <v>28.65987999487103</v>
       </c>
       <c r="R115" t="n">
-        <v>2.207644899280303</v>
+        <v>2.2076448992803</v>
       </c>
       <c r="S115" t="n">
-        <v>0.00794445905433588</v>
+        <v>0.007944459054335953</v>
       </c>
       <c r="T115" t="n">
-        <v>0.1229649217459896</v>
+        <v>0.1229649217459902</v>
       </c>
       <c r="U115" t="n">
         <v>0.008066666666666666</v>
@@ -11040,7 +11040,7 @@
         <v>0.004033333333333333</v>
       </c>
       <c r="W115" t="n">
-        <v>28.4719136932896</v>
+        <v>28.47191369328903</v>
       </c>
       <c r="X115" t="n">
         <v>0.01308713559294417</v>
@@ -11052,7 +11052,7 @@
         <v>0.03226430616673658</v>
       </c>
       <c r="AA115" t="n">
-        <v>0.001176819229347405</v>
+        <v>0.001176819229347417</v>
       </c>
       <c r="AB115" t="n">
         <v>0.03372749788875357</v>
@@ -11114,16 +11114,16 @@
         <v>0.1491197853115378</v>
       </c>
       <c r="Q116" t="n">
-        <v>28.92563754904613</v>
+        <v>28.92563754904579</v>
       </c>
       <c r="R116" t="n">
-        <v>2.213775572077636</v>
+        <v>2.213775572077634</v>
       </c>
       <c r="S116" t="n">
-        <v>0.008420554940362099</v>
+        <v>0.008420554940362222</v>
       </c>
       <c r="T116" t="n">
-        <v>0.1305037237789281</v>
+        <v>0.13050372377893</v>
       </c>
       <c r="U116" t="n">
         <v>0.008653333333333332</v>
@@ -11132,7 +11132,7 @@
         <v>0.004326666666666666</v>
       </c>
       <c r="W116" t="n">
-        <v>28.65987999487133</v>
+        <v>28.65987999487103</v>
       </c>
       <c r="X116" t="n">
         <v>0.01416473965932023</v>
@@ -11144,7 +11144,7 @@
         <v>0.02491516024776152</v>
       </c>
       <c r="AA116" t="n">
-        <v>0.0008945528030802108</v>
+        <v>0.0008945528030802212</v>
       </c>
       <c r="AB116" t="n">
         <v>0.02587551015038141</v>
@@ -11206,16 +11206,16 @@
         <v>0.1918414613393818</v>
       </c>
       <c r="Q117" t="n">
-        <v>29.46262799242935</v>
+        <v>29.46262799242903</v>
       </c>
       <c r="R117" t="n">
-        <v>2.226267723458665</v>
+        <v>2.226267723458661</v>
       </c>
       <c r="S117" t="n">
-        <v>0.009253028608468959</v>
+        <v>0.009253028608469023</v>
       </c>
       <c r="T117" t="n">
-        <v>0.1437185005742468</v>
+        <v>0.143718500574247</v>
       </c>
       <c r="U117" t="n">
         <v>0.009740000000000002</v>
@@ -11224,7 +11224,7 @@
         <v>0.004870000000000001</v>
       </c>
       <c r="W117" t="n">
-        <v>28.92563754904613</v>
+        <v>28.92563754904579</v>
       </c>
       <c r="X117" t="n">
         <v>0.01158551351625574</v>
@@ -11236,7 +11236,7 @@
         <v>0.01583178431944987</v>
       </c>
       <c r="AA117" t="n">
-        <v>0.0005561275272637983</v>
+        <v>0.0005561275272638044</v>
       </c>
       <c r="AB117" t="n">
         <v>0.0163849784521229</v>
@@ -11298,16 +11298,16 @@
         <v>0.2448076315621145</v>
       </c>
       <c r="Q118" t="n">
-        <v>30.73245487142585</v>
+        <v>30.73245487142606</v>
       </c>
       <c r="R118" t="n">
-        <v>2.256376503567415</v>
+        <v>2.256376503567412</v>
       </c>
       <c r="S118" t="n">
-        <v>0.01074722783805307</v>
+        <v>0.01074722221765609</v>
       </c>
       <c r="T118" t="n">
-        <v>0.1673902776698777</v>
+        <v>0.1673901049412822</v>
       </c>
       <c r="U118" t="n">
         <v>0.01196</v>
@@ -11316,7 +11316,7 @@
         <v>0.005979999999999999</v>
       </c>
       <c r="W118" t="n">
-        <v>29.46262799242935</v>
+        <v>29.46262799242903</v>
       </c>
       <c r="X118" t="n">
         <v>0.01018412764647287</v>
@@ -11328,10 +11328,10 @@
         <v>0.003813578138281135</v>
       </c>
       <c r="AA118" t="n">
-        <v>0.000160639813569606</v>
+        <v>0.000160639813569605</v>
       </c>
       <c r="AB118" t="n">
-        <v>0.004936855821082178</v>
+        <v>0.00493685582108218</v>
       </c>
     </row>
     <row r="119">
@@ -11390,16 +11390,16 @@
         <v>0.2862295508009267</v>
       </c>
       <c r="Q119" t="n">
-        <v>31.15248097069052</v>
+        <v>31.15248097068831</v>
       </c>
       <c r="R119" t="n">
-        <v>2.266515763706664</v>
+        <v>2.266515763706662</v>
       </c>
       <c r="S119" t="n">
-        <v>0.01113732683946593</v>
+        <v>0.01113734544500751</v>
       </c>
       <c r="T119" t="n">
-        <v>0.173497795470351</v>
+        <v>0.1734983750791186</v>
       </c>
       <c r="U119" t="n">
         <v>0.01262</v>
@@ -11408,7 +11408,7 @@
         <v>0.00631</v>
       </c>
       <c r="W119" t="n">
-        <v>30.73245487142585</v>
+        <v>30.73245487142606</v>
       </c>
       <c r="X119" t="n">
         <v>0.0085377509283628</v>
@@ -11420,10 +11420,10 @@
         <v>0.002635143243149769</v>
       </c>
       <c r="AA119" t="n">
-        <v>0.000121230682064597</v>
+        <v>0.0001212306820646056</v>
       </c>
       <c r="AB119" t="n">
-        <v>0.003776636516081191</v>
+        <v>0.003776636516081192</v>
       </c>
     </row>
     <row r="120">
@@ -11482,16 +11482,16 @@
         <v>0.2889524121591054</v>
       </c>
       <c r="Q120" t="n">
-        <v>31.55039960381771</v>
+        <v>31.55039960381902</v>
       </c>
       <c r="R120" t="n">
-        <v>2.276205773396665</v>
+        <v>2.276205773396662</v>
       </c>
       <c r="S120" t="n">
-        <v>0.01147068869907342</v>
+        <v>0.0114706754208951</v>
       </c>
       <c r="T120" t="n">
-        <v>0.1786629068909775</v>
+        <v>0.1786624879591527</v>
       </c>
       <c r="U120" t="n">
         <v>0.01322</v>
@@ -11500,7 +11500,7 @@
         <v>0.00661</v>
       </c>
       <c r="W120" t="n">
-        <v>31.15248097069052</v>
+        <v>31.15248097068831</v>
       </c>
       <c r="X120" t="n">
         <v>0.01094124388489767</v>
@@ -11512,10 +11512,10 @@
         <v>0.003468413842637606</v>
       </c>
       <c r="AA120" t="n">
-        <v>0.0001197389718612531</v>
+        <v>0.0001197389718612482</v>
       </c>
       <c r="AB120" t="n">
-        <v>0.003777812410372821</v>
+        <v>0.003777812410372823</v>
       </c>
     </row>
     <row r="121">
@@ -11574,16 +11574,16 @@
         <v>0.2916972101212668</v>
       </c>
       <c r="Q121" t="n">
-        <v>31.95385449141564</v>
+        <v>31.95385449141525</v>
       </c>
       <c r="R121" t="n">
-        <v>2.28611556108422</v>
+        <v>2.286115561084217</v>
       </c>
       <c r="S121" t="n">
-        <v>0.01177718080478872</v>
+        <v>0.01177717876146381</v>
       </c>
       <c r="T121" t="n">
-        <v>0.1833456058247001</v>
+        <v>0.1833455405325909</v>
       </c>
       <c r="U121" t="n">
         <v>0.01380666666666667</v>
@@ -11592,7 +11592,7 @@
         <v>0.006903333333333334</v>
       </c>
       <c r="W121" t="n">
-        <v>31.55039960381771</v>
+        <v>31.55039960381902</v>
       </c>
       <c r="X121" t="n">
         <v>0.01496737650102324</v>
@@ -11604,10 +11604,10 @@
         <v>0.004427144891717553</v>
       </c>
       <c r="AA121" t="n">
-        <v>0.0001359515592164663</v>
+        <v>0.000135951559216468</v>
       </c>
       <c r="AB121" t="n">
-        <v>0.004344176341084041</v>
+        <v>0.004344176341084043</v>
       </c>
     </row>
     <row r="122">
@@ -11666,16 +11666,16 @@
         <v>0.2947411967231239</v>
       </c>
       <c r="Q122" t="n">
-        <v>32.83159453257404</v>
+        <v>32.83159453257299</v>
       </c>
       <c r="R122" t="n">
-        <v>2.307975805166664</v>
+        <v>2.307975805166662</v>
       </c>
       <c r="S122" t="n">
-        <v>0.01235151587956077</v>
+        <v>0.01235152298094111</v>
       </c>
       <c r="T122" t="n">
-        <v>0.1918563046190789</v>
+        <v>0.1918565377687123</v>
       </c>
       <c r="U122" t="n">
         <v>0.01502</v>
@@ -11684,7 +11684,7 @@
         <v>0.007509999999999999</v>
       </c>
       <c r="W122" t="n">
-        <v>31.95385449141564</v>
+        <v>31.95385449141525</v>
       </c>
       <c r="X122" t="n">
         <v>0.01393403278476044</v>
@@ -11696,10 +11696,10 @@
         <v>0.006989072490978496</v>
       </c>
       <c r="AA122" t="n">
-        <v>0.0002310196494435016</v>
+        <v>0.0002310196494435091</v>
       </c>
       <c r="AB122" t="n">
-        <v>0.007584743459586439</v>
+        <v>0.007584743459586441</v>
       </c>
     </row>
     <row r="123">
@@ -11758,16 +11758,16 @@
         <v>0.3061500936386944</v>
       </c>
       <c r="Q123" t="n">
-        <v>33.75408934834007</v>
+        <v>33.75408934834168</v>
       </c>
       <c r="R123" t="n">
-        <v>2.331405828596664</v>
+        <v>2.331405828596663</v>
       </c>
       <c r="S123" t="n">
-        <v>0.01284342625596111</v>
+        <v>0.01284341423264229</v>
       </c>
       <c r="T123" t="n">
-        <v>0.1986850268676124</v>
+        <v>0.1986846210314439</v>
       </c>
       <c r="U123" t="n">
         <v>0.01622</v>
@@ -11776,7 +11776,7 @@
         <v>0.008110000000000001</v>
       </c>
       <c r="W123" t="n">
-        <v>32.83159453257404</v>
+        <v>32.83159453257299</v>
       </c>
       <c r="X123" t="n">
         <v>0.01157922320647989</v>
@@ -11788,7 +11788,7 @@
         <v>0.01216839656025612</v>
       </c>
       <c r="AA123" t="n">
-        <v>0.0004041724259930121</v>
+        <v>0.0004041724259929929</v>
       </c>
       <c r="AB123" t="n">
         <v>0.0136424721791035</v>
@@ -11850,16 +11850,16 @@
         <v>0.3308651428571041</v>
       </c>
       <c r="Q124" t="n">
-        <v>34.61647934279934</v>
+        <v>34.61647934279866</v>
       </c>
       <c r="R124" t="n">
-        <v>2.35374362871222</v>
+        <v>2.353743628712218</v>
       </c>
       <c r="S124" t="n">
-        <v>0.0132203465779301</v>
+        <v>0.01322035179421022</v>
       </c>
       <c r="T124" t="n">
-        <v>0.2034070546972727</v>
+        <v>0.2034072352665216</v>
       </c>
       <c r="U124" t="n">
         <v>0.01728666666666667</v>
@@ -11868,7 +11868,7 @@
         <v>0.008643333333333333</v>
       </c>
       <c r="W124" t="n">
-        <v>33.75408934834007</v>
+        <v>33.75408934834168</v>
       </c>
       <c r="X124" t="n">
         <v>0.009267599997966548</v>
@@ -11880,10 +11880,10 @@
         <v>0.01961652719811411</v>
       </c>
       <c r="AA124" t="n">
-        <v>0.0006187360183830693</v>
+        <v>0.0006187360183830816</v>
       </c>
       <c r="AB124" t="n">
-        <v>0.02141846259900343</v>
+        <v>0.02141846259900344</v>
       </c>
     </row>
     <row r="125">
@@ -11942,16 +11942,16 @@
         <v>0.3724108962071924</v>
       </c>
       <c r="Q125" t="n">
-        <v>35.52745852239729</v>
+        <v>35.52745852239767</v>
       </c>
       <c r="R125" t="n">
-        <v>2.377809652778219</v>
+        <v>2.377809652778218</v>
       </c>
       <c r="S125" t="n">
-        <v>0.013547618883582</v>
+        <v>0.01354761888358185</v>
       </c>
       <c r="T125" t="n">
-        <v>0.2068914320190097</v>
+        <v>0.2068914320190066</v>
       </c>
       <c r="U125" t="n">
         <v>0.01836666666666667</v>
@@ -11960,7 +11960,7 @@
         <v>0.009183333333333333</v>
       </c>
       <c r="W125" t="n">
-        <v>34.61647934279934</v>
+        <v>34.61647934279866</v>
       </c>
       <c r="X125" t="n">
         <v>0.006196243412663805</v>
@@ -11972,7 +11972,7 @@
         <v>0.02963924799363945</v>
       </c>
       <c r="AA125" t="n">
-        <v>0.0008844102245227442</v>
+        <v>0.0008844102245227347</v>
       </c>
       <c r="AB125" t="n">
         <v>0.03142084756851587</v>

--- a/data/processed/BR_processed.xlsx
+++ b/data/processed/BR_processed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD152"/>
+  <dimension ref="A1:AE152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,70 +511,75 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>t_ind_ad</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Xlag1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Plag1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>X_calc</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>V_calc</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>mu_calc</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dXdt_calc</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dVdt_calc</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>FS_calc</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Xlag1_calc</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mu</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>qP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>rP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>qP_calc</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>rP_calc</t>
         </is>
@@ -636,38 +641,38 @@
         <v>-8</v>
       </c>
       <c r="Q2" t="n">
+        <v>-0.3973509933774834</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.2375268817204247</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>0.2375268817204247</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>1.500919151193634</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>0.8697873804353808</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>0.2065978842345928</v>
       </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0.2375268817204247</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>2.755932637154052</v>
       </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
@@ -675,6 +680,9 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -734,38 +742,38 @@
         <v>-7.166666666666664</v>
       </c>
       <c r="Q3" t="n">
+        <v>-0.3559602649006621</v>
+      </c>
+      <c r="R3" t="n">
         <v>0.2375268817204247</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>0.4903420894035738</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>1.500919151193634</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.8697864594635719</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>0.4264929098683047</v>
       </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0.2375268817204247</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>0.7929182707910082</v>
       </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
@@ -773,6 +781,9 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -832,38 +843,38 @@
         <v>-6.383333333333335</v>
       </c>
       <c r="Q4" t="n">
+        <v>-0.3170529801324504</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.758194444444397</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>0.9691654190923694</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1.500919151193634</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>0.8697842876925092</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>0.8429648537014687</v>
       </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
         <v>0.4903420894035738</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>0.8664928233519787</v>
       </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
@@ -871,6 +882,9 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -930,20 +944,20 @@
         <v>-4.616666666666662</v>
       </c>
       <c r="Q5" t="n">
+        <v>-0.2293046357615891</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.19599999999993</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
       <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.954474381720428</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1.500919151193634</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
@@ -954,14 +968,14 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
         <v>0.9691654190923694</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>0.4390733992263243</v>
       </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
@@ -969,6 +983,9 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1028,38 +1045,38 @@
         <v>-3.883333333333331</v>
       </c>
       <c r="Q6" t="n">
+        <v>-0.1928807947019866</v>
+      </c>
+      <c r="R6" t="n">
         <v>5.025440000000001</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>6.787730966341255</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1.537009290085926</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>0.6572400022374468</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>4.218204050808298</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.05501666666666669</v>
       </c>
       <c r="X6" t="n">
         <v>0.05501666666666669</v>
       </c>
       <c r="Y6" t="n">
+        <v>0.05501666666666669</v>
+      </c>
+      <c r="Z6" t="n">
         <v>3.954474381720428</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>0.4900501784306472</v>
       </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
@@ -1067,6 +1084,9 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1126,38 +1146,38 @@
         <v>-2.266666666666666</v>
       </c>
       <c r="Q7" t="n">
+        <v>-0.1125827814569536</v>
+      </c>
+      <c r="R7" t="n">
         <v>6.17500000000001</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
       <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>14.38561313814787</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1.642941373419259</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>0.4009205674164616</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>5.101739460428912</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.07603333333333334</v>
       </c>
       <c r="X7" t="n">
         <v>0.07603333333333334</v>
       </c>
       <c r="Y7" t="n">
+        <v>0.07603333333333334</v>
+      </c>
+      <c r="Z7" t="n">
         <v>6.787730966341255</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>0.3736357386093559</v>
       </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
@@ -1165,6 +1185,9 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1224,38 +1247,38 @@
         <v>-1.466666666666667</v>
       </c>
       <c r="Q8" t="n">
+        <v>-0.0728476821192053</v>
+      </c>
+      <c r="R8" t="n">
         <v>12.87142857142852</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>18.58021293135844</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>1.707928040085926</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>0.3394415878885265</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>5.366605762357398</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.08643333333333333</v>
       </c>
       <c r="X8" t="n">
         <v>0.08643333333333333</v>
       </c>
       <c r="Y8" t="n">
+        <v>0.08643333333333333</v>
+      </c>
+      <c r="Z8" t="n">
         <v>14.38561313814787</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>0.3078573703085496</v>
       </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
@@ -1263,6 +1286,9 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1322,38 +1348,38 @@
         <v>-0.5999999999999961</v>
       </c>
       <c r="Q9" t="n">
+        <v>-0.02980132450331106</v>
+      </c>
+      <c r="R9" t="n">
         <v>16.07142857142854</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
       <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
         <v>23.31328393927748</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>1.787719151197037</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>0.2921430562264026</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>5.536728077529206</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.09770000000000005</v>
       </c>
       <c r="X9" t="n">
         <v>0.09770000000000005</v>
       </c>
       <c r="Y9" t="n">
+        <v>0.09770000000000005</v>
+      </c>
+      <c r="Z9" t="n">
         <v>18.58021293135844</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>0.2585007099421947</v>
       </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
@@ -1361,6 +1387,9 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1420,45 +1449,48 @@
         <v>1.77635683940025e-15</v>
       </c>
       <c r="Q10" t="n">
+        <v>8.822964434107203e-17</v>
+      </c>
+      <c r="R10" t="n">
         <v>19.55000000000009</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
         <v>26.65401311151907</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>1.848679151198421</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>0.225235414492541</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>5.970266593250297</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.0023</v>
       </c>
       <c r="X10" t="n">
         <v>0.0023</v>
       </c>
       <c r="Y10" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="Z10" t="n">
         <v>23.31328393927748</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>0.1678276210381796</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>0.001409663588305178</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>0.03252295278732637</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>0.001220189719696316</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>0.03252295278732637</v>
       </c>
     </row>
@@ -1518,45 +1550,48 @@
         <v>1.283333333333333</v>
       </c>
       <c r="Q11" t="n">
+        <v>0.06374172185430461</v>
+      </c>
+      <c r="R11" t="n">
         <v>23.07142857142841</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
       <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>26.81456003794531</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>1.851713165092423</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>0.006094652876519476</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>0.1282608693858629</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.002428333333333334</v>
       </c>
       <c r="X11" t="n">
         <v>0.002428333333333334</v>
       </c>
       <c r="Y11" t="n">
+        <v>0.002428333333333334</v>
+      </c>
+      <c r="Z11" t="n">
         <v>26.65401311151907</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>0.02650201917316335</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>0.004441501609194717</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>0.1065167260919373</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>0.004012411300956096</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>0.1075910437264175</v>
       </c>
     </row>
@@ -1616,45 +1651,48 @@
         <v>3.033333333333333</v>
       </c>
       <c r="Q12" t="n">
+        <v>0.1506622516556291</v>
+      </c>
+      <c r="R12" t="n">
         <v>23.9821428571428</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>0.1310102834270957</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>27.04656525722954</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>1.856115873425756</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>0.006462734701134105</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>0.1368600617928715</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.002603333333333333</v>
       </c>
       <c r="X12" t="n">
         <v>0.002603333333333333</v>
       </c>
       <c r="Y12" t="n">
+        <v>0.002603333333333333</v>
+      </c>
+      <c r="Z12" t="n">
         <v>26.81456003794531</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>5.19473822208176e-05</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>0.003429009357781865</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>0.08474551698518029</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>0.003294261940258456</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>0.08909847054160794</v>
       </c>
     </row>
@@ -1714,45 +1752,48 @@
         <v>5.15</v>
       </c>
       <c r="Q13" t="n">
+        <v>0.255794701986755</v>
+      </c>
+      <c r="R13" t="n">
         <v>24.71428571428569</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>0.3150449672599142</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>27.34710021724216</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>1.861850276203534</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>0.006890089696224523</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>0.1470768854829419</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.002815</v>
       </c>
       <c r="X13" t="n">
         <v>0.002815</v>
       </c>
       <c r="Y13" t="n">
+        <v>0.002815</v>
+      </c>
+      <c r="Z13" t="n">
         <v>27.04656525722954</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>0.009247963860255975</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>0.00255434852123139</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>0.06448817748780201</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>0.002529907594138958</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>0.06918563651728009</v>
       </c>
     </row>
@@ -1812,45 +1853,48 @@
         <v>7.150000000000002</v>
       </c>
       <c r="Q14" t="n">
+        <v>0.3551324503311259</v>
+      </c>
+      <c r="R14" t="n">
         <v>25.24642857142839</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>0.462353720667521</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>27.65075345784806</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>1.867680276203534</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>0.007275813546525556</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>0.1565450600492553</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.003015</v>
       </c>
       <c r="X14" t="n">
         <v>0.003015</v>
       </c>
       <c r="Y14" t="n">
+        <v>0.003015</v>
+      </c>
+      <c r="Z14" t="n">
         <v>27.34710021724216</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>0.00709381743588283</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>0.004181638843259673</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>0.112121445976553</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>0.004332845827374902</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
         <v>0.1198064517436091</v>
       </c>
     </row>
@@ -1910,45 +1954,48 @@
         <v>9.100000000000005</v>
       </c>
       <c r="Q15" t="n">
+        <v>0.4519867549668876</v>
+      </c>
+      <c r="R15" t="n">
         <v>26.8128</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>0.6209461221159972</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>27.96486690504819</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>1.873749651203535</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>0.007634557396181491</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>0.1655915818766285</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.003210000000000001</v>
       </c>
       <c r="X15" t="n">
         <v>0.003210000000000001</v>
       </c>
       <c r="Y15" t="n">
+        <v>0.003210000000000001</v>
+      </c>
+      <c r="Z15" t="n">
         <v>27.65075345784806</v>
       </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
       <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
         <v>0.0081223021414259</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>0.2218548813486614</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>0.008700430054214312</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
         <v>0.2433063684827845</v>
       </c>
     </row>
@@ -2008,45 +2055,48 @@
         <v>10.15</v>
       </c>
       <c r="Q16" t="n">
+        <v>0.5041390728476821</v>
+      </c>
+      <c r="R16" t="n">
         <v>27.31428571428567</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>0.9523209449429346</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>28.14125939399925</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>1.877175276203535</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.007820572933980099</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>0.1703846797234053</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.003315</v>
       </c>
       <c r="X16" t="n">
         <v>0.003315</v>
       </c>
       <c r="Y16" t="n">
+        <v>0.003315</v>
+      </c>
+      <c r="Z16" t="n">
         <v>27.96486690504819</v>
       </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
       <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
         <v>0.01172475127120083</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>0.3242312467603854</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>0.01278089828636535</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
         <v>0.3596705739649278</v>
       </c>
     </row>
@@ -2106,45 +2156,48 @@
         <v>11.16666666666667</v>
       </c>
       <c r="Q17" t="n">
+        <v>0.554635761589404</v>
+      </c>
+      <c r="R17" t="n">
         <v>27.65357142857139</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>1.25504016023201</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>28.31682006871788</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>1.88059720675909</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>0.007995870233005813</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>0.1749716551927243</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.003416666666666667</v>
       </c>
       <c r="X17" t="n">
         <v>0.003416666666666667</v>
       </c>
       <c r="Y17" t="n">
+        <v>0.003416666666666667</v>
+      </c>
+      <c r="Z17" t="n">
         <v>28.14125939399925</v>
       </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
       <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
         <v>0.01728682448100467</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>0.4847102107155994</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>0.01902416488705136</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
         <v>0.5387038540642539</v>
       </c>
     </row>
@@ -2204,45 +2257,48 @@
         <v>12.13333333333334</v>
       </c>
       <c r="Q18" t="n">
+        <v>0.6026490066225166</v>
+      </c>
+      <c r="R18" t="n">
         <v>28.03928571428575</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>1.69587337268752</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>28.48804706810438</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>1.88394670675909</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>0.008158145763995973</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>0.1792828694602286</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.003513333333333334</v>
       </c>
       <c r="X18" t="n">
         <v>0.003513333333333334</v>
       </c>
       <c r="Y18" t="n">
+        <v>0.003513333333333334</v>
+      </c>
+      <c r="Z18" t="n">
         <v>28.31682006871788</v>
       </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
       <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
         <v>0.02361088313494781</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>0.6709707039456413</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>0.0263790020874605</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AE18" t="n">
         <v>0.7514862530771985</v>
       </c>
     </row>
@@ -2302,38 +2358,38 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="Q19" t="n">
+        <v>-0.4802065404475043</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.1675555555555282</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
       <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
         <v>0.1675555555555282</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>1.543349336870027</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>0.8697884252671494</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>0.1457378828114052</v>
       </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
         <v>0.1675555555555282</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>1.600786172733832</v>
       </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
@@ -2341,6 +2397,9 @@
         <v>0</v>
       </c>
       <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2400,38 +2459,38 @@
         <v>-8.083333333333336</v>
       </c>
       <c r="Q20" t="n">
+        <v>-0.4173838209982789</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.1675555555555282</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
         <v>0.4827780786809643</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>1.543349336870027</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>0.8697874489981209</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>0.41991431348813</v>
       </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.1675555555555282</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>0.3770350248802999</v>
       </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
@@ -2439,6 +2498,9 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2498,38 +2560,38 @@
         <v>-7.25</v>
       </c>
       <c r="Q21" t="n">
+        <v>-0.374354561101549</v>
+      </c>
+      <c r="R21" t="n">
         <v>0.425000000000088</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
       <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
         <v>0.9966296724056876</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>1.543349336870027</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>0.8697854482403329</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>0.866853986342997</v>
       </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
         <v>0.4827780786809643</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
         <v>0.6434421146608056</v>
       </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
@@ -2537,6 +2599,9 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2596,38 +2661,38 @@
         <v>-6.46666666666667</v>
       </c>
       <c r="Q22" t="n">
+        <v>-0.3339070567986233</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.5214285714284982</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
         <v>1.96984333146582</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>1.543349336870027</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>0.869779154705413</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>1.713328667744435</v>
       </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.9966296724056876</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>0.7999569147331987</v>
       </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
@@ -2635,6 +2700,9 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2694,38 +2762,38 @@
         <v>-4.000000000000002</v>
       </c>
       <c r="Q23" t="n">
+        <v>-0.206540447504303</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.003571428571421</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
       <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
         <v>6.396537784808347</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>1.571874336874451</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>0.8643084459495742</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>5.285233324713334</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0.05979999999999999</v>
       </c>
       <c r="X23" t="n">
         <v>0.05979999999999999</v>
       </c>
       <c r="Y23" t="n">
+        <v>0.05979999999999999</v>
+      </c>
+      <c r="Z23" t="n">
         <v>1.96984333146582</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
         <v>0.5416439745143597</v>
       </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
@@ -2733,6 +2801,9 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2792,38 +2863,38 @@
         <v>-2.300000000000002</v>
       </c>
       <c r="Q24" t="n">
+        <v>-0.1187607573149743</v>
+      </c>
+      <c r="R24" t="n">
         <v>5.957142857142867</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
         <v>14.63100687794381</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>1.689429336874451</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>0.3957858543676276</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>5.110910056279625</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.07849999999999997</v>
       </c>
       <c r="X24" t="n">
         <v>0.07849999999999997</v>
       </c>
       <c r="Y24" t="n">
+        <v>0.07849999999999997</v>
+      </c>
+      <c r="Z24" t="n">
         <v>6.396537784808347</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
         <v>0.4518573616580095</v>
       </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
@@ -2831,6 +2902,9 @@
         <v>0</v>
       </c>
       <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2890,38 +2964,38 @@
         <v>-1.566666666666665</v>
       </c>
       <c r="Q25" t="n">
+        <v>-0.08089500860585187</v>
+      </c>
+      <c r="R25" t="n">
         <v>12.12857142857143</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
       <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
         <v>18.43528574605877</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>1.749953781318896</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>0.3344093059642745</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>5.252974891308282</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0.08656666666666669</v>
       </c>
       <c r="X25" t="n">
         <v>0.08656666666666669</v>
       </c>
       <c r="Y25" t="n">
+        <v>0.08656666666666669</v>
+      </c>
+      <c r="Z25" t="n">
         <v>14.63100687794381</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
         <v>0.3951354990954673</v>
       </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
@@ -2929,6 +3003,9 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2988,38 +3065,38 @@
         <v>-0.6833333333333318</v>
       </c>
       <c r="Q26" t="n">
+        <v>-0.03528399311531834</v>
+      </c>
+      <c r="R26" t="n">
         <v>16.20714285714285</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
         <v>23.11964730857996</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>1.830712531318896</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>0.2835003046370873</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>5.338486993343877</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.09628333333333336</v>
       </c>
       <c r="X26" t="n">
         <v>0.09628333333333336</v>
       </c>
       <c r="Y26" t="n">
+        <v>0.09628333333333336</v>
+      </c>
+      <c r="Z26" t="n">
         <v>18.43528574605877</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>0.3288368413306143</v>
       </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
@@ -3027,6 +3104,9 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3086,38 +3166,38 @@
         <v>-0.08333333333333393</v>
       </c>
       <c r="Q27" t="n">
+        <v>-0.004302925989673008</v>
+      </c>
+      <c r="R27" t="n">
         <v>21.77499999999999</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
       <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
         <v>26.3278144559028</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>1.890462531318896</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>0.2576118309548041</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>5.349536070998063</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0.1028833333333333</v>
       </c>
       <c r="X27" t="n">
         <v>0.1028833333333333</v>
       </c>
       <c r="Y27" t="n">
+        <v>0.1028833333333333</v>
+      </c>
+      <c r="Z27" t="n">
         <v>23.11964730857996</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>0.1921794536128573</v>
       </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
@@ -3125,6 +3205,9 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3184,45 +3267,48 @@
         <v>1.199999999999998</v>
       </c>
       <c r="Q28" t="n">
+        <v>0.06196213425129075</v>
+      </c>
+      <c r="R28" t="n">
         <v>26.35714285714281</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
         <v>27.23145296113909</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>1.908002336876444</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>0.01870882202496487</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>0.3981449934364881</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0.007799999999999998</v>
       </c>
       <c r="X28" t="n">
         <v>0.007799999999999998</v>
       </c>
       <c r="Y28" t="n">
+        <v>0.007799999999999998</v>
+      </c>
+      <c r="Z28" t="n">
         <v>26.3278144559028</v>
       </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
       <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
         <v>0.006015752972438381</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
         <v>0.1619956336149481</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
         <v>0.006010640046182784</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AE28" t="n">
         <v>0.1636784616839654</v>
       </c>
     </row>
@@ -3282,45 +3368,48 @@
         <v>2.949999999999998</v>
       </c>
       <c r="Q29" t="n">
+        <v>0.1523235800344233</v>
+      </c>
+      <c r="R29" t="n">
         <v>26.92857142857148</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>0.1961577414134905</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>27.96947227900407</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>1.922571086876444</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>0.02051067912378411</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>0.4449234941784995</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0.008849999999999998</v>
       </c>
       <c r="X29" t="n">
         <v>0.008849999999999998</v>
       </c>
       <c r="Y29" t="n">
+        <v>0.008849999999999998</v>
+      </c>
+      <c r="Z29" t="n">
         <v>27.23145296113909</v>
       </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
       <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
         <v>0.00362725892161148</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
         <v>0.0921971490896749</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
         <v>0.003588200271870521</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AE29" t="n">
         <v>0.1003600680355974</v>
       </c>
     </row>
@@ -3380,45 +3469,48 @@
         <v>5.066666666666665</v>
       </c>
       <c r="Q30" t="n">
+        <v>0.2616179001721169</v>
+      </c>
+      <c r="R30" t="n">
         <v>25.41785714285721</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>0.4648676866334254</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>28.96836793893106</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>1.942647670209777</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>0.022411221550434</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>0.4983091249527896</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0.01012</v>
       </c>
       <c r="X30" t="n">
         <v>0.01012</v>
       </c>
       <c r="Y30" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="Z30" t="n">
         <v>27.96947227900407</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>0.006274829559544594</v>
       </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
         <v>0.000176502193613248</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
         <v>0.005112980486617014</v>
       </c>
     </row>
@@ -3478,45 +3570,48 @@
         <v>7.066666666666666</v>
       </c>
       <c r="Q31" t="n">
+        <v>0.3648881239242685</v>
+      </c>
+      <c r="R31" t="n">
         <v>27.31785714285721</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>0.5273275582417261</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>30.0125510328083</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>1.964087670209778</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>0.02393237056755607</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>0.545294449839189</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.01132</v>
       </c>
       <c r="X31" t="n">
         <v>0.01132</v>
       </c>
       <c r="Y31" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="Z31" t="n">
         <v>28.96836793893106</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>0.02643890324335607</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>0.005986466179688899</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
         <v>0.166038915540943</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
         <v>0.00583462453234216</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AE31" t="n">
         <v>0.1751119665341944</v>
       </c>
     </row>
@@ -3576,45 +3671,48 @@
         <v>8.999999999999996</v>
       </c>
       <c r="Q32" t="n">
+        <v>0.4647160068846814</v>
+      </c>
+      <c r="R32" t="n">
         <v>27.73571428571431</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>0.5669120469218694</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>31.10797224550694</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>1.987094336876444</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>0.02516104333188622</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>0.5873345723081156</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.01248</v>
       </c>
       <c r="X32" t="n">
         <v>0.01248</v>
       </c>
       <c r="Y32" t="n">
+        <v>0.01248</v>
+      </c>
+      <c r="Z32" t="n">
         <v>30.0125510328083</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
         <v>0.00455350837092449</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AB32" t="n">
         <v>0.02262404581012045</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AC32" t="n">
         <v>0.6940734053890505</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AD32" t="n">
         <v>0.02327612397420674</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AE32" t="n">
         <v>0.7240730185726018</v>
       </c>
     </row>
@@ -3674,45 +3772,48 @@
         <v>10.06666666666667</v>
       </c>
       <c r="Q33" t="n">
+        <v>0.5197934595524957</v>
+      </c>
+      <c r="R33" t="n">
         <v>30.67857142857135</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>1.314363106233276</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>31.74613976555108</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>2.000747670209778</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>0.02574269343420017</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>0.6090542906575316</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0.01312</v>
       </c>
       <c r="X33" t="n">
         <v>0.01312</v>
       </c>
       <c r="Y33" t="n">
+        <v>0.01312</v>
+      </c>
+      <c r="Z33" t="n">
         <v>31.10797224550694</v>
       </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
       <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
         <v>0.03368831785424067</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
         <v>1.033509465599738</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AD33" t="n">
         <v>0.0356935510289857</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AE33" t="n">
         <v>1.133132459695009</v>
       </c>
     </row>
@@ -3772,38 +3873,38 @@
         <v>-9.1</v>
       </c>
       <c r="Q34" t="n">
+        <v>-0.609375</v>
+      </c>
+      <c r="R34" t="n">
         <v>0.103563218390794</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
         <v>0.103563218390794</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>1.6359</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>0.8697892354884216</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>0.09007817254884913</v>
       </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
         <v>0.103563218390794</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
         <v>0.1410188726692848</v>
       </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
@@ -3811,6 +3912,9 @@
         <v>0</v>
       </c>
       <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3870,38 +3974,38 @@
         <v>-8.416666666666666</v>
       </c>
       <c r="Q35" t="n">
+        <v>-0.5636160714285714</v>
+      </c>
+      <c r="R35" t="n">
         <v>0.103563218390794</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
       <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
         <v>0.187642422286357</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>1.6359</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>0.8697890237002115</v>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>0.1632093192851932</v>
       </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
         <v>0.103563218390794</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AA35" t="n">
         <v>0.3923394771712953</v>
       </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
@@ -3909,6 +4013,9 @@
         <v>0</v>
       </c>
       <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3968,38 +4075,38 @@
         <v>-7.383333333333334</v>
       </c>
       <c r="Q36" t="n">
+        <v>-0.494419642857143</v>
+      </c>
+      <c r="R36" t="n">
         <v>0.1748717948718132</v>
       </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
         <v>0.4609639396909129</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>1.6359</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>0.8697882737142089</v>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
         <v>0.4009410293482598</v>
       </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
         <v>0.187642422286357</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
         <v>0.9865765782029755</v>
       </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
@@ -4007,6 +4114,9 @@
         <v>0</v>
       </c>
       <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4066,38 +4176,38 @@
         <v>-6.950000000000002</v>
       </c>
       <c r="Q37" t="n">
+        <v>-0.4654017857142859</v>
+      </c>
+      <c r="R37" t="n">
         <v>0.5107407407407478</v>
       </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
       <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
         <v>0.671979567618744</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>1.6359</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>0.8697876206818212</v>
       </c>
-      <c r="V37" t="n">
+      <c r="W37" t="n">
         <v>0.5844795092659064</v>
       </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
         <v>0.4609639396909129</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
         <v>0.859897420449224</v>
       </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
@@ -4105,6 +4215,9 @@
         <v>0</v>
       </c>
       <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4164,38 +4277,38 @@
         <v>-6.433333333333334</v>
       </c>
       <c r="Q38" t="n">
+        <v>-0.4308035714285716</v>
+      </c>
+      <c r="R38" t="n">
         <v>0.7643333333332928</v>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
         <v>1.053231032379058</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>1.6359</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>0.8697862357666482</v>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
         <v>0.9160858550456018</v>
       </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
         <v>0.671979567618744</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AA38" t="n">
         <v>0.8458504575051579</v>
       </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
@@ -4203,6 +4316,9 @@
         <v>0</v>
       </c>
       <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4262,38 +4378,38 @@
         <v>-5.933333333333334</v>
       </c>
       <c r="Q39" t="n">
+        <v>-0.3973214285714286</v>
+      </c>
+      <c r="R39" t="n">
         <v>1.021500000000053</v>
       </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
       <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
         <v>1.627028145219213</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>1.6359</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>0.869783449023764</v>
       </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
         <v>1.415162151807505</v>
       </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
         <v>1.053231032379058</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AA39" t="n">
         <v>1.072647376108041</v>
       </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
@@ -4301,6 +4417,9 @@
         <v>0</v>
       </c>
       <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4360,38 +4479,38 @@
         <v>-5.433333333333334</v>
       </c>
       <c r="Q40" t="n">
+        <v>-0.3638392857142858</v>
+      </c>
+      <c r="R40" t="n">
         <v>1.369999999999916</v>
       </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
         <v>2.513422412649003</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>1.6359</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>0.869775916688127</v>
       </c>
-      <c r="V40" t="n">
+      <c r="W40" t="n">
         <v>2.18611428298627</v>
       </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
         <v>1.627028145219213</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AA40" t="n">
         <v>0.8721620914810805</v>
       </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
@@ -4399,6 +4518,9 @@
         <v>0</v>
       </c>
       <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4458,38 +4580,38 @@
         <v>-4.933333333333333</v>
       </c>
       <c r="Q41" t="n">
+        <v>-0.3303571428571428</v>
+      </c>
+      <c r="R41" t="n">
         <v>2.429000000000059</v>
       </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
       <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
         <v>3.882679078945536</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>1.6359</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>0.8697189075852337</v>
       </c>
-      <c r="V41" t="n">
+      <c r="W41" t="n">
         <v>3.376839407044554</v>
       </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
         <v>2.513422412649003</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AA41" t="n">
         <v>0.7803720364651523</v>
       </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
       <c r="AB41" t="n">
         <v>0</v>
       </c>
@@ -4497,6 +4619,9 @@
         <v>0</v>
       </c>
       <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4556,38 +4681,38 @@
         <v>-4.450000000000002</v>
       </c>
       <c r="Q42" t="n">
+        <v>-0.2979910714285716</v>
+      </c>
+      <c r="R42" t="n">
         <v>3.654000000000046</v>
       </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
         <v>4.882614169638027</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>1.641660000001911</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>0.4571104267996307</v>
       </c>
-      <c r="V42" t="n">
+      <c r="W42" t="n">
         <v>2.144452564019288</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0.02939999999999999</v>
       </c>
       <c r="X42" t="n">
         <v>0.02939999999999999</v>
       </c>
       <c r="Y42" t="n">
+        <v>0.02939999999999999</v>
+      </c>
+      <c r="Z42" t="n">
         <v>3.882679078945536</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AA42" t="n">
         <v>0.5859915840261742</v>
       </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
       <c r="AB42" t="n">
         <v>0</v>
       </c>
@@ -4595,6 +4720,9 @@
         <v>0</v>
       </c>
       <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4654,38 +4782,38 @@
         <v>-3.550000000000002</v>
       </c>
       <c r="Q43" t="n">
+        <v>-0.2377232142857144</v>
+      </c>
+      <c r="R43" t="n">
         <v>5.610714285714247</v>
       </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
       <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
         <v>6.953413241035154</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>1.670550000001911</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>0.3733596676960823</v>
       </c>
-      <c r="V43" t="n">
+      <c r="W43" t="n">
         <v>2.451274288514409</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0.03479999999999999</v>
       </c>
       <c r="X43" t="n">
         <v>0.03479999999999999</v>
       </c>
       <c r="Y43" t="n">
+        <v>0.03479999999999999</v>
+      </c>
+      <c r="Z43" t="n">
         <v>4.882614169638027</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AA43" t="n">
         <v>0.4918158019929457</v>
       </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
       <c r="AB43" t="n">
         <v>0</v>
       </c>
@@ -4693,6 +4821,9 @@
         <v>0</v>
       </c>
       <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4752,38 +4883,38 @@
         <v>-2.600000000000001</v>
       </c>
       <c r="Q44" t="n">
+        <v>-0.1741071428571429</v>
+      </c>
+      <c r="R44" t="n">
         <v>8.060714285714278</v>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
         <v>9.42002122013024</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>1.706317500001911</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>0.314013110258141</v>
       </c>
-      <c r="V44" t="n">
+      <c r="W44" t="n">
         <v>2.734422899159223</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0.04049999999999999</v>
       </c>
       <c r="X44" t="n">
         <v>0.04049999999999999</v>
       </c>
       <c r="Y44" t="n">
+        <v>0.04049999999999999</v>
+      </c>
+      <c r="Z44" t="n">
         <v>6.953413241035154</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AA44" t="n">
         <v>0.4239703641171224</v>
       </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
       <c r="AB44" t="n">
         <v>0</v>
       </c>
@@ -4791,6 +4922,9 @@
         <v>0</v>
       </c>
       <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4850,38 +4984,38 @@
         <v>-2.099999999999998</v>
       </c>
       <c r="Q45" t="n">
+        <v>-0.1406249999999999</v>
+      </c>
+      <c r="R45" t="n">
         <v>12.56785714285716</v>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
       <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
         <v>10.82063195952434</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>1.727317500001911</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>0.2900471785400823</v>
       </c>
-      <c r="V45" t="n">
+      <c r="W45" t="n">
         <v>2.865991760123473</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0.04350000000000001</v>
       </c>
       <c r="X45" t="n">
         <v>0.04350000000000001</v>
       </c>
       <c r="Y45" t="n">
+        <v>0.04350000000000001</v>
+      </c>
+      <c r="Z45" t="n">
         <v>9.42002122013024</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AA45" t="n">
         <v>0.4001175993931018</v>
       </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
       <c r="AB45" t="n">
         <v>0</v>
       </c>
@@ -4889,6 +5023,9 @@
         <v>0</v>
       </c>
       <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4948,38 +5085,38 @@
         <v>-1.383333333333333</v>
       </c>
       <c r="Q46" t="n">
+        <v>-0.09263392857142855</v>
+      </c>
+      <c r="R46" t="n">
         <v>15.0964285714285</v>
       </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
         <v>12.93604311520127</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>1.760033333335244</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>0.2616432146479148</v>
       </c>
-      <c r="V46" t="n">
+      <c r="W46" t="n">
         <v>3.033303388389427</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0.0478</v>
       </c>
       <c r="X46" t="n">
         <v>0.0478</v>
       </c>
       <c r="Y46" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="Z46" t="n">
         <v>10.82063195952434</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AA46" t="n">
         <v>0.456221002086854</v>
       </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
@@ -4987,6 +5124,9 @@
         <v>0</v>
       </c>
       <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5046,38 +5186,38 @@
         <v>-0.75</v>
       </c>
       <c r="Q47" t="n">
+        <v>-0.05022321428571429</v>
+      </c>
+      <c r="R47" t="n">
         <v>19.02857142857142</v>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
       <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
         <v>14.89840120883817</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>1.791510000001911</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>0.2409320563170471</v>
       </c>
-      <c r="V47" t="n">
+      <c r="W47" t="n">
         <v>3.160390961961775</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0.0516</v>
       </c>
       <c r="X47" t="n">
         <v>0.0516</v>
       </c>
       <c r="Y47" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="Z47" t="n">
         <v>12.93604311520127</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AA47" t="n">
         <v>0.3401951848972837</v>
       </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
       <c r="AB47" t="n">
         <v>0</v>
       </c>
@@ -5085,6 +5225,9 @@
         <v>0</v>
       </c>
       <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5144,38 +5287,38 @@
         <v>-0.1333333333333329</v>
       </c>
       <c r="Q48" t="n">
+        <v>-0.008928571428571399</v>
+      </c>
+      <c r="R48" t="n">
         <v>25.25357142857137</v>
       </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
         <v>16.88071110537751</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>1.824470833335245</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>0.2237696413593221</v>
       </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
         <v>3.265733642011696</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0.0553</v>
       </c>
       <c r="X48" t="n">
         <v>0.0553</v>
       </c>
       <c r="Y48" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="Z48" t="n">
         <v>14.89840120883817</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AA48" t="n">
         <v>0.1620066644475431</v>
       </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
@@ -5183,6 +5326,9 @@
         <v>0</v>
       </c>
       <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5242,45 +5388,48 @@
         <v>0.8333333333333321</v>
       </c>
       <c r="Q49" t="n">
+        <v>0.05580357142857136</v>
+      </c>
+      <c r="R49" t="n">
         <v>29.52857142857138</v>
       </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
       <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
         <v>19.99434722445</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>1.878764027775987</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>0.006623944767816831</v>
       </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
         <v>0.1111923506601871</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0.001996666666666667</v>
       </c>
       <c r="X49" t="n">
         <v>0.001996666666666667</v>
       </c>
       <c r="Y49" t="n">
+        <v>0.001996666666666667</v>
+      </c>
+      <c r="Z49" t="n">
         <v>16.88071110537751</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AA49" t="n">
         <v>0.04062202704143002</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AB49" t="n">
         <v>0.002657762910916</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AC49" t="n">
         <v>0.0816312894067058</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AD49" t="n">
         <v>0.004090749458152188</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AE49" t="n">
         <v>0.08179186507452553</v>
       </c>
     </row>
@@ -5340,45 +5489,48 @@
         <v>1.933333333333334</v>
       </c>
       <c r="Q50" t="n">
+        <v>0.1294642857142858</v>
+      </c>
+      <c r="R50" t="n">
         <v>30.71428571428574</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>0.09290978010103844</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>20.11820097013989</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
         <v>1.88099061110932</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>0.006756699312366905</v>
       </c>
-      <c r="V50" t="n">
+      <c r="W50" t="n">
         <v>0.1139889619600565</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0.002051666666666667</v>
       </c>
       <c r="X50" t="n">
         <v>0.002051666666666667</v>
       </c>
       <c r="Y50" t="n">
+        <v>0.002051666666666667</v>
+      </c>
+      <c r="Z50" t="n">
         <v>19.99434722445</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AA50" t="n">
         <v>0.01789804707363351</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AB50" t="n">
         <v>0.001291368036371657</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AC50" t="n">
         <v>0.04078878183453907</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AD50" t="n">
         <v>0.002159985784695504</v>
       </c>
-      <c r="AD50" t="n">
+      <c r="AE50" t="n">
         <v>0.04345502810914946</v>
       </c>
     </row>
@@ -5438,45 +5590,48 @@
         <v>2.866666666666664</v>
       </c>
       <c r="Q51" t="n">
+        <v>0.1919642857142855</v>
+      </c>
+      <c r="R51" t="n">
         <v>31.58571428571431</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>0.1714635834683609</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>20.22568990499862</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>1.882927277775987</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>0.006866587915181886</v>
       </c>
-      <c r="V51" t="n">
+      <c r="W51" t="n">
         <v>0.1163419779098033</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0.002098333333333333</v>
       </c>
       <c r="X51" t="n">
         <v>0.002098333333333333</v>
       </c>
       <c r="Y51" t="n">
+        <v>0.002098333333333333</v>
+      </c>
+      <c r="Z51" t="n">
         <v>20.11820097013989</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AA51" t="n">
         <v>0.001401645203937436</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AB51" t="n">
         <v>0.000732260389109694</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AC51" t="n">
         <v>0.02413582546819065</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AD51" t="n">
         <v>0.001421388845611391</v>
       </c>
-      <c r="AD51" t="n">
+      <c r="AE51" t="n">
         <v>0.02874857002575995</v>
       </c>
     </row>
@@ -5536,45 +5691,48 @@
         <v>3.866666666666667</v>
       </c>
       <c r="Q52" t="n">
+        <v>0.2589285714285715</v>
+      </c>
+      <c r="R52" t="n">
         <v>32.96071428571437</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>0.1940649581558863</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>20.34328539706401</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
         <v>1.88505061110932</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>0.006981716693788993</v>
       </c>
-      <c r="V52" t="n">
+      <c r="W52" t="n">
         <v>0.1188464479797303</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0.002148333333333333</v>
       </c>
       <c r="X52" t="n">
         <v>0.002148333333333333</v>
       </c>
       <c r="Y52" t="n">
+        <v>0.002148333333333333</v>
+      </c>
+      <c r="Z52" t="n">
         <v>20.22568990499862</v>
       </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
       <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
         <v>0.001184262765768505</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AC52" t="n">
         <v>0.03974752399441857</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AD52" t="n">
         <v>0.00225397286104733</v>
       </c>
-      <c r="AD52" t="n">
+      <c r="AE52" t="n">
         <v>0.04585321318952273</v>
       </c>
     </row>
@@ -5634,45 +5792,48 @@
         <v>4.949999999999999</v>
       </c>
       <c r="Q53" t="n">
+        <v>0.3314732142857142</v>
+      </c>
+      <c r="R53" t="n">
         <v>33.56309523809537</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>0.2229784488956445</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>20.47349558554726</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>1.887407312498209</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>0.007103330146140919</v>
       </c>
-      <c r="V53" t="n">
+      <c r="W53" t="n">
         <v>0.1215385607924384</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0.0022025</v>
       </c>
       <c r="X53" t="n">
         <v>0.0022025</v>
       </c>
       <c r="Y53" t="n">
+        <v>0.0022025</v>
+      </c>
+      <c r="Z53" t="n">
         <v>20.34328539706401</v>
       </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
       <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
         <v>0.002253668672706707</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AC53" t="n">
         <v>0.07526448485171559</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AD53" t="n">
         <v>0.004133579428073363</v>
       </c>
-      <c r="AD53" t="n">
+      <c r="AE53" t="n">
         <v>0.08462882017316897</v>
       </c>
     </row>
@@ -5732,45 +5893,48 @@
         <v>5.833333333333332</v>
       </c>
       <c r="Q54" t="n">
+        <v>0.3906249999999999</v>
+      </c>
+      <c r="R54" t="n">
         <v>33.39642857142849</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>0.2989185664601128</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>20.58181820790413</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>1.88937236110932</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>0.007200136731366074</v>
       </c>
-      <c r="V54" t="n">
+      <c r="W54" t="n">
         <v>0.1237179128238205</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0.002246666666666667</v>
       </c>
       <c r="X54" t="n">
         <v>0.002246666666666667</v>
       </c>
       <c r="Y54" t="n">
+        <v>0.002246666666666667</v>
+      </c>
+      <c r="Z54" t="n">
         <v>20.47349558554726</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AA54" t="n">
         <v>0.00396735495458923</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AB54" t="n">
         <v>0.003016123760172439</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AC54" t="n">
         <v>0.102602067198723</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AD54" t="n">
         <v>0.005534928976968097</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AE54" t="n">
         <v>0.1139189019976181</v>
       </c>
     </row>
@@ -5830,38 +5994,38 @@
         <v>-9.1</v>
       </c>
       <c r="Q55" t="n">
+        <v>-0.6100558659217877</v>
+      </c>
+      <c r="R55" t="n">
         <v>0.04347826086957973</v>
       </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
       <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
         <v>0.04347826086957973</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
         <v>1.6309</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>0.8697886689425612</v>
       </c>
-      <c r="V55" t="n">
+      <c r="W55" t="n">
         <v>0.0378168986496892</v>
       </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
       <c r="X55" t="n">
         <v>0</v>
       </c>
       <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
         <v>0.04347826086957973</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AA55" t="n">
         <v>1.241564657307359</v>
       </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
       <c r="AB55" t="n">
         <v>0</v>
       </c>
@@ -5869,6 +6033,9 @@
         <v>0</v>
       </c>
       <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5928,38 +6095,38 @@
         <v>-8.416666666666666</v>
       </c>
       <c r="Q56" t="n">
+        <v>-0.5642458100558659</v>
+      </c>
+      <c r="R56" t="n">
         <v>0.04347826086957973</v>
       </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
         <v>0.07877664907913345</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
         <v>1.6309</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>0.8697885714934919</v>
       </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
         <v>0.06851902906958358</v>
       </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
       <c r="X56" t="n">
         <v>0</v>
       </c>
       <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
         <v>0.04347826086957973</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AA56" t="n">
         <v>0.4980891336844761</v>
       </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
       <c r="AB56" t="n">
         <v>0</v>
       </c>
@@ -5967,6 +6134,9 @@
         <v>0</v>
       </c>
       <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6026,38 +6196,38 @@
         <v>-7.383333333333334</v>
       </c>
       <c r="Q57" t="n">
+        <v>-0.4949720670391062</v>
+      </c>
+      <c r="R57" t="n">
         <v>0.1328787878787904</v>
       </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
       <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
         <v>0.1935233173553177</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>1.6309</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>0.8697882427959001</v>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
         <v>0.1683243061425151</v>
       </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
       <c r="X57" t="n">
         <v>0</v>
       </c>
       <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
         <v>0.07877664907913345</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AA57" t="n">
         <v>0.9497676633868221</v>
       </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
       <c r="AB57" t="n">
         <v>0</v>
       </c>
@@ -6065,6 +6235,9 @@
         <v>0</v>
       </c>
       <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6124,38 +6297,38 @@
         <v>-6.950000000000002</v>
       </c>
       <c r="Q58" t="n">
+        <v>-0.4659217877094974</v>
+      </c>
+      <c r="R58" t="n">
         <v>0.4653846153846239</v>
       </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
         <v>0.2821125734378678</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>1.6309</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>0.8697879758002446</v>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
         <v>0.2453781241983209</v>
       </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
       <c r="X58" t="n">
         <v>0</v>
       </c>
       <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
         <v>0.1935233173553177</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AA58" t="n">
         <v>0.8861519348632451</v>
       </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
       <c r="AB58" t="n">
         <v>0</v>
       </c>
@@ -6163,6 +6336,9 @@
         <v>0</v>
       </c>
       <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6222,38 +6398,38 @@
         <v>-6.483333333333334</v>
       </c>
       <c r="Q59" t="n">
+        <v>-0.43463687150838</v>
+      </c>
+      <c r="R59" t="n">
         <v>0.6816071428571276</v>
       </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
       <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
         <v>0.4233533408346242</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
         <v>1.6309</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>0.8697875240992334</v>
       </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
         <v>0.3682274541436866</v>
       </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
       <c r="X59" t="n">
         <v>0</v>
       </c>
       <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
         <v>0.2821125734378678</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AA59" t="n">
         <v>0.9252948592011343</v>
       </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
       <c r="AB59" t="n">
         <v>0</v>
       </c>
@@ -6261,6 +6437,9 @@
         <v>0</v>
       </c>
       <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6320,38 +6499,38 @@
         <v>-5.933333333333334</v>
       </c>
       <c r="Q60" t="n">
+        <v>-0.3977653631284916</v>
+      </c>
+      <c r="R60" t="n">
         <v>0.9277500000000494</v>
       </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
         <v>0.6830650259502661</v>
       </c>
-      <c r="T60" t="n">
+      <c r="U60" t="n">
         <v>1.6309</v>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
         <v>0.8697865983701208</v>
       </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
         <v>0.5941208053868803</v>
       </c>
-      <c r="W60" t="n">
-        <v>0</v>
-      </c>
       <c r="X60" t="n">
         <v>0</v>
       </c>
       <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
         <v>0.4233533408346242</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AA60" t="n">
         <v>0.9349196591727447</v>
       </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
       <c r="AB60" t="n">
         <v>0</v>
       </c>
@@ -6359,6 +6538,9 @@
         <v>0</v>
       </c>
       <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6418,38 +6600,38 @@
         <v>-5.433333333333334</v>
       </c>
       <c r="Q61" t="n">
+        <v>-0.364245810055866</v>
+      </c>
+      <c r="R61" t="n">
         <v>1.43027777777781</v>
       </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
       <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
         <v>1.055197260918095</v>
       </c>
-      <c r="T61" t="n">
+      <c r="U61" t="n">
         <v>1.6309</v>
       </c>
-      <c r="U61" t="n">
+      <c r="V61" t="n">
         <v>0.8697850039831744</v>
       </c>
-      <c r="V61" t="n">
+      <c r="W61" t="n">
         <v>0.9177947537906795</v>
       </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
       <c r="X61" t="n">
         <v>0</v>
       </c>
       <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="n">
         <v>0.6830650259502661</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AA61" t="n">
         <v>0.8688225638485592</v>
       </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
       <c r="AB61" t="n">
         <v>0</v>
       </c>
@@ -6457,6 +6639,9 @@
         <v>0</v>
       </c>
       <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6516,38 +6701,38 @@
         <v>-4.933333333333333</v>
       </c>
       <c r="Q62" t="n">
+        <v>-0.3307262569832402</v>
+      </c>
+      <c r="R62" t="n">
         <v>2.204500000000031</v>
       </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
         <v>1.630064365262534</v>
       </c>
-      <c r="T62" t="n">
+      <c r="U62" t="n">
         <v>1.6309</v>
       </c>
-      <c r="U62" t="n">
+      <c r="V62" t="n">
         <v>0.8697816274052887</v>
       </c>
-      <c r="V62" t="n">
+      <c r="W62" t="n">
         <v>1.417800036393416</v>
       </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
       <c r="X62" t="n">
         <v>0</v>
       </c>
       <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
         <v>1.055197260918095</v>
       </c>
-      <c r="Z62" t="n">
+      <c r="AA62" t="n">
         <v>0.6800657824740611</v>
       </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
       <c r="AB62" t="n">
         <v>0</v>
       </c>
@@ -6555,6 +6740,9 @@
         <v>0</v>
       </c>
       <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6614,38 +6802,38 @@
         <v>-4.450000000000002</v>
       </c>
       <c r="Q63" t="n">
+        <v>-0.2983240223463688</v>
+      </c>
+      <c r="R63" t="n">
         <v>3.41107142857146</v>
       </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
       <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
         <v>2.481869674424707</v>
       </c>
-      <c r="T63" t="n">
+      <c r="U63" t="n">
         <v>1.6309</v>
       </c>
-      <c r="U63" t="n">
+      <c r="V63" t="n">
         <v>0.8697724285640693</v>
       </c>
-      <c r="V63" t="n">
+      <c r="W63" t="n">
         <v>2.158661814103894</v>
       </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
       <c r="X63" t="n">
         <v>0</v>
       </c>
       <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
         <v>1.630064365262534</v>
       </c>
-      <c r="Z63" t="n">
+      <c r="AA63" t="n">
         <v>0.6441156540974313</v>
       </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
       <c r="AB63" t="n">
         <v>0</v>
       </c>
@@ -6653,6 +6841,9 @@
         <v>0</v>
       </c>
       <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6712,20 +6903,20 @@
         <v>-3.599999999999999</v>
       </c>
       <c r="Q64" t="n">
+        <v>-0.241340782122905</v>
+      </c>
+      <c r="R64" t="n">
         <v>4.485714285714332</v>
       </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
         <v>4.183103260869916</v>
       </c>
-      <c r="T64" t="n">
+      <c r="U64" t="n">
         <v>1.6309</v>
       </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
       <c r="V64" t="n">
         <v>0</v>
       </c>
@@ -6736,14 +6927,14 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
         <v>2.481869674424707</v>
       </c>
-      <c r="Z64" t="n">
+      <c r="AA64" t="n">
         <v>0.4894339946770361</v>
       </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
       <c r="AB64" t="n">
         <v>0</v>
       </c>
@@ -6751,6 +6942,9 @@
         <v>0</v>
       </c>
       <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6810,38 +7004,38 @@
         <v>-2.600000000000001</v>
       </c>
       <c r="Q65" t="n">
+        <v>-0.1743016759776537</v>
+      </c>
+      <c r="R65" t="n">
         <v>8.025000000000075</v>
       </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
       <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
         <v>6.644072703328449</v>
       </c>
-      <c r="T65" t="n">
+      <c r="U65" t="n">
         <v>1.66492000000117</v>
       </c>
-      <c r="U65" t="n">
+      <c r="V65" t="n">
         <v>0.4562848243883437</v>
       </c>
-      <c r="V65" t="n">
+      <c r="W65" t="n">
         <v>2.869969201849478</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0.04049999999999999</v>
       </c>
       <c r="X65" t="n">
         <v>0.04049999999999999</v>
       </c>
       <c r="Y65" t="n">
+        <v>0.04049999999999999</v>
+      </c>
+      <c r="Z65" t="n">
         <v>4.183103260869916</v>
       </c>
-      <c r="Z65" t="n">
+      <c r="AA65" t="n">
         <v>0.4930841029038115</v>
       </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
       <c r="AB65" t="n">
         <v>0</v>
       </c>
@@ -6849,6 +7043,9 @@
         <v>0</v>
       </c>
       <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6908,38 +7105,38 @@
         <v>-2.099999999999998</v>
       </c>
       <c r="Q66" t="n">
+        <v>-0.1407821229050278</v>
+      </c>
+      <c r="R66" t="n">
         <v>11.51785714285718</v>
       </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
         <v>8.113663161493111</v>
       </c>
-      <c r="T66" t="n">
+      <c r="U66" t="n">
         <v>1.68592000000117</v>
       </c>
-      <c r="U66" t="n">
+      <c r="V66" t="n">
         <v>0.3963158904046827</v>
       </c>
-      <c r="V66" t="n">
+      <c r="W66" t="n">
         <v>3.006225422389191</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0.04350000000000001</v>
       </c>
       <c r="X66" t="n">
         <v>0.04350000000000001</v>
       </c>
       <c r="Y66" t="n">
+        <v>0.04350000000000001</v>
+      </c>
+      <c r="Z66" t="n">
         <v>6.644072703328449</v>
       </c>
-      <c r="Z66" t="n">
+      <c r="AA66" t="n">
         <v>0.4398139997631306</v>
       </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
       <c r="AB66" t="n">
         <v>0</v>
       </c>
@@ -6947,6 +7144,9 @@
         <v>0</v>
       </c>
       <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7006,38 +7206,38 @@
         <v>-1.383333333333333</v>
       </c>
       <c r="Q67" t="n">
+        <v>-0.09273743016759774</v>
+      </c>
+      <c r="R67" t="n">
         <v>14.97857142857154</v>
       </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
       <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
         <v>10.33156584378859</v>
       </c>
-      <c r="T67" t="n">
+      <c r="U67" t="n">
         <v>1.718635833334503</v>
       </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
         <v>0.3354923698025998</v>
       </c>
-      <c r="V67" t="n">
+      <c r="W67" t="n">
         <v>3.178812183294828</v>
-      </c>
-      <c r="W67" t="n">
-        <v>0.0478</v>
       </c>
       <c r="X67" t="n">
         <v>0.0478</v>
       </c>
       <c r="Y67" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="Z67" t="n">
         <v>8.113663161493111</v>
       </c>
-      <c r="Z67" t="n">
+      <c r="AA67" t="n">
         <v>0.3354852570926234</v>
       </c>
-      <c r="AA67" t="n">
-        <v>0</v>
-      </c>
       <c r="AB67" t="n">
         <v>0</v>
       </c>
@@ -7045,6 +7245,9 @@
         <v>0</v>
       </c>
       <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7104,38 +7307,38 @@
         <v>-0.75</v>
       </c>
       <c r="Q68" t="n">
+        <v>-0.05027932960893855</v>
+      </c>
+      <c r="R68" t="n">
         <v>19.46071428571426</v>
       </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
         <v>12.38718794936266</v>
       </c>
-      <c r="T68" t="n">
+      <c r="U68" t="n">
         <v>1.750112500001169</v>
       </c>
-      <c r="U68" t="n">
+      <c r="V68" t="n">
         <v>0.2966301161234225</v>
       </c>
-      <c r="V68" t="n">
+      <c r="W68" t="n">
         <v>3.309191393715823</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0.0516</v>
       </c>
       <c r="X68" t="n">
         <v>0.0516</v>
       </c>
       <c r="Y68" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="Z68" t="n">
         <v>10.33156584378859</v>
       </c>
-      <c r="Z68" t="n">
+      <c r="AA68" t="n">
         <v>0.3363582465062418</v>
       </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
       <c r="AB68" t="n">
         <v>0</v>
       </c>
@@ -7143,6 +7346,9 @@
         <v>0</v>
       </c>
       <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7202,38 +7408,38 @@
         <v>-0.03333333333333499</v>
       </c>
       <c r="Q69" t="n">
+        <v>-0.002234636871508491</v>
+      </c>
+      <c r="R69" t="n">
         <v>22.09642857142853</v>
       </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
       <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
         <v>14.80438644820013</v>
       </c>
-      <c r="T69" t="n">
+      <c r="U69" t="n">
         <v>1.788633333334503</v>
       </c>
-      <c r="U69" t="n">
+      <c r="V69" t="n">
         <v>0.2630897958482826</v>
       </c>
-      <c r="V69" t="n">
+      <c r="W69" t="n">
         <v>3.432202822818459</v>
-      </c>
-      <c r="W69" t="n">
-        <v>0.05589999999999999</v>
       </c>
       <c r="X69" t="n">
         <v>0.05589999999999999</v>
       </c>
       <c r="Y69" t="n">
+        <v>0.05589999999999999</v>
+      </c>
+      <c r="Z69" t="n">
         <v>12.38718794936266</v>
       </c>
-      <c r="Z69" t="n">
+      <c r="AA69" t="n">
         <v>0.183772009728279</v>
       </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
       <c r="AB69" t="n">
         <v>0</v>
       </c>
@@ -7241,6 +7447,9 @@
         <v>0</v>
       </c>
       <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7300,45 +7509,48 @@
         <v>0.8333333333333321</v>
       </c>
       <c r="Q70" t="n">
+        <v>0.05586592178770942</v>
+      </c>
+      <c r="R70" t="n">
         <v>28.42857142857147</v>
       </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
         <v>15.01969250829701</v>
       </c>
-      <c r="T70" t="n">
+      <c r="U70" t="n">
         <v>1.792146527775721</v>
       </c>
-      <c r="U70" t="n">
+      <c r="V70" t="n">
         <v>0.009244457741737573</v>
       </c>
-      <c r="V70" t="n">
+      <c r="W70" t="n">
         <v>0.1221151697087406</v>
-      </c>
-      <c r="W70" t="n">
-        <v>0.001996666666666667</v>
       </c>
       <c r="X70" t="n">
         <v>0.001996666666666667</v>
       </c>
       <c r="Y70" t="n">
+        <v>0.001996666666666667</v>
+      </c>
+      <c r="Z70" t="n">
         <v>14.80438644820013</v>
       </c>
-      <c r="Z70" t="n">
+      <c r="AA70" t="n">
         <v>0.02124826378470669</v>
       </c>
-      <c r="AA70" t="n">
+      <c r="AB70" t="n">
         <v>0.002156026816633438</v>
       </c>
-      <c r="AB70" t="n">
+      <c r="AC70" t="n">
         <v>0.06320238611045444</v>
       </c>
-      <c r="AC70" t="n">
+      <c r="AD70" t="n">
         <v>0.00423544589820138</v>
       </c>
-      <c r="AD70" t="n">
+      <c r="AE70" t="n">
         <v>0.06361509502651258</v>
       </c>
     </row>
@@ -7398,45 +7610,48 @@
         <v>1.933333333333334</v>
       </c>
       <c r="Q71" t="n">
+        <v>0.1296089385474861</v>
+      </c>
+      <c r="R71" t="n">
         <v>29.31428571428569</v>
       </c>
-      <c r="R71" t="n">
+      <c r="S71" t="n">
         <v>0.05810793948216079</v>
       </c>
-      <c r="S71" t="n">
+      <c r="T71" t="n">
         <v>15.15569778710702</v>
       </c>
-      <c r="T71" t="n">
+      <c r="U71" t="n">
         <v>1.794373111109054</v>
       </c>
-      <c r="U71" t="n">
+      <c r="V71" t="n">
         <v>0.009402010873351092</v>
       </c>
-      <c r="V71" t="n">
+      <c r="W71" t="n">
         <v>0.1251651756496959</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0.002051666666666667</v>
       </c>
       <c r="X71" t="n">
         <v>0.002051666666666667</v>
       </c>
       <c r="Y71" t="n">
+        <v>0.002051666666666667</v>
+      </c>
+      <c r="Z71" t="n">
         <v>15.01969250829701</v>
       </c>
-      <c r="Z71" t="n">
+      <c r="AA71" t="n">
         <v>0.00139773628339818</v>
       </c>
-      <c r="AA71" t="n">
+      <c r="AB71" t="n">
         <v>0.001694052966529097</v>
       </c>
-      <c r="AB71" t="n">
+      <c r="AC71" t="n">
         <v>0.05093049240086417</v>
       </c>
-      <c r="AC71" t="n">
+      <c r="AD71" t="n">
         <v>0.003538733655060628</v>
       </c>
-      <c r="AD71" t="n">
+      <c r="AE71" t="n">
         <v>0.0536319778251635</v>
       </c>
     </row>
@@ -7496,45 +7711,48 @@
         <v>2.899999999999999</v>
       </c>
       <c r="Q72" t="n">
+        <v>0.194413407821229</v>
+      </c>
+      <c r="R72" t="n">
         <v>30.06428571428577</v>
       </c>
-      <c r="R72" t="n">
+      <c r="S72" t="n">
         <v>0.1219400842896329</v>
       </c>
-      <c r="S72" t="n">
+      <c r="T72" t="n">
         <v>15.27797946896859</v>
       </c>
-      <c r="T72" t="n">
+      <c r="U72" t="n">
         <v>1.796379749997943</v>
       </c>
-      <c r="U72" t="n">
+      <c r="V72" t="n">
         <v>0.00953587058164054</v>
       </c>
-      <c r="V72" t="n">
+      <c r="W72" t="n">
         <v>0.1278286041954265</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0.0021</v>
       </c>
       <c r="X72" t="n">
         <v>0.0021</v>
       </c>
       <c r="Y72" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="Z72" t="n">
         <v>15.15569778710702</v>
       </c>
-      <c r="Z72" t="n">
-        <v>0</v>
-      </c>
       <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
         <v>0.001179849082637842</v>
       </c>
-      <c r="AB72" t="n">
+      <c r="AC72" t="n">
         <v>0.03650228328522884</v>
       </c>
-      <c r="AC72" t="n">
+      <c r="AD72" t="n">
         <v>0.002739726214617911</v>
       </c>
-      <c r="AD72" t="n">
+      <c r="AE72" t="n">
         <v>0.04185748085752747</v>
       </c>
     </row>
@@ -7594,45 +7812,48 @@
         <v>3.899999999999999</v>
       </c>
       <c r="Q73" t="n">
+        <v>0.2614525139664803</v>
+      </c>
+      <c r="R73" t="n">
         <v>30.93809523809523</v>
       </c>
-      <c r="R73" t="n">
+      <c r="S73" t="n">
         <v>0.1703755277559266</v>
       </c>
-      <c r="S73" t="n">
+      <c r="T73" t="n">
         <v>15.40717642247015</v>
       </c>
-      <c r="T73" t="n">
+      <c r="U73" t="n">
         <v>1.798504749997943</v>
       </c>
-      <c r="U73" t="n">
+      <c r="V73" t="n">
         <v>0.009669531246993858</v>
       </c>
-      <c r="V73" t="n">
+      <c r="W73" t="n">
         <v>0.1305618575696002</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0.00215</v>
       </c>
       <c r="X73" t="n">
         <v>0.00215</v>
       </c>
       <c r="Y73" t="n">
+        <v>0.00215</v>
+      </c>
+      <c r="Z73" t="n">
         <v>15.27797946896859</v>
       </c>
-      <c r="Z73" t="n">
-        <v>0</v>
-      </c>
       <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
         <v>0.0005275241763407782</v>
       </c>
-      <c r="AB73" t="n">
+      <c r="AC73" t="n">
         <v>0.01662203559450923</v>
       </c>
-      <c r="AC73" t="n">
+      <c r="AD73" t="n">
         <v>0.001732058081469855</v>
       </c>
-      <c r="AD73" t="n">
+      <c r="AE73" t="n">
         <v>0.02668612443517123</v>
       </c>
     </row>
@@ -7692,35 +7913,35 @@
         <v>4.949999999999999</v>
       </c>
       <c r="Q74" t="n">
+        <v>0.3318435754189944</v>
+      </c>
+      <c r="R74" t="n">
         <v>31.5095238095239</v>
       </c>
-      <c r="R74" t="n">
+      <c r="S74" t="n">
         <v>0.2036432131066642</v>
       </c>
-      <c r="S74" t="n">
+      <c r="T74" t="n">
         <v>15.54576471838671</v>
       </c>
-      <c r="T74" t="n">
+      <c r="U74" t="n">
         <v>1.800789812497944</v>
       </c>
-      <c r="U74" t="n">
+      <c r="V74" t="n">
         <v>0.009804928460010224</v>
       </c>
-      <c r="V74" t="n">
+      <c r="W74" t="n">
         <v>0.1334114833690572</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0.0022025</v>
       </c>
       <c r="X74" t="n">
         <v>0.0022025</v>
       </c>
       <c r="Y74" t="n">
+        <v>0.0022025</v>
+      </c>
+      <c r="Z74" t="n">
         <v>15.40717642247015</v>
       </c>
-      <c r="Z74" t="n">
-        <v>0</v>
-      </c>
       <c r="AA74" t="n">
         <v>0</v>
       </c>
@@ -7728,9 +7949,12 @@
         <v>0</v>
       </c>
       <c r="AC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="n">
         <v>0.0006703122036587197</v>
       </c>
-      <c r="AD74" t="n">
+      <c r="AE74" t="n">
         <v>0.01042051580594177</v>
       </c>
     </row>
@@ -7790,45 +8014,48 @@
         <v>5.816666666666666</v>
       </c>
       <c r="Q75" t="n">
+        <v>0.3899441340782123</v>
+      </c>
+      <c r="R75" t="n">
         <v>31.73214285714281</v>
       </c>
-      <c r="R75" t="n">
+      <c r="S75" t="n">
         <v>0.2220723133576301</v>
       </c>
-      <c r="S75" t="n">
+      <c r="T75" t="n">
         <v>15.66240050600434</v>
       </c>
-      <c r="T75" t="n">
+      <c r="U75" t="n">
         <v>1.802717423609055</v>
       </c>
-      <c r="U75" t="n">
+      <c r="V75" t="n">
         <v>0.009912768032329062</v>
       </c>
-      <c r="V75" t="n">
+      <c r="W75" t="n">
         <v>0.1357454552760376</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0.002245833333333333</v>
       </c>
       <c r="X75" t="n">
         <v>0.002245833333333333</v>
       </c>
       <c r="Y75" t="n">
+        <v>0.002245833333333333</v>
+      </c>
+      <c r="Z75" t="n">
         <v>15.54576471838671</v>
       </c>
-      <c r="Z75" t="n">
+      <c r="AA75" t="n">
         <v>0.07036365759109456</v>
       </c>
-      <c r="AA75" t="n">
-        <v>0</v>
-      </c>
       <c r="AB75" t="n">
         <v>0</v>
       </c>
       <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
         <v>1.795387993961591e-05</v>
       </c>
-      <c r="AD75" t="n">
+      <c r="AE75" t="n">
         <v>0.0002812008582509814</v>
       </c>
     </row>
@@ -7888,38 +8115,38 @@
         <v>-12</v>
       </c>
       <c r="Q76" t="n">
+        <v>-0.2556818181818182</v>
+      </c>
+      <c r="R76" t="n">
         <v>0.2107142857143181</v>
       </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
         <v>0.2107142857143181</v>
       </c>
-      <c r="T76" t="n">
+      <c r="U76" t="n">
         <v>1.74784</v>
       </c>
-      <c r="U76" t="n">
+      <c r="V76" t="n">
         <v>0.869786710518112</v>
       </c>
-      <c r="V76" t="n">
+      <c r="W76" t="n">
         <v>0.1832764854306303</v>
       </c>
-      <c r="W76" t="n">
-        <v>0</v>
-      </c>
       <c r="X76" t="n">
         <v>0</v>
       </c>
       <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="n">
         <v>0.2107142857143181</v>
       </c>
-      <c r="Z76" t="n">
+      <c r="AA76" t="n">
         <v>2.163724434494653</v>
       </c>
-      <c r="AA76" t="n">
-        <v>0</v>
-      </c>
       <c r="AB76" t="n">
         <v>0</v>
       </c>
@@ -7927,6 +8154,9 @@
         <v>0</v>
       </c>
       <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7986,38 +8216,38 @@
         <v>-11.35</v>
       </c>
       <c r="Q77" t="n">
+        <v>-0.2418323863636363</v>
+      </c>
+      <c r="R77" t="n">
         <v>0.2107142857143181</v>
       </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
       <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
         <v>0.3708747103097869</v>
       </c>
-      <c r="T77" t="n">
+      <c r="U77" t="n">
         <v>1.74784</v>
       </c>
-      <c r="U77" t="n">
+      <c r="V77" t="n">
         <v>0.8697860788312274</v>
       </c>
-      <c r="V77" t="n">
+      <c r="W77" t="n">
         <v>0.3225816600180169</v>
       </c>
-      <c r="W77" t="n">
-        <v>0</v>
-      </c>
       <c r="X77" t="n">
         <v>0</v>
       </c>
       <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
         <v>0.2107142857143181</v>
       </c>
-      <c r="Z77" t="n">
+      <c r="AA77" t="n">
         <v>0.4976806198790853</v>
       </c>
-      <c r="AA77" t="n">
-        <v>0</v>
-      </c>
       <c r="AB77" t="n">
         <v>0</v>
       </c>
@@ -8025,6 +8255,9 @@
         <v>0</v>
       </c>
       <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8084,38 +8317,38 @@
         <v>-10.61666666666667</v>
       </c>
       <c r="Q78" t="n">
+        <v>-0.2262073863636364</v>
+      </c>
+      <c r="R78" t="n">
         <v>0.4654761904762265</v>
       </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
         <v>0.7018410420063427</v>
       </c>
-      <c r="T78" t="n">
+      <c r="U78" t="n">
         <v>1.74784</v>
       </c>
-      <c r="U78" t="n">
+      <c r="V78" t="n">
         <v>0.8697845624794525</v>
       </c>
-      <c r="V78" t="n">
+      <c r="W78" t="n">
         <v>0.6104505036516098</v>
       </c>
-      <c r="W78" t="n">
-        <v>0</v>
-      </c>
       <c r="X78" t="n">
         <v>0</v>
       </c>
       <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
         <v>0.3708747103097869</v>
       </c>
-      <c r="Z78" t="n">
+      <c r="AA78" t="n">
         <v>0.6434103325007062</v>
       </c>
-      <c r="AA78" t="n">
-        <v>0</v>
-      </c>
       <c r="AB78" t="n">
         <v>0</v>
       </c>
@@ -8123,6 +8356,9 @@
         <v>0</v>
       </c>
       <c r="AD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8182,38 +8418,38 @@
         <v>-9.85</v>
       </c>
       <c r="Q79" t="n">
+        <v>-0.2098721590909091</v>
+      </c>
+      <c r="R79" t="n">
         <v>0.6464285714286033</v>
       </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
       <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
         <v>1.367227754660794</v>
       </c>
-      <c r="T79" t="n">
+      <c r="U79" t="n">
         <v>1.74784</v>
       </c>
-      <c r="U79" t="n">
+      <c r="V79" t="n">
         <v>0.8697802340254754</v>
       </c>
-      <c r="V79" t="n">
+      <c r="W79" t="n">
         <v>1.189187676414991</v>
       </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
       <c r="X79" t="n">
         <v>0</v>
       </c>
       <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="n">
         <v>0.7018410420063427</v>
       </c>
-      <c r="Z79" t="n">
+      <c r="AA79" t="n">
         <v>0.7086782992882604</v>
       </c>
-      <c r="AA79" t="n">
-        <v>0</v>
-      </c>
       <c r="AB79" t="n">
         <v>0</v>
       </c>
@@ -8221,6 +8457,9 @@
         <v>0</v>
       </c>
       <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8280,38 +8519,38 @@
         <v>-9.266666666666669</v>
       </c>
       <c r="Q80" t="n">
+        <v>-0.1974431818181819</v>
+      </c>
+      <c r="R80" t="n">
         <v>1.175000000000005</v>
       </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
         <v>2.270850110110944</v>
       </c>
-      <c r="T80" t="n">
+      <c r="U80" t="n">
         <v>1.74784</v>
       </c>
-      <c r="U80" t="n">
+      <c r="V80" t="n">
         <v>0.869768079510147</v>
       </c>
-      <c r="V80" t="n">
+      <c r="W80" t="n">
         <v>1.975112939126602</v>
       </c>
-      <c r="W80" t="n">
-        <v>0</v>
-      </c>
       <c r="X80" t="n">
         <v>0</v>
       </c>
       <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
         <v>1.367227754660794</v>
       </c>
-      <c r="Z80" t="n">
+      <c r="AA80" t="n">
         <v>0.7081139676449741</v>
       </c>
-      <c r="AA80" t="n">
-        <v>0</v>
-      </c>
       <c r="AB80" t="n">
         <v>0</v>
       </c>
@@ -8319,6 +8558,9 @@
         <v>0</v>
       </c>
       <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8378,20 +8620,20 @@
         <v>-8.366666666666667</v>
       </c>
       <c r="Q81" t="n">
+        <v>-0.1782670454545454</v>
+      </c>
+      <c r="R81" t="n">
         <v>1.796428571428604</v>
       </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
       <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
         <v>3.740289285714704</v>
       </c>
-      <c r="T81" t="n">
+      <c r="U81" t="n">
         <v>1.74784</v>
       </c>
-      <c r="U81" t="n">
-        <v>0</v>
-      </c>
       <c r="V81" t="n">
         <v>0</v>
       </c>
@@ -8402,14 +8644,14 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="n">
         <v>2.270850110110944</v>
       </c>
-      <c r="Z81" t="n">
+      <c r="AA81" t="n">
         <v>0.5633097792025544</v>
       </c>
-      <c r="AA81" t="n">
-        <v>0</v>
-      </c>
       <c r="AB81" t="n">
         <v>0</v>
       </c>
@@ -8417,6 +8659,9 @@
         <v>0</v>
       </c>
       <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8476,38 +8721,38 @@
         <v>-7.416666666666665</v>
       </c>
       <c r="Q82" t="n">
+        <v>-0.1580255681818181</v>
+      </c>
+      <c r="R82" t="n">
         <v>3.449999999999922</v>
       </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
         <v>5.780684202615478</v>
       </c>
-      <c r="T82" t="n">
+      <c r="U82" t="n">
         <v>1.777849722209515</v>
       </c>
-      <c r="U82" t="n">
+      <c r="V82" t="n">
         <v>0.5739981606752006</v>
       </c>
-      <c r="V82" t="n">
+      <c r="W82" t="n">
         <v>3.164197611172007</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0.04733333333333335</v>
       </c>
       <c r="X82" t="n">
         <v>0.04733333333333335</v>
       </c>
       <c r="Y82" t="n">
+        <v>0.04733333333333335</v>
+      </c>
+      <c r="Z82" t="n">
         <v>3.740289285714704</v>
       </c>
-      <c r="Z82" t="n">
+      <c r="AA82" t="n">
         <v>0.4665723884474225</v>
       </c>
-      <c r="AA82" t="n">
-        <v>0</v>
-      </c>
       <c r="AB82" t="n">
         <v>0</v>
       </c>
@@ -8515,6 +8760,9 @@
         <v>0</v>
       </c>
       <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8574,38 +8822,38 @@
         <v>-6.45</v>
       </c>
       <c r="Q83" t="n">
+        <v>-0.1374289772727273</v>
+      </c>
+      <c r="R83" t="n">
         <v>5.41785714285711</v>
       </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
       <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
         <v>9.058698431912282</v>
       </c>
-      <c r="T83" t="n">
+      <c r="U83" t="n">
         <v>1.828277499987292</v>
       </c>
-      <c r="U83" t="n">
+      <c r="V83" t="n">
         <v>0.4289168597177473</v>
       </c>
-      <c r="V83" t="n">
+      <c r="W83" t="n">
         <v>3.603006472229612</v>
-      </c>
-      <c r="W83" t="n">
-        <v>0.057</v>
       </c>
       <c r="X83" t="n">
         <v>0.057</v>
       </c>
       <c r="Y83" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="Z83" t="n">
         <v>5.780684202615478</v>
       </c>
-      <c r="Z83" t="n">
+      <c r="AA83" t="n">
         <v>0.4598955531383755</v>
       </c>
-      <c r="AA83" t="n">
-        <v>0</v>
-      </c>
       <c r="AB83" t="n">
         <v>0</v>
       </c>
@@ -8613,6 +8861,9 @@
         <v>0</v>
       </c>
       <c r="AD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8672,38 +8923,38 @@
         <v>-5.816666666666666</v>
       </c>
       <c r="Q84" t="n">
+        <v>-0.1239346590909091</v>
+      </c>
+      <c r="R84" t="n">
         <v>7.639285714285721</v>
       </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
         <v>11.41819282221185</v>
       </c>
-      <c r="T84" t="n">
+      <c r="U84" t="n">
         <v>1.866383055542848</v>
       </c>
-      <c r="U84" t="n">
+      <c r="V84" t="n">
         <v>0.3703727268248632</v>
       </c>
-      <c r="V84" t="n">
+      <c r="W84" t="n">
         <v>3.841525371388338</v>
-      </c>
-      <c r="W84" t="n">
-        <v>0.06333333333333334</v>
       </c>
       <c r="X84" t="n">
         <v>0.06333333333333334</v>
       </c>
       <c r="Y84" t="n">
+        <v>0.06333333333333334</v>
+      </c>
+      <c r="Z84" t="n">
         <v>9.058698431912282</v>
       </c>
-      <c r="Z84" t="n">
+      <c r="AA84" t="n">
         <v>0.435983363979242</v>
       </c>
-      <c r="AA84" t="n">
-        <v>0</v>
-      </c>
       <c r="AB84" t="n">
         <v>0</v>
       </c>
@@ -8711,6 +8962,9 @@
         <v>0</v>
       </c>
       <c r="AD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8770,38 +9024,38 @@
         <v>-4.550000000000002</v>
       </c>
       <c r="Q85" t="n">
+        <v>-0.09694602272727275</v>
+      </c>
+      <c r="R85" t="n">
         <v>9.857142857142883</v>
       </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
       <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
         <v>16.52906368490957</v>
       </c>
-      <c r="T85" t="n">
+      <c r="U85" t="n">
         <v>1.954627499987292</v>
       </c>
-      <c r="U85" t="n">
+      <c r="V85" t="n">
         <v>0.2931603739075778</v>
       </c>
-      <c r="V85" t="n">
+      <c r="W85" t="n">
         <v>4.202981968447774</v>
-      </c>
-      <c r="W85" t="n">
-        <v>0.07599999999999998</v>
       </c>
       <c r="X85" t="n">
         <v>0.07599999999999998</v>
       </c>
       <c r="Y85" t="n">
+        <v>0.07599999999999998</v>
+      </c>
+      <c r="Z85" t="n">
         <v>11.41819282221185</v>
       </c>
-      <c r="Z85" t="n">
+      <c r="AA85" t="n">
         <v>0.3176043329592845</v>
       </c>
-      <c r="AA85" t="n">
-        <v>0</v>
-      </c>
       <c r="AB85" t="n">
         <v>0</v>
       </c>
@@ -8809,6 +9063,9 @@
         <v>0</v>
       </c>
       <c r="AD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8868,38 +9125,38 @@
         <v>-3.649999999999999</v>
       </c>
       <c r="Q86" t="n">
+        <v>-0.07776988636363633</v>
+      </c>
+      <c r="R86" t="n">
         <v>15.67142857142846</v>
       </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
         <v>20.39251848222766</v>
       </c>
-      <c r="T86" t="n">
+      <c r="U86" t="n">
         <v>2.027077499987293</v>
       </c>
-      <c r="U86" t="n">
+      <c r="V86" t="n">
         <v>0.256260356669624</v>
       </c>
-      <c r="V86" t="n">
+      <c r="W86" t="n">
         <v>4.370689076734861</v>
-      </c>
-      <c r="W86" t="n">
-        <v>0.08500000000000002</v>
       </c>
       <c r="X86" t="n">
         <v>0.08500000000000002</v>
       </c>
       <c r="Y86" t="n">
+        <v>0.08500000000000002</v>
+      </c>
+      <c r="Z86" t="n">
         <v>16.52906368490957</v>
       </c>
-      <c r="Z86" t="n">
+      <c r="AA86" t="n">
         <v>0.2216739014614701</v>
       </c>
-      <c r="AA86" t="n">
-        <v>0</v>
-      </c>
       <c r="AB86" t="n">
         <v>0</v>
       </c>
@@ -8907,6 +9164,9 @@
         <v>0</v>
       </c>
       <c r="AD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8966,38 +9226,38 @@
         <v>-2.649999999999999</v>
       </c>
       <c r="Q87" t="n">
+        <v>-0.05646306818181815</v>
+      </c>
+      <c r="R87" t="n">
         <v>19.33214285714294</v>
       </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
       <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
         <v>23.31766948669558</v>
       </c>
-      <c r="T87" t="n">
+      <c r="U87" t="n">
         <v>2.085607249984742</v>
       </c>
-      <c r="U87" t="n">
+      <c r="V87" t="n">
         <v>0.01021553947307476</v>
       </c>
-      <c r="V87" t="n">
+      <c r="W87" t="n">
         <v>0.2005250351785432</v>
-      </c>
-      <c r="W87" t="n">
-        <v>0.003370000000000001</v>
       </c>
       <c r="X87" t="n">
         <v>0.003370000000000001</v>
       </c>
       <c r="Y87" t="n">
+        <v>0.003370000000000001</v>
+      </c>
+      <c r="Z87" t="n">
         <v>20.39251848222766</v>
       </c>
-      <c r="Z87" t="n">
+      <c r="AA87" t="n">
         <v>0.1419264349539861</v>
       </c>
-      <c r="AA87" t="n">
-        <v>0</v>
-      </c>
       <c r="AB87" t="n">
         <v>0</v>
       </c>
@@ -9005,6 +9265,9 @@
         <v>0</v>
       </c>
       <c r="AD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9064,38 +9327,38 @@
         <v>-1.5</v>
       </c>
       <c r="Q88" t="n">
+        <v>-0.03196022727272727</v>
+      </c>
+      <c r="R88" t="n">
         <v>21.1678571428572</v>
       </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
         <v>23.51196957074787</v>
       </c>
-      <c r="T88" t="n">
+      <c r="U88" t="n">
         <v>2.089614999984743</v>
       </c>
-      <c r="U88" t="n">
+      <c r="V88" t="n">
         <v>0.01079775923725555</v>
       </c>
-      <c r="V88" t="n">
+      <c r="W88" t="n">
         <v>0.2133700385438203</v>
-      </c>
-      <c r="W88" t="n">
-        <v>0.0036</v>
       </c>
       <c r="X88" t="n">
         <v>0.0036</v>
       </c>
       <c r="Y88" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="Z88" t="n">
         <v>23.31766948669558</v>
       </c>
-      <c r="Z88" t="n">
+      <c r="AA88" t="n">
         <v>0.07721244115214908</v>
       </c>
-      <c r="AA88" t="n">
-        <v>0</v>
-      </c>
       <c r="AB88" t="n">
         <v>0</v>
       </c>
@@ -9103,6 +9366,9 @@
         <v>0</v>
       </c>
       <c r="AD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9162,38 +9428,38 @@
         <v>-0.08333333333333215</v>
       </c>
       <c r="Q89" t="n">
+        <v>-0.001775568181818156</v>
+      </c>
+      <c r="R89" t="n">
         <v>23.35000000000008</v>
       </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
       <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
         <v>23.76781114532759</v>
       </c>
-      <c r="T89" t="n">
+      <c r="U89" t="n">
         <v>2.094915694429186</v>
       </c>
-      <c r="U89" t="n">
+      <c r="V89" t="n">
         <v>0.01150934434104848</v>
       </c>
-      <c r="V89" t="n">
+      <c r="W89" t="n">
         <v>0.2294936660757086</v>
-      </c>
-      <c r="W89" t="n">
-        <v>0.003883333333333334</v>
       </c>
       <c r="X89" t="n">
         <v>0.003883333333333334</v>
       </c>
       <c r="Y89" t="n">
+        <v>0.003883333333333334</v>
+      </c>
+      <c r="Z89" t="n">
         <v>23.51196957074787</v>
       </c>
-      <c r="Z89" t="n">
+      <c r="AA89" t="n">
         <v>0.03322042971089017</v>
       </c>
-      <c r="AA89" t="n">
-        <v>0</v>
-      </c>
       <c r="AB89" t="n">
         <v>0</v>
       </c>
@@ -9201,6 +9467,9 @@
         <v>0</v>
       </c>
       <c r="AD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9260,45 +9529,48 @@
         <v>0.8166666666666629</v>
       </c>
       <c r="Q90" t="n">
+        <v>0.0174005681818181</v>
+      </c>
+      <c r="R90" t="n">
         <v>24.49345238095237</v>
       </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
         <v>23.93967898481781</v>
       </c>
-      <c r="T90" t="n">
+      <c r="U90" t="n">
         <v>2.098491694429187</v>
       </c>
-      <c r="U90" t="n">
+      <c r="V90" t="n">
         <v>0.01007990389195562</v>
       </c>
-      <c r="V90" t="n">
+      <c r="W90" t="n">
         <v>0.194954990695357</v>
-      </c>
-      <c r="W90" t="n">
-        <v>0.004063333333333333</v>
       </c>
       <c r="X90" t="n">
         <v>0.004063333333333333</v>
       </c>
       <c r="Y90" t="n">
+        <v>0.004063333333333333</v>
+      </c>
+      <c r="Z90" t="n">
         <v>23.76781114532759</v>
       </c>
-      <c r="Z90" t="n">
+      <c r="AA90" t="n">
         <v>0.01703599848924725</v>
       </c>
-      <c r="AA90" t="n">
+      <c r="AB90" t="n">
         <v>0.002931631959375182</v>
       </c>
-      <c r="AB90" t="n">
+      <c r="AC90" t="n">
         <v>0.07399229663180125</v>
       </c>
-      <c r="AC90" t="n">
+      <c r="AD90" t="n">
         <v>0.003096509180803947</v>
       </c>
-      <c r="AD90" t="n">
+      <c r="AE90" t="n">
         <v>0.07412943576198766</v>
       </c>
     </row>
@@ -9358,45 +9630,48 @@
         <v>2.249999999999996</v>
       </c>
       <c r="Q91" t="n">
+        <v>0.04794034090909083</v>
+      </c>
+      <c r="R91" t="n">
         <v>25.23928571428564</v>
       </c>
-      <c r="R91" t="n">
+      <c r="S91" t="n">
         <v>0.06375494686076261</v>
       </c>
-      <c r="S91" t="n">
+      <c r="T91" t="n">
         <v>24.22814583540682</v>
       </c>
-      <c r="T91" t="n">
+      <c r="U91" t="n">
         <v>2.104521249984743</v>
       </c>
-      <c r="U91" t="n">
+      <c r="V91" t="n">
         <v>0.01063211162014986</v>
       </c>
-      <c r="V91" t="n">
+      <c r="W91" t="n">
         <v>0.2075172963667405</v>
-      </c>
-      <c r="W91" t="n">
-        <v>0.00435</v>
       </c>
       <c r="X91" t="n">
         <v>0.00435</v>
       </c>
       <c r="Y91" t="n">
+        <v>0.00435</v>
+      </c>
+      <c r="Z91" t="n">
         <v>23.93967898481781</v>
       </c>
-      <c r="Z91" t="n">
+      <c r="AA91" t="n">
         <v>0.003897200232591663</v>
       </c>
-      <c r="AA91" t="n">
+      <c r="AB91" t="n">
         <v>0.002618004611547352</v>
       </c>
-      <c r="AB91" t="n">
+      <c r="AC91" t="n">
         <v>0.06485638924285067</v>
       </c>
-      <c r="AC91" t="n">
+      <c r="AD91" t="n">
         <v>0.00271569751353864</v>
       </c>
-      <c r="AD91" t="n">
+      <c r="AE91" t="n">
         <v>0.06579631540286586</v>
       </c>
     </row>
@@ -9456,45 +9731,48 @@
         <v>3.75</v>
       </c>
       <c r="Q92" t="n">
+        <v>0.07990056818181818</v>
+      </c>
+      <c r="R92" t="n">
         <v>24.77321428571426</v>
       </c>
-      <c r="R92" t="n">
+      <c r="S92" t="n">
         <v>0.1716212668026328</v>
       </c>
-      <c r="S92" t="n">
+      <c r="T92" t="n">
         <v>24.54912556934151</v>
       </c>
-      <c r="T92" t="n">
+      <c r="U92" t="n">
         <v>2.111271249984743</v>
       </c>
-      <c r="U92" t="n">
+      <c r="V92" t="n">
         <v>0.01118090177937685</v>
       </c>
-      <c r="V92" t="n">
+      <c r="W92" t="n">
         <v>0.2204127839316294</v>
-      </c>
-      <c r="W92" t="n">
-        <v>0.00465</v>
       </c>
       <c r="X92" t="n">
         <v>0.00465</v>
       </c>
       <c r="Y92" t="n">
+        <v>0.00465</v>
+      </c>
+      <c r="Z92" t="n">
         <v>24.22814583540682</v>
       </c>
-      <c r="Z92" t="n">
+      <c r="AA92" t="n">
         <v>0.01411667984325947</v>
       </c>
-      <c r="AA92" t="n">
+      <c r="AB92" t="n">
         <v>0.00194663879778472</v>
       </c>
-      <c r="AB92" t="n">
+      <c r="AC92" t="n">
         <v>0.04872158819598323</v>
       </c>
-      <c r="AC92" t="n">
+      <c r="AD92" t="n">
         <v>0.002019535772512294</v>
       </c>
-      <c r="AD92" t="n">
+      <c r="AE92" t="n">
         <v>0.0495778372711814</v>
       </c>
     </row>
@@ -9554,45 +9832,48 @@
         <v>5.75</v>
       </c>
       <c r="Q93" t="n">
+        <v>0.1225142045454545</v>
+      </c>
+      <c r="R93" t="n">
         <v>25.0285714285714</v>
       </c>
-      <c r="R93" t="n">
+      <c r="S93" t="n">
         <v>0.2547670720457892</v>
       </c>
-      <c r="S93" t="n">
+      <c r="T93" t="n">
         <v>25.00680786687655</v>
       </c>
-      <c r="T93" t="n">
+      <c r="U93" t="n">
         <v>2.120971249984743</v>
       </c>
-      <c r="U93" t="n">
+      <c r="V93" t="n">
         <v>0.01186590939888761</v>
       </c>
-      <c r="V93" t="n">
+      <c r="W93" t="n">
         <v>0.2371876907011177</v>
-      </c>
-      <c r="W93" t="n">
-        <v>0.005050000000000001</v>
       </c>
       <c r="X93" t="n">
         <v>0.005050000000000001</v>
       </c>
       <c r="Y93" t="n">
+        <v>0.005050000000000001</v>
+      </c>
+      <c r="Z93" t="n">
         <v>24.54912556934151</v>
       </c>
-      <c r="Z93" t="n">
+      <c r="AA93" t="n">
         <v>0.01729347944990734</v>
       </c>
-      <c r="AA93" t="n">
+      <c r="AB93" t="n">
         <v>0.001250719091027115</v>
       </c>
-      <c r="AB93" t="n">
+      <c r="AC93" t="n">
         <v>0.03284030984725474</v>
       </c>
-      <c r="AC93" t="n">
+      <c r="AD93" t="n">
         <v>0.001332234624952042</v>
       </c>
-      <c r="AD93" t="n">
+      <c r="AE93" t="n">
         <v>0.03331493529977605</v>
       </c>
     </row>
@@ -9652,45 +9933,48 @@
         <v>10.08333333333333</v>
       </c>
       <c r="Q94" t="n">
+        <v>0.2148437499999999</v>
+      </c>
+      <c r="R94" t="n">
         <v>26.25714285714279</v>
       </c>
-      <c r="R94" t="n">
+      <c r="S94" t="n">
         <v>0.3345630000595383</v>
       </c>
-      <c r="S94" t="n">
+      <c r="T94" t="n">
         <v>26.11045456330866</v>
       </c>
-      <c r="T94" t="n">
+      <c r="U94" t="n">
         <v>2.144732361095854</v>
       </c>
-      <c r="U94" t="n">
+      <c r="V94" t="n">
         <v>0.01316720038405787</v>
       </c>
-      <c r="V94" t="n">
+      <c r="W94" t="n">
         <v>0.2717707554568806</v>
-      </c>
-      <c r="W94" t="n">
-        <v>0.005916666666666667</v>
       </c>
       <c r="X94" t="n">
         <v>0.005916666666666667</v>
       </c>
       <c r="Y94" t="n">
+        <v>0.005916666666666667</v>
+      </c>
+      <c r="Z94" t="n">
         <v>25.00680786687655</v>
       </c>
-      <c r="Z94" t="n">
+      <c r="AA94" t="n">
         <v>0.01396089162246411</v>
       </c>
-      <c r="AA94" t="n">
+      <c r="AB94" t="n">
         <v>0.0001013561359319036</v>
       </c>
-      <c r="AB94" t="n">
+      <c r="AC94" t="n">
         <v>0.002777158124534164</v>
       </c>
-      <c r="AC94" t="n">
+      <c r="AD94" t="n">
         <v>0.0001589641491270462</v>
       </c>
-      <c r="AD94" t="n">
+      <c r="AE94" t="n">
         <v>0.004150626192976761</v>
       </c>
     </row>
@@ -9750,45 +10034,48 @@
         <v>11.75</v>
       </c>
       <c r="Q95" t="n">
+        <v>0.2503551136363636</v>
+      </c>
+      <c r="R95" t="n">
         <v>27.40000000000004</v>
       </c>
-      <c r="R95" t="n">
+      <c r="S95" t="n">
         <v>0.4114676331552647</v>
       </c>
-      <c r="S95" t="n">
+      <c r="T95" t="n">
         <v>26.57397314534754</v>
       </c>
-      <c r="T95" t="n">
+      <c r="U95" t="n">
         <v>2.154871249984743</v>
       </c>
-      <c r="U95" t="n">
+      <c r="V95" t="n">
         <v>0.01360207800305404</v>
       </c>
-      <c r="V95" t="n">
+      <c r="W95" t="n">
         <v>0.2843859629506359</v>
-      </c>
-      <c r="W95" t="n">
-        <v>0.00625</v>
       </c>
       <c r="X95" t="n">
         <v>0.00625</v>
       </c>
       <c r="Y95" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="Z95" t="n">
         <v>26.11045456330866</v>
       </c>
-      <c r="Z95" t="n">
+      <c r="AA95" t="n">
         <v>0.01145255846603085</v>
       </c>
-      <c r="AA95" t="n">
-        <v>0</v>
-      </c>
       <c r="AB95" t="n">
         <v>0</v>
       </c>
       <c r="AC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD95" t="n">
         <v>4.43986780696222e-05</v>
       </c>
-      <c r="AD95" t="n">
+      <c r="AE95" t="n">
         <v>0.001179849278711071</v>
       </c>
     </row>
@@ -9848,45 +10135,48 @@
         <v>14.25</v>
       </c>
       <c r="Q96" t="n">
+        <v>0.3036221590909091</v>
+      </c>
+      <c r="R96" t="n">
         <v>28.4607142857143</v>
       </c>
-      <c r="R96" t="n">
+      <c r="S96" t="n">
         <v>0.4067877264015557</v>
       </c>
-      <c r="S96" t="n">
+      <c r="T96" t="n">
         <v>27.30784322790872</v>
       </c>
-      <c r="T96" t="n">
+      <c r="U96" t="n">
         <v>2.171121249984743</v>
       </c>
-      <c r="U96" t="n">
+      <c r="V96" t="n">
         <v>0.01418845246147928</v>
       </c>
-      <c r="V96" t="n">
+      <c r="W96" t="n">
         <v>0.3025561516882164</v>
-      </c>
-      <c r="W96" t="n">
-        <v>0.006750000000000001</v>
       </c>
       <c r="X96" t="n">
         <v>0.006750000000000001</v>
       </c>
       <c r="Y96" t="n">
+        <v>0.006750000000000001</v>
+      </c>
+      <c r="Z96" t="n">
         <v>26.57397314534754</v>
       </c>
-      <c r="Z96" t="n">
+      <c r="AA96" t="n">
         <v>0.009152735978746178</v>
       </c>
-      <c r="AA96" t="n">
+      <c r="AB96" t="n">
         <v>6.146505253398153e-05</v>
       </c>
-      <c r="AB96" t="n">
+      <c r="AC96" t="n">
         <v>0.001762949417501451</v>
       </c>
-      <c r="AC96" t="n">
+      <c r="AD96" t="n">
         <v>4.578707085297215e-05</v>
       </c>
-      <c r="AD96" t="n">
+      <c r="AE96" t="n">
         <v>0.001250346152718112</v>
       </c>
     </row>
@@ -9946,45 +10236,48 @@
         <v>15.91666666666666</v>
       </c>
       <c r="Q97" t="n">
+        <v>0.3391335227272727</v>
+      </c>
+      <c r="R97" t="n">
         <v>28.6821428571429</v>
       </c>
-      <c r="R97" t="n">
+      <c r="S97" t="n">
         <v>0.4021708299263646</v>
       </c>
-      <c r="S97" t="n">
+      <c r="T97" t="n">
         <v>27.82182632859923</v>
       </c>
-      <c r="T97" t="n">
+      <c r="U97" t="n">
         <v>2.182649027762521</v>
       </c>
-      <c r="U97" t="n">
+      <c r="V97" t="n">
         <v>0.01453689738861425</v>
       </c>
-      <c r="V97" t="n">
+      <c r="W97" t="n">
         <v>0.3141530853075174</v>
-      </c>
-      <c r="W97" t="n">
-        <v>0.007083333333333334</v>
       </c>
       <c r="X97" t="n">
         <v>0.007083333333333334</v>
       </c>
       <c r="Y97" t="n">
+        <v>0.007083333333333334</v>
+      </c>
+      <c r="Z97" t="n">
         <v>27.30784322790872</v>
       </c>
-      <c r="Z97" t="n">
+      <c r="AA97" t="n">
         <v>0.00813246080612828</v>
       </c>
-      <c r="AA97" t="n">
+      <c r="AB97" t="n">
         <v>5.722124060260651e-05</v>
       </c>
-      <c r="AB97" t="n">
+      <c r="AC97" t="n">
         <v>0.001647154283060745</v>
       </c>
-      <c r="AC97" t="n">
+      <c r="AD97" t="n">
         <v>4.518776391829954e-05</v>
       </c>
-      <c r="AD97" t="n">
+      <c r="AE97" t="n">
         <v>0.001257206119912673</v>
       </c>
     </row>
@@ -10044,45 +10337,48 @@
         <v>18.7</v>
       </c>
       <c r="Q98" t="n">
+        <v>0.3984374999999999</v>
+      </c>
+      <c r="R98" t="n">
         <v>28.78571428571429</v>
       </c>
-      <c r="R98" t="n">
+      <c r="S98" t="n">
         <v>0.3873938421634567</v>
       </c>
-      <c r="S98" t="n">
+      <c r="T98" t="n">
         <v>28.72212538793305</v>
       </c>
-      <c r="T98" t="n">
+      <c r="U98" t="n">
         <v>2.203138999984743</v>
       </c>
-      <c r="U98" t="n">
+      <c r="V98" t="n">
         <v>0.01504659661323521</v>
       </c>
-      <c r="V98" t="n">
+      <c r="W98" t="n">
         <v>0.3325682403572446</v>
-      </c>
-      <c r="W98" t="n">
-        <v>0.007640000000000001</v>
       </c>
       <c r="X98" t="n">
         <v>0.007640000000000001</v>
       </c>
       <c r="Y98" t="n">
+        <v>0.007640000000000001</v>
+      </c>
+      <c r="Z98" t="n">
         <v>27.82182632859923</v>
       </c>
-      <c r="Z98" t="n">
+      <c r="AA98" t="n">
         <v>0.007018151213335786</v>
       </c>
-      <c r="AA98" t="n">
+      <c r="AB98" t="n">
         <v>1.910531806293016e-05</v>
       </c>
-      <c r="AB98" t="n">
+      <c r="AC98" t="n">
         <v>0.0005503013934911842</v>
       </c>
-      <c r="AC98" t="n">
+      <c r="AD98" t="n">
         <v>4.454302433905062e-05</v>
       </c>
-      <c r="AD98" t="n">
+      <c r="AE98" t="n">
         <v>0.001279370330223965</v>
       </c>
     </row>
@@ -10142,45 +10438,48 @@
         <v>21.75</v>
       </c>
       <c r="Q99" t="n">
+        <v>0.4634232954545454</v>
+      </c>
+      <c r="R99" t="n">
         <v>28.80357142857139</v>
       </c>
-      <c r="R99" t="n">
+      <c r="S99" t="n">
         <v>0.3689307159607038</v>
       </c>
-      <c r="S99" t="n">
+      <c r="T99" t="n">
         <v>29.76547646571371</v>
       </c>
-      <c r="T99" t="n">
+      <c r="U99" t="n">
         <v>2.227371249984743</v>
       </c>
-      <c r="U99" t="n">
+      <c r="V99" t="n">
         <v>0.0155078415118352</v>
       </c>
-      <c r="V99" t="n">
+      <c r="W99" t="n">
         <v>0.3513494137153382</v>
-      </c>
-      <c r="W99" t="n">
-        <v>0.00825</v>
       </c>
       <c r="X99" t="n">
         <v>0.00825</v>
       </c>
       <c r="Y99" t="n">
+        <v>0.00825</v>
+      </c>
+      <c r="Z99" t="n">
         <v>28.72212538793305</v>
       </c>
-      <c r="Z99" t="n">
+      <c r="AA99" t="n">
         <v>0.01009923569250023</v>
       </c>
-      <c r="AA99" t="n">
+      <c r="AB99" t="n">
         <v>1.425389975077348e-05</v>
       </c>
-      <c r="AB99" t="n">
+      <c r="AC99" t="n">
         <v>0.0004247662125730495</v>
       </c>
-      <c r="AC99" t="n">
+      <c r="AD99" t="n">
         <v>4.408174559026023e-05</v>
       </c>
-      <c r="AD99" t="n">
+      <c r="AE99" t="n">
         <v>0.00131211416093447</v>
       </c>
     </row>
@@ -10240,45 +10539,48 @@
         <v>24.75</v>
       </c>
       <c r="Q100" t="n">
+        <v>0.52734375</v>
+      </c>
+      <c r="R100" t="n">
         <v>29.79999999999999</v>
       </c>
-      <c r="R100" t="n">
+      <c r="S100" t="n">
         <v>0.3542503465167628</v>
       </c>
-      <c r="S100" t="n">
+      <c r="T100" t="n">
         <v>30.84541916498249</v>
       </c>
-      <c r="T100" t="n">
+      <c r="U100" t="n">
         <v>2.253021249984743</v>
       </c>
-      <c r="U100" t="n">
+      <c r="V100" t="n">
         <v>0.01587051773015364</v>
       </c>
-      <c r="V100" t="n">
+      <c r="W100" t="n">
         <v>0.3683701508436424</v>
-      </c>
-      <c r="W100" t="n">
-        <v>0.00885</v>
       </c>
       <c r="X100" t="n">
         <v>0.00885</v>
       </c>
       <c r="Y100" t="n">
+        <v>0.00885</v>
+      </c>
+      <c r="Z100" t="n">
         <v>29.76547646571371</v>
       </c>
-      <c r="Z100" t="n">
+      <c r="AA100" t="n">
         <v>0.007799312579268405</v>
       </c>
-      <c r="AA100" t="n">
+      <c r="AB100" t="n">
         <v>0.0002877005497867221</v>
       </c>
-      <c r="AB100" t="n">
+      <c r="AC100" t="n">
         <v>0.008954679612111731</v>
       </c>
-      <c r="AC100" t="n">
+      <c r="AD100" t="n">
         <v>0.0003012099228746798</v>
       </c>
-      <c r="AD100" t="n">
+      <c r="AE100" t="n">
         <v>0.009290946327721546</v>
       </c>
     </row>
@@ -10338,45 +10640,48 @@
         <v>27.33333333333334</v>
       </c>
       <c r="Q101" t="n">
+        <v>0.5823863636363636</v>
+      </c>
+      <c r="R101" t="n">
         <v>31.12500000000002</v>
       </c>
-      <c r="R101" t="n">
+      <c r="S101" t="n">
         <v>0.363160750555521</v>
       </c>
-      <c r="S101" t="n">
+      <c r="T101" t="n">
         <v>31.81469618008588</v>
       </c>
-      <c r="T101" t="n">
+      <c r="U101" t="n">
         <v>2.276551111095854</v>
       </c>
-      <c r="U101" t="n">
+      <c r="V101" t="n">
         <v>0.01611696629211079</v>
       </c>
-      <c r="V101" t="n">
+      <c r="W101" t="n">
         <v>0.3818576537329387</v>
-      </c>
-      <c r="W101" t="n">
-        <v>0.009366666666666667</v>
       </c>
       <c r="X101" t="n">
         <v>0.009366666666666667</v>
       </c>
       <c r="Y101" t="n">
+        <v>0.009366666666666667</v>
+      </c>
+      <c r="Z101" t="n">
         <v>30.84541916498249</v>
       </c>
-      <c r="Z101" t="n">
+      <c r="AA101" t="n">
         <v>0.006429284455135683</v>
       </c>
-      <c r="AA101" t="n">
+      <c r="AB101" t="n">
         <v>0.0007098662467225611</v>
       </c>
-      <c r="AB101" t="n">
+      <c r="AC101" t="n">
         <v>0.02192219084074996</v>
       </c>
-      <c r="AC101" t="n">
+      <c r="AD101" t="n">
         <v>0.0006841428405296224</v>
       </c>
-      <c r="AD101" t="n">
+      <c r="AE101" t="n">
         <v>0.02176579661523088</v>
       </c>
     </row>
@@ -10436,45 +10741,48 @@
         <v>34.93333333333334</v>
       </c>
       <c r="Q102" t="n">
+        <v>0.7443181818181819</v>
+      </c>
+      <c r="R102" t="n">
         <v>30.88214285714287</v>
       </c>
-      <c r="R102" t="n">
+      <c r="S102" t="n">
         <v>0.3954213588988506</v>
       </c>
-      <c r="S102" t="n">
+      <c r="T102" t="n">
         <v>34.84968576356192</v>
       </c>
-      <c r="T102" t="n">
+      <c r="U102" t="n">
         <v>2.353513777762521</v>
       </c>
-      <c r="U102" t="n">
+      <c r="V102" t="n">
         <v>0.01654179887468306</v>
       </c>
-      <c r="V102" t="n">
+      <c r="W102" t="n">
         <v>0.4152720349990343</v>
-      </c>
-      <c r="W102" t="n">
-        <v>0.01088666666666667</v>
       </c>
       <c r="X102" t="n">
         <v>0.01088666666666667</v>
       </c>
       <c r="Y102" t="n">
+        <v>0.01088666666666667</v>
+      </c>
+      <c r="Z102" t="n">
         <v>31.81469618008588</v>
       </c>
-      <c r="Z102" t="n">
+      <c r="AA102" t="n">
         <v>0.02024773721229721</v>
       </c>
-      <c r="AA102" t="n">
+      <c r="AB102" t="n">
         <v>0.002400167963573594</v>
       </c>
-      <c r="AB102" t="n">
+      <c r="AC102" t="n">
         <v>0.07665107832241122</v>
       </c>
-      <c r="AC102" t="n">
+      <c r="AD102" t="n">
         <v>0.002076037952137568</v>
       </c>
-      <c r="AD102" t="n">
+      <c r="AE102" t="n">
         <v>0.07234927026522282</v>
       </c>
     </row>
@@ -10534,38 +10842,38 @@
         <v>-10</v>
       </c>
       <c r="Q103" t="n">
+        <v>-0.2154398563734291</v>
+      </c>
+      <c r="R103" t="n">
         <v>0.1803571428572935</v>
       </c>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
       <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
         <v>0.1803571428572935</v>
       </c>
-      <c r="T103" t="n">
+      <c r="U103" t="n">
         <v>1.7528</v>
       </c>
-      <c r="U103" t="n">
+      <c r="V103" t="n">
         <v>0.8697868869746461</v>
       </c>
-      <c r="V103" t="n">
+      <c r="W103" t="n">
         <v>0.1568722778294868</v>
       </c>
-      <c r="W103" t="n">
-        <v>0</v>
-      </c>
       <c r="X103" t="n">
         <v>0</v>
       </c>
       <c r="Y103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" t="n">
         <v>0.1803571428572935</v>
       </c>
-      <c r="Z103" t="n">
+      <c r="AA103" t="n">
         <v>0.2993817189618296</v>
       </c>
-      <c r="AA103" t="n">
-        <v>0</v>
-      </c>
       <c r="AB103" t="n">
         <v>0</v>
       </c>
@@ -10573,6 +10881,9 @@
         <v>0</v>
       </c>
       <c r="AD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10632,38 +10943,38 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="Q104" t="n">
+        <v>-0.1982046678635548</v>
+      </c>
+      <c r="R104" t="n">
         <v>0.1803571428572935</v>
       </c>
-      <c r="R104" t="n">
-        <v>0</v>
-      </c>
       <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
         <v>0.3616830505930247</v>
       </c>
-      <c r="T104" t="n">
+      <c r="U104" t="n">
         <v>1.7528</v>
       </c>
-      <c r="U104" t="n">
+      <c r="V104" t="n">
         <v>0.8697861867769351</v>
       </c>
-      <c r="V104" t="n">
+      <c r="W104" t="n">
         <v>0.3145869213971563</v>
       </c>
-      <c r="W104" t="n">
-        <v>0</v>
-      </c>
       <c r="X104" t="n">
         <v>0</v>
       </c>
       <c r="Y104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" t="n">
         <v>0.1803571428572935</v>
       </c>
-      <c r="Z104" t="n">
+      <c r="AA104" t="n">
         <v>1.543307739364463</v>
       </c>
-      <c r="AA104" t="n">
-        <v>0</v>
-      </c>
       <c r="AB104" t="n">
         <v>0</v>
       </c>
@@ -10671,6 +10982,9 @@
         <v>0</v>
       </c>
       <c r="AD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10730,38 +11044,38 @@
         <v>-8.15</v>
       </c>
       <c r="Q105" t="n">
+        <v>-0.1755834829443447</v>
+      </c>
+      <c r="R105" t="n">
         <v>0.3392857142857694</v>
       </c>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
       <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
         <v>0.9014843522334873</v>
       </c>
-      <c r="T105" t="n">
+      <c r="U105" t="n">
         <v>1.7528</v>
       </c>
-      <c r="U105" t="n">
+      <c r="V105" t="n">
         <v>0.869783575992696</v>
       </c>
-      <c r="V105" t="n">
+      <c r="W105" t="n">
         <v>0.7840962835871017</v>
       </c>
-      <c r="W105" t="n">
-        <v>0</v>
-      </c>
       <c r="X105" t="n">
         <v>0</v>
       </c>
       <c r="Y105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" t="n">
         <v>0.3616830505930247</v>
       </c>
-      <c r="Z105" t="n">
+      <c r="AA105" t="n">
         <v>1.03160607166846</v>
       </c>
-      <c r="AA105" t="n">
-        <v>0</v>
-      </c>
       <c r="AB105" t="n">
         <v>0</v>
       </c>
@@ -10769,6 +11083,9 @@
         <v>0</v>
       </c>
       <c r="AD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10828,38 +11145,38 @@
         <v>-6.966666666666667</v>
       </c>
       <c r="Q106" t="n">
+        <v>-0.1500897666068223</v>
+      </c>
+      <c r="R106" t="n">
         <v>0.8962500000000428</v>
       </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
       <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
         <v>2.523189877060152</v>
       </c>
-      <c r="T106" t="n">
+      <c r="U106" t="n">
         <v>1.7528</v>
       </c>
-      <c r="U106" t="n">
+      <c r="V106" t="n">
         <v>0.869761996914966</v>
       </c>
-      <c r="V106" t="n">
+      <c r="W106" t="n">
         <v>2.194574666067465</v>
       </c>
-      <c r="W106" t="n">
-        <v>0</v>
-      </c>
       <c r="X106" t="n">
         <v>0</v>
       </c>
       <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
         <v>0.9014843522334873</v>
       </c>
-      <c r="Z106" t="n">
+      <c r="AA106" t="n">
         <v>0.779274995510789</v>
       </c>
-      <c r="AA106" t="n">
-        <v>0</v>
-      </c>
       <c r="AB106" t="n">
         <v>0</v>
       </c>
@@ -10867,6 +11184,9 @@
         <v>0</v>
       </c>
       <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10926,38 +11246,38 @@
         <v>-5.999999999999999</v>
       </c>
       <c r="Q107" t="n">
+        <v>-0.1292639138240574</v>
+      </c>
+      <c r="R107" t="n">
         <v>2.504651162790685</v>
       </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
       <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
         <v>4.837087486134564</v>
       </c>
-      <c r="T107" t="n">
+      <c r="U107" t="n">
         <v>1.768600015796089</v>
       </c>
-      <c r="U107" t="n">
+      <c r="V107" t="n">
         <v>0.6045883105005354</v>
       </c>
-      <c r="V107" t="n">
+      <c r="W107" t="n">
         <v>2.697443125811001</v>
       </c>
-      <c r="W107" t="n">
+      <c r="X107" t="n">
         <v>0.08300000000000002</v>
       </c>
-      <c r="X107" t="n">
+      <c r="Y107" t="n">
         <v>0.04150000000000001</v>
       </c>
-      <c r="Y107" t="n">
+      <c r="Z107" t="n">
         <v>2.523189877060152</v>
       </c>
-      <c r="Z107" t="n">
+      <c r="AA107" t="n">
         <v>0.4089904904144481</v>
       </c>
-      <c r="AA107" t="n">
-        <v>0</v>
-      </c>
       <c r="AB107" t="n">
         <v>0</v>
       </c>
@@ -10965,6 +11285,9 @@
         <v>0</v>
       </c>
       <c r="AD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11024,38 +11347,38 @@
         <v>-5.033333333333334</v>
       </c>
       <c r="Q108" t="n">
+        <v>-0.1084380610412927</v>
+      </c>
+      <c r="R108" t="n">
         <v>5.678571428571439</v>
       </c>
-      <c r="R108" t="n">
-        <v>0</v>
-      </c>
       <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
         <v>7.795781238820468</v>
       </c>
-      <c r="T108" t="n">
+      <c r="U108" t="n">
         <v>1.813388949473866</v>
       </c>
-      <c r="U108" t="n">
+      <c r="V108" t="n">
         <v>0.4510700441714365</v>
       </c>
-      <c r="V108" t="n">
+      <c r="W108" t="n">
         <v>3.076511138055088</v>
       </c>
-      <c r="W108" t="n">
+      <c r="X108" t="n">
         <v>0.1023333333333333</v>
       </c>
-      <c r="X108" t="n">
+      <c r="Y108" t="n">
         <v>0.05116666666666666</v>
       </c>
-      <c r="Y108" t="n">
+      <c r="Z108" t="n">
         <v>4.837087486134564</v>
       </c>
-      <c r="Z108" t="n">
+      <c r="AA108" t="n">
         <v>0.4130305359490459</v>
       </c>
-      <c r="AA108" t="n">
-        <v>0</v>
-      </c>
       <c r="AB108" t="n">
         <v>0</v>
       </c>
@@ -11063,6 +11386,9 @@
         <v>0</v>
       </c>
       <c r="AD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11122,38 +11448,38 @@
         <v>-4.166666666666667</v>
       </c>
       <c r="Q109" t="n">
+        <v>-0.08976660682226213</v>
+      </c>
+      <c r="R109" t="n">
         <v>7.142857142857149</v>
       </c>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
       <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
         <v>10.81459998402953</v>
       </c>
-      <c r="T109" t="n">
+      <c r="U109" t="n">
         <v>1.861488997573866</v>
       </c>
-      <c r="U109" t="n">
+      <c r="V109" t="n">
         <v>0.3704055830971815</v>
       </c>
-      <c r="V109" t="n">
+      <c r="W109" t="n">
         <v>3.310566735451119</v>
       </c>
-      <c r="W109" t="n">
+      <c r="X109" t="n">
         <v>0.1196666666666667</v>
       </c>
-      <c r="X109" t="n">
+      <c r="Y109" t="n">
         <v>0.05983333333333334</v>
       </c>
-      <c r="Y109" t="n">
+      <c r="Z109" t="n">
         <v>7.795781238820468</v>
       </c>
-      <c r="Z109" t="n">
+      <c r="AA109" t="n">
         <v>0.4207785721774875</v>
       </c>
-      <c r="AA109" t="n">
-        <v>0</v>
-      </c>
       <c r="AB109" t="n">
         <v>0</v>
       </c>
@@ -11161,6 +11487,9 @@
         <v>0</v>
       </c>
       <c r="AD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11220,38 +11549,38 @@
         <v>-3.083333333333333</v>
       </c>
       <c r="Q110" t="n">
+        <v>-0.06642728904847396</v>
+      </c>
+      <c r="R110" t="n">
         <v>10.17142857142859</v>
       </c>
-      <c r="R110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
         <v>14.97827936533493</v>
       </c>
-      <c r="T110" t="n">
+      <c r="U110" t="n">
         <v>1.932176568261367</v>
       </c>
-      <c r="U110" t="n">
+      <c r="V110" t="n">
         <v>0.3043058652189708</v>
       </c>
-      <c r="V110" t="n">
+      <c r="W110" t="n">
         <v>3.4623588525017</v>
       </c>
-      <c r="W110" t="n">
+      <c r="X110" t="n">
         <v>0.1413333333333333</v>
       </c>
-      <c r="X110" t="n">
+      <c r="Y110" t="n">
         <v>0.07066666666666667</v>
       </c>
-      <c r="Y110" t="n">
+      <c r="Z110" t="n">
         <v>10.81459998402953</v>
       </c>
-      <c r="Z110" t="n">
+      <c r="AA110" t="n">
         <v>0.3884586048784459</v>
       </c>
-      <c r="AA110" t="n">
-        <v>0</v>
-      </c>
       <c r="AB110" t="n">
         <v>0</v>
       </c>
@@ -11259,6 +11588,9 @@
         <v>0</v>
       </c>
       <c r="AD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11318,38 +11650,38 @@
         <v>-2.366666666666666</v>
       </c>
       <c r="Q111" t="n">
+        <v>-0.05098743267504488</v>
+      </c>
+      <c r="R111" t="n">
         <v>14.40357142857142</v>
       </c>
-      <c r="R111" t="n">
-        <v>0</v>
-      </c>
       <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
         <v>17.91702948957649</v>
       </c>
-      <c r="T111" t="n">
+      <c r="U111" t="n">
         <v>1.985389121473867</v>
       </c>
-      <c r="U111" t="n">
+      <c r="V111" t="n">
         <v>0.2726830989271983</v>
       </c>
-      <c r="V111" t="n">
+      <c r="W111" t="n">
         <v>3.480866279710169</v>
       </c>
-      <c r="W111" t="n">
+      <c r="X111" t="n">
         <v>0.1556666666666667</v>
       </c>
-      <c r="X111" t="n">
+      <c r="Y111" t="n">
         <v>0.07783333333333334</v>
       </c>
-      <c r="Y111" t="n">
+      <c r="Z111" t="n">
         <v>14.97827936533493</v>
       </c>
-      <c r="Z111" t="n">
+      <c r="AA111" t="n">
         <v>0.3668120739327594</v>
       </c>
-      <c r="AA111" t="n">
-        <v>0</v>
-      </c>
       <c r="AB111" t="n">
         <v>0</v>
       </c>
@@ -11357,6 +11689,9 @@
         <v>0</v>
       </c>
       <c r="AD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11416,38 +11751,38 @@
         <v>-1.75</v>
       </c>
       <c r="Q112" t="n">
+        <v>-0.03770197486535009</v>
+      </c>
+      <c r="R112" t="n">
         <v>17.9821428571429</v>
       </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
       <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
         <v>20.53315308798466</v>
       </c>
-      <c r="T112" t="n">
+      <c r="U112" t="n">
         <v>2.035287782483589</v>
       </c>
-      <c r="U112" t="n">
+      <c r="V112" t="n">
         <v>0.2504966616746517</v>
       </c>
-      <c r="V112" t="n">
+      <c r="W112" t="n">
         <v>3.448605731265319</v>
       </c>
-      <c r="W112" t="n">
+      <c r="X112" t="n">
         <v>0.168</v>
       </c>
-      <c r="X112" t="n">
+      <c r="Y112" t="n">
         <v>0.08400000000000001</v>
       </c>
-      <c r="Y112" t="n">
+      <c r="Z112" t="n">
         <v>17.91702948957649</v>
       </c>
-      <c r="Z112" t="n">
+      <c r="AA112" t="n">
         <v>0.280189813438795</v>
       </c>
-      <c r="AA112" t="n">
-        <v>0</v>
-      </c>
       <c r="AB112" t="n">
         <v>0</v>
       </c>
@@ -11455,6 +11790,9 @@
         <v>0</v>
       </c>
       <c r="AD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11514,38 +11852,38 @@
         <v>-0.9499999999999993</v>
       </c>
       <c r="Q113" t="n">
+        <v>-0.02046678635547575</v>
+      </c>
+      <c r="R113" t="n">
         <v>22.1892857142858</v>
       </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
       <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
         <v>24.01327123307239</v>
       </c>
-      <c r="T113" t="n">
+      <c r="U113" t="n">
         <v>2.10568785288359</v>
       </c>
-      <c r="U113" t="n">
+      <c r="V113" t="n">
         <v>0.2267496097821178</v>
       </c>
-      <c r="V113" t="n">
+      <c r="W113" t="n">
         <v>3.346663273615921</v>
       </c>
-      <c r="W113" t="n">
+      <c r="X113" t="n">
         <v>0.184</v>
       </c>
-      <c r="X113" t="n">
+      <c r="Y113" t="n">
         <v>0.09200000000000001</v>
       </c>
-      <c r="Y113" t="n">
+      <c r="Z113" t="n">
         <v>20.53315308798466</v>
       </c>
-      <c r="Z113" t="n">
+      <c r="AA113" t="n">
         <v>0.1463215789183206</v>
       </c>
-      <c r="AA113" t="n">
-        <v>0</v>
-      </c>
       <c r="AB113" t="n">
         <v>0</v>
       </c>
@@ -11553,6 +11891,9 @@
         <v>0</v>
       </c>
       <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11612,45 +11953,48 @@
         <v>0.1333333333333329</v>
       </c>
       <c r="Q114" t="n">
+        <v>0.002872531418312378</v>
+      </c>
+      <c r="R114" t="n">
         <v>25.66428571428573</v>
       </c>
-      <c r="R114" t="n">
-        <v>0</v>
-      </c>
       <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
         <v>28.24180486627298</v>
       </c>
-      <c r="T114" t="n">
+      <c r="U114" t="n">
         <v>2.198068889704301</v>
       </c>
-      <c r="U114" t="n">
+      <c r="V114" t="n">
         <v>0.007080005996886602</v>
       </c>
-      <c r="V114" t="n">
+      <c r="W114" t="n">
         <v>0.1093276616638276</v>
       </c>
-      <c r="W114" t="n">
+      <c r="X114" t="n">
         <v>0.007053333333333333</v>
       </c>
-      <c r="X114" t="n">
+      <c r="Y114" t="n">
         <v>0.003526666666666667</v>
       </c>
-      <c r="Y114" t="n">
+      <c r="Z114" t="n">
         <v>24.01327123307239</v>
       </c>
-      <c r="Z114" t="n">
+      <c r="AA114" t="n">
         <v>0.04682466286201208</v>
       </c>
-      <c r="AA114" t="n">
+      <c r="AB114" t="n">
         <v>0.001543705722077936</v>
       </c>
-      <c r="AB114" t="n">
+      <c r="AC114" t="n">
         <v>0.04292053230848831</v>
       </c>
-      <c r="AC114" t="n">
+      <c r="AD114" t="n">
         <v>0.001524917290400108</v>
       </c>
-      <c r="AD114" t="n">
+      <c r="AE114" t="n">
         <v>0.04306641655268557</v>
       </c>
     </row>
@@ -11710,45 +12054,48 @@
         <v>1.566666666666666</v>
       </c>
       <c r="Q115" t="n">
+        <v>0.03375224416517055</v>
+      </c>
+      <c r="R115" t="n">
         <v>27.80357142857142</v>
       </c>
-      <c r="R115" t="n">
+      <c r="S115" t="n">
         <v>0.05060060245371522</v>
       </c>
-      <c r="S115" t="n">
+      <c r="T115" t="n">
         <v>28.4719136932899</v>
       </c>
-      <c r="T115" t="n">
+      <c r="U115" t="n">
         <v>2.203329228297969</v>
       </c>
-      <c r="U115" t="n">
+      <c r="V115" t="n">
         <v>0.007575520339906265</v>
       </c>
-      <c r="V115" t="n">
+      <c r="W115" t="n">
         <v>0.1171360667459857</v>
       </c>
-      <c r="W115" t="n">
+      <c r="X115" t="n">
         <v>0.007626666666666667</v>
       </c>
-      <c r="X115" t="n">
+      <c r="Y115" t="n">
         <v>0.003813333333333334</v>
       </c>
-      <c r="Y115" t="n">
+      <c r="Z115" t="n">
         <v>28.24180486627298</v>
       </c>
-      <c r="Z115" t="n">
+      <c r="AA115" t="n">
         <v>0.009793628241382288</v>
       </c>
-      <c r="AA115" t="n">
+      <c r="AB115" t="n">
         <v>0.001301027884616268</v>
       </c>
-      <c r="AB115" t="n">
+      <c r="AC115" t="n">
         <v>0.03670292593065684</v>
       </c>
-      <c r="AC115" t="n">
+      <c r="AD115" t="n">
         <v>0.001330806855107732</v>
       </c>
-      <c r="AD115" t="n">
+      <c r="AE115" t="n">
         <v>0.03789061792106591</v>
       </c>
     </row>
@@ -11808,45 +12155,48 @@
         <v>2.666666666666668</v>
       </c>
       <c r="Q116" t="n">
+        <v>0.05745062836624779</v>
+      </c>
+      <c r="R116" t="n">
         <v>28.21071428571433</v>
       </c>
-      <c r="R116" t="n">
+      <c r="S116" t="n">
         <v>0.1044036282464569</v>
       </c>
-      <c r="S116" t="n">
+      <c r="T116" t="n">
         <v>28.65987999487189</v>
       </c>
-      <c r="T116" t="n">
+      <c r="U116" t="n">
         <v>2.207644899280302</v>
       </c>
-      <c r="U116" t="n">
+      <c r="V116" t="n">
         <v>0.007944459054335712</v>
       </c>
-      <c r="V116" t="n">
+      <c r="W116" t="n">
         <v>0.1229649217459871</v>
       </c>
-      <c r="W116" t="n">
+      <c r="X116" t="n">
         <v>0.008066666666666666</v>
       </c>
-      <c r="X116" t="n">
+      <c r="Y116" t="n">
         <v>0.004033333333333333</v>
       </c>
-      <c r="Y116" t="n">
+      <c r="Z116" t="n">
         <v>28.4719136932899</v>
       </c>
-      <c r="Z116" t="n">
+      <c r="AA116" t="n">
         <v>0.01308713559294417</v>
       </c>
-      <c r="AA116" t="n">
+      <c r="AB116" t="n">
         <v>0.00111834683420231</v>
       </c>
-      <c r="AB116" t="n">
+      <c r="AC116" t="n">
         <v>0.03226430616673658</v>
       </c>
-      <c r="AC116" t="n">
+      <c r="AD116" t="n">
         <v>0.001176819229347382</v>
       </c>
-      <c r="AD116" t="n">
+      <c r="AE116" t="n">
         <v>0.03372749788875357</v>
       </c>
     </row>
@@ -11906,45 +12256,48 @@
         <v>4.133333333333333</v>
       </c>
       <c r="Q117" t="n">
+        <v>0.08904847396768402</v>
+      </c>
+      <c r="R117" t="n">
         <v>28.84999999999995</v>
       </c>
-      <c r="R117" t="n">
+      <c r="S117" t="n">
         <v>0.1491197853115378</v>
       </c>
-      <c r="S117" t="n">
+      <c r="T117" t="n">
         <v>28.92563754904663</v>
       </c>
-      <c r="T117" t="n">
+      <c r="U117" t="n">
         <v>2.213775572077636</v>
       </c>
-      <c r="U117" t="n">
+      <c r="V117" t="n">
         <v>0.008420554940361971</v>
       </c>
-      <c r="V117" t="n">
+      <c r="W117" t="n">
         <v>0.1305037237789266</v>
       </c>
-      <c r="W117" t="n">
+      <c r="X117" t="n">
         <v>0.008653333333333332</v>
       </c>
-      <c r="X117" t="n">
+      <c r="Y117" t="n">
         <v>0.004326666666666666</v>
       </c>
-      <c r="Y117" t="n">
+      <c r="Z117" t="n">
         <v>28.65987999487189</v>
       </c>
-      <c r="Z117" t="n">
+      <c r="AA117" t="n">
         <v>0.01416473965932023</v>
       </c>
-      <c r="AA117" t="n">
+      <c r="AB117" t="n">
         <v>0.0008354784274698437</v>
       </c>
-      <c r="AB117" t="n">
+      <c r="AC117" t="n">
         <v>0.02491516024776152</v>
       </c>
-      <c r="AC117" t="n">
+      <c r="AD117" t="n">
         <v>0.0008945528030801951</v>
       </c>
-      <c r="AD117" t="n">
+      <c r="AE117" t="n">
         <v>0.02587551015038141</v>
       </c>
     </row>
@@ -12004,45 +12357,48 @@
         <v>6.850000000000001</v>
       </c>
       <c r="Q118" t="n">
+        <v>0.147576301615799</v>
+      </c>
+      <c r="R118" t="n">
         <v>29.8214285714287</v>
       </c>
-      <c r="R118" t="n">
+      <c r="S118" t="n">
         <v>0.1918414613393818</v>
       </c>
-      <c r="S118" t="n">
+      <c r="T118" t="n">
         <v>29.46262799242987</v>
       </c>
-      <c r="T118" t="n">
+      <c r="U118" t="n">
         <v>2.226267723458663</v>
       </c>
-      <c r="U118" t="n">
+      <c r="V118" t="n">
         <v>0.009253028608468754</v>
       </c>
-      <c r="V118" t="n">
+      <c r="W118" t="n">
         <v>0.1437185005742433</v>
       </c>
-      <c r="W118" t="n">
+      <c r="X118" t="n">
         <v>0.009740000000000002</v>
       </c>
-      <c r="X118" t="n">
+      <c r="Y118" t="n">
         <v>0.004870000000000001</v>
       </c>
-      <c r="Y118" t="n">
+      <c r="Z118" t="n">
         <v>28.92563754904663</v>
       </c>
-      <c r="Z118" t="n">
+      <c r="AA118" t="n">
         <v>0.01158551351625574</v>
       </c>
-      <c r="AA118" t="n">
+      <c r="AB118" t="n">
         <v>0.0005244793669481728</v>
       </c>
-      <c r="AB118" t="n">
+      <c r="AC118" t="n">
         <v>0.01583178431944987</v>
       </c>
-      <c r="AC118" t="n">
+      <c r="AD118" t="n">
         <v>0.0005561275272637884</v>
       </c>
-      <c r="AD118" t="n">
+      <c r="AE118" t="n">
         <v>0.0163849784521229</v>
       </c>
     </row>
@@ -12102,45 +12458,48 @@
         <v>12.4</v>
       </c>
       <c r="Q119" t="n">
+        <v>0.2671454219030521</v>
+      </c>
+      <c r="R119" t="n">
         <v>30.18571428571434</v>
       </c>
-      <c r="R119" t="n">
+      <c r="S119" t="n">
         <v>0.2448076315621145</v>
       </c>
-      <c r="S119" t="n">
+      <c r="T119" t="n">
         <v>30.7324548714269</v>
       </c>
-      <c r="T119" t="n">
+      <c r="U119" t="n">
         <v>2.256376503567413</v>
       </c>
-      <c r="U119" t="n">
+      <c r="V119" t="n">
         <v>0.0107472221904619</v>
       </c>
-      <c r="V119" t="n">
+      <c r="W119" t="n">
         <v>0.1673901041055427</v>
       </c>
-      <c r="W119" t="n">
+      <c r="X119" t="n">
         <v>0.01196</v>
       </c>
-      <c r="X119" t="n">
+      <c r="Y119" t="n">
         <v>0.005979999999999999</v>
       </c>
-      <c r="Y119" t="n">
+      <c r="Z119" t="n">
         <v>29.46262799242987</v>
       </c>
-      <c r="Z119" t="n">
+      <c r="AA119" t="n">
         <v>0.01018412764647287</v>
       </c>
-      <c r="AA119" t="n">
+      <c r="AB119" t="n">
         <v>0.0001173795623522832</v>
       </c>
-      <c r="AB119" t="n">
+      <c r="AC119" t="n">
         <v>0.003813578138281135</v>
       </c>
-      <c r="AC119" t="n">
+      <c r="AD119" t="n">
         <v>0.0001606398135696006</v>
       </c>
-      <c r="AD119" t="n">
+      <c r="AE119" t="n">
         <v>0.004936855821082179</v>
       </c>
     </row>
@@ -12200,45 +12559,48 @@
         <v>14.05</v>
       </c>
       <c r="Q120" t="n">
+        <v>0.3026929982046678</v>
+      </c>
+      <c r="R120" t="n">
         <v>32.48928571428564</v>
       </c>
-      <c r="R120" t="n">
+      <c r="S120" t="n">
         <v>0.2862295508009267</v>
       </c>
-      <c r="S120" t="n">
+      <c r="T120" t="n">
         <v>31.15248097068912</v>
       </c>
-      <c r="T120" t="n">
+      <c r="U120" t="n">
         <v>2.266515763706663</v>
       </c>
-      <c r="U120" t="n">
+      <c r="V120" t="n">
         <v>0.01113734553511684</v>
       </c>
-      <c r="V120" t="n">
+      <c r="W120" t="n">
         <v>0.1734983778862526</v>
       </c>
-      <c r="W120" t="n">
+      <c r="X120" t="n">
         <v>0.01262</v>
       </c>
-      <c r="X120" t="n">
+      <c r="Y120" t="n">
         <v>0.00631</v>
       </c>
-      <c r="Y120" t="n">
+      <c r="Z120" t="n">
         <v>30.7324548714269</v>
       </c>
-      <c r="Z120" t="n">
+      <c r="AA120" t="n">
         <v>0.0085377509283628</v>
       </c>
-      <c r="AA120" t="n">
+      <c r="AB120" t="n">
         <v>8.001736341849413e-05</v>
       </c>
-      <c r="AB120" t="n">
+      <c r="AC120" t="n">
         <v>0.002635143243149769</v>
       </c>
-      <c r="AC120" t="n">
+      <c r="AD120" t="n">
         <v>0.0001212306820646025</v>
       </c>
-      <c r="AD120" t="n">
+      <c r="AE120" t="n">
         <v>0.003776636516081191</v>
       </c>
     </row>
@@ -12298,45 +12660,48 @@
         <v>15.55</v>
       </c>
       <c r="Q121" t="n">
+        <v>0.3350089766606822</v>
+      </c>
+      <c r="R121" t="n">
         <v>32.9321428571429</v>
       </c>
-      <c r="R121" t="n">
+      <c r="S121" t="n">
         <v>0.2889524121591054</v>
       </c>
-      <c r="S121" t="n">
+      <c r="T121" t="n">
         <v>31.55039960381982</v>
       </c>
-      <c r="T121" t="n">
+      <c r="U121" t="n">
         <v>2.276205773396663</v>
       </c>
-      <c r="U121" t="n">
+      <c r="V121" t="n">
         <v>0.01147067535725597</v>
       </c>
-      <c r="V121" t="n">
+      <c r="W121" t="n">
         <v>0.1786624859513175</v>
       </c>
-      <c r="W121" t="n">
+      <c r="X121" t="n">
         <v>0.01322</v>
       </c>
-      <c r="X121" t="n">
+      <c r="Y121" t="n">
         <v>0.00661</v>
       </c>
-      <c r="Y121" t="n">
+      <c r="Z121" t="n">
         <v>31.15248097068912</v>
       </c>
-      <c r="Z121" t="n">
+      <c r="AA121" t="n">
         <v>0.01094124388489767</v>
       </c>
-      <c r="AA121" t="n">
+      <c r="AB121" t="n">
         <v>0.0001048376628482425</v>
       </c>
-      <c r="AB121" t="n">
+      <c r="AC121" t="n">
         <v>0.003468413842637606</v>
       </c>
-      <c r="AC121" t="n">
+      <c r="AD121" t="n">
         <v>0.0001197389718612452</v>
       </c>
-      <c r="AD121" t="n">
+      <c r="AE121" t="n">
         <v>0.003777812410372822</v>
       </c>
     </row>
@@ -12396,45 +12761,48 @@
         <v>17.01666666666667</v>
       </c>
       <c r="Q122" t="n">
+        <v>0.3666068222621185</v>
+      </c>
+      <c r="R122" t="n">
         <v>33.08366238246173</v>
       </c>
-      <c r="R122" t="n">
+      <c r="S122" t="n">
         <v>0.2916972101212668</v>
       </c>
-      <c r="S122" t="n">
+      <c r="T122" t="n">
         <v>31.95385449141603</v>
       </c>
-      <c r="T122" t="n">
+      <c r="U122" t="n">
         <v>2.286115561084218</v>
       </c>
-      <c r="U122" t="n">
+      <c r="V122" t="n">
         <v>0.01177717880123003</v>
       </c>
-      <c r="V122" t="n">
+      <c r="W122" t="n">
         <v>0.1833455418032794</v>
       </c>
-      <c r="W122" t="n">
+      <c r="X122" t="n">
         <v>0.01380666666666667</v>
       </c>
-      <c r="X122" t="n">
+      <c r="Y122" t="n">
         <v>0.006903333333333334</v>
       </c>
-      <c r="Y122" t="n">
+      <c r="Z122" t="n">
         <v>31.55039960381982</v>
       </c>
-      <c r="Z122" t="n">
+      <c r="AA122" t="n">
         <v>0.01496737650102324</v>
       </c>
-      <c r="AA122" t="n">
+      <c r="AB122" t="n">
         <v>0.0001330031843039391</v>
       </c>
-      <c r="AB122" t="n">
+      <c r="AC122" t="n">
         <v>0.004427144891717553</v>
       </c>
-      <c r="AC122" t="n">
+      <c r="AD122" t="n">
         <v>0.0001359515592164647</v>
       </c>
-      <c r="AD122" t="n">
+      <c r="AE122" t="n">
         <v>0.004344176341084042</v>
       </c>
     </row>
@@ -12494,45 +12862,48 @@
         <v>20.05</v>
       </c>
       <c r="Q123" t="n">
+        <v>0.4319569120287253</v>
+      </c>
+      <c r="R123" t="n">
         <v>33.286006759061</v>
       </c>
-      <c r="R123" t="n">
+      <c r="S123" t="n">
         <v>0.2947411967231239</v>
       </c>
-      <c r="S123" t="n">
+      <c r="T123" t="n">
         <v>32.83159453257377</v>
       </c>
-      <c r="T123" t="n">
+      <c r="U123" t="n">
         <v>2.307975805166663</v>
       </c>
-      <c r="U123" t="n">
+      <c r="V123" t="n">
         <v>0.01235152301479269</v>
       </c>
-      <c r="V123" t="n">
+      <c r="W123" t="n">
         <v>0.1918565388801183</v>
       </c>
-      <c r="W123" t="n">
+      <c r="X123" t="n">
         <v>0.01502</v>
       </c>
-      <c r="X123" t="n">
+      <c r="Y123" t="n">
         <v>0.007509999999999999</v>
       </c>
-      <c r="Y123" t="n">
+      <c r="Z123" t="n">
         <v>31.95385449141603</v>
       </c>
-      <c r="Z123" t="n">
+      <c r="AA123" t="n">
         <v>0.01393403278476044</v>
       </c>
-      <c r="AA123" t="n">
+      <c r="AB123" t="n">
         <v>0.0002001166067567213</v>
       </c>
-      <c r="AB123" t="n">
+      <c r="AC123" t="n">
         <v>0.006989072490978496</v>
       </c>
-      <c r="AC123" t="n">
+      <c r="AD123" t="n">
         <v>0.0002310196494435036</v>
       </c>
-      <c r="AD123" t="n">
+      <c r="AE123" t="n">
         <v>0.00758474345958644</v>
       </c>
     </row>
@@ -12592,45 +12963,48 @@
         <v>23.05</v>
       </c>
       <c r="Q124" t="n">
+        <v>0.4965888689407542</v>
+      </c>
+      <c r="R124" t="n">
         <v>34.92500000000002</v>
       </c>
-      <c r="R124" t="n">
+      <c r="S124" t="n">
         <v>0.3061500936386944</v>
       </c>
-      <c r="S124" t="n">
+      <c r="T124" t="n">
         <v>33.75408934834246</v>
       </c>
-      <c r="T124" t="n">
+      <c r="U124" t="n">
         <v>2.331405828596663</v>
       </c>
-      <c r="U124" t="n">
+      <c r="V124" t="n">
         <v>0.01284341417557715</v>
       </c>
-      <c r="V124" t="n">
+      <c r="W124" t="n">
         <v>0.1986846191052666</v>
       </c>
-      <c r="W124" t="n">
+      <c r="X124" t="n">
         <v>0.01622</v>
       </c>
-      <c r="X124" t="n">
+      <c r="Y124" t="n">
         <v>0.008110000000000001</v>
       </c>
-      <c r="Y124" t="n">
+      <c r="Z124" t="n">
         <v>32.83159453257377</v>
       </c>
-      <c r="Z124" t="n">
+      <c r="AA124" t="n">
         <v>0.01157922320647989</v>
       </c>
-      <c r="AA124" t="n">
+      <c r="AB124" t="n">
         <v>0.0003444698247772432</v>
       </c>
-      <c r="AB124" t="n">
+      <c r="AC124" t="n">
         <v>0.01216839656025612</v>
       </c>
-      <c r="AC124" t="n">
+      <c r="AD124" t="n">
         <v>0.0004041724259929835</v>
       </c>
-      <c r="AD124" t="n">
+      <c r="AE124" t="n">
         <v>0.0136424721791035</v>
       </c>
     </row>
@@ -12690,45 +13064,48 @@
         <v>25.71666666666666</v>
       </c>
       <c r="Q125" t="n">
+        <v>0.5540394973070017</v>
+      </c>
+      <c r="R125" t="n">
         <v>35.32500000000002</v>
       </c>
-      <c r="R125" t="n">
+      <c r="S125" t="n">
         <v>0.3308651428571041</v>
       </c>
-      <c r="S125" t="n">
+      <c r="T125" t="n">
         <v>34.61647934279947</v>
       </c>
-      <c r="T125" t="n">
+      <c r="U125" t="n">
         <v>2.353743628712218</v>
       </c>
-      <c r="U125" t="n">
+      <c r="V125" t="n">
         <v>0.01322035169194992</v>
       </c>
-      <c r="V125" t="n">
+      <c r="W125" t="n">
         <v>0.2034072317266347</v>
       </c>
-      <c r="W125" t="n">
+      <c r="X125" t="n">
         <v>0.01728666666666667</v>
       </c>
-      <c r="X125" t="n">
+      <c r="Y125" t="n">
         <v>0.008643333333333333</v>
       </c>
-      <c r="Y125" t="n">
+      <c r="Z125" t="n">
         <v>33.75408934834246</v>
       </c>
-      <c r="Z125" t="n">
+      <c r="AA125" t="n">
         <v>0.009267599997966548</v>
       </c>
-      <c r="AA125" t="n">
+      <c r="AB125" t="n">
         <v>0.0005343022972248991</v>
       </c>
-      <c r="AB125" t="n">
+      <c r="AC125" t="n">
         <v>0.01961652719811411</v>
       </c>
-      <c r="AC125" t="n">
+      <c r="AD125" t="n">
         <v>0.000618736018383067</v>
       </c>
-      <c r="AD125" t="n">
+      <c r="AE125" t="n">
         <v>0.02141846259900344</v>
       </c>
     </row>
@@ -12788,45 +13165,48 @@
         <v>28.41666666666666</v>
       </c>
       <c r="Q126" t="n">
+        <v>0.6122082585278277</v>
+      </c>
+      <c r="R126" t="n">
         <v>36.71428571428564</v>
       </c>
-      <c r="R126" t="n">
+      <c r="S126" t="n">
         <v>0.3724108962071924</v>
       </c>
-      <c r="S126" t="n">
+      <c r="T126" t="n">
         <v>35.52745852239852</v>
       </c>
-      <c r="T126" t="n">
+      <c r="U126" t="n">
         <v>2.377809652778218</v>
       </c>
-      <c r="U126" t="n">
+      <c r="V126" t="n">
         <v>0.01354761888358153</v>
       </c>
-      <c r="V126" t="n">
+      <c r="W126" t="n">
         <v>0.2068914320190001</v>
       </c>
-      <c r="W126" t="n">
+      <c r="X126" t="n">
         <v>0.01836666666666667</v>
       </c>
-      <c r="X126" t="n">
+      <c r="Y126" t="n">
         <v>0.009183333333333333</v>
       </c>
-      <c r="Y126" t="n">
+      <c r="Z126" t="n">
         <v>34.61647934279947</v>
       </c>
-      <c r="Z126" t="n">
+      <c r="AA126" t="n">
         <v>0.006196243412663805</v>
       </c>
-      <c r="AA126" t="n">
+      <c r="AB126" t="n">
         <v>0.0008109233377192746</v>
       </c>
-      <c r="AB126" t="n">
+      <c r="AC126" t="n">
         <v>0.02963924799363945</v>
       </c>
-      <c r="AC126" t="n">
+      <c r="AD126" t="n">
         <v>0.0008844102245227135</v>
       </c>
-      <c r="AD126" t="n">
+      <c r="AE126" t="n">
         <v>0.03142084756851587</v>
       </c>
     </row>
@@ -12886,45 +13266,48 @@
         <v>36.41666666666666</v>
       </c>
       <c r="Q127" t="n">
+        <v>0.7845601436265709</v>
+      </c>
+      <c r="R127" t="n">
         <v>36.54999999999995</v>
       </c>
-      <c r="R127" t="n">
+      <c r="S127" t="n">
         <v>0.4370511859323505</v>
       </c>
-      <c r="S127" t="n">
+      <c r="T127" t="n">
         <v>38.42283179752014</v>
       </c>
-      <c r="T127" t="n">
+      <c r="U127" t="n">
         <v>2.457676399311551</v>
       </c>
-      <c r="U127" t="n">
+      <c r="V127" t="n">
         <v>0.01423124238248902</v>
       </c>
-      <c r="V127" t="n">
+      <c r="W127" t="n">
         <v>0.2096355868065772</v>
       </c>
-      <c r="W127" t="n">
+      <c r="X127" t="n">
         <v>0.02156666666666666</v>
       </c>
-      <c r="X127" t="n">
+      <c r="Y127" t="n">
         <v>0.01078333333333333</v>
       </c>
-      <c r="Y127" t="n">
+      <c r="Z127" t="n">
         <v>35.52745852239852</v>
       </c>
-      <c r="Z127" t="n">
+      <c r="AA127" t="n">
         <v>0.01541414394739185</v>
       </c>
-      <c r="AA127" t="n">
+      <c r="AB127" t="n">
         <v>0.001781396691915808</v>
       </c>
-      <c r="AB127" t="n">
+      <c r="AC127" t="n">
         <v>0.06671966824328958</v>
       </c>
-      <c r="AC127" t="n">
+      <c r="AD127" t="n">
         <v>0.001733285414237923</v>
       </c>
-      <c r="AD127" t="n">
+      <c r="AE127" t="n">
         <v>0.06659773392835873</v>
       </c>
     </row>
@@ -12984,38 +13367,38 @@
         <v>-10</v>
       </c>
       <c r="Q128" t="n">
+        <v>-0.272108843537415</v>
+      </c>
+      <c r="R128" t="n">
         <v>0.2740000000001075</v>
       </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
       <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
         <v>0.2740000000001075</v>
       </c>
-      <c r="T128" t="n">
+      <c r="U128" t="n">
         <v>1.7518</v>
       </c>
-      <c r="U128" t="n">
+      <c r="V128" t="n">
         <v>0.8697868789829178</v>
       </c>
-      <c r="V128" t="n">
+      <c r="W128" t="n">
         <v>0.238321604841413</v>
       </c>
-      <c r="W128" t="n">
-        <v>0</v>
-      </c>
       <c r="X128" t="n">
         <v>0</v>
       </c>
       <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
         <v>0.2740000000001075</v>
       </c>
-      <c r="Z128" t="n">
+      <c r="AA128" t="n">
         <v>0.4637116778292156</v>
       </c>
-      <c r="AA128" t="n">
-        <v>0</v>
-      </c>
       <c r="AB128" t="n">
         <v>0</v>
       </c>
@@ -13023,6 +13406,9 @@
         <v>0</v>
       </c>
       <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13082,38 +13468,38 @@
         <v>-8.866666666666667</v>
       </c>
       <c r="Q129" t="n">
+        <v>-0.2412698412698413</v>
+      </c>
+      <c r="R129" t="n">
         <v>0.2740000000001075</v>
       </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
       <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
         <v>0.734276524839871</v>
       </c>
-      <c r="T129" t="n">
+      <c r="U129" t="n">
         <v>1.7518</v>
       </c>
-      <c r="U129" t="n">
+      <c r="V129" t="n">
         <v>0.8697849399988962</v>
       </c>
-      <c r="V129" t="n">
+      <c r="W129" t="n">
         <v>0.6386626631004453</v>
       </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
       <c r="X129" t="n">
         <v>0</v>
       </c>
       <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
         <v>0.2740000000001075</v>
       </c>
-      <c r="Z129" t="n">
+      <c r="AA129" t="n">
         <v>0.7453679311071638</v>
       </c>
-      <c r="AA129" t="n">
-        <v>0</v>
-      </c>
       <c r="AB129" t="n">
         <v>0</v>
       </c>
@@ -13121,6 +13507,9 @@
         <v>0</v>
       </c>
       <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13180,38 +13569,38 @@
         <v>-8.050000000000001</v>
       </c>
       <c r="Q130" t="n">
+        <v>-0.2190476190476191</v>
+      </c>
+      <c r="R130" t="n">
         <v>0.6966666666666418</v>
       </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
       <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
         <v>1.493994212599856</v>
       </c>
-      <c r="T130" t="n">
+      <c r="U130" t="n">
         <v>1.7518</v>
       </c>
-      <c r="U130" t="n">
+      <c r="V130" t="n">
         <v>0.8697800815789629</v>
       </c>
-      <c r="V130" t="n">
+      <c r="W130" t="n">
         <v>1.299446408113601</v>
       </c>
-      <c r="W130" t="n">
-        <v>0</v>
-      </c>
       <c r="X130" t="n">
         <v>0</v>
       </c>
       <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
         <v>0.734276524839871</v>
       </c>
-      <c r="Z130" t="n">
+      <c r="AA130" t="n">
         <v>0.8971601367795489</v>
       </c>
-      <c r="AA130" t="n">
-        <v>0</v>
-      </c>
       <c r="AB130" t="n">
         <v>0</v>
       </c>
@@ -13219,6 +13608,9 @@
         <v>0</v>
       </c>
       <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13278,38 +13670,38 @@
         <v>-7.05</v>
       </c>
       <c r="Q131" t="n">
+        <v>-0.1918367346938775</v>
+      </c>
+      <c r="R131" t="n">
         <v>1.346000000000203</v>
       </c>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
       <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
         <v>3.5651687097501</v>
       </c>
-      <c r="T131" t="n">
+      <c r="U131" t="n">
         <v>1.7518</v>
       </c>
-      <c r="U131" t="n">
+      <c r="V131" t="n">
         <v>0.8696347056376073</v>
       </c>
-      <c r="V131" t="n">
+      <c r="W131" t="n">
         <v>3.100394441451936</v>
       </c>
-      <c r="W131" t="n">
-        <v>0</v>
-      </c>
       <c r="X131" t="n">
         <v>0</v>
       </c>
       <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="n">
         <v>1.493994212599856</v>
       </c>
-      <c r="Z131" t="n">
+      <c r="AA131" t="n">
         <v>0.6919878856836935</v>
       </c>
-      <c r="AA131" t="n">
-        <v>0</v>
-      </c>
       <c r="AB131" t="n">
         <v>0</v>
       </c>
@@ -13317,6 +13709,9 @@
         <v>0</v>
       </c>
       <c r="AD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13376,38 +13771,38 @@
         <v>-5.833333333333334</v>
       </c>
       <c r="Q132" t="n">
+        <v>-0.1587301587301587</v>
+      </c>
+      <c r="R132" t="n">
         <v>3.026136363636255</v>
       </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
       <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
         <v>5.404249754812128</v>
       </c>
-      <c r="T132" t="n">
+      <c r="U132" t="n">
         <v>1.774655578403517</v>
       </c>
-      <c r="U132" t="n">
+      <c r="V132" t="n">
         <v>0.5609388874953546</v>
       </c>
-      <c r="V132" t="n">
+      <c r="W132" t="n">
         <v>2.768548241906347</v>
       </c>
-      <c r="W132" t="n">
+      <c r="X132" t="n">
         <v>0.08633333333333333</v>
       </c>
-      <c r="X132" t="n">
+      <c r="Y132" t="n">
         <v>0.04316666666666667</v>
       </c>
-      <c r="Y132" t="n">
+      <c r="Z132" t="n">
         <v>3.5651687097501</v>
       </c>
-      <c r="Z132" t="n">
+      <c r="AA132" t="n">
         <v>0.5026713404005696</v>
       </c>
-      <c r="AA132" t="n">
-        <v>0</v>
-      </c>
       <c r="AB132" t="n">
         <v>0</v>
       </c>
@@ -13415,6 +13810,9 @@
         <v>0</v>
       </c>
       <c r="AD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13474,38 +13872,38 @@
         <v>-4.866666666666665</v>
       </c>
       <c r="Q133" t="n">
+        <v>-0.1324263038548752</v>
+      </c>
+      <c r="R133" t="n">
         <v>5.885714285714225</v>
       </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
       <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
         <v>8.441995341407473</v>
       </c>
-      <c r="T133" t="n">
+      <c r="U133" t="n">
         <v>1.821055624803517</v>
       </c>
-      <c r="U133" t="n">
+      <c r="V133" t="n">
         <v>0.4282982830769928</v>
       </c>
-      <c r="V133" t="n">
+      <c r="W133" t="n">
         <v>3.125845729286283</v>
       </c>
-      <c r="W133" t="n">
+      <c r="X133" t="n">
         <v>0.1056666666666667</v>
       </c>
-      <c r="X133" t="n">
+      <c r="Y133" t="n">
         <v>0.05283333333333335</v>
       </c>
-      <c r="Y133" t="n">
+      <c r="Z133" t="n">
         <v>5.404249754812128</v>
       </c>
-      <c r="Z133" t="n">
+      <c r="AA133" t="n">
         <v>0.4114966666264407</v>
       </c>
-      <c r="AA133" t="n">
-        <v>0</v>
-      </c>
       <c r="AB133" t="n">
         <v>0</v>
       </c>
@@ -13513,6 +13911,9 @@
         <v>0</v>
       </c>
       <c r="AD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13572,38 +13973,38 @@
         <v>-3.866666666666667</v>
       </c>
       <c r="Q134" t="n">
+        <v>-0.1052154195011338</v>
+      </c>
+      <c r="R134" t="n">
         <v>8.642857142857142</v>
       </c>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
         <v>12.01818119841178</v>
       </c>
-      <c r="T134" t="n">
+      <c r="U134" t="n">
         <v>1.878889015970184</v>
       </c>
-      <c r="U134" t="n">
+      <c r="V134" t="n">
         <v>0.3467808654092747</v>
       </c>
-      <c r="V134" t="n">
+      <c r="W134" t="n">
         <v>3.363857298153381</v>
       </c>
-      <c r="W134" t="n">
+      <c r="X134" t="n">
         <v>0.1256666666666666</v>
       </c>
-      <c r="X134" t="n">
+      <c r="Y134" t="n">
         <v>0.06283333333333332</v>
       </c>
-      <c r="Y134" t="n">
+      <c r="Z134" t="n">
         <v>8.441995341407473</v>
       </c>
-      <c r="Z134" t="n">
+      <c r="AA134" t="n">
         <v>0.3503266780181019</v>
       </c>
-      <c r="AA134" t="n">
-        <v>0</v>
-      </c>
       <c r="AB134" t="n">
         <v>0</v>
       </c>
@@ -13611,6 +14012,9 @@
         <v>0</v>
       </c>
       <c r="AD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13670,38 +14074,38 @@
         <v>-3</v>
       </c>
       <c r="Q135" t="n">
+        <v>-0.08163265306122448</v>
+      </c>
+      <c r="R135" t="n">
         <v>12.06428571428577</v>
       </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
       <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
         <v>15.40208363976879</v>
       </c>
-      <c r="T135" t="n">
+      <c r="U135" t="n">
         <v>1.937100185292406</v>
       </c>
-      <c r="U135" t="n">
+      <c r="V135" t="n">
         <v>0.2986612582351104</v>
       </c>
-      <c r="V135" t="n">
+      <c r="W135" t="n">
         <v>3.462997910048928</v>
       </c>
-      <c r="W135" t="n">
+      <c r="X135" t="n">
         <v>0.143</v>
       </c>
-      <c r="X135" t="n">
+      <c r="Y135" t="n">
         <v>0.07150000000000001</v>
       </c>
-      <c r="Y135" t="n">
+      <c r="Z135" t="n">
         <v>12.01818119841178</v>
       </c>
-      <c r="Z135" t="n">
+      <c r="AA135" t="n">
         <v>0.2789527328089635</v>
       </c>
-      <c r="AA135" t="n">
-        <v>0</v>
-      </c>
       <c r="AB135" t="n">
         <v>0</v>
       </c>
@@ -13709,6 +14113,9 @@
         <v>0</v>
       </c>
       <c r="AD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13768,38 +14175,38 @@
         <v>-1.966666666666665</v>
       </c>
       <c r="Q136" t="n">
+        <v>-0.05351473922902489</v>
+      </c>
+      <c r="R136" t="n">
         <v>15.77142857142857</v>
       </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
       <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
         <v>19.69349055319588</v>
       </c>
-      <c r="T136" t="n">
+      <c r="U136" t="n">
         <v>2.016322486736851</v>
       </c>
-      <c r="U136" t="n">
+      <c r="V136" t="n">
         <v>0.2568335199339056</v>
       </c>
-      <c r="V136" t="n">
+      <c r="W136" t="n">
         <v>3.459410578624159</v>
       </c>
-      <c r="W136" t="n">
+      <c r="X136" t="n">
         <v>0.1636666666666667</v>
       </c>
-      <c r="X136" t="n">
+      <c r="Y136" t="n">
         <v>0.08183333333333336</v>
       </c>
-      <c r="Y136" t="n">
+      <c r="Z136" t="n">
         <v>15.40208363976879</v>
       </c>
-      <c r="Z136" t="n">
+      <c r="AA136" t="n">
         <v>0.2084246345121031</v>
       </c>
-      <c r="AA136" t="n">
-        <v>0</v>
-      </c>
       <c r="AB136" t="n">
         <v>0</v>
       </c>
@@ -13807,6 +14214,9 @@
         <v>0</v>
       </c>
       <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13866,38 +14276,38 @@
         <v>-1.350000000000001</v>
       </c>
       <c r="Q137" t="n">
+        <v>-0.03673469387755106</v>
+      </c>
+      <c r="R137" t="n">
         <v>19.10357142857136</v>
       </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
       <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
         <v>22.34964322948165</v>
       </c>
-      <c r="T137" t="n">
+      <c r="U137" t="n">
         <v>2.068687816879906</v>
       </c>
-      <c r="U137" t="n">
+      <c r="V137" t="n">
         <v>0.2372035556461162</v>
       </c>
-      <c r="V137" t="n">
+      <c r="W137" t="n">
         <v>3.399949972617945</v>
       </c>
-      <c r="W137" t="n">
+      <c r="X137" t="n">
         <v>0.176</v>
       </c>
-      <c r="X137" t="n">
+      <c r="Y137" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="Y137" t="n">
+      <c r="Z137" t="n">
         <v>19.69349055319588</v>
       </c>
-      <c r="Z137" t="n">
+      <c r="AA137" t="n">
         <v>0.1351840441944742</v>
       </c>
-      <c r="AA137" t="n">
-        <v>0</v>
-      </c>
       <c r="AB137" t="n">
         <v>0</v>
       </c>
@@ -13905,6 +14315,9 @@
         <v>0</v>
       </c>
       <c r="AD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13964,38 +14377,38 @@
         <v>-0.6500000000000004</v>
       </c>
       <c r="Q138" t="n">
+        <v>-0.01768707482993198</v>
+      </c>
+      <c r="R138" t="n">
         <v>21.08928571428573</v>
       </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
       <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
         <v>25.42114791934122</v>
       </c>
-      <c r="T138" t="n">
+      <c r="U138" t="n">
         <v>2.132737880929906</v>
       </c>
-      <c r="U138" t="n">
+      <c r="V138" t="n">
         <v>0.2183710078857313</v>
       </c>
-      <c r="V138" t="n">
+      <c r="W138" t="n">
         <v>3.286538586079387</v>
       </c>
-      <c r="W138" t="n">
+      <c r="X138" t="n">
         <v>0.19</v>
       </c>
-      <c r="X138" t="n">
+      <c r="Y138" t="n">
         <v>0.095</v>
       </c>
-      <c r="Y138" t="n">
+      <c r="Z138" t="n">
         <v>22.34964322948165</v>
       </c>
-      <c r="Z138" t="n">
+      <c r="AA138" t="n">
         <v>0.06997246239386802</v>
       </c>
-      <c r="AA138" t="n">
-        <v>0</v>
-      </c>
       <c r="AB138" t="n">
         <v>0</v>
       </c>
@@ -14003,6 +14416,9 @@
         <v>0</v>
       </c>
       <c r="AD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14062,38 +14478,38 @@
         <v>0.08333333333333215</v>
       </c>
       <c r="Q139" t="n">
+        <v>0.002267573696145093</v>
+      </c>
+      <c r="R139" t="n">
         <v>21.79285714285717</v>
       </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
       <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
         <v>28.31815807004039</v>
       </c>
-      <c r="T139" t="n">
+      <c r="U139" t="n">
         <v>2.196892806206484</v>
       </c>
-      <c r="U139" t="n">
+      <c r="V139" t="n">
         <v>0.01041196717294989</v>
       </c>
-      <c r="V139" t="n">
+      <c r="W139" t="n">
         <v>0.2041873938903916</v>
       </c>
-      <c r="W139" t="n">
+      <c r="X139" t="n">
         <v>0.007033333333333333</v>
       </c>
-      <c r="X139" t="n">
+      <c r="Y139" t="n">
         <v>0.003516666666666667</v>
       </c>
-      <c r="Y139" t="n">
+      <c r="Z139" t="n">
         <v>25.42114791934122</v>
       </c>
-      <c r="Z139" t="n">
+      <c r="AA139" t="n">
         <v>0.04417757490269928</v>
       </c>
-      <c r="AA139" t="n">
-        <v>0</v>
-      </c>
       <c r="AB139" t="n">
         <v>0</v>
       </c>
@@ -14101,6 +14517,9 @@
         <v>0</v>
       </c>
       <c r="AD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14160,38 +14579,38 @@
         <v>1.200000000000001</v>
       </c>
       <c r="Q140" t="n">
+        <v>0.03265306122448983</v>
+      </c>
+      <c r="R140" t="n">
         <v>22.74159954433088</v>
       </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
       <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
         <v>28.49544506515976</v>
       </c>
-      <c r="T140" t="n">
+      <c r="U140" t="n">
         <v>2.200944449147011</v>
       </c>
-      <c r="U140" t="n">
+      <c r="V140" t="n">
         <v>0.01098357032200971</v>
       </c>
-      <c r="V140" t="n">
+      <c r="W140" t="n">
         <v>0.2161387857045839</v>
       </c>
-      <c r="W140" t="n">
+      <c r="X140" t="n">
         <v>0.007480000000000001</v>
       </c>
-      <c r="X140" t="n">
+      <c r="Y140" t="n">
         <v>0.00374</v>
       </c>
-      <c r="Y140" t="n">
+      <c r="Z140" t="n">
         <v>28.31815807004039</v>
       </c>
-      <c r="Z140" t="n">
+      <c r="AA140" t="n">
         <v>0.02615548495855645</v>
       </c>
-      <c r="AA140" t="n">
-        <v>0</v>
-      </c>
       <c r="AB140" t="n">
         <v>0</v>
       </c>
@@ -14199,6 +14618,9 @@
         <v>0</v>
       </c>
       <c r="AD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14258,38 +14680,38 @@
         <v>2.666666666666666</v>
       </c>
       <c r="Q141" t="n">
+        <v>0.07256235827664398</v>
+      </c>
+      <c r="R141" t="n">
         <v>22.97108767528296</v>
       </c>
-      <c r="R141" t="n">
-        <v>0</v>
-      </c>
       <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
         <v>28.74377626618266</v>
       </c>
-      <c r="T141" t="n">
+      <c r="U141" t="n">
         <v>2.2066448992919</v>
       </c>
-      <c r="U141" t="n">
+      <c r="V141" t="n">
         <v>0.01171780391374263</v>
       </c>
-      <c r="V141" t="n">
+      <c r="W141" t="n">
         <v>0.2317374616169707</v>
       </c>
-      <c r="W141" t="n">
+      <c r="X141" t="n">
         <v>0.008066666666666666</v>
       </c>
-      <c r="X141" t="n">
+      <c r="Y141" t="n">
         <v>0.004033333333333333</v>
       </c>
-      <c r="Y141" t="n">
+      <c r="Z141" t="n">
         <v>28.49544506515976</v>
       </c>
-      <c r="Z141" t="n">
+      <c r="AA141" t="n">
         <v>0.02647932083128075</v>
       </c>
-      <c r="AA141" t="n">
-        <v>0</v>
-      </c>
       <c r="AB141" t="n">
         <v>0</v>
       </c>
@@ -14297,6 +14719,9 @@
         <v>0</v>
       </c>
       <c r="AD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14356,38 +14781,38 @@
         <v>3.849999999999998</v>
       </c>
       <c r="Q142" t="n">
+        <v>0.1047619047619047</v>
+      </c>
+      <c r="R142" t="n">
         <v>24.12500000000008</v>
       </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
       <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
         <v>28.95676810363952</v>
       </c>
-      <c r="T142" t="n">
+      <c r="U142" t="n">
         <v>2.211557709760262</v>
       </c>
-      <c r="U142" t="n">
+      <c r="V142" t="n">
         <v>0.01228108243496568</v>
       </c>
-      <c r="V142" t="n">
+      <c r="W142" t="n">
         <v>0.2438029808221922</v>
       </c>
-      <c r="W142" t="n">
+      <c r="X142" t="n">
         <v>0.008539999999999999</v>
       </c>
-      <c r="X142" t="n">
+      <c r="Y142" t="n">
         <v>0.004269999999999999</v>
       </c>
-      <c r="Y142" t="n">
+      <c r="Z142" t="n">
         <v>28.74377626618266</v>
       </c>
-      <c r="Z142" t="n">
+      <c r="AA142" t="n">
         <v>0.02163341820285943</v>
       </c>
-      <c r="AA142" t="n">
-        <v>0</v>
-      </c>
       <c r="AB142" t="n">
         <v>0</v>
       </c>
@@ -14395,6 +14820,9 @@
         <v>0</v>
       </c>
       <c r="AD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14454,38 +14882,38 @@
         <v>5.31666666666667</v>
       </c>
       <c r="Q143" t="n">
+        <v>0.144671201814059</v>
+      </c>
+      <c r="R143" t="n">
         <v>24.57500000000017</v>
       </c>
-      <c r="R143" t="n">
-        <v>0</v>
-      </c>
       <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
         <v>29.2361661686984</v>
       </c>
-      <c r="T143" t="n">
+      <c r="U143" t="n">
         <v>2.218035494015818</v>
       </c>
-      <c r="U143" t="n">
+      <c r="V143" t="n">
         <v>0.01296737669517052</v>
       </c>
-      <c r="V143" t="n">
+      <c r="W143" t="n">
         <v>0.2588167976329628</v>
       </c>
-      <c r="W143" t="n">
+      <c r="X143" t="n">
         <v>0.009126666666666668</v>
       </c>
-      <c r="X143" t="n">
+      <c r="Y143" t="n">
         <v>0.004563333333333334</v>
       </c>
-      <c r="Y143" t="n">
+      <c r="Z143" t="n">
         <v>28.95676810363952</v>
       </c>
-      <c r="Z143" t="n">
+      <c r="AA143" t="n">
         <v>0.01944191146369945</v>
       </c>
-      <c r="AA143" t="n">
-        <v>0</v>
-      </c>
       <c r="AB143" t="n">
         <v>0</v>
       </c>
@@ -14493,6 +14921,9 @@
         <v>0</v>
       </c>
       <c r="AD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14552,38 +14983,38 @@
         <v>7.983333333333334</v>
       </c>
       <c r="Q144" t="n">
+        <v>0.217233560090703</v>
+      </c>
+      <c r="R144" t="n">
         <v>25.06785714285721</v>
       </c>
-      <c r="R144" t="n">
-        <v>0</v>
-      </c>
       <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
         <v>29.78688303253967</v>
       </c>
-      <c r="T144" t="n">
+      <c r="U144" t="n">
         <v>2.230915506895817</v>
       </c>
-      <c r="U144" t="n">
+      <c r="V144" t="n">
         <v>0.01413309295165512</v>
       </c>
-      <c r="V144" t="n">
+      <c r="W144" t="n">
         <v>0.2848807744362734</v>
       </c>
-      <c r="W144" t="n">
+      <c r="X144" t="n">
         <v>0.01019333333333333</v>
       </c>
-      <c r="X144" t="n">
+      <c r="Y144" t="n">
         <v>0.005096666666666667</v>
       </c>
-      <c r="Y144" t="n">
+      <c r="Z144" t="n">
         <v>29.2361661686984</v>
       </c>
-      <c r="Z144" t="n">
+      <c r="AA144" t="n">
         <v>0.01658310436687791</v>
       </c>
-      <c r="AA144" t="n">
-        <v>0</v>
-      </c>
       <c r="AB144" t="n">
         <v>0</v>
       </c>
@@ -14591,6 +15022,9 @@
         <v>0</v>
       </c>
       <c r="AD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14650,38 +15084,38 @@
         <v>13.56666666666667</v>
       </c>
       <c r="Q145" t="n">
+        <v>0.3691609977324263</v>
+      </c>
+      <c r="R145" t="n">
         <v>25.90000000000013</v>
       </c>
-      <c r="R145" t="n">
-        <v>0</v>
-      </c>
       <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
         <v>31.11037299665006</v>
       </c>
-      <c r="T145" t="n">
+      <c r="U145" t="n">
         <v>2.262489288469567</v>
       </c>
-      <c r="U145" t="n">
+      <c r="V145" t="n">
         <v>0.01625124162510059</v>
       </c>
-      <c r="V145" t="n">
+      <c r="W145" t="n">
         <v>0.3347092315256564</v>
       </c>
-      <c r="W145" t="n">
+      <c r="X145" t="n">
         <v>0.01242666666666667</v>
       </c>
-      <c r="X145" t="n">
+      <c r="Y145" t="n">
         <v>0.006213333333333333</v>
       </c>
-      <c r="Y145" t="n">
+      <c r="Z145" t="n">
         <v>29.78688303253967</v>
       </c>
-      <c r="Z145" t="n">
+      <c r="AA145" t="n">
         <v>0.01821926693166444</v>
       </c>
-      <c r="AA145" t="n">
-        <v>0</v>
-      </c>
       <c r="AB145" t="n">
         <v>0</v>
       </c>
@@ -14689,6 +15123,9 @@
         <v>0</v>
       </c>
       <c r="AD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14748,38 +15185,38 @@
         <v>15.13333333333333</v>
       </c>
       <c r="Q146" t="n">
+        <v>0.4117913832199546</v>
+      </c>
+      <c r="R146" t="n">
         <v>27.37499999999996</v>
       </c>
-      <c r="R146" t="n">
-        <v>0</v>
-      </c>
       <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
         <v>31.52104556228423</v>
       </c>
-      <c r="T146" t="n">
+      <c r="U146" t="n">
         <v>2.272468965115901</v>
       </c>
-      <c r="U146" t="n">
+      <c r="V146" t="n">
         <v>0.01679004299276455</v>
       </c>
-      <c r="V146" t="n">
+      <c r="W146" t="n">
         <v>0.3481790571704745</v>
       </c>
-      <c r="W146" t="n">
+      <c r="X146" t="n">
         <v>0.01305333333333333</v>
       </c>
-      <c r="X146" t="n">
+      <c r="Y146" t="n">
         <v>0.006526666666666667</v>
       </c>
-      <c r="Y146" t="n">
+      <c r="Z146" t="n">
         <v>31.11037299665006</v>
       </c>
-      <c r="Z146" t="n">
+      <c r="AA146" t="n">
         <v>0.01480594697664882</v>
       </c>
-      <c r="AA146" t="n">
-        <v>0</v>
-      </c>
       <c r="AB146" t="n">
         <v>0</v>
       </c>
@@ -14787,6 +15224,9 @@
         <v>0</v>
       </c>
       <c r="AD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14846,38 +15286,38 @@
         <v>16.68333333333333</v>
       </c>
       <c r="Q147" t="n">
+        <v>0.4539682539682539</v>
+      </c>
+      <c r="R147" t="n">
         <v>28.11428571428576</v>
       </c>
-      <c r="R147" t="n">
-        <v>0</v>
-      </c>
       <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
         <v>31.94343200509588</v>
       </c>
-      <c r="T147" t="n">
+      <c r="U147" t="n">
         <v>2.282825558805818</v>
       </c>
-      <c r="U147" t="n">
+      <c r="V147" t="n">
         <v>0.01726816390210312</v>
       </c>
-      <c r="V147" t="n">
+      <c r="W147" t="n">
         <v>0.360274340850948</v>
       </c>
-      <c r="W147" t="n">
+      <c r="X147" t="n">
         <v>0.01367333333333333</v>
       </c>
-      <c r="X147" t="n">
+      <c r="Y147" t="n">
         <v>0.006836666666666666</v>
       </c>
-      <c r="Y147" t="n">
+      <c r="Z147" t="n">
         <v>31.52104556228423</v>
       </c>
-      <c r="Z147" t="n">
+      <c r="AA147" t="n">
         <v>0.01899552184075797</v>
       </c>
-      <c r="AA147" t="n">
-        <v>0</v>
-      </c>
       <c r="AB147" t="n">
         <v>0</v>
       </c>
@@ -14885,6 +15325,9 @@
         <v>0</v>
       </c>
       <c r="AD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14944,38 +15387,38 @@
         <v>18.15</v>
       </c>
       <c r="Q148" t="n">
+        <v>0.4938775510204081</v>
+      </c>
+      <c r="R148" t="n">
         <v>28.14285714285706</v>
       </c>
-      <c r="R148" t="n">
-        <v>0</v>
-      </c>
       <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
         <v>32.3574018720367</v>
       </c>
-      <c r="T148" t="n">
+      <c r="U148" t="n">
         <v>2.293067791270262</v>
       </c>
-      <c r="U148" t="n">
+      <c r="V148" t="n">
         <v>0.01769926440963473</v>
       </c>
-      <c r="V148" t="n">
+      <c r="W148" t="n">
         <v>0.3714798347284995</v>
       </c>
-      <c r="W148" t="n">
+      <c r="X148" t="n">
         <v>0.01426</v>
       </c>
-      <c r="X148" t="n">
+      <c r="Y148" t="n">
         <v>0.007129999999999999</v>
       </c>
-      <c r="Y148" t="n">
+      <c r="Z148" t="n">
         <v>31.94343200509588</v>
       </c>
-      <c r="Z148" t="n">
+      <c r="AA148" t="n">
         <v>0.02233579751349438</v>
       </c>
-      <c r="AA148" t="n">
-        <v>0</v>
-      </c>
       <c r="AB148" t="n">
         <v>0</v>
       </c>
@@ -14983,6 +15426,9 @@
         <v>0</v>
       </c>
       <c r="AD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15042,38 +15488,38 @@
         <v>21.18333333333333</v>
       </c>
       <c r="Q149" t="n">
+        <v>0.5764172335600906</v>
+      </c>
+      <c r="R149" t="n">
         <v>29.46071428571427</v>
       </c>
-      <c r="R149" t="n">
-        <v>0</v>
-      </c>
       <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
         <v>33.25583249482232</v>
       </c>
-      <c r="T149" t="n">
+      <c r="U149" t="n">
         <v>2.315615591595817</v>
       </c>
-      <c r="U149" t="n">
+      <c r="V149" t="n">
         <v>0.01851308273432502</v>
       </c>
-      <c r="V149" t="n">
+      <c r="W149" t="n">
         <v>0.3934469053539372</v>
       </c>
-      <c r="W149" t="n">
+      <c r="X149" t="n">
         <v>0.01547333333333333</v>
       </c>
-      <c r="X149" t="n">
+      <c r="Y149" t="n">
         <v>0.007736666666666666</v>
       </c>
-      <c r="Y149" t="n">
+      <c r="Z149" t="n">
         <v>32.3574018720367</v>
       </c>
-      <c r="Z149" t="n">
+      <c r="AA149" t="n">
         <v>0.01014663618242141</v>
       </c>
-      <c r="AA149" t="n">
-        <v>0</v>
-      </c>
       <c r="AB149" t="n">
         <v>0</v>
       </c>
@@ -15081,6 +15527,9 @@
         <v>0</v>
       </c>
       <c r="AD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15140,38 +15589,38 @@
         <v>24.18333333333334</v>
       </c>
       <c r="Q150" t="n">
+        <v>0.6580498866213152</v>
+      </c>
+      <c r="R150" t="n">
         <v>30.54107142857147</v>
       </c>
-      <c r="R150" t="n">
-        <v>0</v>
-      </c>
       <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
         <v>34.19735342816631</v>
       </c>
-      <c r="T150" t="n">
+      <c r="U150" t="n">
         <v>2.339725615705817</v>
       </c>
-      <c r="U150" t="n">
+      <c r="V150" t="n">
         <v>0.01919070522193477</v>
       </c>
-      <c r="V150" t="n">
+      <c r="W150" t="n">
         <v>0.4125744318193387</v>
       </c>
-      <c r="W150" t="n">
+      <c r="X150" t="n">
         <v>0.01667333333333334</v>
       </c>
-      <c r="X150" t="n">
+      <c r="Y150" t="n">
         <v>0.008336666666666668</v>
       </c>
-      <c r="Y150" t="n">
+      <c r="Z150" t="n">
         <v>33.25583249482232</v>
       </c>
-      <c r="Z150" t="n">
+      <c r="AA150" t="n">
         <v>0.00902987934884078</v>
       </c>
-      <c r="AA150" t="n">
-        <v>0</v>
-      </c>
       <c r="AB150" t="n">
         <v>0</v>
       </c>
@@ -15179,6 +15628,9 @@
         <v>0</v>
       </c>
       <c r="AD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15238,38 +15690,38 @@
         <v>25.7</v>
       </c>
       <c r="Q151" t="n">
+        <v>0.6993197278911566</v>
+      </c>
+      <c r="R151" t="n">
         <v>30.00357142857132</v>
       </c>
-      <c r="R151" t="n">
-        <v>0</v>
-      </c>
       <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
         <v>34.69219227608998</v>
       </c>
-      <c r="T151" t="n">
+      <c r="U151" t="n">
         <v>2.352599600802012</v>
       </c>
-      <c r="U151" t="n">
+      <c r="V151" t="n">
         <v>0.01948896483444288</v>
       </c>
-      <c r="V151" t="n">
+      <c r="W151" t="n">
         <v>0.4212984636054069</v>
       </c>
-      <c r="W151" t="n">
+      <c r="X151" t="n">
         <v>0.01728</v>
       </c>
-      <c r="X151" t="n">
+      <c r="Y151" t="n">
         <v>0.00864</v>
       </c>
-      <c r="Y151" t="n">
+      <c r="Z151" t="n">
         <v>34.19735342816631</v>
       </c>
-      <c r="Z151" t="n">
+      <c r="AA151" t="n">
         <v>0.01371968923896166</v>
       </c>
-      <c r="AA151" t="n">
-        <v>0</v>
-      </c>
       <c r="AB151" t="n">
         <v>0</v>
       </c>
@@ -15277,6 +15729,9 @@
         <v>0</v>
       </c>
       <c r="AD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15336,38 +15791,38 @@
         <v>26.75</v>
       </c>
       <c r="Q152" t="n">
+        <v>0.7278911564625851</v>
+      </c>
+      <c r="R152" t="n">
         <v>30.12857142857151</v>
       </c>
-      <c r="R152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
         <v>35.04183579224857</v>
       </c>
-      <c r="T152" t="n">
+      <c r="U152" t="n">
         <v>2.361781859984262</v>
       </c>
-      <c r="U152" t="n">
+      <c r="V152" t="n">
         <v>0.01970497485318354</v>
       </c>
-      <c r="V152" t="n">
+      <c r="W152" t="n">
         <v>0.4278830060214355</v>
       </c>
-      <c r="W152" t="n">
+      <c r="X152" t="n">
         <v>0.0177</v>
       </c>
-      <c r="X152" t="n">
+      <c r="Y152" t="n">
         <v>0.00885</v>
       </c>
-      <c r="Y152" t="n">
+      <c r="Z152" t="n">
         <v>34.69219227608998</v>
       </c>
-      <c r="Z152" t="n">
+      <c r="AA152" t="n">
         <v>0.0224321685275548</v>
       </c>
-      <c r="AA152" t="n">
-        <v>0</v>
-      </c>
       <c r="AB152" t="n">
         <v>0</v>
       </c>
@@ -15375,6 +15830,9 @@
         <v>0</v>
       </c>
       <c r="AD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="n">
         <v>0</v>
       </c>
     </row>
